--- a/Ocorrências Literatura.xlsx
+++ b/Ocorrências Literatura.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faculdade\Laboratorio\lagostas_carapaca\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1CA78EC-E0D1-447A-A4BB-B3AEA12FE60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1DE25C-A56E-41E4-9CB4-4A917A550F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20880" yWindow="975" windowWidth="17520" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="96">
   <si>
     <t>origem</t>
   </si>
@@ -214,9 +214,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Cruz, R. (2016)</t>
-  </si>
-  <si>
     <t>Offshore area around Pau Amarelo Beach, Pernambuco</t>
   </si>
   <si>
@@ -229,14 +226,113 @@
     <t>34°49′14,3″</t>
   </si>
   <si>
-    <t>Systematic and biogeographic overview of Panulirus species in the Atlantic Ocean</t>
+    <t>Giraldes, B (2016)</t>
+  </si>
+  <si>
+    <t>document</t>
+  </si>
+  <si>
+    <t>Alencar et al. (2021)</t>
+  </si>
+  <si>
+    <t>5°59</t>
+  </si>
+  <si>
+    <t>35°7</t>
+  </si>
+  <si>
+    <t>Pirangi</t>
+  </si>
+  <si>
+    <t>Alencaretal.2021</t>
+  </si>
+  <si>
+    <t>México (Bahía de la Ascensión)</t>
+  </si>
+  <si>
+    <t>Fourzán, P (2019)</t>
+  </si>
+  <si>
+    <t>0718-560X-lajar-47-04-0694</t>
+  </si>
+  <si>
+    <t>0718-560X-lajar-47-04-0695</t>
+  </si>
+  <si>
+    <t>Panulirus echinatus</t>
+  </si>
+  <si>
+    <t>Tamandaré, PE (inshore)</t>
+  </si>
+  <si>
+    <t>Tamandaré, PE (offshore)</t>
+  </si>
+  <si>
+    <t>08°45′31,2″</t>
+  </si>
+  <si>
+    <t>35°05′07,7″</t>
+  </si>
+  <si>
+    <t>35°05′48,9″</t>
+  </si>
+  <si>
+    <t>08°46′57,2″</t>
+  </si>
+  <si>
+    <t>08°45′35,0″</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 35°04′57,5″</t>
+  </si>
+  <si>
+    <t>08°47′01,2″</t>
+  </si>
+  <si>
+    <t>35°05′42,0″</t>
+  </si>
+  <si>
+    <t>BARRETO, A. V. et al. (2009)</t>
+  </si>
+  <si>
+    <t>sim</t>
+  </si>
+  <si>
+    <t>biometric-relationships-of-the-spotted-lobster-panulirus-echinatus-from-tamandare-coastal-reefs-pernambuco-state-brazil</t>
+  </si>
+  <si>
+    <t>2°46′</t>
+  </si>
+  <si>
+    <t>40°05′</t>
+  </si>
+  <si>
+    <t>Acaraú</t>
+  </si>
+  <si>
+    <t>South of Cuba</t>
+  </si>
+  <si>
+    <t>21°34′</t>
+  </si>
+  <si>
+    <t>83°31′</t>
+  </si>
+  <si>
+    <t>3°32,981′</t>
+  </si>
+  <si>
+    <t>38°48.669′</t>
+  </si>
+  <si>
+    <t>Cruz, R. (2025)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,12 +345,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -295,11 +385,32 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -392,52 +503,56 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -722,16 +837,18 @@
   <dimension ref="A1:R495"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.28515625" style="3" customWidth="1"/>
     <col min="9" max="9" width="45" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="9.140625" style="3"/>
+    <col min="10" max="11" width="9.140625" style="3"/>
+    <col min="12" max="12" width="13" style="3" customWidth="1"/>
+    <col min="13" max="15" width="9.140625" style="3"/>
     <col min="16" max="17" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="84.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="9.140625" style="3"/>
@@ -741,55 +858,55 @@
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="21" t="s">
         <v>25</v>
       </c>
     </row>
@@ -812,7 +929,7 @@
       <c r="F2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="13" t="s">
         <v>21</v>
       </c>
       <c r="H2" s="3" t="s">
@@ -853,7 +970,7 @@
         <f t="shared" ref="Q2:Q7" si="7">((((O2/60)+N2)/60)+M2)*IF(D2="W",-1, 1)</f>
         <v>-41.136111111111113</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="R2" s="14" t="s">
         <v>32</v>
       </c>
     </row>
@@ -870,19 +987,19 @@
       <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="13" t="s">
         <v>21</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J3" s="3" t="str">
@@ -917,7 +1034,7 @@
         <f t="shared" si="7"/>
         <v>-37.355277777777779</v>
       </c>
-      <c r="R3" s="21" t="s">
+      <c r="R3" s="14" t="s">
         <v>32</v>
       </c>
     </row>
@@ -940,7 +1057,7 @@
       <c r="F4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="13" t="s">
         <v>21</v>
       </c>
       <c r="H4" s="3" t="s">
@@ -981,7 +1098,7 @@
         <f t="shared" si="7"/>
         <v>-41.136111111111113</v>
       </c>
-      <c r="R4" s="21" t="s">
+      <c r="R4" s="14" t="s">
         <v>32</v>
       </c>
     </row>
@@ -998,19 +1115,19 @@
       <c r="D5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="13" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J5" s="3" t="str">
@@ -1045,7 +1162,7 @@
         <f t="shared" si="7"/>
         <v>-37.355277777777779</v>
       </c>
-      <c r="R5" s="21" t="s">
+      <c r="R5" s="14" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1068,7 +1185,7 @@
       <c r="F6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="13" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
@@ -1109,7 +1226,7 @@
         <f t="shared" si="7"/>
         <v>-39.791944444444447</v>
       </c>
-      <c r="R6" s="21" t="s">
+      <c r="R6" s="14" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1126,16 +1243,19 @@
       <c r="D7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="11" t="s">
         <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="G7" s="8" t="s">
+        <v>95</v>
+      </c>
       <c r="H7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="19" t="s">
         <v>36</v>
       </c>
       <c r="J7" s="3" t="str">
@@ -1170,7 +1290,7 @@
         <f t="shared" si="7"/>
         <v>-39.225000000000001</v>
       </c>
-      <c r="R7" s="21" t="s">
+      <c r="R7" s="14" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1187,19 +1307,19 @@
       <c r="D8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="8" t="s">
         <v>56</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="20" t="s">
         <v>43</v>
       </c>
       <c r="J8" s="3" t="str">
@@ -1234,7 +1354,7 @@
         <f t="shared" ref="Q8:Q23" si="14">((((O8/60)+N8)/60)+M8)*IF(D8="W",-1, 1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R8" s="22" t="s">
+      <c r="R8" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1251,19 +1371,19 @@
       <c r="D9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="8" t="s">
         <v>56</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="I9" s="20" t="s">
         <v>37</v>
       </c>
       <c r="J9" s="3" t="str">
@@ -1298,7 +1418,7 @@
         <f t="shared" si="14"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R9" s="22" t="s">
+      <c r="R9" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1315,19 +1435,19 @@
       <c r="D10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="8" t="s">
         <v>56</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="I10" s="12" t="s">
         <v>49</v>
       </c>
       <c r="J10" s="3" t="str">
@@ -1362,7 +1482,7 @@
         <f t="shared" si="14"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R10" s="22" t="s">
+      <c r="R10" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1379,19 +1499,19 @@
       <c r="D11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="8" t="s">
         <v>56</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="17" t="s">
+      <c r="I11" s="12" t="s">
         <v>48</v>
       </c>
       <c r="J11" s="3" t="str">
@@ -1426,7 +1546,7 @@
         <f t="shared" si="14"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R11" s="22" t="s">
+      <c r="R11" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1443,19 +1563,19 @@
       <c r="D12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="8" t="s">
         <v>56</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="I12" s="12" t="s">
         <v>49</v>
       </c>
       <c r="J12" s="3" t="str">
@@ -1490,7 +1610,7 @@
         <f t="shared" si="14"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R12" s="22" t="s">
+      <c r="R12" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1507,19 +1627,19 @@
       <c r="D13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="12" t="s">
         <v>54</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="8" t="s">
         <v>56</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="17" t="s">
+      <c r="I13" s="12" t="s">
         <v>53</v>
       </c>
       <c r="J13" s="3" t="str">
@@ -1554,7 +1674,7 @@
         <f t="shared" si="14"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R13" s="22" t="s">
+      <c r="R13" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1571,19 +1691,19 @@
       <c r="D14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="12" t="s">
         <v>55</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="8" t="s">
         <v>56</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I14" s="17" t="s">
+      <c r="I14" s="12" t="s">
         <v>53</v>
       </c>
       <c r="J14" s="3" t="str">
@@ -1618,7 +1738,7 @@
         <f t="shared" si="14"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R14" s="22" t="s">
+      <c r="R14" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1635,19 +1755,19 @@
       <c r="D15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="8" t="s">
         <v>56</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="I15" s="20" t="s">
         <v>43</v>
       </c>
       <c r="J15" s="3" t="str">
@@ -1682,7 +1802,7 @@
         <f t="shared" si="14"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R15" s="22" t="s">
+      <c r="R15" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1699,19 +1819,19 @@
       <c r="D16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="8" t="s">
         <v>56</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="16" t="s">
+      <c r="I16" s="20" t="s">
         <v>37</v>
       </c>
       <c r="J16" s="3" t="str">
@@ -1746,7 +1866,7 @@
         <f t="shared" si="14"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R16" s="22" t="s">
+      <c r="R16" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1763,19 +1883,19 @@
       <c r="D17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="8" t="s">
         <v>56</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="17" t="s">
+      <c r="I17" s="12" t="s">
         <v>49</v>
       </c>
       <c r="J17" s="3" t="str">
@@ -1810,7 +1930,7 @@
         <f t="shared" si="14"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R17" s="22" t="s">
+      <c r="R17" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1827,19 +1947,19 @@
       <c r="D18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="8" t="s">
         <v>56</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I18" s="17" t="s">
+      <c r="I18" s="12" t="s">
         <v>48</v>
       </c>
       <c r="J18" s="3" t="str">
@@ -1874,7 +1994,7 @@
         <f t="shared" si="14"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R18" s="22" t="s">
+      <c r="R18" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1891,19 +2011,19 @@
       <c r="D19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="8" t="s">
         <v>56</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I19" s="17" t="s">
+      <c r="I19" s="12" t="s">
         <v>49</v>
       </c>
       <c r="J19" s="3" t="str">
@@ -1938,7 +2058,7 @@
         <f t="shared" si="14"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R19" s="22" t="s">
+      <c r="R19" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1955,19 +2075,19 @@
       <c r="D20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="12" t="s">
         <v>54</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="8" t="s">
         <v>56</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I20" s="17" t="s">
+      <c r="I20" s="12" t="s">
         <v>53</v>
       </c>
       <c r="J20" s="3" t="str">
@@ -2002,7 +2122,7 @@
         <f t="shared" si="14"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R20" s="22" t="s">
+      <c r="R20" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2019,19 +2139,19 @@
       <c r="D21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="12" t="s">
         <v>55</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="8" t="s">
         <v>56</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I21" s="17" t="s">
+      <c r="I21" s="12" t="s">
         <v>53</v>
       </c>
       <c r="J21" s="3" t="str">
@@ -2066,7 +2186,7 @@
         <f t="shared" si="14"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R21" s="22" t="s">
+      <c r="R21" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2075,28 +2195,28 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="F22" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" s="8" t="s">
         <v>62</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J22" s="3" t="str">
         <f t="shared" si="8"/>
@@ -2130,36 +2250,60 @@
         <f t="shared" si="14"/>
         <v>-34.820638888888887</v>
       </c>
-      <c r="R22" s="23" t="s">
+      <c r="R22" s="15" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="J23" s="3" t="e">
+      <c r="B23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J23" s="3" t="str">
         <f t="shared" ref="J23:J30" si="16">MID(E23,1,FIND("°",E23,1)-1)</f>
-        <v>#VALUE!</v>
+        <v>5</v>
       </c>
       <c r="K23" s="3" t="e">
-        <f t="shared" ref="K23:K30" si="17">MID(E23,FIND("°",E23,1)+1,(FIND("′",E23,1)-FIND("°",E23,1))-1)</f>
+        <f>MID(E23,FIND("°",E23,1)+1,(FIND("′",E23,1)-FIND("°",E23,1))-1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L23" s="3" t="e">
-        <f t="shared" ref="L23:L30" si="18">MID(E23,FIND("′",E23,1)+1,(FIND("″",E23,1)-FIND("′",E23,1))-1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M23" s="3" t="e">
-        <f t="shared" ref="M23:M30" si="19">MID(F23,1,FIND("°",F23,1)-1)</f>
-        <v>#VALUE!</v>
+        <f t="shared" ref="L23:L30" si="17">MID(E23,FIND("′",E23,1)+1,(FIND("″",E23,1)-FIND("′",E23,1))-1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M23" s="3" t="str">
+        <f t="shared" ref="M23:M30" si="18">MID(F23,1,FIND("°",F23,1)-1)</f>
+        <v>35</v>
       </c>
       <c r="N23" s="3" t="e">
-        <f t="shared" ref="N23:N30" si="20">MID(F23,FIND("°",F23,1)+1,(FIND("′",F23,1)-FIND("°",F23,1))-1)</f>
+        <f t="shared" ref="N23:N30" si="19">MID(F23,FIND("°",F23,1)+1,(FIND("′",F23,1)-FIND("°",F23,1))-1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="O23" s="3" t="e">
-        <f t="shared" ref="O23:O30" si="21">MID(F23,FIND("′",F23,1)+1,(FIND("″",F23,1)-FIND("′",F23,1))-1)</f>
+        <f t="shared" ref="O23:O30" si="20">MID(F23,FIND("′",F23,1)+1,(FIND("″",F23,1)-FIND("′",F23,1))-1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="P23" s="1" t="e">
@@ -2170,34 +2314,60 @@
         <f t="shared" si="14"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R23" s="24"/>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R23" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="J24" s="3" t="e">
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J24" s="3" t="str">
         <f t="shared" si="16"/>
-        <v>#VALUE!</v>
+        <v>5</v>
       </c>
       <c r="K24" s="3" t="e">
+        <f t="shared" ref="K24:K30" si="21">MID(E24,FIND("°",E24,1)+1,(FIND("′",E24,1)-FIND("°",E24,1))-1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L24" s="3" t="e">
         <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L24" s="3" t="e">
+      <c r="M24" s="3" t="str">
         <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M24" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="N24" s="3" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N24" s="3" t="e">
+      <c r="O24" s="3" t="e">
         <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O24" s="3" t="e">
-        <f t="shared" si="21"/>
         <v>#VALUE!</v>
       </c>
       <c r="P24" s="1" t="e">
@@ -2208,34 +2378,54 @@
         <f t="shared" ref="Q24:Q30" si="23">((((O24/60)+N24)/60)+M24)*IF(D24="W",-1, 1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R24" s="24"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R24" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>24</v>
       </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="J25" s="3" t="e">
         <f t="shared" si="16"/>
         <v>#VALUE!</v>
       </c>
       <c r="K25" s="3" t="e">
+        <f t="shared" si="21"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L25" s="3" t="e">
         <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L25" s="3" t="e">
+      <c r="M25" s="3" t="e">
         <f t="shared" si="18"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M25" s="3" t="e">
+      <c r="N25" s="3" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N25" s="3" t="e">
+      <c r="O25" s="3" t="e">
         <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O25" s="3" t="e">
-        <f t="shared" si="21"/>
         <v>#VALUE!</v>
       </c>
       <c r="P25" s="1" t="e">
@@ -2246,34 +2436,54 @@
         <f t="shared" si="23"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R25" s="24"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R25" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>25</v>
       </c>
+      <c r="B26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="J26" s="3" t="e">
         <f t="shared" si="16"/>
         <v>#VALUE!</v>
       </c>
       <c r="K26" s="3" t="e">
+        <f t="shared" si="21"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L26" s="3" t="e">
         <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L26" s="3" t="e">
+      <c r="M26" s="3" t="e">
         <f t="shared" si="18"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M26" s="3" t="e">
+      <c r="N26" s="3" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N26" s="3" t="e">
+      <c r="O26" s="3" t="e">
         <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O26" s="3" t="e">
-        <f t="shared" si="21"/>
         <v>#VALUE!</v>
       </c>
       <c r="P26" s="1" t="e">
@@ -2284,679 +2494,5137 @@
         <f t="shared" si="23"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R26" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="J27" s="3" t="e">
+      <c r="B27" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" t="s">
+        <v>84</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J27" s="3" t="str">
         <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K27" s="3" t="e">
+        <v>08</v>
+      </c>
+      <c r="K27" s="3" t="str">
+        <f>MID(E27,FIND("°",E27,1)+1,(FIND("′",E27,1)-FIND("°",E27,1))-1)</f>
+        <v>45</v>
+      </c>
+      <c r="L27" s="3" t="str">
         <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L27" s="3" t="e">
+        <v>31,2</v>
+      </c>
+      <c r="M27" s="3" t="str">
         <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M27" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="N27" s="3" t="str">
         <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N27" s="3" t="e">
+        <v>05</v>
+      </c>
+      <c r="O27" s="3" t="str">
         <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O27" s="3" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P27" s="1" t="e">
+        <v>07,7</v>
+      </c>
+      <c r="P27" s="1">
         <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q27" s="1" t="e">
+        <v>-8.7586666666666666</v>
+      </c>
+      <c r="Q27" s="1">
         <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-35.085472222222222</v>
+      </c>
+      <c r="R27" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="J28" s="3" t="e">
+      <c r="B28" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28" t="s">
+        <v>84</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J28" s="3" t="str">
         <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K28" s="3" t="e">
+        <v>08</v>
+      </c>
+      <c r="K28" s="3" t="str">
+        <f t="shared" si="21"/>
+        <v>46</v>
+      </c>
+      <c r="L28" s="3" t="str">
         <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L28" s="3" t="e">
+        <v>57,2</v>
+      </c>
+      <c r="M28" s="3" t="str">
         <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M28" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="N28" s="3" t="str">
         <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N28" s="3" t="e">
+        <v>05</v>
+      </c>
+      <c r="O28" s="3" t="str">
         <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O28" s="3" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P28" s="1" t="e">
+        <v>48,9</v>
+      </c>
+      <c r="P28" s="1">
         <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q28" s="1" t="e">
+        <v>-8.7825555555555557</v>
+      </c>
+      <c r="Q28" s="1">
         <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-35.096916666666665</v>
+      </c>
+      <c r="R28" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="J29" s="3" t="e">
+      <c r="B29" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" t="s">
+        <v>84</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J29" s="3" t="str">
         <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K29" s="3" t="e">
+        <v>08</v>
+      </c>
+      <c r="K29" s="3" t="str">
+        <f t="shared" si="21"/>
+        <v>45</v>
+      </c>
+      <c r="L29" s="3" t="str">
         <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L29" s="3" t="e">
+        <v>35,0</v>
+      </c>
+      <c r="M29" s="3" t="str">
         <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M29" s="3" t="e">
+        <v xml:space="preserve"> 35</v>
+      </c>
+      <c r="N29" s="3" t="str">
         <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N29" s="3" t="e">
+        <v>04</v>
+      </c>
+      <c r="O29" s="3" t="str">
         <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O29" s="3" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P29" s="1" t="e">
+        <v>57,5</v>
+      </c>
+      <c r="P29" s="1">
         <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q29" s="1" t="e">
+        <v>-8.7597222222222229</v>
+      </c>
+      <c r="Q29" s="1">
         <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-35.082638888888887</v>
+      </c>
+      <c r="R29" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="J30" s="3" t="e">
+      <c r="B30" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G30" t="s">
+        <v>84</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J30" s="3" t="str">
         <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K30" s="3" t="e">
+        <v>08</v>
+      </c>
+      <c r="K30" s="3" t="str">
+        <f t="shared" si="21"/>
+        <v>47</v>
+      </c>
+      <c r="L30" s="3" t="str">
         <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L30" s="3" t="e">
+        <v>01,2</v>
+      </c>
+      <c r="M30" s="3" t="str">
         <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M30" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="N30" s="3" t="str">
         <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N30" s="3" t="e">
+        <v>05</v>
+      </c>
+      <c r="O30" s="3" t="str">
         <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O30" s="3" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P30" s="1" t="e">
+        <v>42,0</v>
+      </c>
+      <c r="P30" s="1">
         <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q30" s="1" t="e">
+        <v>-8.783666666666667</v>
+      </c>
+      <c r="Q30" s="1">
         <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-35.094999999999999</v>
+      </c>
+      <c r="R30" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-    </row>
-    <row r="33" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" t="s">
+        <v>87</v>
+      </c>
+      <c r="F31" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="J31" s="3" t="str">
+        <f t="shared" ref="J31:J94" si="24">MID(E31,1,FIND("°",E31,1)-1)</f>
+        <v>2</v>
+      </c>
+      <c r="K31" s="3" t="str">
+        <f t="shared" ref="K31:K94" si="25">MID(E31,FIND("°",E31,1)+1,(FIND("′",E31,1)-FIND("°",E31,1))-1)</f>
+        <v>46</v>
+      </c>
+      <c r="L31" s="3" t="e">
+        <f t="shared" ref="L31:L94" si="26">MID(E31,FIND("′",E31,1)+1,(FIND("″",E31,1)-FIND("′",E31,1))-1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M31" s="3" t="str">
+        <f t="shared" ref="M31:M94" si="27">MID(F31,1,FIND("°",F31,1)-1)</f>
+        <v>40</v>
+      </c>
+      <c r="N31" s="3" t="str">
+        <f t="shared" ref="N31:N94" si="28">MID(F31,FIND("°",F31,1)+1,(FIND("′",F31,1)-FIND("°",F31,1))-1)</f>
+        <v>05</v>
+      </c>
+      <c r="O31" s="3" t="e">
+        <f t="shared" ref="O31:O94" si="29">MID(F31,FIND("′",F31,1)+1,(FIND("″",F31,1)-FIND("′",F31,1))-1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P31" s="1" t="e">
+        <f t="shared" ref="P31:P94" si="30">((((L31/60)+K31)/60)+J31)*IF(C31="S",-1, 1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q31" s="1" t="e">
+        <f t="shared" ref="Q31:Q94" si="31">((((O31/60)+N31)/60)+M31)*IF(D31="W",-1, 1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R31" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J32" s="3" t="str">
+        <f t="shared" si="24"/>
+        <v>21</v>
+      </c>
+      <c r="K32" s="3" t="str">
+        <f t="shared" si="25"/>
+        <v>34</v>
+      </c>
+      <c r="L32" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M32" s="3" t="str">
+        <f t="shared" si="27"/>
+        <v>83</v>
+      </c>
+      <c r="N32" s="3" t="str">
+        <f t="shared" si="28"/>
+        <v>31</v>
+      </c>
+      <c r="O32" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P32" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q32" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R32" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" t="s">
+        <v>93</v>
+      </c>
+      <c r="F33" t="s">
+        <v>94</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="I33" s="5"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-    </row>
-    <row r="34" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="J33" s="3" t="str">
+        <f t="shared" si="24"/>
+        <v>3</v>
+      </c>
+      <c r="K33" s="3" t="str">
+        <f t="shared" si="25"/>
+        <v>32,981</v>
+      </c>
+      <c r="L33" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M33" s="3" t="str">
+        <f t="shared" si="27"/>
+        <v>38</v>
+      </c>
+      <c r="N33" s="3" t="str">
+        <f t="shared" si="28"/>
+        <v>48.669</v>
+      </c>
+      <c r="O33" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P33" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q33" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R33" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="I34" s="5"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-    </row>
-    <row r="35" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="J34" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K34" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L34" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M34" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N34" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O34" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P34" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q34" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="I35" s="5"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-    </row>
-    <row r="36" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="J35" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K35" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L35" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M35" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N35" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O35" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P35" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q35" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="I36" s="5"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-    </row>
-    <row r="37" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-    </row>
-    <row r="38" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-    </row>
-    <row r="39" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-    </row>
-    <row r="40" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="P40" s="1"/>
-      <c r="Q40" s="1"/>
-    </row>
-    <row r="41" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="J36" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K36" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L36" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M36" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N36" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O36" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P36" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q36" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K37" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L37" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M37" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N37" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O37" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P37" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q37" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K38" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L38" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M38" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N38" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O38" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P38" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q38" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K39" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L39" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M39" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N39" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O39" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P39" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q39" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J40" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K40" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L40" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M40" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N40" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O40" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P40" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q40" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="I41" s="5"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
-    </row>
-    <row r="42" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="J41" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K41" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L41" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M41" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N41" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O41" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P41" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q41" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="I42" s="5"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
-    </row>
-    <row r="43" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="J42" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K42" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L42" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M42" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N42" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O42" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P42" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q42" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="I43" s="5"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-    </row>
-    <row r="44" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="J43" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K43" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L43" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M43" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N43" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O43" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P43" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q43" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="I44" s="5"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-    </row>
-    <row r="45" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="P45" s="1"/>
-      <c r="Q45" s="1"/>
-    </row>
-    <row r="46" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
-    </row>
-    <row r="47" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="P47" s="1"/>
-      <c r="Q47" s="1"/>
-    </row>
-    <row r="48" spans="9:17" x14ac:dyDescent="0.25">
-      <c r="P48" s="1"/>
-      <c r="Q48" s="1"/>
-    </row>
-    <row r="49" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J44" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K44" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L44" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M44" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N44" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O44" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P44" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q44" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <v>44</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K45" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L45" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M45" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N45" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O45" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P45" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q45" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J46" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K46" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L46" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M46" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N46" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O46" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P46" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q46" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K47" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L47" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M47" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N47" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O47" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P47" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q47" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J48" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K48" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L48" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M48" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N48" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O48" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P48" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q48" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="I49" s="5"/>
-      <c r="P49" s="1"/>
-      <c r="Q49" s="1"/>
-    </row>
-    <row r="50" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J49" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K49" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L49" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M49" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N49" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O49" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P49" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q49" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="I50" s="5"/>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
-    </row>
-    <row r="51" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J50" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K50" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L50" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M50" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N50" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O50" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P50" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q50" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="I51" s="5"/>
-      <c r="P51" s="1"/>
-      <c r="Q51" s="1"/>
-    </row>
-    <row r="52" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J51" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K51" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L51" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M51" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N51" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O51" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P51" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q51" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="I52" s="5"/>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1"/>
-    </row>
-    <row r="53" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J52" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K52" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L52" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M52" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N52" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O52" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P52" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q52" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
+        <v>52</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
-      <c r="P53" s="1"/>
-      <c r="Q53" s="1"/>
-    </row>
-    <row r="54" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J53" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K53" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L53" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M53" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N53" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O53" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P53" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q53" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E54" s="2"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
-    </row>
-    <row r="55" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J54" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K54" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L54" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M54" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N54" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O54" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P54" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q54" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
+        <v>54</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
-      <c r="P55" s="1"/>
-      <c r="Q55" s="1"/>
-    </row>
-    <row r="56" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J55" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K55" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L55" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M55" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N55" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O55" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P55" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q55" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <v>55</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
-      <c r="P56" s="1"/>
-      <c r="Q56" s="1"/>
-    </row>
-    <row r="57" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J56" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K56" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L56" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M56" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N56" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O56" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P56" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q56" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
+        <v>56</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
-      <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
-    </row>
-    <row r="58" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J57" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K57" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L57" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M57" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N57" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O57" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P57" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q57" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
+        <v>57</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
-    </row>
-    <row r="59" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J58" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K58" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L58" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M58" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N58" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O58" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P58" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q58" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
+        <v>58</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
-      <c r="P59" s="1"/>
-      <c r="Q59" s="1"/>
-    </row>
-    <row r="60" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J59" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K59" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L59" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M59" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N59" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O59" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P59" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q59" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
+        <v>59</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
-      <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
-    </row>
-    <row r="61" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J60" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K60" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L60" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M60" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N60" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O60" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P60" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q60" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
+        <v>60</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
-      <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
-    </row>
-    <row r="62" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J61" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K61" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L61" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M61" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N61" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O61" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P61" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q61" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
+        <v>61</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
-    </row>
-    <row r="63" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J62" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K62" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L62" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M62" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N62" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O62" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P62" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q62" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
+        <v>62</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
-      <c r="P63" s="1"/>
-      <c r="Q63" s="1"/>
-    </row>
-    <row r="64" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J63" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K63" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L63" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M63" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N63" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O63" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P63" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q63" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
+        <v>63</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
-      <c r="P64" s="1"/>
-      <c r="Q64" s="1"/>
-    </row>
-    <row r="65" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J64" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K64" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L64" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M64" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N64" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O64" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P64" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q64" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
+        <v>64</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
-      <c r="P65" s="1"/>
-      <c r="Q65" s="1"/>
-    </row>
-    <row r="66" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J65" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K65" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L65" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M65" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N65" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O65" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P65" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q65" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
+        <v>65</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
-      <c r="P66" s="1"/>
-      <c r="Q66" s="1"/>
-    </row>
-    <row r="67" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J66" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K66" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L66" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M66" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N66" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O66" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P66" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q66" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
+        <v>66</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
-      <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
-    </row>
-    <row r="68" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J67" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K67" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L67" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M67" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N67" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O67" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P67" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q67" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
+        <v>67</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E68" s="2"/>
-      <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
-    </row>
-    <row r="69" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J68" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K68" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L68" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M68" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N68" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O68" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P68" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q68" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
+        <v>68</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
-      <c r="P69" s="1"/>
-      <c r="Q69" s="1"/>
-    </row>
-    <row r="70" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J69" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K69" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L69" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M69" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N69" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O69" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P69" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q69" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
+        <v>69</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
-      <c r="P70" s="1"/>
-      <c r="Q70" s="1"/>
-    </row>
-    <row r="71" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J70" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K70" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L70" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M70" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N70" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O70" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P70" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q70" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
+        <v>70</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
-      <c r="P71" s="1"/>
-      <c r="Q71" s="1"/>
-    </row>
-    <row r="72" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J71" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K71" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L71" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M71" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N71" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O71" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P71" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q71" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
+        <v>71</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E72" s="7"/>
       <c r="F72" s="2"/>
-      <c r="P72" s="1"/>
-      <c r="Q72" s="1"/>
-    </row>
-    <row r="73" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J72" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K72" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L72" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M72" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N72" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O72" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P72" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q72" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A73" s="3">
+        <v>72</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E73" s="2"/>
-      <c r="P73" s="1"/>
-      <c r="Q73" s="1"/>
-    </row>
-    <row r="74" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P74" s="1"/>
-      <c r="Q74" s="1"/>
-    </row>
-    <row r="75" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P75" s="1"/>
-      <c r="Q75" s="1"/>
-    </row>
-    <row r="76" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P76" s="1"/>
-      <c r="Q76" s="1"/>
-    </row>
-    <row r="77" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P77" s="1"/>
-      <c r="Q77" s="1"/>
-    </row>
-    <row r="78" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P78" s="1"/>
-      <c r="Q78" s="1"/>
-    </row>
-    <row r="79" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P79" s="1"/>
-      <c r="Q79" s="1"/>
-    </row>
-    <row r="80" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P80" s="1"/>
-      <c r="Q80" s="1"/>
-    </row>
-    <row r="81" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P81" s="1"/>
-      <c r="Q81" s="1"/>
-    </row>
-    <row r="82" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P82" s="1"/>
-      <c r="Q82" s="1"/>
-    </row>
-    <row r="83" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P83" s="1"/>
-      <c r="Q83" s="1"/>
-    </row>
-    <row r="84" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P84" s="1"/>
-      <c r="Q84" s="1"/>
-    </row>
-    <row r="85" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P85" s="1"/>
-      <c r="Q85" s="1"/>
-    </row>
-    <row r="86" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P86" s="1"/>
-      <c r="Q86" s="1"/>
-    </row>
-    <row r="87" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P87" s="1"/>
-      <c r="Q87" s="1"/>
-    </row>
-    <row r="88" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P88" s="1"/>
-      <c r="Q88" s="1"/>
-    </row>
-    <row r="89" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P89" s="1"/>
-      <c r="Q89" s="1"/>
-    </row>
-    <row r="90" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P90" s="1"/>
-      <c r="Q90" s="1"/>
-    </row>
-    <row r="91" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P91" s="1"/>
-      <c r="Q91" s="1"/>
-    </row>
-    <row r="92" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P92" s="1"/>
-      <c r="Q92" s="1"/>
-    </row>
-    <row r="93" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P93" s="1"/>
-      <c r="Q93" s="1"/>
-    </row>
-    <row r="94" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P94" s="1"/>
-      <c r="Q94" s="1"/>
-    </row>
-    <row r="95" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P95" s="1"/>
-      <c r="Q95" s="1"/>
-    </row>
-    <row r="96" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P96" s="1"/>
-      <c r="Q96" s="1"/>
-    </row>
-    <row r="97" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P97" s="1"/>
-      <c r="Q97" s="1"/>
-    </row>
-    <row r="98" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P98" s="1"/>
-      <c r="Q98" s="1"/>
-    </row>
-    <row r="99" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P99" s="1"/>
-      <c r="Q99" s="1"/>
-    </row>
-    <row r="100" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P100" s="1"/>
-      <c r="Q100" s="1"/>
-    </row>
-    <row r="101" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P101" s="1"/>
-      <c r="Q101" s="1"/>
-    </row>
-    <row r="102" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P102" s="1"/>
-      <c r="Q102" s="1"/>
-    </row>
-    <row r="103" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P103" s="1"/>
-      <c r="Q103" s="1"/>
-    </row>
-    <row r="104" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P104" s="1"/>
-      <c r="Q104" s="1"/>
-    </row>
-    <row r="105" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J73" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K73" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L73" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M73" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N73" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O73" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P73" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q73" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
+        <v>73</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J74" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K74" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L74" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M74" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N74" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O74" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P74" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q74" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
+        <v>74</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J75" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K75" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L75" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M75" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N75" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O75" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P75" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q75" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
+        <v>75</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J76" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K76" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L76" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M76" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N76" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O76" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P76" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q76" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
+        <v>76</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J77" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K77" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L77" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M77" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N77" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O77" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P77" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q77" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
+        <v>77</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J78" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K78" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L78" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M78" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N78" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O78" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P78" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q78" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
+        <v>78</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J79" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K79" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L79" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M79" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N79" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O79" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P79" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q79" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
+        <v>79</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J80" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K80" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L80" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M80" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N80" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O80" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P80" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q80" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
+        <v>80</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J81" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K81" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L81" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M81" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N81" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O81" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P81" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q81" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
+        <v>81</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J82" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K82" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L82" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M82" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N82" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O82" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P82" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q82" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83" s="3">
+        <v>82</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K83" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L83" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M83" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N83" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O83" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P83" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q83" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84" s="3">
+        <v>83</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J84" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K84" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L84" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M84" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N84" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O84" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P84" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q84" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85" s="3">
+        <v>84</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J85" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K85" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L85" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M85" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N85" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O85" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P85" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q85" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86" s="3">
+        <v>85</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J86" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K86" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L86" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M86" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N86" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O86" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P86" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q86" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87" s="3">
+        <v>86</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J87" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K87" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L87" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M87" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N87" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O87" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P87" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q87" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88" s="3">
+        <v>87</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J88" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K88" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L88" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M88" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N88" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O88" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P88" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q88" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89" s="3">
+        <v>88</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J89" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K89" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L89" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M89" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N89" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O89" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P89" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q89" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
+        <v>89</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J90" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K90" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L90" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M90" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N90" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O90" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P90" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q90" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91" s="3">
+        <v>90</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J91" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K91" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L91" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M91" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N91" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O91" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P91" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q91" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92" s="3">
+        <v>91</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J92" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K92" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L92" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M92" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N92" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O92" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P92" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q92" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93" s="3">
+        <v>92</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J93" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K93" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L93" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M93" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N93" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O93" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P93" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q93" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94" s="3">
+        <v>93</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J94" s="3" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K94" s="3" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L94" s="3" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M94" s="3" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N94" s="3" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O94" s="3" t="e">
+        <f t="shared" si="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P94" s="1" t="e">
+        <f t="shared" si="30"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q94" s="1" t="e">
+        <f t="shared" si="31"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95" s="3">
+        <v>94</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J95" s="3" t="e">
+        <f t="shared" ref="J95:J140" si="32">MID(E95,1,FIND("°",E95,1)-1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K95" s="3" t="e">
+        <f t="shared" ref="K95:K140" si="33">MID(E95,FIND("°",E95,1)+1,(FIND("′",E95,1)-FIND("°",E95,1))-1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L95" s="3" t="e">
+        <f t="shared" ref="L95:L140" si="34">MID(E95,FIND("′",E95,1)+1,(FIND("″",E95,1)-FIND("′",E95,1))-1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M95" s="3" t="e">
+        <f t="shared" ref="M95:M140" si="35">MID(F95,1,FIND("°",F95,1)-1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N95" s="3" t="e">
+        <f t="shared" ref="N95:N140" si="36">MID(F95,FIND("°",F95,1)+1,(FIND("′",F95,1)-FIND("°",F95,1))-1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O95" s="3" t="e">
+        <f t="shared" ref="O95:O140" si="37">MID(F95,FIND("′",F95,1)+1,(FIND("″",F95,1)-FIND("′",F95,1))-1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P95" s="1" t="e">
+        <f t="shared" ref="P95:P140" si="38">((((L95/60)+K95)/60)+J95)*IF(C95="S",-1, 1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q95" s="1" t="e">
+        <f t="shared" ref="Q95:Q140" si="39">((((O95/60)+N95)/60)+M95)*IF(D95="W",-1, 1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96" s="3">
+        <v>95</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K96" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L96" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M96" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N96" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O96" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P96" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q96" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A97" s="3">
+        <v>96</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J97" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K97" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L97" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M97" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N97" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O97" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P97" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q97" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A98" s="3">
+        <v>97</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J98" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K98" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L98" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M98" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N98" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O98" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P98" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q98" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99" s="3">
+        <v>98</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J99" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K99" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L99" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M99" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N99" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O99" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P99" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q99" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A100" s="3">
+        <v>99</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J100" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K100" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L100" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M100" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N100" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O100" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P100" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q100" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A101" s="3">
+        <v>100</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K101" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L101" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M101" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N101" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O101" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P101" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q101" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A102" s="3">
+        <v>101</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J102" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K102" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L102" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M102" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N102" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O102" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P102" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q102" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103" s="3">
+        <v>102</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J103" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K103" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L103" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M103" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N103" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O103" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P103" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q103" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104" s="3">
+        <v>103</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J104" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K104" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L104" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M104" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N104" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O104" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P104" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q104" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A105" s="3">
+        <v>104</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E105" s="7"/>
-      <c r="P105" s="1"/>
-      <c r="Q105" s="1"/>
-    </row>
-    <row r="106" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J105" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K105" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L105" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M105" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N105" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O105" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P105" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q105" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A106" s="3">
+        <v>105</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E106" s="7"/>
-      <c r="P106" s="1"/>
-      <c r="Q106" s="1"/>
-    </row>
-    <row r="107" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J106" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K106" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L106" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M106" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N106" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O106" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P106" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q106" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A107" s="3">
+        <v>106</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E107" s="7"/>
-      <c r="P107" s="1"/>
-      <c r="Q107" s="1"/>
-    </row>
-    <row r="108" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P108" s="1"/>
-      <c r="Q108" s="1"/>
-    </row>
-    <row r="109" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P109" s="1"/>
-      <c r="Q109" s="1"/>
-    </row>
-    <row r="110" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P110" s="1"/>
-      <c r="Q110" s="1"/>
-    </row>
-    <row r="111" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P111" s="1"/>
-      <c r="Q111" s="1"/>
-    </row>
-    <row r="112" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P112" s="1"/>
-      <c r="Q112" s="1"/>
-    </row>
-    <row r="113" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P113" s="1"/>
-      <c r="Q113" s="1"/>
-    </row>
-    <row r="114" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J107" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K107" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L107" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M107" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N107" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O107" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P107" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q107" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A108" s="3">
+        <v>107</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J108" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K108" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L108" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M108" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N108" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O108" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P108" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q108" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109" s="3">
+        <v>108</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J109" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K109" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L109" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M109" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N109" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O109" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P109" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q109" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110" s="3">
+        <v>109</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J110" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K110" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L110" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M110" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N110" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O110" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P110" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q110" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111" s="3">
+        <v>110</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J111" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K111" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L111" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M111" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N111" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O111" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P111" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q111" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A112" s="3">
+        <v>111</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J112" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K112" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L112" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M112" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N112" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O112" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P112" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q112" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A113" s="3">
+        <v>112</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J113" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K113" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L113" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M113" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N113" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O113" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P113" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q113" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A114" s="3">
+        <v>113</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E114" s="7"/>
-      <c r="P114" s="1"/>
-      <c r="Q114" s="1"/>
-    </row>
-    <row r="115" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J114" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K114" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L114" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M114" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N114" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O114" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P114" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q114" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A115" s="3">
+        <v>114</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E115" s="7"/>
-      <c r="P115" s="1"/>
-      <c r="Q115" s="1"/>
-    </row>
-    <row r="116" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J115" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K115" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L115" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M115" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N115" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O115" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P115" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q115" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A116" s="3">
+        <v>115</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E116" s="7"/>
-      <c r="P116" s="1"/>
-      <c r="Q116" s="1"/>
-    </row>
-    <row r="117" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J116" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K116" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L116" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M116" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N116" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O116" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P116" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q116" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A117" s="3">
+        <v>116</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E117" s="7"/>
-      <c r="P117" s="1"/>
-      <c r="Q117" s="1"/>
-    </row>
-    <row r="118" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P118" s="1"/>
-      <c r="Q118" s="1"/>
-    </row>
-    <row r="119" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P119" s="1"/>
-      <c r="Q119" s="1"/>
-    </row>
-    <row r="120" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P120" s="1"/>
-      <c r="Q120" s="1"/>
-    </row>
-    <row r="121" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P121" s="1"/>
-      <c r="Q121" s="1"/>
-    </row>
-    <row r="122" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P122" s="1"/>
-      <c r="Q122" s="1"/>
-    </row>
-    <row r="123" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P123" s="1"/>
-      <c r="Q123" s="1"/>
-    </row>
-    <row r="124" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P124" s="1"/>
-      <c r="Q124" s="1"/>
-    </row>
-    <row r="125" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P125" s="1"/>
-      <c r="Q125" s="1"/>
-    </row>
-    <row r="126" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P126" s="1"/>
-      <c r="Q126" s="1"/>
-    </row>
-    <row r="127" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P127" s="1"/>
-      <c r="Q127" s="1"/>
-    </row>
-    <row r="128" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P128" s="1"/>
-      <c r="Q128" s="1"/>
-    </row>
-    <row r="129" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J117" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K117" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L117" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M117" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N117" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O117" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P117" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q117" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A118" s="3">
+        <v>117</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J118" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K118" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L118" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M118" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N118" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O118" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P118" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q118" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119" s="3">
+        <v>118</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J119" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K119" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L119" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M119" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N119" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O119" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P119" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q119" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A120" s="3">
+        <v>119</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J120" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K120" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L120" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M120" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N120" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O120" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P120" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q120" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A121" s="3">
+        <v>120</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J121" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K121" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L121" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M121" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N121" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O121" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P121" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q121" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A122" s="3">
+        <v>121</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J122" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K122" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L122" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M122" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N122" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O122" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P122" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q122" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A123" s="3">
+        <v>122</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J123" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K123" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L123" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M123" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N123" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O123" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P123" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q123" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A124" s="3">
+        <v>123</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J124" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K124" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L124" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M124" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N124" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O124" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P124" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q124" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A125" s="3">
+        <v>124</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J125" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K125" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L125" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M125" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N125" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O125" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P125" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q125" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A126" s="3">
+        <v>125</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J126" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K126" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L126" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M126" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N126" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O126" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P126" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q126" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A127" s="3">
+        <v>126</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J127" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K127" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L127" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M127" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N127" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O127" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P127" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q127" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A128" s="3">
+        <v>127</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J128" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K128" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L128" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M128" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N128" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O128" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P128" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q128" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A129" s="3">
+        <v>128</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E129" s="7"/>
-      <c r="P129" s="1"/>
-      <c r="Q129" s="1"/>
-    </row>
-    <row r="130" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J129" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K129" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L129" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M129" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N129" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O129" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P129" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q129" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A130" s="3">
+        <v>129</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E130" s="7"/>
-      <c r="P130" s="1"/>
-      <c r="Q130" s="1"/>
-    </row>
-    <row r="131" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P131" s="1"/>
-      <c r="Q131" s="1"/>
-    </row>
-    <row r="132" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P132" s="1"/>
-      <c r="Q132" s="1"/>
-    </row>
-    <row r="133" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P133" s="1"/>
-      <c r="Q133" s="1"/>
-    </row>
-    <row r="134" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P134" s="1"/>
-      <c r="Q134" s="1"/>
-    </row>
-    <row r="135" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P135" s="1"/>
-      <c r="Q135" s="1"/>
-    </row>
-    <row r="136" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P136" s="1"/>
-      <c r="Q136" s="1"/>
-    </row>
-    <row r="137" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P137" s="1"/>
-      <c r="Q137" s="1"/>
-    </row>
-    <row r="138" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J130" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K130" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L130" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M130" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N130" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O130" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P130" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q130" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A131" s="3">
+        <v>130</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J131" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K131" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L131" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M131" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N131" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O131" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P131" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q131" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A132" s="3">
+        <v>131</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J132" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K132" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L132" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M132" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N132" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O132" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P132" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q132" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A133" s="3">
+        <v>132</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J133" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K133" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L133" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M133" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N133" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O133" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P133" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q133" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A134" s="3">
+        <v>133</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J134" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K134" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L134" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M134" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N134" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O134" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P134" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q134" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A135" s="3">
+        <v>134</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J135" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K135" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L135" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M135" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N135" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O135" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P135" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q135" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A136" s="3">
+        <v>135</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J136" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K136" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L136" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M136" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N136" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O136" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P136" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q136" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A137" s="3">
+        <v>136</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J137" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K137" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L137" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M137" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N137" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O137" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P137" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q137" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A138" s="3">
+        <v>137</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
-      <c r="P138" s="1"/>
-      <c r="Q138" s="1"/>
-    </row>
-    <row r="139" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J138" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K138" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L138" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M138" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N138" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O138" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P138" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q138" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A139" s="3">
+        <v>138</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
-      <c r="P139" s="1"/>
-      <c r="Q139" s="1"/>
-    </row>
-    <row r="140" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J139" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K139" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L139" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M139" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N139" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O139" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P139" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q139" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A140" s="3">
+        <v>139</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
-      <c r="P140" s="1"/>
-      <c r="Q140" s="1"/>
-    </row>
-    <row r="141" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J140" s="3" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K140" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L140" s="3" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M140" s="3" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N140" s="3" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O140" s="3" t="e">
+        <f t="shared" si="37"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P140" s="1" t="e">
+        <f t="shared" si="38"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q140" s="1" t="e">
+        <f t="shared" si="39"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
       <c r="P141" s="1"/>
       <c r="Q141" s="1"/>
     </row>
-    <row r="142" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="P142" s="1"/>
       <c r="Q142" s="1"/>
     </row>
-    <row r="143" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="P143" s="1"/>
       <c r="Q143" s="1"/>
     </row>
-    <row r="144" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="P144" s="1"/>
       <c r="Q144" s="1"/>
     </row>
@@ -4407,480 +9075,480 @@
       <c r="Q434" s="1"/>
     </row>
     <row r="435" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B435" s="10"/>
+      <c r="B435" s="8"/>
       <c r="E435" s="7"/>
-      <c r="G435" s="10"/>
-      <c r="H435" s="10"/>
+      <c r="G435" s="8"/>
+      <c r="H435" s="8"/>
       <c r="P435" s="1"/>
       <c r="Q435" s="1"/>
     </row>
     <row r="436" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B436" s="11"/>
-      <c r="E436" s="11"/>
-      <c r="F436" s="11"/>
-      <c r="G436" s="10"/>
-      <c r="H436" s="10"/>
-      <c r="I436" s="12"/>
+      <c r="B436" s="9"/>
+      <c r="E436" s="9"/>
+      <c r="F436" s="9"/>
+      <c r="G436" s="8"/>
+      <c r="H436" s="8"/>
+      <c r="I436" s="10"/>
       <c r="P436" s="1"/>
       <c r="Q436" s="1"/>
     </row>
     <row r="437" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B437" s="11"/>
-      <c r="E437" s="11"/>
-      <c r="F437" s="11"/>
-      <c r="G437" s="10"/>
-      <c r="H437" s="10"/>
-      <c r="I437" s="12"/>
+      <c r="B437" s="9"/>
+      <c r="E437" s="9"/>
+      <c r="F437" s="9"/>
+      <c r="G437" s="8"/>
+      <c r="H437" s="8"/>
+      <c r="I437" s="10"/>
       <c r="P437" s="1"/>
       <c r="Q437" s="1"/>
     </row>
     <row r="438" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B438" s="11"/>
-      <c r="E438" s="11"/>
-      <c r="F438" s="11"/>
-      <c r="G438" s="10"/>
-      <c r="H438" s="10"/>
-      <c r="I438" s="12"/>
+      <c r="B438" s="9"/>
+      <c r="E438" s="9"/>
+      <c r="F438" s="9"/>
+      <c r="G438" s="8"/>
+      <c r="H438" s="8"/>
+      <c r="I438" s="10"/>
       <c r="P438" s="1"/>
       <c r="Q438" s="1"/>
     </row>
     <row r="439" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B439" s="11"/>
-      <c r="E439" s="11"/>
-      <c r="F439" s="11"/>
-      <c r="G439" s="10"/>
-      <c r="H439" s="10"/>
-      <c r="I439" s="12"/>
+      <c r="B439" s="9"/>
+      <c r="E439" s="9"/>
+      <c r="F439" s="9"/>
+      <c r="G439" s="8"/>
+      <c r="H439" s="8"/>
+      <c r="I439" s="10"/>
       <c r="P439" s="1"/>
       <c r="Q439" s="1"/>
     </row>
     <row r="440" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B440" s="11"/>
-      <c r="E440" s="11"/>
-      <c r="F440" s="11"/>
-      <c r="G440" s="10"/>
-      <c r="H440" s="10"/>
-      <c r="I440" s="12"/>
+      <c r="B440" s="9"/>
+      <c r="E440" s="9"/>
+      <c r="F440" s="9"/>
+      <c r="G440" s="8"/>
+      <c r="H440" s="8"/>
+      <c r="I440" s="10"/>
       <c r="P440" s="1"/>
       <c r="Q440" s="1"/>
     </row>
     <row r="441" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B441" s="11"/>
-      <c r="E441" s="11"/>
-      <c r="F441" s="11"/>
-      <c r="G441" s="10"/>
-      <c r="H441" s="10"/>
-      <c r="I441" s="12"/>
+      <c r="B441" s="9"/>
+      <c r="E441" s="9"/>
+      <c r="F441" s="9"/>
+      <c r="G441" s="8"/>
+      <c r="H441" s="8"/>
+      <c r="I441" s="10"/>
       <c r="P441" s="1"/>
       <c r="Q441" s="1"/>
     </row>
     <row r="442" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B442" s="11"/>
-      <c r="E442" s="12"/>
-      <c r="F442" s="12"/>
-      <c r="G442" s="10"/>
-      <c r="H442" s="10"/>
-      <c r="I442" s="12"/>
+      <c r="B442" s="9"/>
+      <c r="E442" s="10"/>
+      <c r="F442" s="10"/>
+      <c r="G442" s="8"/>
+      <c r="H442" s="8"/>
+      <c r="I442" s="10"/>
       <c r="P442" s="1"/>
       <c r="Q442" s="1"/>
     </row>
     <row r="443" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B443" s="11"/>
-      <c r="E443" s="12"/>
-      <c r="F443" s="12"/>
-      <c r="G443" s="10"/>
-      <c r="H443" s="10"/>
-      <c r="I443" s="12"/>
+      <c r="B443" s="9"/>
+      <c r="E443" s="10"/>
+      <c r="F443" s="10"/>
+      <c r="G443" s="8"/>
+      <c r="H443" s="8"/>
+      <c r="I443" s="10"/>
       <c r="P443" s="1"/>
       <c r="Q443" s="1"/>
     </row>
     <row r="444" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B444" s="11"/>
-      <c r="E444" s="12"/>
-      <c r="F444" s="12"/>
-      <c r="G444" s="10"/>
-      <c r="H444" s="10"/>
-      <c r="I444" s="12"/>
+      <c r="B444" s="9"/>
+      <c r="E444" s="10"/>
+      <c r="F444" s="10"/>
+      <c r="G444" s="8"/>
+      <c r="H444" s="8"/>
+      <c r="I444" s="10"/>
       <c r="P444" s="1"/>
       <c r="Q444" s="1"/>
     </row>
     <row r="445" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B445" s="11"/>
-      <c r="E445" s="12"/>
-      <c r="F445" s="12"/>
-      <c r="G445" s="10"/>
-      <c r="H445" s="10"/>
-      <c r="I445" s="12"/>
+      <c r="B445" s="9"/>
+      <c r="E445" s="10"/>
+      <c r="F445" s="10"/>
+      <c r="G445" s="8"/>
+      <c r="H445" s="8"/>
+      <c r="I445" s="10"/>
       <c r="P445" s="1"/>
       <c r="Q445" s="1"/>
     </row>
     <row r="446" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B446" s="11"/>
-      <c r="E446" s="12"/>
-      <c r="F446" s="12"/>
-      <c r="G446" s="10"/>
-      <c r="H446" s="10"/>
-      <c r="I446" s="12"/>
+      <c r="B446" s="9"/>
+      <c r="E446" s="10"/>
+      <c r="F446" s="10"/>
+      <c r="G446" s="8"/>
+      <c r="H446" s="8"/>
+      <c r="I446" s="10"/>
       <c r="P446" s="1"/>
       <c r="Q446" s="1"/>
     </row>
     <row r="447" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B447" s="11"/>
-      <c r="E447" s="12"/>
-      <c r="F447" s="12"/>
-      <c r="G447" s="10"/>
-      <c r="H447" s="10"/>
-      <c r="I447" s="12"/>
+      <c r="B447" s="9"/>
+      <c r="E447" s="10"/>
+      <c r="F447" s="10"/>
+      <c r="G447" s="8"/>
+      <c r="H447" s="8"/>
+      <c r="I447" s="10"/>
       <c r="P447" s="1"/>
       <c r="Q447" s="1"/>
     </row>
     <row r="448" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B448" s="11"/>
-      <c r="E448" s="12"/>
-      <c r="F448" s="12"/>
-      <c r="G448" s="10"/>
-      <c r="H448" s="10"/>
-      <c r="I448" s="12"/>
+      <c r="B448" s="9"/>
+      <c r="E448" s="10"/>
+      <c r="F448" s="10"/>
+      <c r="G448" s="8"/>
+      <c r="H448" s="8"/>
+      <c r="I448" s="10"/>
       <c r="P448" s="1"/>
       <c r="Q448" s="1"/>
     </row>
     <row r="449" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B449" s="11"/>
-      <c r="E449" s="12"/>
-      <c r="F449" s="12"/>
-      <c r="G449" s="10"/>
-      <c r="H449" s="10"/>
-      <c r="I449" s="12"/>
+      <c r="B449" s="9"/>
+      <c r="E449" s="10"/>
+      <c r="F449" s="10"/>
+      <c r="G449" s="8"/>
+      <c r="H449" s="8"/>
+      <c r="I449" s="10"/>
       <c r="P449" s="1"/>
       <c r="Q449" s="1"/>
     </row>
     <row r="450" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B450" s="11"/>
-      <c r="E450" s="12"/>
-      <c r="F450" s="12"/>
-      <c r="G450" s="10"/>
-      <c r="H450" s="10"/>
-      <c r="I450" s="12"/>
+      <c r="B450" s="9"/>
+      <c r="E450" s="10"/>
+      <c r="F450" s="10"/>
+      <c r="G450" s="8"/>
+      <c r="H450" s="8"/>
+      <c r="I450" s="10"/>
       <c r="P450" s="1"/>
       <c r="Q450" s="1"/>
     </row>
     <row r="451" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B451" s="11"/>
-      <c r="E451" s="12"/>
-      <c r="F451" s="12"/>
-      <c r="G451" s="10"/>
-      <c r="H451" s="10"/>
-      <c r="I451" s="12"/>
+      <c r="B451" s="9"/>
+      <c r="E451" s="10"/>
+      <c r="F451" s="10"/>
+      <c r="G451" s="8"/>
+      <c r="H451" s="8"/>
+      <c r="I451" s="10"/>
       <c r="P451" s="1"/>
       <c r="Q451" s="1"/>
     </row>
     <row r="452" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B452" s="11"/>
-      <c r="E452" s="12"/>
-      <c r="F452" s="12"/>
-      <c r="G452" s="10"/>
-      <c r="H452" s="10"/>
-      <c r="I452" s="12"/>
+      <c r="B452" s="9"/>
+      <c r="E452" s="10"/>
+      <c r="F452" s="10"/>
+      <c r="G452" s="8"/>
+      <c r="H452" s="8"/>
+      <c r="I452" s="10"/>
       <c r="P452" s="1"/>
       <c r="Q452" s="1"/>
     </row>
     <row r="453" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B453" s="11"/>
-      <c r="E453" s="12"/>
-      <c r="F453" s="12"/>
-      <c r="G453" s="10"/>
-      <c r="H453" s="10"/>
-      <c r="I453" s="12"/>
+      <c r="B453" s="9"/>
+      <c r="E453" s="10"/>
+      <c r="F453" s="10"/>
+      <c r="G453" s="8"/>
+      <c r="H453" s="8"/>
+      <c r="I453" s="10"/>
       <c r="P453" s="1"/>
       <c r="Q453" s="1"/>
     </row>
     <row r="454" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B454" s="11"/>
-      <c r="E454" s="12"/>
-      <c r="F454" s="12"/>
-      <c r="G454" s="10"/>
-      <c r="H454" s="10"/>
-      <c r="I454" s="12"/>
+      <c r="B454" s="9"/>
+      <c r="E454" s="10"/>
+      <c r="F454" s="10"/>
+      <c r="G454" s="8"/>
+      <c r="H454" s="8"/>
+      <c r="I454" s="10"/>
       <c r="P454" s="1"/>
       <c r="Q454" s="1"/>
     </row>
     <row r="455" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B455" s="11"/>
-      <c r="E455" s="12"/>
-      <c r="F455" s="12"/>
-      <c r="G455" s="10"/>
-      <c r="H455" s="10"/>
-      <c r="I455" s="12"/>
+      <c r="B455" s="9"/>
+      <c r="E455" s="10"/>
+      <c r="F455" s="10"/>
+      <c r="G455" s="8"/>
+      <c r="H455" s="8"/>
+      <c r="I455" s="10"/>
       <c r="P455" s="1"/>
       <c r="Q455" s="1"/>
     </row>
     <row r="456" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B456" s="11"/>
-      <c r="E456" s="12"/>
-      <c r="F456" s="12"/>
-      <c r="G456" s="10"/>
-      <c r="H456" s="10"/>
-      <c r="I456" s="12"/>
+      <c r="B456" s="9"/>
+      <c r="E456" s="10"/>
+      <c r="F456" s="10"/>
+      <c r="G456" s="8"/>
+      <c r="H456" s="8"/>
+      <c r="I456" s="10"/>
       <c r="P456" s="1"/>
       <c r="Q456" s="1"/>
     </row>
     <row r="457" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B457" s="11"/>
-      <c r="E457" s="12"/>
-      <c r="F457" s="12"/>
-      <c r="G457" s="10"/>
-      <c r="H457" s="10"/>
-      <c r="I457" s="12"/>
+      <c r="B457" s="9"/>
+      <c r="E457" s="10"/>
+      <c r="F457" s="10"/>
+      <c r="G457" s="8"/>
+      <c r="H457" s="8"/>
+      <c r="I457" s="10"/>
       <c r="P457" s="1"/>
       <c r="Q457" s="1"/>
     </row>
     <row r="458" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B458" s="11"/>
-      <c r="E458" s="12"/>
-      <c r="F458" s="12"/>
-      <c r="G458" s="10"/>
-      <c r="H458" s="10"/>
-      <c r="I458" s="12"/>
+      <c r="B458" s="9"/>
+      <c r="E458" s="10"/>
+      <c r="F458" s="10"/>
+      <c r="G458" s="8"/>
+      <c r="H458" s="8"/>
+      <c r="I458" s="10"/>
       <c r="P458" s="1"/>
       <c r="Q458" s="1"/>
     </row>
     <row r="459" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B459" s="11"/>
-      <c r="E459" s="12"/>
-      <c r="F459" s="12"/>
-      <c r="G459" s="10"/>
-      <c r="H459" s="10"/>
-      <c r="I459" s="12"/>
+      <c r="B459" s="9"/>
+      <c r="E459" s="10"/>
+      <c r="F459" s="10"/>
+      <c r="G459" s="8"/>
+      <c r="H459" s="8"/>
+      <c r="I459" s="10"/>
       <c r="P459" s="1"/>
       <c r="Q459" s="1"/>
     </row>
     <row r="460" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B460" s="11"/>
-      <c r="E460" s="12"/>
-      <c r="F460" s="12"/>
-      <c r="G460" s="10"/>
-      <c r="H460" s="10"/>
-      <c r="I460" s="12"/>
+      <c r="B460" s="9"/>
+      <c r="E460" s="10"/>
+      <c r="F460" s="10"/>
+      <c r="G460" s="8"/>
+      <c r="H460" s="8"/>
+      <c r="I460" s="10"/>
       <c r="P460" s="1"/>
       <c r="Q460" s="1"/>
     </row>
     <row r="461" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B461" s="12"/>
-      <c r="E461" s="11"/>
-      <c r="F461" s="11"/>
-      <c r="G461" s="10"/>
-      <c r="H461" s="10"/>
-      <c r="I461" s="12"/>
+      <c r="B461" s="10"/>
+      <c r="E461" s="9"/>
+      <c r="F461" s="9"/>
+      <c r="G461" s="8"/>
+      <c r="H461" s="8"/>
+      <c r="I461" s="10"/>
       <c r="P461" s="1"/>
       <c r="Q461" s="1"/>
     </row>
     <row r="462" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B462" s="12"/>
-      <c r="E462" s="11"/>
-      <c r="F462" s="11"/>
-      <c r="G462" s="10"/>
-      <c r="H462" s="10"/>
-      <c r="I462" s="12"/>
+      <c r="B462" s="10"/>
+      <c r="E462" s="9"/>
+      <c r="F462" s="9"/>
+      <c r="G462" s="8"/>
+      <c r="H462" s="8"/>
+      <c r="I462" s="10"/>
       <c r="P462" s="1"/>
       <c r="Q462" s="1"/>
     </row>
     <row r="463" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B463" s="12"/>
-      <c r="E463" s="11"/>
-      <c r="F463" s="11"/>
-      <c r="G463" s="10"/>
-      <c r="H463" s="10"/>
-      <c r="I463" s="12"/>
+      <c r="B463" s="10"/>
+      <c r="E463" s="9"/>
+      <c r="F463" s="9"/>
+      <c r="G463" s="8"/>
+      <c r="H463" s="8"/>
+      <c r="I463" s="10"/>
       <c r="P463" s="1"/>
       <c r="Q463" s="1"/>
     </row>
     <row r="464" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B464" s="12"/>
-      <c r="E464" s="12"/>
-      <c r="F464" s="12"/>
-      <c r="G464" s="10"/>
-      <c r="H464" s="10"/>
-      <c r="I464" s="12"/>
+      <c r="B464" s="10"/>
+      <c r="E464" s="10"/>
+      <c r="F464" s="10"/>
+      <c r="G464" s="8"/>
+      <c r="H464" s="8"/>
+      <c r="I464" s="10"/>
       <c r="P464" s="1"/>
       <c r="Q464" s="1"/>
     </row>
     <row r="465" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B465" s="12"/>
-      <c r="E465" s="12"/>
-      <c r="F465" s="12"/>
-      <c r="G465" s="10"/>
-      <c r="H465" s="10"/>
-      <c r="I465" s="12"/>
+      <c r="B465" s="10"/>
+      <c r="E465" s="10"/>
+      <c r="F465" s="10"/>
+      <c r="G465" s="8"/>
+      <c r="H465" s="8"/>
+      <c r="I465" s="10"/>
       <c r="P465" s="1"/>
       <c r="Q465" s="1"/>
     </row>
     <row r="466" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B466" s="12"/>
-      <c r="E466" s="12"/>
-      <c r="F466" s="12"/>
-      <c r="G466" s="10"/>
-      <c r="H466" s="10"/>
-      <c r="I466" s="12"/>
+      <c r="B466" s="10"/>
+      <c r="E466" s="10"/>
+      <c r="F466" s="10"/>
+      <c r="G466" s="8"/>
+      <c r="H466" s="8"/>
+      <c r="I466" s="10"/>
       <c r="P466" s="1"/>
       <c r="Q466" s="1"/>
     </row>
     <row r="467" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B467" s="12"/>
-      <c r="E467" s="11"/>
-      <c r="F467" s="11"/>
-      <c r="G467" s="10"/>
-      <c r="H467" s="10"/>
-      <c r="I467" s="12"/>
+      <c r="B467" s="10"/>
+      <c r="E467" s="9"/>
+      <c r="F467" s="9"/>
+      <c r="G467" s="8"/>
+      <c r="H467" s="8"/>
+      <c r="I467" s="10"/>
       <c r="P467" s="1"/>
       <c r="Q467" s="1"/>
     </row>
     <row r="468" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B468" s="12"/>
-      <c r="E468" s="11"/>
-      <c r="F468" s="11"/>
-      <c r="G468" s="10"/>
-      <c r="H468" s="10"/>
-      <c r="I468" s="12"/>
+      <c r="B468" s="10"/>
+      <c r="E468" s="9"/>
+      <c r="F468" s="9"/>
+      <c r="G468" s="8"/>
+      <c r="H468" s="8"/>
+      <c r="I468" s="10"/>
       <c r="P468" s="1"/>
       <c r="Q468" s="1"/>
     </row>
     <row r="469" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B469" s="12"/>
-      <c r="E469" s="12"/>
-      <c r="F469" s="12"/>
-      <c r="G469" s="10"/>
-      <c r="H469" s="10"/>
-      <c r="I469" s="12"/>
+      <c r="B469" s="10"/>
+      <c r="E469" s="10"/>
+      <c r="F469" s="10"/>
+      <c r="G469" s="8"/>
+      <c r="H469" s="8"/>
+      <c r="I469" s="10"/>
       <c r="P469" s="1"/>
       <c r="Q469" s="1"/>
     </row>
     <row r="470" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B470" s="12"/>
-      <c r="E470" s="12"/>
-      <c r="F470" s="12"/>
-      <c r="G470" s="10"/>
-      <c r="H470" s="10"/>
-      <c r="I470" s="12"/>
+      <c r="B470" s="10"/>
+      <c r="E470" s="10"/>
+      <c r="F470" s="10"/>
+      <c r="G470" s="8"/>
+      <c r="H470" s="8"/>
+      <c r="I470" s="10"/>
       <c r="P470" s="1"/>
       <c r="Q470" s="1"/>
     </row>
     <row r="471" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B471" s="11"/>
-      <c r="E471" s="11"/>
-      <c r="F471" s="11"/>
-      <c r="G471" s="10"/>
-      <c r="H471" s="10"/>
-      <c r="I471" s="12"/>
+      <c r="B471" s="9"/>
+      <c r="E471" s="9"/>
+      <c r="F471" s="9"/>
+      <c r="G471" s="8"/>
+      <c r="H471" s="8"/>
+      <c r="I471" s="10"/>
       <c r="P471" s="1"/>
       <c r="Q471" s="1"/>
     </row>
     <row r="472" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B472" s="11"/>
-      <c r="E472" s="11"/>
-      <c r="F472" s="11"/>
-      <c r="G472" s="10"/>
-      <c r="H472" s="10"/>
-      <c r="I472" s="12"/>
+      <c r="B472" s="9"/>
+      <c r="E472" s="9"/>
+      <c r="F472" s="9"/>
+      <c r="G472" s="8"/>
+      <c r="H472" s="8"/>
+      <c r="I472" s="10"/>
       <c r="P472" s="1"/>
       <c r="Q472" s="1"/>
     </row>
     <row r="473" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B473" s="11"/>
-      <c r="E473" s="11"/>
-      <c r="F473" s="11"/>
-      <c r="G473" s="10"/>
-      <c r="H473" s="10"/>
-      <c r="I473" s="12"/>
+      <c r="B473" s="9"/>
+      <c r="E473" s="9"/>
+      <c r="F473" s="9"/>
+      <c r="G473" s="8"/>
+      <c r="H473" s="8"/>
+      <c r="I473" s="10"/>
       <c r="P473" s="1"/>
       <c r="Q473" s="1"/>
     </row>
     <row r="474" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B474" s="11"/>
-      <c r="E474" s="11"/>
-      <c r="F474" s="11"/>
-      <c r="G474" s="10"/>
-      <c r="H474" s="10"/>
-      <c r="I474" s="12"/>
+      <c r="B474" s="9"/>
+      <c r="E474" s="9"/>
+      <c r="F474" s="9"/>
+      <c r="G474" s="8"/>
+      <c r="H474" s="8"/>
+      <c r="I474" s="10"/>
       <c r="P474" s="1"/>
       <c r="Q474" s="1"/>
     </row>
     <row r="475" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B475" s="11"/>
-      <c r="E475" s="12"/>
-      <c r="F475" s="12"/>
-      <c r="G475" s="10"/>
-      <c r="H475" s="10"/>
-      <c r="I475" s="12"/>
+      <c r="B475" s="9"/>
+      <c r="E475" s="10"/>
+      <c r="F475" s="10"/>
+      <c r="G475" s="8"/>
+      <c r="H475" s="8"/>
+      <c r="I475" s="10"/>
       <c r="P475" s="1"/>
       <c r="Q475" s="1"/>
     </row>
     <row r="476" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B476" s="11"/>
-      <c r="E476" s="12"/>
-      <c r="F476" s="12"/>
-      <c r="G476" s="10"/>
-      <c r="H476" s="10"/>
-      <c r="I476" s="12"/>
+      <c r="B476" s="9"/>
+      <c r="E476" s="10"/>
+      <c r="F476" s="10"/>
+      <c r="G476" s="8"/>
+      <c r="H476" s="8"/>
+      <c r="I476" s="10"/>
       <c r="P476" s="1"/>
       <c r="Q476" s="1"/>
     </row>
     <row r="477" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B477" s="11"/>
-      <c r="E477" s="12"/>
-      <c r="F477" s="12"/>
-      <c r="G477" s="10"/>
-      <c r="H477" s="10"/>
-      <c r="I477" s="12"/>
+      <c r="B477" s="9"/>
+      <c r="E477" s="10"/>
+      <c r="F477" s="10"/>
+      <c r="G477" s="8"/>
+      <c r="H477" s="8"/>
+      <c r="I477" s="10"/>
       <c r="P477" s="1"/>
       <c r="Q477" s="1"/>
     </row>
     <row r="478" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B478" s="11"/>
-      <c r="E478" s="11"/>
-      <c r="F478" s="11"/>
-      <c r="G478" s="10"/>
-      <c r="H478" s="10"/>
-      <c r="I478" s="12"/>
+      <c r="B478" s="9"/>
+      <c r="E478" s="9"/>
+      <c r="F478" s="9"/>
+      <c r="G478" s="8"/>
+      <c r="H478" s="8"/>
+      <c r="I478" s="10"/>
       <c r="P478" s="1"/>
       <c r="Q478" s="1"/>
     </row>
     <row r="479" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B479" s="11"/>
-      <c r="E479" s="11"/>
-      <c r="F479" s="11"/>
-      <c r="G479" s="10"/>
-      <c r="H479" s="10"/>
-      <c r="I479" s="12"/>
+      <c r="B479" s="9"/>
+      <c r="E479" s="9"/>
+      <c r="F479" s="9"/>
+      <c r="G479" s="8"/>
+      <c r="H479" s="8"/>
+      <c r="I479" s="10"/>
       <c r="P479" s="1"/>
       <c r="Q479" s="1"/>
     </row>
     <row r="480" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B480" s="11"/>
-      <c r="E480" s="12"/>
-      <c r="F480" s="12"/>
-      <c r="G480" s="10"/>
-      <c r="H480" s="10"/>
-      <c r="I480" s="12"/>
+      <c r="B480" s="9"/>
+      <c r="E480" s="10"/>
+      <c r="F480" s="10"/>
+      <c r="G480" s="8"/>
+      <c r="H480" s="8"/>
+      <c r="I480" s="10"/>
       <c r="P480" s="1"/>
       <c r="Q480" s="1"/>
     </row>
     <row r="481" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B481" s="11"/>
-      <c r="E481" s="12"/>
-      <c r="F481" s="12"/>
-      <c r="G481" s="10"/>
-      <c r="H481" s="10"/>
-      <c r="I481" s="12"/>
+      <c r="B481" s="9"/>
+      <c r="E481" s="10"/>
+      <c r="F481" s="10"/>
+      <c r="G481" s="8"/>
+      <c r="H481" s="8"/>
+      <c r="I481" s="10"/>
       <c r="P481" s="1"/>
       <c r="Q481" s="1"/>
     </row>
     <row r="482" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B482" s="11"/>
-      <c r="E482" s="12"/>
-      <c r="F482" s="12"/>
-      <c r="G482" s="10"/>
-      <c r="H482" s="10"/>
-      <c r="I482" s="12"/>
+      <c r="B482" s="9"/>
+      <c r="E482" s="10"/>
+      <c r="F482" s="10"/>
+      <c r="G482" s="8"/>
+      <c r="H482" s="8"/>
+      <c r="I482" s="10"/>
       <c r="P482" s="1"/>
       <c r="Q482" s="1"/>
     </row>
@@ -4938,6 +9606,7 @@
     </row>
   </sheetData>
   <autoFilter ref="B1:I482" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Ocorrências Literatura.xlsx
+++ b/Ocorrências Literatura.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faculdade\Laboratorio\lagostas_carapaca\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1DE25C-A56E-41E4-9CB4-4A917A550F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EEE8A1-169B-44F9-A319-6912070AF953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="143">
   <si>
     <t>origem</t>
   </si>
@@ -326,6 +326,147 @@
   </si>
   <si>
     <t>Cruz, R. (2025)</t>
+  </si>
+  <si>
+    <t>8°30′07″</t>
+  </si>
+  <si>
+    <t>35°00′08″</t>
+  </si>
+  <si>
+    <t>Porto de Galinhas</t>
+  </si>
+  <si>
+    <t>08°44′23″</t>
+  </si>
+  <si>
+    <t>35°02′28″</t>
+  </si>
+  <si>
+    <t>Tamandaré, PE</t>
+  </si>
+  <si>
+    <t>1-s2.0-S1470160X21011304-main</t>
+  </si>
+  <si>
+    <t>Giraldes, B (2021)</t>
+  </si>
+  <si>
+    <t>Guarapari (ES)</t>
+  </si>
+  <si>
+    <t>20°39′</t>
+  </si>
+  <si>
+    <t>40°30′</t>
+  </si>
+  <si>
+    <t>20°43′</t>
+  </si>
+  <si>
+    <t>40°46′</t>
+  </si>
+  <si>
+    <t>21°02′</t>
+  </si>
+  <si>
+    <t>40°49′</t>
+  </si>
+  <si>
+    <t>Anchieta (ES)</t>
+  </si>
+  <si>
+    <t>Marataízes (ES)</t>
+  </si>
+  <si>
+    <t>MELO, Andressa C. M. (2025)</t>
+  </si>
+  <si>
+    <t>Fisheries Management Eco - 2025 - Melo - Reproductive Biology of the Smoothtail Spiny Lobster  Panulirus laevicauda  to</t>
+  </si>
+  <si>
+    <t>São Pedro e São Paulo</t>
+  </si>
+  <si>
+    <t>0°55′10″</t>
+  </si>
+  <si>
+    <t>29°20′33″</t>
+  </si>
+  <si>
+    <t>0°54.787′</t>
+  </si>
+  <si>
+    <t>29°21.451′</t>
+  </si>
+  <si>
+    <t>0°55.681′</t>
+  </si>
+  <si>
+    <t>29°19.804′</t>
+  </si>
+  <si>
+    <t>Nunesetal2017DeepSeaDecapodCrustaceansSPSPA</t>
+  </si>
+  <si>
+    <t>NUNES, Diogo Martins (2017)</t>
+  </si>
+  <si>
+    <t>8°59′57″</t>
+  </si>
+  <si>
+    <t>35°10′49″</t>
+  </si>
+  <si>
+    <t>Alagoas (Maragogi / São José da Coroa Grande)</t>
+  </si>
+  <si>
+    <t>Bragrança</t>
+  </si>
+  <si>
+    <t>1°03′57″</t>
+  </si>
+  <si>
+    <t>46°47′22″W</t>
+  </si>
+  <si>
+    <t>PANAMJAS_16(2)_123-128</t>
+  </si>
+  <si>
+    <t>peerj-19586</t>
+  </si>
+  <si>
+    <t>GAETA, Juliana de Carvalho (2021)</t>
+  </si>
+  <si>
+    <t>SOUSA, Jefferson (2025)</t>
+  </si>
+  <si>
+    <t>Recife (PE)</t>
+  </si>
+  <si>
+    <t>08°10′</t>
+  </si>
+  <si>
+    <t>34°49′</t>
+  </si>
+  <si>
+    <t>s00435-019-00461-5</t>
+  </si>
+  <si>
+    <t>HAMILTON, Santiago (2019)</t>
+  </si>
+  <si>
+    <t>8°30′54″</t>
+  </si>
+  <si>
+    <t>34°59′47″</t>
+  </si>
+  <si>
+    <t>Giraldes, B (2012)</t>
+  </si>
+  <si>
+    <t>Composition and spatial distribution of subtidal Decapoda on the “Reef Coast”, northeastern Brazil, evaluated through a low-impact visual census technique</t>
   </si>
 </sst>
 </file>
@@ -482,7 +623,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -553,6 +694,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -843,7 +987,7 @@
     <col min="4" max="4" width="9.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.28515625" style="3" customWidth="1"/>
     <col min="9" max="9" width="45" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="9.140625" style="3"/>
@@ -1383,7 +1527,7 @@
       <c r="H9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="25" t="s">
         <v>37</v>
       </c>
       <c r="J9" s="3" t="str">
@@ -2517,7 +2661,7 @@
       <c r="F27" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="8" t="s">
         <v>84</v>
       </c>
       <c r="H27" s="3" t="s">
@@ -2581,7 +2725,7 @@
       <c r="F28" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="8" t="s">
         <v>84</v>
       </c>
       <c r="H28" s="3" t="s">
@@ -2645,7 +2789,7 @@
       <c r="F29" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="8" t="s">
         <v>84</v>
       </c>
       <c r="H29" s="3" t="s">
@@ -2709,7 +2853,7 @@
       <c r="F30" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="8" t="s">
         <v>84</v>
       </c>
       <c r="H30" s="3" t="s">
@@ -2767,10 +2911,10 @@
       <c r="D31" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="8" t="s">
         <v>88</v>
       </c>
       <c r="G31" s="8" t="s">
@@ -2831,10 +2975,10 @@
       <c r="D32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="8" t="s">
         <v>92</v>
       </c>
       <c r="G32" s="8" t="s">
@@ -2895,10 +3039,10 @@
       <c r="D33" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="8" t="s">
         <v>94</v>
       </c>
       <c r="G33" s="8" t="s">
@@ -2907,7 +3051,9 @@
       <c r="H33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I33" s="5"/>
+      <c r="I33" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="J33" s="3" t="str">
         <f t="shared" si="24"/>
         <v>3</v>
@@ -2944,210 +3090,309 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>33</v>
       </c>
+      <c r="B34" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C34" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I34" s="5"/>
-      <c r="J34" s="3" t="e">
+      <c r="E34" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J34" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K34" s="3" t="e">
+        <v>8</v>
+      </c>
+      <c r="K34" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L34" s="3" t="e">
+        <v>30</v>
+      </c>
+      <c r="L34" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M34" s="3" t="e">
+        <v>07</v>
+      </c>
+      <c r="M34" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N34" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="N34" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O34" s="3" t="e">
+        <v>00</v>
+      </c>
+      <c r="O34" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P34" s="1" t="e">
+        <v>08</v>
+      </c>
+      <c r="P34" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q34" s="1" t="e">
+        <v>-8.5019444444444439</v>
+      </c>
+      <c r="Q34" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-35.002222222222223</v>
+      </c>
+      <c r="R34" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>34</v>
       </c>
+      <c r="B35" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C35" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I35" s="5"/>
-      <c r="J35" s="3" t="e">
+      <c r="E35" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J35" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K35" s="3" t="e">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L35" s="3" t="e">
+        <v>30</v>
+      </c>
+      <c r="L35" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M35" s="3" t="e">
+        <v>07</v>
+      </c>
+      <c r="M35" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N35" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="N35" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O35" s="3" t="e">
+        <v>00</v>
+      </c>
+      <c r="O35" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P35" s="1" t="e">
+        <v>08</v>
+      </c>
+      <c r="P35" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q35" s="1" t="e">
+        <v>-8.5019444444444439</v>
+      </c>
+      <c r="Q35" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-35.002222222222223</v>
+      </c>
+      <c r="R35" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>35</v>
       </c>
+      <c r="B36" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C36" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I36" s="5"/>
-      <c r="J36" s="3" t="e">
+      <c r="E36" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J36" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K36" s="3" t="e">
+        <v>8</v>
+      </c>
+      <c r="K36" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L36" s="3" t="e">
+        <v>30</v>
+      </c>
+      <c r="L36" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M36" s="3" t="e">
+        <v>07</v>
+      </c>
+      <c r="M36" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N36" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="N36" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O36" s="3" t="e">
+        <v>00</v>
+      </c>
+      <c r="O36" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P36" s="1" t="e">
+        <v>08</v>
+      </c>
+      <c r="P36" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q36" s="1" t="e">
+        <v>-8.5019444444444439</v>
+      </c>
+      <c r="Q36" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-35.002222222222223</v>
+      </c>
+      <c r="R36" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>36</v>
       </c>
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C37" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J37" s="3" t="e">
+      <c r="E37" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="J37" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K37" s="3" t="e">
+        <v>08</v>
+      </c>
+      <c r="K37" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L37" s="3" t="e">
+        <v>44</v>
+      </c>
+      <c r="L37" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M37" s="3" t="e">
+        <v>23</v>
+      </c>
+      <c r="M37" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N37" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="N37" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O37" s="3" t="e">
+        <v>02</v>
+      </c>
+      <c r="O37" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P37" s="1" t="e">
+        <v>28</v>
+      </c>
+      <c r="P37" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q37" s="1" t="e">
+        <v>-8.7397222222222215</v>
+      </c>
+      <c r="Q37" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-35.041111111111114</v>
+      </c>
+      <c r="R37" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>37</v>
       </c>
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C38" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J38" s="3" t="e">
+      <c r="E38" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="J38" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K38" s="3" t="e">
+        <v>20</v>
+      </c>
+      <c r="K38" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>39</v>
       </c>
       <c r="L38" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M38" s="3" t="e">
+      <c r="M38" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N38" s="3" t="e">
+        <v>40</v>
+      </c>
+      <c r="N38" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>30</v>
       </c>
       <c r="O38" s="3" t="e">
         <f t="shared" si="29"/>
@@ -3161,36 +3406,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R38" s="14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>38</v>
       </c>
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C39" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J39" s="3" t="e">
+      <c r="E39" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="J39" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K39" s="3" t="e">
+        <v>20</v>
+      </c>
+      <c r="K39" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>43</v>
       </c>
       <c r="L39" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M39" s="3" t="e">
+      <c r="M39" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N39" s="3" t="e">
+        <v>40</v>
+      </c>
+      <c r="N39" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>46</v>
       </c>
       <c r="O39" s="3" t="e">
         <f t="shared" si="29"/>
@@ -3204,36 +3470,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R39" s="14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>39</v>
       </c>
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C40" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J40" s="3" t="e">
+      <c r="E40" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="J40" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K40" s="3" t="e">
+        <v>21</v>
+      </c>
+      <c r="K40" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>02</v>
       </c>
       <c r="L40" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M40" s="3" t="e">
+      <c r="M40" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N40" s="3" t="e">
+        <v>40</v>
+      </c>
+      <c r="N40" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>49</v>
       </c>
       <c r="O40" s="3" t="e">
         <f t="shared" si="29"/>
@@ -3247,81 +3534,121 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R40" s="14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>40</v>
       </c>
+      <c r="B41" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C41" s="3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I41" s="5"/>
-      <c r="J41" s="3" t="e">
+      <c r="E41" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J41" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K41" s="3" t="e">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L41" s="3" t="e">
+        <v>55</v>
+      </c>
+      <c r="L41" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M41" s="3" t="e">
+        <v>10</v>
+      </c>
+      <c r="M41" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N41" s="3" t="e">
+        <v>29</v>
+      </c>
+      <c r="N41" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O41" s="3" t="e">
+        <v>20</v>
+      </c>
+      <c r="O41" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P41" s="1" t="e">
+        <v>33</v>
+      </c>
+      <c r="P41" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q41" s="1" t="e">
+        <v>0.9194444444444444</v>
+      </c>
+      <c r="Q41" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-29.342500000000001</v>
+      </c>
+      <c r="R41" s="14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>41</v>
       </c>
+      <c r="B42" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C42" s="3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I42" s="5"/>
-      <c r="J42" s="3" t="e">
+      <c r="E42" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J42" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K42" s="3" t="e">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>54.787</v>
       </c>
       <c r="L42" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M42" s="3" t="e">
+      <c r="M42" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N42" s="3" t="e">
+        <v>29</v>
+      </c>
+      <c r="N42" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>21.451</v>
       </c>
       <c r="O42" s="3" t="e">
         <f t="shared" si="29"/>
@@ -3335,37 +3662,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R42" s="14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>42</v>
       </c>
+      <c r="B43" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C43" s="3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="5"/>
-      <c r="J43" s="3" t="e">
+      <c r="E43" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J43" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K43" s="3" t="e">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>55.681</v>
       </c>
       <c r="L43" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M43" s="3" t="e">
+      <c r="M43" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N43" s="3" t="e">
+        <v>29</v>
+      </c>
+      <c r="N43" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>19.804</v>
       </c>
       <c r="O43" s="3" t="e">
         <f t="shared" si="29"/>
@@ -3379,80 +3726,121 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R43" s="14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>43</v>
       </c>
+      <c r="B44" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C44" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I44" s="5"/>
-      <c r="J44" s="3" t="e">
+      <c r="E44" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J44" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K44" s="3" t="e">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L44" s="3" t="e">
+        <v>55</v>
+      </c>
+      <c r="L44" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M44" s="3" t="e">
+        <v>10</v>
+      </c>
+      <c r="M44" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N44" s="3" t="e">
+        <v>29</v>
+      </c>
+      <c r="N44" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O44" s="3" t="e">
+        <v>20</v>
+      </c>
+      <c r="O44" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P44" s="1" t="e">
+        <v>33</v>
+      </c>
+      <c r="P44" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q44" s="1" t="e">
+        <v>-0.9194444444444444</v>
+      </c>
+      <c r="Q44" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-29.342500000000001</v>
+      </c>
+      <c r="R44" s="14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>44</v>
       </c>
+      <c r="B45" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C45" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J45" s="3" t="e">
+      <c r="E45" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J45" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K45" s="3" t="e">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>54.787</v>
       </c>
       <c r="L45" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M45" s="3" t="e">
+      <c r="M45" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N45" s="3" t="e">
+        <v>29</v>
+      </c>
+      <c r="N45" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>21.451</v>
       </c>
       <c r="O45" s="3" t="e">
         <f t="shared" si="29"/>
@@ -3466,36 +3854,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R45" s="14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45</v>
       </c>
+      <c r="B46" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C46" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J46" s="3" t="e">
+      <c r="E46" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J46" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K46" s="3" t="e">
+        <v>0</v>
+      </c>
+      <c r="K46" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>55.681</v>
       </c>
       <c r="L46" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M46" s="3" t="e">
+      <c r="M46" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N46" s="3" t="e">
+        <v>29</v>
+      </c>
+      <c r="N46" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>19.804</v>
       </c>
       <c r="O46" s="3" t="e">
         <f t="shared" si="29"/>
@@ -3509,167 +3918,249 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R46" s="14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>46</v>
       </c>
+      <c r="B47" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C47" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J47" s="3" t="e">
+      <c r="E47" t="s">
+        <v>124</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J47" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K47" s="3" t="e">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L47" s="3" t="e">
+        <v>59</v>
+      </c>
+      <c r="L47" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M47" s="3" t="e">
+        <v>57</v>
+      </c>
+      <c r="M47" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N47" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="N47" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O47" s="3" t="e">
+        <v>10</v>
+      </c>
+      <c r="O47" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P47" s="1" t="e">
+        <v>49</v>
+      </c>
+      <c r="P47" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q47" s="1" t="e">
+        <v>-8.9991666666666674</v>
+      </c>
+      <c r="Q47" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-35.180277777777775</v>
+      </c>
+      <c r="R47" s="14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>47</v>
       </c>
+      <c r="B48" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C48" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J48" s="3" t="e">
+      <c r="E48" t="s">
+        <v>128</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J48" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K48" s="3" t="e">
+        <v>1</v>
+      </c>
+      <c r="K48" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L48" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="L48" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M48" s="3" t="e">
+        <v>57</v>
+      </c>
+      <c r="M48" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N48" s="3" t="e">
+        <v>46</v>
+      </c>
+      <c r="N48" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O48" s="3" t="e">
+        <v>47</v>
+      </c>
+      <c r="O48" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P48" s="1" t="e">
+        <v>22</v>
+      </c>
+      <c r="P48" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q48" s="1" t="e">
+        <v>-1.0658333333333334</v>
+      </c>
+      <c r="Q48" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-46.789444444444442</v>
+      </c>
+      <c r="R48" s="14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>48</v>
       </c>
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C49" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I49" s="5"/>
-      <c r="J49" s="3" t="e">
+      <c r="E49" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J49" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K49" s="3" t="e">
+        <v>1</v>
+      </c>
+      <c r="K49" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L49" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="L49" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M49" s="3" t="e">
+        <v>57</v>
+      </c>
+      <c r="M49" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N49" s="3" t="e">
+        <v>46</v>
+      </c>
+      <c r="N49" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O49" s="3" t="e">
+        <v>47</v>
+      </c>
+      <c r="O49" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P49" s="1" t="e">
+        <v>22</v>
+      </c>
+      <c r="P49" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q49" s="1" t="e">
+        <v>-1.0658333333333334</v>
+      </c>
+      <c r="Q49" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-46.789444444444442</v>
+      </c>
+      <c r="R49" s="14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>49</v>
       </c>
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C50" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I50" s="5"/>
-      <c r="J50" s="3" t="e">
+      <c r="E50" t="s">
+        <v>135</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J50" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K50" s="3" t="e">
+        <v>08</v>
+      </c>
+      <c r="K50" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>10</v>
       </c>
       <c r="L50" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M50" s="3" t="e">
+      <c r="M50" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N50" s="3" t="e">
+        <v>34</v>
+      </c>
+      <c r="N50" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>49</v>
       </c>
       <c r="O50" s="3" t="e">
         <f t="shared" si="29"/>
@@ -3683,37 +4174,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R50" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>50</v>
       </c>
+      <c r="B51" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C51" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I51" s="5"/>
-      <c r="J51" s="3" t="e">
+      <c r="E51" t="s">
+        <v>135</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J51" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K51" s="3" t="e">
+        <v>08</v>
+      </c>
+      <c r="K51" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>10</v>
       </c>
       <c r="L51" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M51" s="3" t="e">
+      <c r="M51" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N51" s="3" t="e">
+        <v>34</v>
+      </c>
+      <c r="N51" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>49</v>
       </c>
       <c r="O51" s="3" t="e">
         <f t="shared" si="29"/>
@@ -3727,141 +4238,203 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R51" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>51</v>
       </c>
+      <c r="B52" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C52" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I52" s="5"/>
-      <c r="J52" s="3" t="e">
+      <c r="E52" t="s">
+        <v>139</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J52" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K52" s="3" t="e">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L52" s="3" t="e">
+        <v>30</v>
+      </c>
+      <c r="L52" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M52" s="3" t="e">
+        <v>54</v>
+      </c>
+      <c r="M52" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N52" s="3" t="e">
+        <v>34</v>
+      </c>
+      <c r="N52" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O52" s="3" t="e">
+        <v>59</v>
+      </c>
+      <c r="O52" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P52" s="1" t="e">
+        <v>47</v>
+      </c>
+      <c r="P52" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q52" s="1" t="e">
+        <v>-8.5150000000000006</v>
+      </c>
+      <c r="Q52" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-34.996388888888887</v>
+      </c>
+      <c r="R52" s="14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>52</v>
       </c>
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C53" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="J53" s="3" t="e">
+      <c r="E53" t="s">
+        <v>139</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J53" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K53" s="3" t="e">
+        <v>8</v>
+      </c>
+      <c r="K53" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L53" s="3" t="e">
+        <v>30</v>
+      </c>
+      <c r="L53" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M53" s="3" t="e">
+        <v>54</v>
+      </c>
+      <c r="M53" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N53" s="3" t="e">
+        <v>34</v>
+      </c>
+      <c r="N53" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O53" s="3" t="e">
+        <v>59</v>
+      </c>
+      <c r="O53" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P53" s="1" t="e">
+        <v>47</v>
+      </c>
+      <c r="P53" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q53" s="1" t="e">
+        <v>-8.5150000000000006</v>
+      </c>
+      <c r="Q53" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-34.996388888888887</v>
+      </c>
+      <c r="R53" s="14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>53</v>
       </c>
+      <c r="B54" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C54" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E54" s="2"/>
-      <c r="J54" s="3" t="e">
+      <c r="E54" t="s">
+        <v>139</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J54" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K54" s="3" t="e">
+        <v>8</v>
+      </c>
+      <c r="K54" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L54" s="3" t="e">
+        <v>30</v>
+      </c>
+      <c r="L54" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M54" s="3" t="e">
+        <v>54</v>
+      </c>
+      <c r="M54" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N54" s="3" t="e">
+        <v>34</v>
+      </c>
+      <c r="N54" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O54" s="3" t="e">
+        <v>59</v>
+      </c>
+      <c r="O54" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P54" s="1" t="e">
+        <v>47</v>
+      </c>
+      <c r="P54" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q54" s="1" t="e">
+        <v>-8.5150000000000006</v>
+      </c>
+      <c r="Q54" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-34.996388888888887</v>
+      </c>
+      <c r="R54" s="14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -3905,8 +4478,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R55" s="14"/>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -3951,7 +4525,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -3996,7 +4570,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -4041,7 +4615,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -4086,7 +4660,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -4131,7 +4705,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -4176,7 +4750,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -4221,7 +4795,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -4266,7 +4840,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>63</v>
       </c>

--- a/Ocorrências Literatura.xlsx
+++ b/Ocorrências Literatura.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faculdade\Laboratorio\lagostas_carapaca\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EEE8A1-169B-44F9-A319-6912070AF953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04A7F3C-0B61-4FF5-AA07-AB2615B93860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="178">
   <si>
     <t>origem</t>
   </si>
@@ -467,13 +467,153 @@
   </si>
   <si>
     <t>Composition and spatial distribution of subtidal Decapoda on the “Reef Coast”, northeastern Brazil, evaluated through a low-impact visual census technique</t>
+  </si>
+  <si>
+    <t>18°01′15″</t>
+  </si>
+  <si>
+    <t>38°43′16″</t>
+  </si>
+  <si>
+    <t>Arquipélogo de Abrolhos (BA)</t>
+  </si>
+  <si>
+    <t>Belém (PA)</t>
+  </si>
+  <si>
+    <t>São Paulo Capital (SP)</t>
+  </si>
+  <si>
+    <t>01°27′</t>
+  </si>
+  <si>
+    <t>48°30′</t>
+  </si>
+  <si>
+    <t>23°32′</t>
+  </si>
+  <si>
+    <t>46°38′</t>
+  </si>
+  <si>
+    <t>03°50′</t>
+  </si>
+  <si>
+    <t>38°20′</t>
+  </si>
+  <si>
+    <t>23°17′</t>
+  </si>
+  <si>
+    <t>44°10′</t>
+  </si>
+  <si>
+    <r>
+      <t>Baía da Ilha Grande</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, no litoral sul do Rio de Janeiro (Costa Verde).</t>
+    </r>
+  </si>
+  <si>
+    <t>Região costeira do Ceará, nas proximidades de Aquiraz</t>
+  </si>
+  <si>
+    <t>4°25′</t>
+  </si>
+  <si>
+    <t>37°16′</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Litoral leste do </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ceará</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, na região de Aracati (próximo ao estuário do Rio Jaguaribe).</t>
+    </r>
+  </si>
+  <si>
+    <t>Santa Barbara Island</t>
+  </si>
+  <si>
+    <t>Redonda Island</t>
+  </si>
+  <si>
+    <t>Siriba Island</t>
+  </si>
+  <si>
+    <t>FARIA JÚNIOR, Edson (2013)</t>
+  </si>
+  <si>
+    <t>1.pdf</t>
+  </si>
+  <si>
+    <t>17°57′29″</t>
+  </si>
+  <si>
+    <t>38°42′09″</t>
+  </si>
+  <si>
+    <t>17°57′38″</t>
+  </si>
+  <si>
+    <t>38°42′55″</t>
+  </si>
+  <si>
+    <t>17°57′59″</t>
+  </si>
+  <si>
+    <t>38°42′52″</t>
+  </si>
+  <si>
+    <t>32°24′</t>
+  </si>
+  <si>
+    <t>Arquipélago de Fernando de Noronha</t>
+  </si>
+  <si>
+    <t>03°45′</t>
+  </si>
+  <si>
+    <t>32°19′</t>
+  </si>
+  <si>
+    <t>Atol das Rocas</t>
+  </si>
+  <si>
+    <t>1-s2.0-S2351989415001031-main</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -553,6 +693,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -623,7 +778,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -697,6 +852,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3935,7 +4093,7 @@
       <c r="D47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="8" t="s">
         <v>124</v>
       </c>
       <c r="F47" s="1" t="s">
@@ -3999,7 +4157,7 @@
       <c r="D48" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="8" t="s">
         <v>128</v>
       </c>
       <c r="F48" s="1" t="s">
@@ -4063,7 +4221,7 @@
       <c r="D49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="8" t="s">
         <v>128</v>
       </c>
       <c r="F49" s="1" t="s">
@@ -4127,7 +4285,7 @@
       <c r="D50" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="8" t="s">
         <v>135</v>
       </c>
       <c r="F50" s="1" t="s">
@@ -4191,7 +4349,7 @@
       <c r="D51" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="8" t="s">
         <v>135</v>
       </c>
       <c r="F51" s="1" t="s">
@@ -4255,7 +4413,7 @@
       <c r="D52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F52" s="1" t="s">
@@ -4319,7 +4477,7 @@
       <c r="D53" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F53" s="1" t="s">
@@ -4383,7 +4541,7 @@
       <c r="D54" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F54" s="1" t="s">
@@ -4438,169 +4596,241 @@
       <c r="A55" s="3">
         <v>54</v>
       </c>
+      <c r="B55" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C55" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="J55" s="3" t="e">
+      <c r="E55" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="J55" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K55" s="3" t="e">
+        <v>18</v>
+      </c>
+      <c r="K55" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L55" s="3" t="e">
+        <v>01</v>
+      </c>
+      <c r="L55" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M55" s="3" t="e">
+        <v>15</v>
+      </c>
+      <c r="M55" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N55" s="3" t="e">
+        <v>38</v>
+      </c>
+      <c r="N55" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O55" s="3" t="e">
+        <v>43</v>
+      </c>
+      <c r="O55" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P55" s="1" t="e">
+        <v>16</v>
+      </c>
+      <c r="P55" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q55" s="1" t="e">
+        <v>-18.020833333333332</v>
+      </c>
+      <c r="Q55" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R55" s="14"/>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-38.721111111111114</v>
+      </c>
+      <c r="R55" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>55</v>
       </c>
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C56" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="J56" s="3" t="e">
+      <c r="E56" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="J56" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K56" s="3" t="e">
+        <v>18</v>
+      </c>
+      <c r="K56" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L56" s="3" t="e">
+        <v>01</v>
+      </c>
+      <c r="L56" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M56" s="3" t="e">
+        <v>15</v>
+      </c>
+      <c r="M56" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N56" s="3" t="e">
+        <v>38</v>
+      </c>
+      <c r="N56" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O56" s="3" t="e">
+        <v>43</v>
+      </c>
+      <c r="O56" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P56" s="1" t="e">
+        <v>16</v>
+      </c>
+      <c r="P56" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q56" s="1" t="e">
+        <v>-18.020833333333332</v>
+      </c>
+      <c r="Q56" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-38.721111111111114</v>
+      </c>
+      <c r="R56" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>56</v>
       </c>
+      <c r="B57" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C57" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="J57" s="3" t="e">
+      <c r="E57" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="J57" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K57" s="3" t="e">
+        <v>18</v>
+      </c>
+      <c r="K57" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L57" s="3" t="e">
+        <v>01</v>
+      </c>
+      <c r="L57" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M57" s="3" t="e">
+        <v>15</v>
+      </c>
+      <c r="M57" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N57" s="3" t="e">
+        <v>38</v>
+      </c>
+      <c r="N57" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O57" s="3" t="e">
+        <v>43</v>
+      </c>
+      <c r="O57" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P57" s="1" t="e">
+        <v>16</v>
+      </c>
+      <c r="P57" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q57" s="1" t="e">
+        <v>-18.020833333333332</v>
+      </c>
+      <c r="Q57" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-38.721111111111114</v>
+      </c>
+      <c r="R57" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>57</v>
       </c>
+      <c r="B58" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C58" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="J58" s="3" t="e">
+      <c r="E58" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="J58" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K58" s="3" t="e">
+        <v>01</v>
+      </c>
+      <c r="K58" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>27</v>
       </c>
       <c r="L58" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M58" s="3" t="e">
+      <c r="M58" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N58" s="3" t="e">
+        <v>48</v>
+      </c>
+      <c r="N58" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>30</v>
       </c>
       <c r="O58" s="3" t="e">
         <f t="shared" si="29"/>
@@ -4614,38 +4844,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R58" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>58</v>
       </c>
+      <c r="B59" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C59" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="J59" s="3" t="e">
+      <c r="E59" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J59" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K59" s="3" t="e">
+        <v>23</v>
+      </c>
+      <c r="K59" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>32</v>
       </c>
       <c r="L59" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M59" s="3" t="e">
+      <c r="M59" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N59" s="3" t="e">
+        <v>46</v>
+      </c>
+      <c r="N59" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>38</v>
       </c>
       <c r="O59" s="3" t="e">
         <f t="shared" si="29"/>
@@ -4659,38 +4908,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R59" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>59</v>
       </c>
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C60" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="J60" s="3" t="e">
+      <c r="E60" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I60" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="J60" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K60" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="K60" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>50</v>
       </c>
       <c r="L60" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M60" s="3" t="e">
+      <c r="M60" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N60" s="3" t="e">
+        <v>38</v>
+      </c>
+      <c r="N60" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>20</v>
       </c>
       <c r="O60" s="3" t="e">
         <f t="shared" si="29"/>
@@ -4704,38 +4972,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R60" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>60</v>
       </c>
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C61" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="J61" s="3" t="e">
+      <c r="E61" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I61" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="J61" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K61" s="3" t="e">
+        <v>23</v>
+      </c>
+      <c r="K61" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>17</v>
       </c>
       <c r="L61" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M61" s="3" t="e">
+      <c r="M61" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N61" s="3" t="e">
+        <v>44</v>
+      </c>
+      <c r="N61" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>10</v>
       </c>
       <c r="O61" s="3" t="e">
         <f t="shared" si="29"/>
@@ -4749,38 +5036,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R61" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>61</v>
       </c>
+      <c r="B62" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C62" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="J62" s="3" t="e">
+      <c r="E62" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="J62" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K62" s="3" t="e">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>25</v>
       </c>
       <c r="L62" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M62" s="3" t="e">
+      <c r="M62" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N62" s="3" t="e">
+        <v>37</v>
+      </c>
+      <c r="N62" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>16</v>
       </c>
       <c r="O62" s="3" t="e">
         <f t="shared" si="29"/>
@@ -4794,173 +5100,249 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R62" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>62</v>
       </c>
+      <c r="B63" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C63" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="J63" s="3" t="e">
+      <c r="E63" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J63" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K63" s="3" t="e">
+        <v>17</v>
+      </c>
+      <c r="K63" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L63" s="3" t="e">
+        <v>57</v>
+      </c>
+      <c r="L63" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M63" s="3" t="e">
+        <v>29</v>
+      </c>
+      <c r="M63" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N63" s="3" t="e">
+        <v>38</v>
+      </c>
+      <c r="N63" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O63" s="3" t="e">
+        <v>42</v>
+      </c>
+      <c r="O63" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P63" s="1" t="e">
+        <v>09</v>
+      </c>
+      <c r="P63" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q63" s="1" t="e">
+        <v>-17.958055555555557</v>
+      </c>
+      <c r="Q63" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-38.702500000000001</v>
+      </c>
+      <c r="R63" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>63</v>
       </c>
+      <c r="B64" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C64" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="J64" s="3" t="e">
+      <c r="E64" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="J64" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K64" s="3" t="e">
+        <v>17</v>
+      </c>
+      <c r="K64" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L64" s="3" t="e">
+        <v>57</v>
+      </c>
+      <c r="L64" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M64" s="3" t="e">
+        <v>38</v>
+      </c>
+      <c r="M64" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N64" s="3" t="e">
+        <v>38</v>
+      </c>
+      <c r="N64" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O64" s="3" t="e">
+        <v>42</v>
+      </c>
+      <c r="O64" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P64" s="1" t="e">
+        <v>55</v>
+      </c>
+      <c r="P64" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q64" s="1" t="e">
+        <v>-17.960555555555555</v>
+      </c>
+      <c r="Q64" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-38.715277777777779</v>
+      </c>
+      <c r="R64" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>64</v>
       </c>
+      <c r="B65" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C65" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="J65" s="3" t="e">
+      <c r="E65" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J65" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K65" s="3" t="e">
+        <v>17</v>
+      </c>
+      <c r="K65" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L65" s="3" t="e">
+        <v>57</v>
+      </c>
+      <c r="L65" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M65" s="3" t="e">
+        <v>59</v>
+      </c>
+      <c r="M65" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N65" s="3" t="e">
+        <v>38</v>
+      </c>
+      <c r="N65" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O65" s="3" t="e">
+        <v>42</v>
+      </c>
+      <c r="O65" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P65" s="1" t="e">
+        <v>52</v>
+      </c>
+      <c r="P65" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q65" s="1" t="e">
+        <v>-17.96638888888889</v>
+      </c>
+      <c r="Q65" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-38.714444444444446</v>
+      </c>
+      <c r="R65" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>65</v>
       </c>
+      <c r="B66" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C66" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="J66" s="3" t="e">
+      <c r="E66" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J66" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K66" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="K66" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>50</v>
       </c>
       <c r="L66" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M66" s="3" t="e">
+      <c r="M66" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N66" s="3" t="e">
+        <v>32</v>
+      </c>
+      <c r="N66" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>24</v>
       </c>
       <c r="O66" s="3" t="e">
         <f t="shared" si="29"/>
@@ -4974,38 +5356,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R66" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>66</v>
       </c>
+      <c r="B67" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C67" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="J67" s="3" t="e">
+      <c r="E67" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I67" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="J67" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K67" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="K67" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>45</v>
       </c>
       <c r="L67" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M67" s="3" t="e">
+      <c r="M67" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N67" s="3" t="e">
+        <v>32</v>
+      </c>
+      <c r="N67" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>19</v>
       </c>
       <c r="O67" s="3" t="e">
         <f t="shared" si="29"/>
@@ -5019,37 +5420,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R67" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>67</v>
       </c>
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C68" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E68" s="2"/>
-      <c r="J68" s="3" t="e">
+      <c r="E68" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J68" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K68" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="K68" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>50</v>
       </c>
       <c r="L68" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M68" s="3" t="e">
+      <c r="M68" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N68" s="3" t="e">
+        <v>32</v>
+      </c>
+      <c r="N68" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>24</v>
       </c>
       <c r="O68" s="3" t="e">
         <f t="shared" si="29"/>
@@ -5063,8 +5484,11 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R68" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -5074,42 +5498,55 @@
       <c r="D69" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="J69" s="3" t="e">
+      <c r="E69" t="s">
+        <v>139</v>
+      </c>
+      <c r="F69" t="s">
+        <v>140</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J69" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K69" s="3" t="e">
+        <v>8</v>
+      </c>
+      <c r="K69" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L69" s="3" t="e">
+        <v>30</v>
+      </c>
+      <c r="L69" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M69" s="3" t="e">
+        <v>54</v>
+      </c>
+      <c r="M69" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N69" s="3" t="e">
+        <v>34</v>
+      </c>
+      <c r="N69" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O69" s="3" t="e">
+        <v>59</v>
+      </c>
+      <c r="O69" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P69" s="1" t="e">
+        <v>47</v>
+      </c>
+      <c r="P69" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q69" s="1" t="e">
+        <v>-8.5150000000000006</v>
+      </c>
+      <c r="Q69" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-34.996388888888887</v>
+      </c>
+      <c r="R69" s="14" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -5153,8 +5590,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R70" s="14"/>
+    </row>
+    <row r="71" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -5198,8 +5636,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R71" s="14"/>
+    </row>
+    <row r="72" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -5243,8 +5682,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R72" s="14"/>
+    </row>
+    <row r="73" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -5287,8 +5727,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R73" s="14"/>
+    </row>
+    <row r="74" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -5330,8 +5771,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R74" s="14"/>
+    </row>
+    <row r="75" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -5373,8 +5815,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R75" s="14"/>
+    </row>
+    <row r="76" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -5416,8 +5859,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R76" s="14"/>
+    </row>
+    <row r="77" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -5459,8 +5903,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R77" s="14"/>
+    </row>
+    <row r="78" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -5502,8 +5947,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R78" s="14"/>
+    </row>
+    <row r="79" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -5545,8 +5991,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R79" s="14"/>
+    </row>
+    <row r="80" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -5588,8 +6035,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R80" s="14"/>
+    </row>
+    <row r="81" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -5631,8 +6079,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R81" s="14"/>
+    </row>
+    <row r="82" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -5674,8 +6123,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R82" s="14"/>
+    </row>
+    <row r="83" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -5717,8 +6167,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R83" s="14"/>
+    </row>
+    <row r="84" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -5760,8 +6211,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R84" s="14"/>
+    </row>
+    <row r="85" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -5803,8 +6255,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R85" s="14"/>
+    </row>
+    <row r="86" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -5846,8 +6299,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R86" s="14"/>
+    </row>
+    <row r="87" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -5889,8 +6343,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R87" s="14"/>
+    </row>
+    <row r="88" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -5932,8 +6387,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R88" s="14"/>
+    </row>
+    <row r="89" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -5975,8 +6431,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R89" s="14"/>
+    </row>
+    <row r="90" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -6018,8 +6475,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R90" s="14"/>
+    </row>
+    <row r="91" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -6061,8 +6519,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R91" s="14"/>
+    </row>
+    <row r="92" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -6104,8 +6563,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R92" s="14"/>
+    </row>
+    <row r="93" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -6147,8 +6607,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R93" s="14"/>
+    </row>
+    <row r="94" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -6190,8 +6651,9 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R94" s="14"/>
+    </row>
+    <row r="95" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -6233,8 +6695,9 @@
         <f t="shared" ref="Q95:Q140" si="39">((((O95/60)+N95)/60)+M95)*IF(D95="W",-1, 1)</f>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R95" s="14"/>
+    </row>
+    <row r="96" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -6276,8 +6739,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R96" s="14"/>
+    </row>
+    <row r="97" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -6319,8 +6783,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R97" s="14"/>
+    </row>
+    <row r="98" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -6362,8 +6827,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R98" s="14"/>
+    </row>
+    <row r="99" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -6405,8 +6871,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R99" s="14"/>
+    </row>
+    <row r="100" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -6448,8 +6915,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R100" s="14"/>
+    </row>
+    <row r="101" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -6491,8 +6959,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R101" s="14"/>
+    </row>
+    <row r="102" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -6534,8 +7003,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R102" s="14"/>
+    </row>
+    <row r="103" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -6577,8 +7047,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R103" s="14"/>
+    </row>
+    <row r="104" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -6620,8 +7091,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R104" s="14"/>
+    </row>
+    <row r="105" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -6664,8 +7136,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R105" s="14"/>
+    </row>
+    <row r="106" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -6708,8 +7181,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R106" s="14"/>
+    </row>
+    <row r="107" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -6752,8 +7226,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R107" s="14"/>
+    </row>
+    <row r="108" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -6795,8 +7270,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R108" s="14"/>
+    </row>
+    <row r="109" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -6838,8 +7314,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R109" s="14"/>
+    </row>
+    <row r="110" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -6881,8 +7358,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R110" s="14"/>
+    </row>
+    <row r="111" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -6924,8 +7402,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R111" s="14"/>
+    </row>
+    <row r="112" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -6967,8 +7446,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R112" s="14"/>
+    </row>
+    <row r="113" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -7010,8 +7490,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R113" s="14"/>
+    </row>
+    <row r="114" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -7054,8 +7535,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R114" s="14"/>
+    </row>
+    <row r="115" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -7098,8 +7580,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R115" s="14"/>
+    </row>
+    <row r="116" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -7142,8 +7625,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R116" s="14"/>
+    </row>
+    <row r="117" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -7186,8 +7670,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R117" s="14"/>
+    </row>
+    <row r="118" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -7229,8 +7714,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R118" s="14"/>
+    </row>
+    <row r="119" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -7272,8 +7758,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R119" s="14"/>
+    </row>
+    <row r="120" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -7315,8 +7802,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R120" s="14"/>
+    </row>
+    <row r="121" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -7358,8 +7846,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R121" s="14"/>
+    </row>
+    <row r="122" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
         <v>121</v>
       </c>
@@ -7401,8 +7890,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R122" s="14"/>
+    </row>
+    <row r="123" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -7444,8 +7934,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R123" s="14"/>
+    </row>
+    <row r="124" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -7487,8 +7978,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R124" s="14"/>
+    </row>
+    <row r="125" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -7530,8 +8022,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R125" s="14"/>
+    </row>
+    <row r="126" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -7573,8 +8066,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R126" s="14"/>
+    </row>
+    <row r="127" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -7616,8 +8110,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R127" s="14"/>
+    </row>
+    <row r="128" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -7659,8 +8154,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R128" s="14"/>
+    </row>
+    <row r="129" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
         <v>128</v>
       </c>
@@ -7703,8 +8199,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R129" s="14"/>
+    </row>
+    <row r="130" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="3">
         <v>129</v>
       </c>
@@ -7747,8 +8244,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R130" s="14"/>
+    </row>
+    <row r="131" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -7790,8 +8288,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R131" s="14"/>
+    </row>
+    <row r="132" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
         <v>131</v>
       </c>
@@ -7833,8 +8332,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R132" s="14"/>
+    </row>
+    <row r="133" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -7876,8 +8376,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R133" s="14"/>
+    </row>
+    <row r="134" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -7919,8 +8420,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R134" s="14"/>
+    </row>
+    <row r="135" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="3">
         <v>134</v>
       </c>
@@ -7962,8 +8464,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R135" s="14"/>
+    </row>
+    <row r="136" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="3">
         <v>135</v>
       </c>
@@ -8005,8 +8508,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R136" s="14"/>
+    </row>
+    <row r="137" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -8048,8 +8552,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R137" s="14"/>
+    </row>
+    <row r="138" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -8093,8 +8598,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R138" s="14"/>
+    </row>
+    <row r="139" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -8138,8 +8644,9 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R139" s="14"/>
+    </row>
+    <row r="140" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -8183,22 +8690,23 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R140" s="14"/>
+    </row>
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
       <c r="P141" s="1"/>
       <c r="Q141" s="1"/>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P142" s="1"/>
       <c r="Q142" s="1"/>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P143" s="1"/>
       <c r="Q143" s="1"/>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P144" s="1"/>
       <c r="Q144" s="1"/>
     </row>

--- a/Ocorrências Literatura.xlsx
+++ b/Ocorrências Literatura.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faculdade\Laboratorio\lagostas_carapaca\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04A7F3C-0B61-4FF5-AA07-AB2615B93860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72398547-794C-442B-8B18-709BA096E485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="214">
   <si>
     <t>origem</t>
   </si>
@@ -608,12 +608,143 @@
   <si>
     <t>1-s2.0-S2351989415001031-main</t>
   </si>
+  <si>
+    <t>Área de Proteção Ambiental (APA) Costa dos Corais Tamandaré</t>
+  </si>
+  <si>
+    <t>35°07′29″</t>
+  </si>
+  <si>
+    <t>08°44′41″</t>
+  </si>
+  <si>
+    <t>Giraldes, B (2015)</t>
+  </si>
+  <si>
+    <t>03°52′</t>
+  </si>
+  <si>
+    <t>33°48′</t>
+  </si>
+  <si>
+    <t>Fernando de Noronha</t>
+  </si>
+  <si>
+    <t>Trindade e Martim Vaz</t>
+  </si>
+  <si>
+    <t>03°51′</t>
+  </si>
+  <si>
+    <t>32°25′</t>
+  </si>
+  <si>
+    <t>20°28′</t>
+  </si>
+  <si>
+    <t>29°21′</t>
+  </si>
+  <si>
+    <t>Aquatic Conservation - 2020 - Gaeta - Genetic differentiation among Atlantic island populations of the brown spiny lobster</t>
+  </si>
+  <si>
+    <t>GAETA, Juliana de Carvalho (2019)</t>
+  </si>
+  <si>
+    <t>21°17′</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 40°56′</t>
+  </si>
+  <si>
+    <t>(Espírito Santo)</t>
+  </si>
+  <si>
+    <t>(Amapá)</t>
+  </si>
+  <si>
+    <t>Crustaceana_86_3_336_356_ASSESSMENT_OF_W</t>
+  </si>
+  <si>
+    <t>Cruz, R. (2013)</t>
+  </si>
+  <si>
+    <t>gaeta2019</t>
+  </si>
+  <si>
+    <t>Gaeta, J. (2019)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">a longitude </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>24°57′W</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cai literalmente no meio do Oceano Atlântico, a mais de 1.000 km da costa, possivel erro, se for 34 ao inves de 24 da certo no litoral</t>
+    </r>
+  </si>
+  <si>
+    <t>8°45′</t>
+  </si>
+  <si>
+    <t>24°57′</t>
+  </si>
+  <si>
+    <t>konishi2006</t>
+  </si>
+  <si>
+    <t>KONISHI, Kooichi (2006)</t>
+  </si>
+  <si>
+    <t>00°55′01″</t>
+  </si>
+  <si>
+    <t>29°20′44″</t>
+  </si>
+  <si>
+    <t>PINHEIRO, Allysson P. (2006)</t>
+  </si>
+  <si>
+    <t>Reproductive_Biology_of_Panulirus_echina</t>
+  </si>
+  <si>
+    <t>s00338-024-02569-7</t>
+  </si>
+  <si>
+    <t>37°30′22,9″</t>
+  </si>
+  <si>
+    <t>04°37′48,0″</t>
+  </si>
+  <si>
+    <t>Ceará</t>
+  </si>
+  <si>
+    <t>BAKER, Alyssa M. (2024)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -694,13 +825,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -709,7 +833,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -719,6 +843,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -778,7 +908,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -856,6 +986,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3896,7 +4027,7 @@
         <v>20</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>16</v>
@@ -3942,7 +4073,7 @@
       </c>
       <c r="P44" s="1">
         <f t="shared" si="30"/>
-        <v>-0.9194444444444444</v>
+        <v>0.9194444444444444</v>
       </c>
       <c r="Q44" s="1">
         <f t="shared" si="31"/>
@@ -3960,7 +4091,7 @@
         <v>20</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>16</v>
@@ -4024,7 +4155,7 @@
         <v>20</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>16</v>
@@ -5492,17 +5623,23 @@
       <c r="A69" s="3">
         <v>68</v>
       </c>
+      <c r="B69" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C69" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="F69" t="s">
+      <c r="F69" s="8" t="s">
         <v>140</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>12</v>
@@ -5550,390 +5687,561 @@
       <c r="A70" s="3">
         <v>69</v>
       </c>
+      <c r="B70" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C70" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="J70" s="3" t="e">
+      <c r="E70" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I70" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="J70" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K70" s="3" t="e">
+        <v>08</v>
+      </c>
+      <c r="K70" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L70" s="3" t="e">
+        <v>44</v>
+      </c>
+      <c r="L70" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M70" s="3" t="e">
+        <v>23</v>
+      </c>
+      <c r="M70" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N70" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="N70" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O70" s="3" t="e">
+        <v>07</v>
+      </c>
+      <c r="O70" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P70" s="1" t="e">
+        <v>29</v>
+      </c>
+      <c r="P70" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q70" s="1" t="e">
+        <v>-8.7397222222222215</v>
+      </c>
+      <c r="Q70" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R70" s="14"/>
+        <v>-35.124722222222225</v>
+      </c>
+      <c r="R70" s="14" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="71" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>70</v>
       </c>
+      <c r="B71" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C71" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="J71" s="3" t="e">
+      <c r="E71" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I71" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="J71" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K71" s="3" t="e">
+        <v>08</v>
+      </c>
+      <c r="K71" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L71" s="3" t="e">
+        <v>44</v>
+      </c>
+      <c r="L71" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M71" s="3" t="e">
+        <v>41</v>
+      </c>
+      <c r="M71" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N71" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="N71" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O71" s="3" t="e">
+        <v>02</v>
+      </c>
+      <c r="O71" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P71" s="1" t="e">
+        <v>28</v>
+      </c>
+      <c r="P71" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q71" s="1" t="e">
+        <v>-8.7447222222222223</v>
+      </c>
+      <c r="Q71" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R71" s="14"/>
+        <v>-35.041111111111114</v>
+      </c>
+      <c r="R71" s="14" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="72" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>71</v>
       </c>
+      <c r="B72" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C72" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E72" s="7"/>
-      <c r="F72" s="2"/>
-      <c r="J72" s="3" t="e">
+      <c r="E72" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J72" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K72" s="3" t="e">
+        <v>8</v>
+      </c>
+      <c r="K72" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L72" s="3" t="e">
+        <v>30</v>
+      </c>
+      <c r="L72" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M72" s="3" t="e">
+        <v>54</v>
+      </c>
+      <c r="M72" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N72" s="3" t="e">
+        <v>34</v>
+      </c>
+      <c r="N72" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O72" s="3" t="e">
+        <v>59</v>
+      </c>
+      <c r="O72" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P72" s="1" t="e">
+        <v>47</v>
+      </c>
+      <c r="P72" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q72" s="1" t="e">
+        <v>-8.5150000000000006</v>
+      </c>
+      <c r="Q72" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R72" s="14"/>
+        <v>-34.996388888888887</v>
+      </c>
+      <c r="R72" s="14" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="73" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>72</v>
       </c>
+      <c r="B73" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C73" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E73" s="2"/>
-      <c r="J73" s="3" t="e">
+      <c r="E73" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I73" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="J73" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K73" s="3" t="e">
+        <v>08</v>
+      </c>
+      <c r="K73" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L73" s="3" t="e">
+        <v>44</v>
+      </c>
+      <c r="L73" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M73" s="3" t="e">
+        <v>23</v>
+      </c>
+      <c r="M73" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N73" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="N73" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O73" s="3" t="e">
+        <v>07</v>
+      </c>
+      <c r="O73" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P73" s="1" t="e">
+        <v>29</v>
+      </c>
+      <c r="P73" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q73" s="1" t="e">
+        <v>-8.7397222222222215</v>
+      </c>
+      <c r="Q73" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R73" s="14"/>
+        <v>-35.124722222222225</v>
+      </c>
+      <c r="R73" s="14" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="74" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>73</v>
       </c>
+      <c r="B74" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C74" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J74" s="3" t="e">
+      <c r="E74" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I74" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="J74" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K74" s="3" t="e">
+        <v>08</v>
+      </c>
+      <c r="K74" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L74" s="3" t="e">
+        <v>44</v>
+      </c>
+      <c r="L74" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M74" s="3" t="e">
+        <v>41</v>
+      </c>
+      <c r="M74" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N74" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="N74" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O74" s="3" t="e">
+        <v>02</v>
+      </c>
+      <c r="O74" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P74" s="1" t="e">
+        <v>28</v>
+      </c>
+      <c r="P74" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q74" s="1" t="e">
+        <v>-8.7447222222222223</v>
+      </c>
+      <c r="Q74" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R74" s="14"/>
+        <v>-35.041111111111114</v>
+      </c>
+      <c r="R74" s="14" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="75" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>74</v>
       </c>
+      <c r="B75" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C75" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J75" s="3" t="e">
+      <c r="E75" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J75" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K75" s="3" t="e">
+        <v>8</v>
+      </c>
+      <c r="K75" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L75" s="3" t="e">
+        <v>30</v>
+      </c>
+      <c r="L75" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M75" s="3" t="e">
+        <v>54</v>
+      </c>
+      <c r="M75" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N75" s="3" t="e">
+        <v>34</v>
+      </c>
+      <c r="N75" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O75" s="3" t="e">
+        <v>59</v>
+      </c>
+      <c r="O75" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P75" s="1" t="e">
+        <v>47</v>
+      </c>
+      <c r="P75" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q75" s="1" t="e">
+        <v>-8.5150000000000006</v>
+      </c>
+      <c r="Q75" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R75" s="14"/>
+        <v>-34.996388888888887</v>
+      </c>
+      <c r="R75" s="14" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="76" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>75</v>
       </c>
+      <c r="B76" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C76" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J76" s="3" t="e">
+      <c r="E76" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I76" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="J76" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K76" s="3" t="e">
+        <v>08</v>
+      </c>
+      <c r="K76" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L76" s="3" t="e">
+        <v>44</v>
+      </c>
+      <c r="L76" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M76" s="3" t="e">
+        <v>23</v>
+      </c>
+      <c r="M76" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N76" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="N76" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O76" s="3" t="e">
+        <v>07</v>
+      </c>
+      <c r="O76" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P76" s="1" t="e">
+        <v>29</v>
+      </c>
+      <c r="P76" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q76" s="1" t="e">
+        <v>-8.7397222222222215</v>
+      </c>
+      <c r="Q76" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R76" s="14"/>
+        <v>-35.124722222222225</v>
+      </c>
+      <c r="R76" s="14" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="77" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>76</v>
       </c>
+      <c r="B77" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C77" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J77" s="3" t="e">
+      <c r="E77" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I77" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="J77" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K77" s="3" t="e">
+        <v>08</v>
+      </c>
+      <c r="K77" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L77" s="3" t="e">
+        <v>44</v>
+      </c>
+      <c r="L77" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M77" s="3" t="e">
+        <v>41</v>
+      </c>
+      <c r="M77" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N77" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="N77" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O77" s="3" t="e">
+        <v>02</v>
+      </c>
+      <c r="O77" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P77" s="1" t="e">
+        <v>28</v>
+      </c>
+      <c r="P77" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q77" s="1" t="e">
+        <v>-8.7447222222222223</v>
+      </c>
+      <c r="Q77" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R77" s="14"/>
+        <v>-35.041111111111114</v>
+      </c>
+      <c r="R77" s="14" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="78" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>77</v>
       </c>
+      <c r="B78" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C78" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J78" s="3" t="e">
+      <c r="E78" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="J78" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K78" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="K78" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>52</v>
       </c>
       <c r="L78" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M78" s="3" t="e">
+      <c r="M78" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N78" s="3" t="e">
+        <v>33</v>
+      </c>
+      <c r="N78" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>48</v>
       </c>
       <c r="O78" s="3" t="e">
         <f t="shared" si="29"/>
@@ -5947,37 +6255,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R78" s="14"/>
+      <c r="R78" s="14" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="79" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>78</v>
       </c>
+      <c r="B79" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C79" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J79" s="3" t="e">
+      <c r="E79" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="J79" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K79" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="K79" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>51</v>
       </c>
       <c r="L79" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M79" s="3" t="e">
+      <c r="M79" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N79" s="3" t="e">
+        <v>32</v>
+      </c>
+      <c r="N79" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>25</v>
       </c>
       <c r="O79" s="3" t="e">
         <f t="shared" si="29"/>
@@ -5991,37 +6319,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R79" s="14"/>
+      <c r="R79" s="14" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="80" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>79</v>
       </c>
+      <c r="B80" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C80" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J80" s="3" t="e">
+      <c r="E80" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="J80" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K80" s="3" t="e">
+        <v>20</v>
+      </c>
+      <c r="K80" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>28</v>
       </c>
       <c r="L80" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M80" s="3" t="e">
+      <c r="M80" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N80" s="3" t="e">
+        <v>29</v>
+      </c>
+      <c r="N80" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>21</v>
       </c>
       <c r="O80" s="3" t="e">
         <f t="shared" si="29"/>
@@ -6035,37 +6383,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R80" s="14"/>
+      <c r="R80" s="14" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="81" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>80</v>
       </c>
+      <c r="B81" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C81" s="3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J81" s="3" t="e">
+      <c r="E81" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I81" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="J81" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K81" s="3" t="e">
+        <v>04</v>
+      </c>
+      <c r="K81" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>26</v>
       </c>
       <c r="L81" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M81" s="3" t="e">
+      <c r="M81" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N81" s="3" t="e">
+        <v>51</v>
+      </c>
+      <c r="N81" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>32</v>
       </c>
       <c r="O81" s="3" t="e">
         <f t="shared" si="29"/>
@@ -6079,37 +6447,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R81" s="14"/>
+      <c r="R81" s="14" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="82" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>81</v>
       </c>
+      <c r="B82" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C82" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J82" s="3" t="e">
+      <c r="E82" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I82" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="J82" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K82" s="3" t="e">
+        <v>21</v>
+      </c>
+      <c r="K82" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>17</v>
       </c>
       <c r="L82" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M82" s="3" t="e">
+      <c r="M82" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N82" s="3" t="e">
+        <v xml:space="preserve"> 40</v>
+      </c>
+      <c r="N82" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>56</v>
       </c>
       <c r="O82" s="3" t="e">
         <f t="shared" si="29"/>
@@ -6123,37 +6511,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R82" s="14"/>
+      <c r="R82" s="14" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="83" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>82</v>
       </c>
+      <c r="B83" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C83" s="3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J83" s="3" t="e">
+      <c r="E83" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I83" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="J83" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K83" s="3" t="e">
+        <v>04</v>
+      </c>
+      <c r="K83" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>26</v>
       </c>
       <c r="L83" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M83" s="3" t="e">
+      <c r="M83" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N83" s="3" t="e">
+        <v>51</v>
+      </c>
+      <c r="N83" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>32</v>
       </c>
       <c r="O83" s="3" t="e">
         <f t="shared" si="29"/>
@@ -6167,37 +6575,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R83" s="14"/>
+      <c r="R83" s="14" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="84" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>83</v>
       </c>
+      <c r="B84" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C84" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J84" s="3" t="e">
+      <c r="E84" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I84" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="J84" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K84" s="3" t="e">
+        <v>21</v>
+      </c>
+      <c r="K84" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>17</v>
       </c>
       <c r="L84" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M84" s="3" t="e">
+      <c r="M84" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N84" s="3" t="e">
+        <v xml:space="preserve"> 40</v>
+      </c>
+      <c r="N84" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>56</v>
       </c>
       <c r="O84" s="3" t="e">
         <f t="shared" si="29"/>
@@ -6211,37 +6639,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R84" s="14"/>
+      <c r="R84" s="14" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="85" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>84</v>
       </c>
+      <c r="B85" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C85" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J85" s="3" t="e">
+      <c r="E85" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="J85" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K85" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="K85" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>51</v>
       </c>
       <c r="L85" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M85" s="3" t="e">
+      <c r="M85" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N85" s="3" t="e">
+        <v>33</v>
+      </c>
+      <c r="N85" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>48</v>
       </c>
       <c r="O85" s="3" t="e">
         <f t="shared" si="29"/>
@@ -6255,37 +6703,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R85" s="14"/>
+      <c r="R85" s="14" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="86" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>85</v>
       </c>
+      <c r="B86" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C86" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J86" s="3" t="e">
+      <c r="E86" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="J86" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K86" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="K86" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>51</v>
       </c>
       <c r="L86" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M86" s="3" t="e">
+      <c r="M86" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N86" s="3" t="e">
+        <v>33</v>
+      </c>
+      <c r="N86" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>48</v>
       </c>
       <c r="O86" s="3" t="e">
         <f t="shared" si="29"/>
@@ -6299,37 +6767,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R86" s="14"/>
+      <c r="R86" s="14" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="87" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>86</v>
       </c>
+      <c r="B87" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C87" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J87" s="3" t="e">
+      <c r="E87" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="J87" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K87" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="K87" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>51</v>
       </c>
       <c r="L87" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M87" s="3" t="e">
+      <c r="M87" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N87" s="3" t="e">
+        <v>33</v>
+      </c>
+      <c r="N87" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>48</v>
       </c>
       <c r="O87" s="3" t="e">
         <f t="shared" si="29"/>
@@ -6343,37 +6831,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R87" s="14"/>
+      <c r="R87" s="14" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="88" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>87</v>
       </c>
+      <c r="B88" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C88" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J88" s="3" t="e">
+      <c r="E88" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I88" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="J88" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K88" s="3" t="e">
+        <v>8</v>
+      </c>
+      <c r="K88" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>45</v>
       </c>
       <c r="L88" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M88" s="3" t="e">
+      <c r="M88" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N88" s="3" t="e">
+        <v>24</v>
+      </c>
+      <c r="N88" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>57</v>
       </c>
       <c r="O88" s="3" t="e">
         <f t="shared" si="29"/>
@@ -6387,95 +6895,137 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R88" s="14"/>
+      <c r="R88" s="14" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="89" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>88</v>
       </c>
+      <c r="B89" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C89" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J89" s="3" t="e">
+      <c r="E89" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J89" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K89" s="3" t="e">
+        <v>00</v>
+      </c>
+      <c r="K89" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L89" s="3" t="e">
+        <v>55</v>
+      </c>
+      <c r="L89" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M89" s="3" t="e">
+        <v>01</v>
+      </c>
+      <c r="M89" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N89" s="3" t="e">
+        <v>29</v>
+      </c>
+      <c r="N89" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O89" s="3" t="e">
+        <v>20</v>
+      </c>
+      <c r="O89" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P89" s="1" t="e">
+        <v>44</v>
+      </c>
+      <c r="P89" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q89" s="1" t="e">
+        <v>-0.91694444444444445</v>
+      </c>
+      <c r="Q89" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R89" s="14"/>
+        <v>-29.345555555555556</v>
+      </c>
+      <c r="R89" s="14" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="90" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>89</v>
       </c>
+      <c r="B90" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="C90" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J90" s="3" t="e">
+      <c r="E90" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J90" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K90" s="3" t="e">
+        <v>04</v>
+      </c>
+      <c r="K90" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L90" s="3" t="e">
+        <v>37</v>
+      </c>
+      <c r="L90" s="3" t="str">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M90" s="3" t="e">
+        <v>48,0</v>
+      </c>
+      <c r="M90" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N90" s="3" t="e">
+        <v>37</v>
+      </c>
+      <c r="N90" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O90" s="3" t="e">
+        <v>30</v>
+      </c>
+      <c r="O90" s="3" t="str">
         <f t="shared" si="29"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P90" s="1" t="e">
+        <v>22,9</v>
+      </c>
+      <c r="P90" s="1">
         <f t="shared" si="30"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q90" s="1" t="e">
+        <v>-4.63</v>
+      </c>
+      <c r="Q90" s="1">
         <f t="shared" si="31"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R90" s="14"/>
+        <v>-37.506361111111111</v>
+      </c>
+      <c r="R90" s="14" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="91" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="3">

--- a/Ocorrências Literatura.xlsx
+++ b/Ocorrências Literatura.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faculdade\Laboratorio\lagostas_carapaca\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95489391-683F-4132-8E66-D252FCA147E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA36930-029B-40E9-8259-A5AF32AA04D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="277">
   <si>
     <t>origem</t>
   </si>
@@ -168,19 +168,7 @@
     <t>diversity-13-00507-v2.pdf</t>
   </si>
   <si>
-    <t>O clima no Sul do Brasil (S) (34° S a 22° S) varia de subtropical a temperado, com regimes topográficos e hidrodinâmicos complexos.</t>
-  </si>
-  <si>
-    <t>34°</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22° </t>
-  </si>
-  <si>
     <t>Cruz, R. (2021)</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Offshore area around Pau Amarelo Beach, Pernambuco</t>
@@ -629,9 +617,6 @@
     <t>(Espírito Santo)</t>
   </si>
   <si>
-    <t>(Amapá)</t>
-  </si>
-  <si>
     <t>Crustaceana_86_3_336_356_ASSESSMENT_OF_W</t>
   </si>
   <si>
@@ -714,12 +699,340 @@
   <si>
     <t>Population_biology_of_Panulirus_echinatu</t>
   </si>
+  <si>
+    <t>1989.90_art_tevgesteira</t>
+  </si>
+  <si>
+    <t>1996_art_ctcivo</t>
+  </si>
+  <si>
+    <t>Município de Iguape (CE)</t>
+  </si>
+  <si>
+    <t>IVO, Carlos Tassito Corrêa; (1996)</t>
+  </si>
+  <si>
+    <t>GESTEIRA, Tereza Cristina Vasconcelos (1989/1990)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 38°13′</t>
+  </si>
+  <si>
+    <t>Entre os municípios de Iguape e Aquiraz</t>
+  </si>
+  <si>
+    <t>03°38′</t>
+  </si>
+  <si>
+    <t>38°13′</t>
+  </si>
+  <si>
+    <t>03°31′</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 38°12′</t>
+  </si>
+  <si>
+    <t>2°53′22″</t>
+  </si>
+  <si>
+    <t>41°13′46″</t>
+  </si>
+  <si>
+    <t>4°06′06″</t>
+  </si>
+  <si>
+    <t>38°08′56″</t>
+  </si>
+  <si>
+    <t>24°49′13″</t>
+  </si>
+  <si>
+    <t>80°48′03″</t>
+  </si>
+  <si>
+    <t>80°48′48″</t>
+  </si>
+  <si>
+    <t>24°50′55″</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">guas viradas para o Oceano Atlântico, mesmo ao largo da costa de Long Key. A sigla </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>KML</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> significa </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Keys Marine Laboratory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fica nas águas do lado oposto (virado para o lado mais calmo da Baía da Flórida / Golfo do México). A sigla </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>KOA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> refere-se à pequena ilha vizinha de Fiesta Key, que é muito famosa pelo seu parque de campismo para autocaravanas chamado </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fiesta Key KOA Resort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>1-s2.0-002209819290070Q-main</t>
+  </si>
+  <si>
+    <t>SMITH, Kenneth N. (1997)</t>
+  </si>
+  <si>
+    <t>Rio Grande do Norte(RN); Ela fica no oceano, a cerca de 30 km a leste do município de Touros</t>
+  </si>
+  <si>
+    <t>05°13′</t>
+  </si>
+  <si>
+    <t>35°10′</t>
+  </si>
+  <si>
+    <t>SARVER, Shane K. (1998)</t>
+  </si>
+  <si>
+    <t>GOLDSTEIN, Jason S. (2008)</t>
+  </si>
+  <si>
+    <t>80°59'37"</t>
+  </si>
+  <si>
+    <t>24°44'20"</t>
+  </si>
+  <si>
+    <t>Keys Marine Laboratory (KML), sul da Florida</t>
+  </si>
+  <si>
+    <t>jcb0177</t>
+  </si>
+  <si>
+    <t>jcb0306</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 80°92′</t>
+  </si>
+  <si>
+    <t>24°78′</t>
+  </si>
+  <si>
+    <t>Limnology   Oceanography - 2009 - Goldsteina - Behavioral enhancement of onshore transport by postlarval Caribbean spiny</t>
+  </si>
+  <si>
+    <t>GOLDSTEIN, Jason S. (2007)</t>
+  </si>
+  <si>
+    <t>19°27′00″</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 87°17′24″</t>
+  </si>
+  <si>
+    <t>Bahia de la Ascensión, que fica dentro da Reserva da Biosfera de Sian Ka'an, na Península de Yucatán</t>
+  </si>
+  <si>
+    <t>EGGLESTON, David B. (1990)</t>
+  </si>
+  <si>
+    <t>m062p079</t>
+  </si>
+  <si>
+    <t>25°01′46″</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 80°23′53″</t>
+  </si>
+  <si>
+    <t>NEVITT, Gabrielle (2000)</t>
+  </si>
+  <si>
+    <r>
+      <t>Three Sisters Reef</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>m203p225</t>
+  </si>
+  <si>
+    <t>Fowey Rocks, Parque Nacional de Biscayne</t>
+  </si>
+  <si>
+    <t>25°35′28″</t>
+  </si>
+  <si>
+    <t>80°05′49″</t>
+  </si>
+  <si>
+    <t>KOUGH, Andrew S. (2014)</t>
+  </si>
+  <si>
+    <t>m504p207</t>
+  </si>
+  <si>
+    <t>s17</t>
+  </si>
+  <si>
+    <t>24°50′30″</t>
+  </si>
+  <si>
+    <t>KOA</t>
+  </si>
+  <si>
+    <t>FORCUCCI, David; (1994)</t>
+  </si>
+  <si>
+    <t>BRIONES-FOURZÁN, Patricia; (2006)</t>
+  </si>
+  <si>
+    <t>80°47′48″</t>
+  </si>
+  <si>
+    <t>s00227-005-0191-2</t>
+  </si>
+  <si>
+    <t>20°51′00″</t>
+  </si>
+  <si>
+    <t>86°55′00″</t>
+  </si>
+  <si>
+    <t>Unidad Académica Puerto Morelos</t>
+  </si>
+  <si>
+    <t>s002270050148</t>
+  </si>
+  <si>
+    <t>ACOSTA, C. A (1997)</t>
+  </si>
+  <si>
+    <t>Big Munson Key</t>
+  </si>
+  <si>
+    <t>25°36′11″</t>
+  </si>
+  <si>
+    <t>81°24′10″</t>
+  </si>
+  <si>
+    <t>Amapá</t>
+  </si>
+  <si>
+    <t>Espírito Santo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 51°32′</t>
+  </si>
+  <si>
+    <t>40°56′</t>
+  </si>
+  <si>
+    <t>salazar2019</t>
+  </si>
+  <si>
+    <t>ORELLANA SALAZAR, Ivo S (2009)</t>
+  </si>
+  <si>
+    <t>Península de Yucatán, no estado de Quintana Roo</t>
+  </si>
+  <si>
+    <t>10.1071@mf01093</t>
+  </si>
+  <si>
+    <t>LOZANO-ÁLVAREZ, Enrique (2001)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -795,6 +1108,21 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -949,7 +1277,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1326,7 +1656,7 @@
         <v>25</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>12</v>
@@ -1390,7 +1720,7 @@
         <v>30</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>12</v>
@@ -1454,7 +1784,7 @@
         <v>32</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>12</v>
@@ -1518,7 +1848,7 @@
         <v>37</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>12</v>
@@ -1582,7 +1912,7 @@
         <v>41</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>12</v>
@@ -1646,7 +1976,7 @@
         <v>35</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>12</v>
@@ -1703,52 +2033,52 @@
       <c r="D8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>47</v>
+      <c r="E8" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>213</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>43</v>
+        <v>197</v>
       </c>
       <c r="J8" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>34</v>
-      </c>
-      <c r="K8" s="3" t="e">
+        <v>2</v>
+      </c>
+      <c r="K8" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L8" s="3" t="e">
+        <v>53</v>
+      </c>
+      <c r="L8" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M8" s="3" t="e">
+        <v>22</v>
+      </c>
+      <c r="M8" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N8" s="3" t="e">
+        <v>41</v>
+      </c>
+      <c r="N8" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O8" s="3" t="e">
+        <v>13</v>
+      </c>
+      <c r="O8" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P8" s="1" t="e">
+        <v>46</v>
+      </c>
+      <c r="P8" s="1">
         <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q8" s="1" t="e">
+        <v>-2.8894444444444445</v>
+      </c>
+      <c r="Q8" s="1">
         <f t="shared" si="14"/>
-        <v>#VALUE!</v>
+        <v>-41.229444444444447</v>
       </c>
       <c r="R8" s="14" t="s">
         <v>42</v>
@@ -1767,52 +2097,52 @@
       <c r="D9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="12" t="s">
-        <v>45</v>
+      <c r="E9" s="8" t="s">
+        <v>214</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>47</v>
+        <v>215</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>43</v>
+        <v>197</v>
       </c>
       <c r="J9" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>22</v>
-      </c>
-      <c r="K9" s="3" t="e">
+        <v>4</v>
+      </c>
+      <c r="K9" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L9" s="3" t="e">
-        <f>MID(E9,FIND("′",E9,1)+1,(FIND("″",E9,1)-FIND("′",E9,1))-1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M9" s="3" t="e">
+        <v>06</v>
+      </c>
+      <c r="L9" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>06</v>
+      </c>
+      <c r="M9" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N9" s="3" t="e">
+        <v>38</v>
+      </c>
+      <c r="N9" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O9" s="3" t="e">
+        <v>08</v>
+      </c>
+      <c r="O9" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P9" s="1" t="e">
+        <v>56</v>
+      </c>
+      <c r="P9" s="1">
         <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q9" s="1" t="e">
+        <v>-4.1016666666666666</v>
+      </c>
+      <c r="Q9" s="1">
         <f t="shared" si="14"/>
-        <v>#VALUE!</v>
+        <v>-38.148888888888891</v>
       </c>
       <c r="R9" s="14" t="s">
         <v>42</v>
@@ -1838,7 +2168,7 @@
         <v>30</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>12</v>
@@ -1902,7 +2232,7 @@
         <v>32</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>12</v>
@@ -1966,7 +2296,7 @@
         <v>37</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
@@ -2030,7 +2360,7 @@
         <v>41</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>12</v>
@@ -2094,7 +2424,7 @@
         <v>35</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>12</v>
@@ -2151,52 +2481,52 @@
       <c r="D15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>47</v>
+      <c r="E15" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>213</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>43</v>
+        <v>197</v>
       </c>
       <c r="J15" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>34</v>
-      </c>
-      <c r="K15" s="3" t="e">
+        <v>2</v>
+      </c>
+      <c r="K15" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L15" s="3" t="e">
+        <v>53</v>
+      </c>
+      <c r="L15" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M15" s="3" t="e">
+        <v>22</v>
+      </c>
+      <c r="M15" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N15" s="3" t="e">
+        <v>41</v>
+      </c>
+      <c r="N15" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O15" s="3" t="e">
+        <v>13</v>
+      </c>
+      <c r="O15" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P15" s="1" t="e">
+        <v>46</v>
+      </c>
+      <c r="P15" s="1">
         <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q15" s="1" t="e">
+        <v>-2.8894444444444445</v>
+      </c>
+      <c r="Q15" s="1">
         <f t="shared" si="14"/>
-        <v>#VALUE!</v>
+        <v>-41.229444444444447</v>
       </c>
       <c r="R15" s="14" t="s">
         <v>42</v>
@@ -2215,52 +2545,52 @@
       <c r="D16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="12" t="s">
-        <v>45</v>
+      <c r="E16" s="8" t="s">
+        <v>214</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>47</v>
+        <v>215</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>43</v>
+        <v>197</v>
       </c>
       <c r="J16" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>22</v>
-      </c>
-      <c r="K16" s="3" t="e">
+        <v>4</v>
+      </c>
+      <c r="K16" s="3" t="str">
         <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L16" s="3" t="e">
+        <v>06</v>
+      </c>
+      <c r="L16" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M16" s="3" t="e">
+        <v>06</v>
+      </c>
+      <c r="M16" s="3" t="str">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N16" s="3" t="e">
+        <v>38</v>
+      </c>
+      <c r="N16" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O16" s="3" t="e">
+        <v>08</v>
+      </c>
+      <c r="O16" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P16" s="1" t="e">
+        <v>56</v>
+      </c>
+      <c r="P16" s="1">
         <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q16" s="1" t="e">
+        <v>-4.1016666666666666</v>
+      </c>
+      <c r="Q16" s="1">
         <f t="shared" si="14"/>
-        <v>#VALUE!</v>
+        <v>-38.148888888888891</v>
       </c>
       <c r="R16" s="14" t="s">
         <v>42</v>
@@ -2271,7 +2601,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>15</v>
@@ -2280,19 +2610,19 @@
         <v>16</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J17" s="3" t="str">
         <f t="shared" si="8"/>
@@ -2327,7 +2657,7 @@
         <v>-34.820638888888887</v>
       </c>
       <c r="R17" s="14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2335,7 +2665,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>15</v>
@@ -2344,19 +2674,19 @@
         <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J18" s="3" t="str">
         <f t="shared" ref="J18:J25" si="16">MID(E18,1,FIND("°",E18,1)-1)</f>
@@ -2391,7 +2721,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R18" s="14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2408,19 +2738,19 @@
         <v>16</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J19" s="3" t="str">
         <f t="shared" si="16"/>
@@ -2455,7 +2785,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R19" s="14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2472,13 +2802,13 @@
         <v>16</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J20" s="3" t="e">
         <f t="shared" si="16"/>
@@ -2513,7 +2843,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R20" s="14" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2521,7 +2851,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>15</v>
@@ -2530,13 +2860,13 @@
         <v>16</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J21" s="3" t="e">
         <f t="shared" si="16"/>
@@ -2571,7 +2901,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R21" s="14" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2579,7 +2909,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>15</v>
@@ -2588,19 +2918,19 @@
         <v>16</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J22" s="3" t="str">
         <f t="shared" si="16"/>
@@ -2635,7 +2965,7 @@
         <v>-35.085472222222222</v>
       </c>
       <c r="R22" s="14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2643,7 +2973,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>15</v>
@@ -2652,19 +2982,19 @@
         <v>16</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J23" s="3" t="str">
         <f t="shared" si="16"/>
@@ -2699,7 +3029,7 @@
         <v>-35.096916666666665</v>
       </c>
       <c r="R23" s="14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2707,7 +3037,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>15</v>
@@ -2716,19 +3046,19 @@
         <v>16</v>
       </c>
       <c r="E24" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G24" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>74</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="J24" s="3" t="str">
         <f t="shared" si="16"/>
@@ -2763,7 +3093,7 @@
         <v>-35.082638888888887</v>
       </c>
       <c r="R24" s="14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2771,7 +3101,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>15</v>
@@ -2780,19 +3110,19 @@
         <v>16</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="J25" s="3" t="str">
         <f t="shared" si="16"/>
@@ -2827,7 +3157,7 @@
         <v>-35.094999999999999</v>
       </c>
       <c r="R25" s="14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2844,19 +3174,19 @@
         <v>16</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J26" s="3" t="str">
         <f t="shared" ref="J26:J89" si="24">MID(E26,1,FIND("°",E26,1)-1)</f>
@@ -2908,19 +3238,19 @@
         <v>16</v>
       </c>
       <c r="E27" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G27" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>85</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J27" s="3" t="str">
         <f t="shared" si="24"/>
@@ -2972,19 +3302,19 @@
         <v>16</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J28" s="3" t="str">
         <f t="shared" si="24"/>
@@ -3036,19 +3366,19 @@
         <v>16</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J29" s="3" t="str">
         <f t="shared" si="24"/>
@@ -3083,7 +3413,7 @@
         <v>-35.002222222222223</v>
       </c>
       <c r="R29" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3091,7 +3421,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>15</v>
@@ -3100,19 +3430,19 @@
         <v>16</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J30" s="3" t="str">
         <f t="shared" si="24"/>
@@ -3147,7 +3477,7 @@
         <v>-35.002222222222223</v>
       </c>
       <c r="R30" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3155,7 +3485,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>15</v>
@@ -3164,19 +3494,19 @@
         <v>16</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J31" s="3" t="str">
         <f t="shared" si="24"/>
@@ -3211,7 +3541,7 @@
         <v>-35.002222222222223</v>
       </c>
       <c r="R31" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3228,19 +3558,19 @@
         <v>16</v>
       </c>
       <c r="E32" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="J32" s="3" t="str">
         <f t="shared" si="24"/>
@@ -3275,7 +3605,7 @@
         <v>-35.041111111111114</v>
       </c>
       <c r="R32" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3292,19 +3622,19 @@
         <v>16</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="J33" s="3" t="str">
         <f t="shared" si="24"/>
@@ -3339,7 +3669,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R33" s="13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3356,19 +3686,19 @@
         <v>16</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J34" s="3" t="str">
         <f t="shared" si="24"/>
@@ -3403,7 +3733,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R34" s="13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3420,19 +3750,19 @@
         <v>16</v>
       </c>
       <c r="E35" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G35" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>103</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J35" s="3" t="str">
         <f t="shared" si="24"/>
@@ -3467,7 +3797,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R35" s="13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3475,7 +3805,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>29</v>
@@ -3484,19 +3814,19 @@
         <v>16</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J36" s="3" t="str">
         <f t="shared" si="24"/>
@@ -3531,7 +3861,7 @@
         <v>-29.342500000000001</v>
       </c>
       <c r="R36" s="13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3539,7 +3869,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>29</v>
@@ -3548,19 +3878,19 @@
         <v>16</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F37" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="G37" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J37" s="3" t="str">
         <f t="shared" si="24"/>
@@ -3595,7 +3925,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R37" s="13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3603,7 +3933,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>29</v>
@@ -3612,19 +3942,19 @@
         <v>16</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J38" s="3" t="str">
         <f t="shared" si="24"/>
@@ -3659,7 +3989,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R38" s="13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3676,19 +4006,19 @@
         <v>16</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J39" s="3" t="str">
         <f t="shared" si="24"/>
@@ -3723,7 +4053,7 @@
         <v>-29.342500000000001</v>
       </c>
       <c r="R39" s="13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3740,19 +4070,19 @@
         <v>16</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F40" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="G40" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J40" s="3" t="str">
         <f t="shared" si="24"/>
@@ -3787,7 +4117,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R40" s="13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3804,19 +4134,19 @@
         <v>16</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J41" s="3" t="str">
         <f t="shared" si="24"/>
@@ -3851,7 +4181,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R41" s="13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3859,7 +4189,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>15</v>
@@ -3868,19 +4198,19 @@
         <v>16</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J42" s="3" t="str">
         <f t="shared" si="24"/>
@@ -3915,7 +4245,7 @@
         <v>-35.180277777777775</v>
       </c>
       <c r="R42" s="13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3923,7 +4253,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>15</v>
@@ -3932,19 +4262,19 @@
         <v>16</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F43" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G43" s="8" t="s">
         <v>119</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>123</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J43" s="3" t="str">
         <f t="shared" si="24"/>
@@ -3979,7 +4309,7 @@
         <v>-46.789444444444442</v>
       </c>
       <c r="R43" s="13" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3996,19 +4326,19 @@
         <v>16</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F44" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G44" s="8" t="s">
         <v>119</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>123</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J44" s="3" t="str">
         <f t="shared" si="24"/>
@@ -4043,7 +4373,7 @@
         <v>-46.789444444444442</v>
       </c>
       <c r="R44" s="13" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -4060,19 +4390,19 @@
         <v>16</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="J45" s="3" t="str">
         <f t="shared" si="24"/>
@@ -4107,7 +4437,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R45" s="13" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -4115,7 +4445,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>15</v>
@@ -4124,19 +4454,19 @@
         <v>16</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="J46" s="3" t="str">
         <f t="shared" si="24"/>
@@ -4171,7 +4501,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R46" s="13" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -4179,7 +4509,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>15</v>
@@ -4188,19 +4518,19 @@
         <v>16</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J47" s="3" t="str">
         <f t="shared" si="24"/>
@@ -4235,7 +4565,7 @@
         <v>-34.996388888888887</v>
       </c>
       <c r="R47" s="13" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -4252,19 +4582,19 @@
         <v>16</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J48" s="3" t="str">
         <f t="shared" si="24"/>
@@ -4299,7 +4629,7 @@
         <v>-34.996388888888887</v>
       </c>
       <c r="R48" s="13" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -4316,19 +4646,19 @@
         <v>16</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J49" s="3" t="str">
         <f t="shared" si="24"/>
@@ -4363,7 +4693,7 @@
         <v>-34.996388888888887</v>
       </c>
       <c r="R49" s="13" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -4371,7 +4701,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>15</v>
@@ -4380,19 +4710,19 @@
         <v>16</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="J50" s="3" t="str">
         <f t="shared" si="24"/>
@@ -4427,7 +4757,7 @@
         <v>-38.721111111111114</v>
       </c>
       <c r="R50" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -4444,19 +4774,19 @@
         <v>16</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="J51" s="3" t="str">
         <f t="shared" si="24"/>
@@ -4491,7 +4821,7 @@
         <v>-38.721111111111114</v>
       </c>
       <c r="R51" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -4508,19 +4838,19 @@
         <v>16</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="J52" s="3" t="str">
         <f t="shared" si="24"/>
@@ -4555,7 +4885,7 @@
         <v>-38.721111111111114</v>
       </c>
       <c r="R52" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -4572,19 +4902,19 @@
         <v>16</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J53" s="3" t="str">
         <f t="shared" si="24"/>
@@ -4619,7 +4949,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R53" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="54" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -4636,19 +4966,19 @@
         <v>16</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="J54" s="3" t="str">
         <f t="shared" si="24"/>
@@ -4683,7 +5013,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R54" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -4700,19 +5030,19 @@
         <v>16</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I55" s="24" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="J55" s="3" t="str">
         <f t="shared" si="24"/>
@@ -4747,7 +5077,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R55" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -4764,19 +5094,19 @@
         <v>16</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I56" s="24" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="J56" s="3" t="str">
         <f t="shared" si="24"/>
@@ -4811,7 +5141,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R56" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -4819,7 +5149,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>15</v>
@@ -4828,19 +5158,19 @@
         <v>16</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J57" s="3" t="str">
         <f t="shared" si="24"/>
@@ -4875,7 +5205,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R57" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -4883,7 +5213,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>15</v>
@@ -4892,19 +5222,19 @@
         <v>16</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="J58" s="3" t="str">
         <f t="shared" si="24"/>
@@ -4939,7 +5269,7 @@
         <v>-38.702500000000001</v>
       </c>
       <c r="R58" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -4947,7 +5277,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>15</v>
@@ -4956,19 +5286,19 @@
         <v>16</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="J59" s="3" t="str">
         <f t="shared" si="24"/>
@@ -5003,7 +5333,7 @@
         <v>-38.715277777777779</v>
       </c>
       <c r="R59" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="60" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -5011,7 +5341,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>15</v>
@@ -5020,19 +5350,19 @@
         <v>16</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="J60" s="3" t="str">
         <f t="shared" si="24"/>
@@ -5067,7 +5397,7 @@
         <v>-38.714444444444446</v>
       </c>
       <c r="R60" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="61" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -5084,19 +5414,19 @@
         <v>16</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J61" s="3" t="str">
         <f t="shared" si="24"/>
@@ -5131,7 +5461,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R61" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -5148,19 +5478,19 @@
         <v>16</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I62" s="24" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="J62" s="3" t="str">
         <f t="shared" si="24"/>
@@ -5195,7 +5525,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R62" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="63" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -5212,19 +5542,19 @@
         <v>16</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J63" s="3" t="str">
         <f t="shared" si="24"/>
@@ -5259,7 +5589,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R63" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="64" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -5267,7 +5597,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>15</v>
@@ -5276,19 +5606,19 @@
         <v>16</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J64" s="3" t="str">
         <f t="shared" si="24"/>
@@ -5323,7 +5653,7 @@
         <v>-34.996388888888887</v>
       </c>
       <c r="R64" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="65" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -5331,7 +5661,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>15</v>
@@ -5340,19 +5670,19 @@
         <v>16</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I65" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J65" s="3" t="str">
         <f t="shared" si="24"/>
@@ -5387,7 +5717,7 @@
         <v>-35.124722222222225</v>
       </c>
       <c r="R65" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -5395,7 +5725,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>15</v>
@@ -5404,19 +5734,19 @@
         <v>16</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I66" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J66" s="3" t="str">
         <f t="shared" si="24"/>
@@ -5451,7 +5781,7 @@
         <v>-35.041111111111114</v>
       </c>
       <c r="R66" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -5468,19 +5798,19 @@
         <v>16</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J67" s="3" t="str">
         <f t="shared" si="24"/>
@@ -5515,7 +5845,7 @@
         <v>-34.996388888888887</v>
       </c>
       <c r="R67" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="68" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -5532,19 +5862,19 @@
         <v>16</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I68" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J68" s="3" t="str">
         <f t="shared" si="24"/>
@@ -5579,7 +5909,7 @@
         <v>-35.124722222222225</v>
       </c>
       <c r="R68" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -5596,19 +5926,19 @@
         <v>16</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I69" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J69" s="3" t="str">
         <f t="shared" si="24"/>
@@ -5643,7 +5973,7 @@
         <v>-35.041111111111114</v>
       </c>
       <c r="R69" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -5660,19 +5990,19 @@
         <v>16</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J70" s="3" t="str">
         <f t="shared" si="24"/>
@@ -5707,7 +6037,7 @@
         <v>-34.996388888888887</v>
       </c>
       <c r="R70" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -5724,19 +6054,19 @@
         <v>16</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I71" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J71" s="3" t="str">
         <f t="shared" si="24"/>
@@ -5771,7 +6101,7 @@
         <v>-35.124722222222225</v>
       </c>
       <c r="R71" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -5788,19 +6118,19 @@
         <v>16</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I72" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J72" s="3" t="str">
         <f t="shared" si="24"/>
@@ -5835,7 +6165,7 @@
         <v>-35.041111111111114</v>
       </c>
       <c r="R72" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -5843,7 +6173,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>15</v>
@@ -5852,19 +6182,19 @@
         <v>16</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="J73" s="3" t="str">
         <f t="shared" si="24"/>
@@ -5899,7 +6229,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R73" s="13" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="74" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -5907,7 +6237,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>15</v>
@@ -5916,19 +6246,19 @@
         <v>16</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F74" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G74" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="J74" s="3" t="str">
         <f t="shared" si="24"/>
@@ -5963,7 +6293,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R74" s="13" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="75" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -5971,7 +6301,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>15</v>
@@ -5980,19 +6310,19 @@
         <v>16</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="J75" s="3" t="str">
         <f t="shared" si="24"/>
@@ -6027,7 +6357,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R75" s="13" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="76" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -6050,13 +6380,13 @@
         <v>30</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I76" s="24" t="s">
-        <v>185</v>
+      <c r="I76" s="8" t="s">
+        <v>268</v>
       </c>
       <c r="J76" s="3" t="str">
         <f t="shared" si="24"/>
@@ -6091,7 +6421,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R76" s="13" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="77" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -6108,19 +6438,19 @@
         <v>16</v>
       </c>
       <c r="E77" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G77" s="8" t="s">
         <v>182</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G77" s="8" t="s">
-        <v>187</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I77" s="24" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J77" s="3" t="str">
         <f t="shared" si="24"/>
@@ -6155,7 +6485,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R77" s="13" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="78" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -6178,13 +6508,13 @@
         <v>30</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I78" s="24" t="s">
-        <v>185</v>
+      <c r="I78" s="8" t="s">
+        <v>268</v>
       </c>
       <c r="J78" s="3" t="str">
         <f t="shared" si="24"/>
@@ -6219,7 +6549,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R78" s="13" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="79" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -6236,19 +6566,19 @@
         <v>16</v>
       </c>
       <c r="E79" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G79" s="8" t="s">
         <v>182</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>187</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I79" s="24" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J79" s="3" t="str">
         <f t="shared" si="24"/>
@@ -6283,7 +6613,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R79" s="13" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="80" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -6300,19 +6630,19 @@
         <v>16</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="J80" s="3" t="str">
         <f t="shared" si="24"/>
@@ -6347,7 +6677,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R80" s="13" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -6364,19 +6694,19 @@
         <v>16</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="J81" s="3" t="str">
         <f t="shared" si="24"/>
@@ -6411,7 +6741,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R81" s="13" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="82" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -6419,7 +6749,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>15</v>
@@ -6428,19 +6758,19 @@
         <v>16</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="J82" s="3" t="str">
         <f t="shared" si="24"/>
@@ -6475,7 +6805,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R82" s="13" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="83" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -6483,7 +6813,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>15</v>
@@ -6492,19 +6822,19 @@
         <v>16</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I83" s="25" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J83" s="3" t="str">
         <f t="shared" si="24"/>
@@ -6539,7 +6869,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R83" s="13" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="84" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -6547,7 +6877,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>29</v>
@@ -6556,19 +6886,19 @@
         <v>16</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J84" s="3" t="str">
         <f t="shared" si="24"/>
@@ -6603,7 +6933,7 @@
         <v>-29.345555555555556</v>
       </c>
       <c r="R84" s="13" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="85" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -6611,7 +6941,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>15</v>
@@ -6620,19 +6950,19 @@
         <v>16</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="J85" s="3" t="str">
         <f t="shared" si="24"/>
@@ -6667,7 +6997,7 @@
         <v>-37.506361111111111</v>
       </c>
       <c r="R85" s="13" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="86" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -6684,19 +7014,19 @@
         <v>16</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J86" s="3" t="str">
         <f t="shared" si="24"/>
@@ -6731,7 +7061,7 @@
         <v>-29.345555555555556</v>
       </c>
       <c r="R86" s="13" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="87" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -6748,19 +7078,19 @@
         <v>16</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J87" s="3" t="str">
         <f t="shared" si="24"/>
@@ -6795,38 +7125,56 @@
         <v>-29.345555555555556</v>
       </c>
       <c r="R87" s="13" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="88" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>87</v>
       </c>
+      <c r="B88" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="C88" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J88" s="3" t="e">
+      <c r="E88" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="J88" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K88" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="K88" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>45</v>
       </c>
       <c r="L88" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M88" s="3" t="e">
+      <c r="M88" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N88" s="3" t="e">
+        <v xml:space="preserve"> 38</v>
+      </c>
+      <c r="N88" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>13</v>
       </c>
       <c r="O88" s="3" t="e">
         <f t="shared" si="29"/>
@@ -6840,37 +7188,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R88" s="13"/>
+      <c r="R88" s="13" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="89" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>88</v>
       </c>
+      <c r="B89" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="C89" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J89" s="3" t="e">
+      <c r="E89" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J89" s="3" t="str">
         <f t="shared" si="24"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K89" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="K89" s="3" t="str">
         <f t="shared" si="25"/>
-        <v>#VALUE!</v>
+        <v>45</v>
       </c>
       <c r="L89" s="3" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M89" s="3" t="e">
+      <c r="M89" s="3" t="str">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N89" s="3" t="e">
+        <v xml:space="preserve"> 38</v>
+      </c>
+      <c r="N89" s="3" t="str">
         <f t="shared" si="28"/>
-        <v>#VALUE!</v>
+        <v>13</v>
       </c>
       <c r="O89" s="3" t="e">
         <f t="shared" si="29"/>
@@ -6884,37 +7252,57 @@
         <f t="shared" si="31"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R89" s="13"/>
+      <c r="R89" s="13" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="90" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>89</v>
       </c>
+      <c r="B90" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="C90" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J90" s="3" t="e">
+      <c r="E90" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J90" s="3" t="str">
         <f t="shared" ref="J90:J135" si="32">MID(E90,1,FIND("°",E90,1)-1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K90" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="K90" s="3" t="str">
         <f t="shared" ref="K90:K135" si="33">MID(E90,FIND("°",E90,1)+1,(FIND("′",E90,1)-FIND("°",E90,1))-1)</f>
-        <v>#VALUE!</v>
+        <v>38</v>
       </c>
       <c r="L90" s="3" t="e">
         <f t="shared" ref="L90:L135" si="34">MID(E90,FIND("′",E90,1)+1,(FIND("″",E90,1)-FIND("′",E90,1))-1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M90" s="3" t="e">
+      <c r="M90" s="3" t="str">
         <f t="shared" ref="M90:M135" si="35">MID(F90,1,FIND("°",F90,1)-1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N90" s="3" t="e">
+        <v>38</v>
+      </c>
+      <c r="N90" s="3" t="str">
         <f t="shared" ref="N90:N135" si="36">MID(F90,FIND("°",F90,1)+1,(FIND("′",F90,1)-FIND("°",F90,1))-1)</f>
-        <v>#VALUE!</v>
+        <v>13</v>
       </c>
       <c r="O90" s="3" t="e">
         <f t="shared" ref="O90:O135" si="37">MID(F90,FIND("′",F90,1)+1,(FIND("″",F90,1)-FIND("′",F90,1))-1)</f>
@@ -6928,37 +7316,57 @@
         <f t="shared" ref="Q90:Q135" si="39">((((O90/60)+N90)/60)+M90)*IF(D90="W",-1, 1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R90" s="13"/>
+      <c r="R90" s="13" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="91" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>90</v>
       </c>
+      <c r="B91" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="C91" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J91" s="3" t="e">
+      <c r="E91" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J91" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K91" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="K91" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
+        <v>31</v>
       </c>
       <c r="L91" s="3" t="e">
         <f t="shared" si="34"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M91" s="3" t="e">
+      <c r="M91" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N91" s="3" t="e">
+        <v xml:space="preserve"> 38</v>
+      </c>
+      <c r="N91" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
+        <v>12</v>
       </c>
       <c r="O91" s="3" t="e">
         <f t="shared" si="37"/>
@@ -6972,37 +7380,57 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R91" s="13"/>
+      <c r="R91" s="13" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="92" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>91</v>
       </c>
+      <c r="B92" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C92" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J92" s="3" t="e">
+      <c r="E92" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J92" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K92" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="K92" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
+        <v>45</v>
       </c>
       <c r="L92" s="3" t="e">
         <f t="shared" si="34"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M92" s="3" t="e">
+      <c r="M92" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N92" s="3" t="e">
+        <v xml:space="preserve"> 38</v>
+      </c>
+      <c r="N92" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
+        <v>13</v>
       </c>
       <c r="O92" s="3" t="e">
         <f t="shared" si="37"/>
@@ -7016,37 +7444,57 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R92" s="13"/>
+      <c r="R92" s="13" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="93" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>92</v>
       </c>
+      <c r="B93" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C93" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J93" s="3" t="e">
+      <c r="E93" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J93" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K93" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="K93" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
+        <v>38</v>
       </c>
       <c r="L93" s="3" t="e">
         <f t="shared" si="34"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M93" s="3" t="e">
+      <c r="M93" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N93" s="3" t="e">
+        <v>38</v>
+      </c>
+      <c r="N93" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
+        <v>13</v>
       </c>
       <c r="O93" s="3" t="e">
         <f t="shared" si="37"/>
@@ -7060,37 +7508,57 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R93" s="13"/>
+      <c r="R93" s="13" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="94" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>93</v>
       </c>
+      <c r="B94" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C94" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J94" s="3" t="e">
+      <c r="E94" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J94" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K94" s="3" t="e">
+        <v>03</v>
+      </c>
+      <c r="K94" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
+        <v>31</v>
       </c>
       <c r="L94" s="3" t="e">
         <f t="shared" si="34"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M94" s="3" t="e">
+      <c r="M94" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N94" s="3" t="e">
+        <v xml:space="preserve"> 38</v>
+      </c>
+      <c r="N94" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
+        <v>12</v>
       </c>
       <c r="O94" s="3" t="e">
         <f t="shared" si="37"/>
@@ -7104,125 +7572,185 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R94" s="13"/>
+      <c r="R94" s="13" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="95" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>94</v>
       </c>
+      <c r="B95" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C95" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J95" s="3" t="e">
+      <c r="E95" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="J95" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K95" s="3" t="e">
+        <v>24</v>
+      </c>
+      <c r="K95" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L95" s="3" t="e">
+        <v>49</v>
+      </c>
+      <c r="L95" s="3" t="str">
         <f t="shared" si="34"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M95" s="3" t="e">
+        <v>13</v>
+      </c>
+      <c r="M95" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N95" s="3" t="e">
+        <v>80</v>
+      </c>
+      <c r="N95" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O95" s="3" t="e">
+        <v>48</v>
+      </c>
+      <c r="O95" s="3" t="str">
         <f t="shared" si="37"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P95" s="1" t="e">
+        <v>48</v>
+      </c>
+      <c r="P95" s="1">
         <f t="shared" si="38"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q95" s="1" t="e">
+        <v>24.820277777777779</v>
+      </c>
+      <c r="Q95" s="1">
         <f t="shared" si="39"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R95" s="13"/>
+        <v>-80.813333333333333</v>
+      </c>
+      <c r="R95" s="14" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="96" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>95</v>
       </c>
+      <c r="B96" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C96" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J96" s="3" t="e">
+      <c r="E96" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="J96" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K96" s="3" t="e">
+        <v>24</v>
+      </c>
+      <c r="K96" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L96" s="3" t="e">
+        <v>50</v>
+      </c>
+      <c r="L96" s="3" t="str">
         <f t="shared" si="34"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M96" s="3" t="e">
+        <v>55</v>
+      </c>
+      <c r="M96" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N96" s="3" t="e">
+        <v>80</v>
+      </c>
+      <c r="N96" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O96" s="3" t="e">
+        <v>48</v>
+      </c>
+      <c r="O96" s="3" t="str">
         <f t="shared" si="37"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P96" s="1" t="e">
+        <v>03</v>
+      </c>
+      <c r="P96" s="1">
         <f t="shared" si="38"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q96" s="1" t="e">
+        <v>24.848611111111111</v>
+      </c>
+      <c r="Q96" s="1">
         <f t="shared" si="39"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R96" s="13"/>
+        <v>-80.80083333333333</v>
+      </c>
+      <c r="R96" s="14" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="97" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>96</v>
       </c>
+      <c r="B97" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C97" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J97" s="3" t="e">
+      <c r="E97" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="J97" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K97" s="3" t="e">
+        <v>05</v>
+      </c>
+      <c r="K97" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
+        <v>13</v>
       </c>
       <c r="L97" s="3" t="e">
         <f t="shared" si="34"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M97" s="3" t="e">
+      <c r="M97" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N97" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="N97" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
+        <v>10</v>
       </c>
       <c r="O97" s="3" t="e">
         <f t="shared" si="37"/>
@@ -7236,21 +7764,41 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R97" s="13"/>
+      <c r="R97" s="13" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="98" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>97</v>
       </c>
+      <c r="B98" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C98" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J98" s="3" t="e">
+      <c r="E98" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="J98" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
+        <v>24</v>
       </c>
       <c r="K98" s="3" t="e">
         <f t="shared" si="33"/>
@@ -7260,9 +7808,9 @@
         <f t="shared" si="34"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M98" s="3" t="e">
+      <c r="M98" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
+        <v>80</v>
       </c>
       <c r="N98" s="3" t="e">
         <f t="shared" si="36"/>
@@ -7280,37 +7828,57 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R98" s="13"/>
+      <c r="R98" s="13" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="99" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>98</v>
       </c>
+      <c r="B99" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C99" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J99" s="3" t="e">
+      <c r="E99" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="J99" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K99" s="3" t="e">
+        <v>24</v>
+      </c>
+      <c r="K99" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
+        <v>78</v>
       </c>
       <c r="L99" s="3" t="e">
         <f t="shared" si="34"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M99" s="3" t="e">
+      <c r="M99" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N99" s="3" t="e">
+        <v xml:space="preserve"> 80</v>
+      </c>
+      <c r="N99" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
+        <v>92</v>
       </c>
       <c r="O99" s="3" t="e">
         <f t="shared" si="37"/>
@@ -7324,304 +7892,441 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R99" s="13"/>
+      <c r="R99" s="13" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="100" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>99</v>
       </c>
+      <c r="B100" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C100" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E100" s="7"/>
-      <c r="J100" s="3" t="e">
+      <c r="E100" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I100" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="J100" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K100" s="3" t="e">
+        <v>19</v>
+      </c>
+      <c r="K100" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L100" s="3" t="e">
+        <v>27</v>
+      </c>
+      <c r="L100" s="3" t="str">
         <f t="shared" si="34"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M100" s="3" t="e">
+        <v>00</v>
+      </c>
+      <c r="M100" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N100" s="3" t="e">
+        <v xml:space="preserve"> 87</v>
+      </c>
+      <c r="N100" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O100" s="3" t="e">
+        <v>17</v>
+      </c>
+      <c r="O100" s="3" t="str">
         <f t="shared" si="37"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P100" s="1" t="e">
+        <v>24</v>
+      </c>
+      <c r="P100" s="1">
         <f t="shared" si="38"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q100" s="1" t="e">
+        <v>19.45</v>
+      </c>
+      <c r="Q100" s="1">
         <f t="shared" si="39"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R100" s="13"/>
+        <v>-87.29</v>
+      </c>
+      <c r="R100" s="13" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="101" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>100</v>
       </c>
+      <c r="B101" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C101" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E101" s="7"/>
-      <c r="J101" s="3" t="e">
+      <c r="E101" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I101" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="J101" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K101" s="3" t="e">
+        <v>25</v>
+      </c>
+      <c r="K101" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L101" s="3" t="e">
+        <v>01</v>
+      </c>
+      <c r="L101" s="3" t="str">
         <f t="shared" si="34"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M101" s="3" t="e">
+        <v>46</v>
+      </c>
+      <c r="M101" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N101" s="3" t="e">
+        <v xml:space="preserve"> 80</v>
+      </c>
+      <c r="N101" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O101" s="3" t="e">
+        <v>23</v>
+      </c>
+      <c r="O101" s="3" t="str">
         <f t="shared" si="37"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P101" s="1" t="e">
+        <v>53</v>
+      </c>
+      <c r="P101" s="1">
         <f t="shared" si="38"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q101" s="1" t="e">
+        <v>25.029444444444444</v>
+      </c>
+      <c r="Q101" s="1">
         <f t="shared" si="39"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R101" s="13"/>
+        <v>-80.398055555555558</v>
+      </c>
+      <c r="R101" s="13" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="102" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>101</v>
       </c>
+      <c r="B102" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C102" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E102" s="7"/>
-      <c r="J102" s="3" t="e">
+      <c r="E102" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="J102" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K102" s="3" t="e">
+        <v>25</v>
+      </c>
+      <c r="K102" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L102" s="3" t="e">
+        <v>35</v>
+      </c>
+      <c r="L102" s="3" t="str">
         <f t="shared" si="34"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M102" s="3" t="e">
+        <v>28</v>
+      </c>
+      <c r="M102" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N102" s="3" t="e">
+        <v>80</v>
+      </c>
+      <c r="N102" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O102" s="3" t="e">
+        <v>05</v>
+      </c>
+      <c r="O102" s="3" t="str">
         <f t="shared" si="37"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P102" s="1" t="e">
+        <v>49</v>
+      </c>
+      <c r="P102" s="1">
         <f t="shared" si="38"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q102" s="1" t="e">
+        <v>25.591111111111111</v>
+      </c>
+      <c r="Q102" s="1">
         <f t="shared" si="39"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R102" s="13"/>
+        <v>-80.096944444444446</v>
+      </c>
+      <c r="R102" s="13" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="103" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>102</v>
       </c>
+      <c r="B103" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C103" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J103" s="3" t="e">
+      <c r="E103" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="J103" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K103" s="3" t="e">
+        <v>24</v>
+      </c>
+      <c r="K103" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L103" s="3" t="e">
+        <v>50</v>
+      </c>
+      <c r="L103" s="3" t="str">
         <f t="shared" si="34"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M103" s="3" t="e">
+        <v>30</v>
+      </c>
+      <c r="M103" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N103" s="3" t="e">
+        <v>80</v>
+      </c>
+      <c r="N103" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O103" s="3" t="e">
+        <v>47</v>
+      </c>
+      <c r="O103" s="3" t="str">
         <f t="shared" si="37"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P103" s="1" t="e">
+        <v>48</v>
+      </c>
+      <c r="P103" s="1">
         <f t="shared" si="38"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q103" s="1" t="e">
+        <v>24.841666666666665</v>
+      </c>
+      <c r="Q103" s="1">
         <f t="shared" si="39"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R103" s="13"/>
+        <v>-80.796666666666667</v>
+      </c>
+      <c r="R103" s="13" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="104" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>103</v>
       </c>
+      <c r="B104" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C104" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J104" s="3" t="e">
+      <c r="E104" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I104" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="J104" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K104" s="3" t="e">
+        <v>20</v>
+      </c>
+      <c r="K104" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L104" s="3" t="e">
+        <v>51</v>
+      </c>
+      <c r="L104" s="3" t="str">
         <f t="shared" si="34"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M104" s="3" t="e">
+        <v>00</v>
+      </c>
+      <c r="M104" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N104" s="3" t="e">
+        <v>86</v>
+      </c>
+      <c r="N104" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O104" s="3" t="e">
+        <v>55</v>
+      </c>
+      <c r="O104" s="3" t="str">
         <f t="shared" si="37"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P104" s="1" t="e">
+        <v>00</v>
+      </c>
+      <c r="P104" s="1">
         <f t="shared" si="38"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q104" s="1" t="e">
+        <v>20.85</v>
+      </c>
+      <c r="Q104" s="1">
         <f t="shared" si="39"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R104" s="13"/>
+        <v>-86.916666666666671</v>
+      </c>
+      <c r="R104" s="13" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="105" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>104</v>
       </c>
+      <c r="B105" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C105" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J105" s="3" t="e">
+      <c r="E105" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I105" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="J105" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K105" s="3" t="e">
+        <v>25</v>
+      </c>
+      <c r="K105" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L105" s="3" t="e">
+        <v>36</v>
+      </c>
+      <c r="L105" s="3" t="str">
         <f t="shared" si="34"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M105" s="3" t="e">
+        <v>11</v>
+      </c>
+      <c r="M105" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N105" s="3" t="e">
+        <v>81</v>
+      </c>
+      <c r="N105" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O105" s="3" t="e">
+        <v>24</v>
+      </c>
+      <c r="O105" s="3" t="str">
         <f t="shared" si="37"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P105" s="1" t="e">
+        <v>10</v>
+      </c>
+      <c r="P105" s="1">
         <f t="shared" si="38"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q105" s="1" t="e">
+        <v>-25.603055555555557</v>
+      </c>
+      <c r="Q105" s="1">
         <f t="shared" si="39"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R105" s="13"/>
+        <v>-81.402777777777771</v>
+      </c>
+      <c r="R105" s="13" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="106" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>105</v>
       </c>
+      <c r="B106" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C106" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J106" s="3" t="e">
+      <c r="E106" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="J106" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K106" s="3" t="e">
+        <v>04</v>
+      </c>
+      <c r="K106" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
+        <v>26</v>
       </c>
       <c r="L106" s="3" t="e">
         <f t="shared" si="34"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M106" s="3" t="e">
+      <c r="M106" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N106" s="3" t="e">
+        <v xml:space="preserve"> 51</v>
+      </c>
+      <c r="N106" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
+        <v>32</v>
       </c>
       <c r="O106" s="3" t="e">
         <f t="shared" si="37"/>
@@ -7635,37 +8340,57 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R106" s="13"/>
+      <c r="R106" s="13" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="107" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>106</v>
       </c>
+      <c r="B107" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C107" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J107" s="3" t="e">
+      <c r="E107" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="J107" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K107" s="3" t="e">
+        <v>21</v>
+      </c>
+      <c r="K107" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
+        <v>17</v>
       </c>
       <c r="L107" s="3" t="e">
         <f t="shared" si="34"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M107" s="3" t="e">
+      <c r="M107" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N107" s="3" t="e">
+        <v>40</v>
+      </c>
+      <c r="N107" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
+        <v>56</v>
       </c>
       <c r="O107" s="3" t="e">
         <f t="shared" si="37"/>
@@ -7679,37 +8404,57 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R107" s="13"/>
+      <c r="R107" s="13" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="108" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>107</v>
       </c>
+      <c r="B108" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="C108" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J108" s="3" t="e">
+      <c r="E108" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="J108" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K108" s="3" t="e">
+        <v>04</v>
+      </c>
+      <c r="K108" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
+        <v>26</v>
       </c>
       <c r="L108" s="3" t="e">
         <f t="shared" si="34"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M108" s="3" t="e">
+      <c r="M108" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N108" s="3" t="e">
+        <v xml:space="preserve"> 51</v>
+      </c>
+      <c r="N108" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
+        <v>32</v>
       </c>
       <c r="O108" s="3" t="e">
         <f t="shared" si="37"/>
@@ -7723,38 +8468,57 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R108" s="13"/>
+      <c r="R108" s="13" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="109" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>108</v>
       </c>
+      <c r="B109" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="C109" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E109" s="7"/>
-      <c r="J109" s="3" t="e">
+      <c r="E109" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="J109" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K109" s="3" t="e">
+        <v>21</v>
+      </c>
+      <c r="K109" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
+        <v>17</v>
       </c>
       <c r="L109" s="3" t="e">
         <f t="shared" si="34"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M109" s="3" t="e">
+      <c r="M109" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N109" s="3" t="e">
+        <v>40</v>
+      </c>
+      <c r="N109" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
+        <v>56</v>
       </c>
       <c r="O109" s="3" t="e">
         <f t="shared" si="37"/>
@@ -7768,52 +8532,73 @@
         <f t="shared" si="39"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R109" s="13"/>
+      <c r="R109" s="13" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="110" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>109</v>
       </c>
+      <c r="B110" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C110" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E110" s="7"/>
-      <c r="J110" s="3" t="e">
+      <c r="E110" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="J110" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K110" s="3" t="e">
+        <v>20</v>
+      </c>
+      <c r="K110" s="3" t="str">
         <f t="shared" si="33"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L110" s="3" t="e">
+        <v>51</v>
+      </c>
+      <c r="L110" s="3" t="str">
         <f t="shared" si="34"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M110" s="3" t="e">
+        <v>00</v>
+      </c>
+      <c r="M110" s="3" t="str">
         <f t="shared" si="35"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N110" s="3" t="e">
+        <v>86</v>
+      </c>
+      <c r="N110" s="3" t="str">
         <f t="shared" si="36"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O110" s="3" t="e">
+        <v>55</v>
+      </c>
+      <c r="O110" s="3" t="str">
         <f t="shared" si="37"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P110" s="1" t="e">
+        <v>00</v>
+      </c>
+      <c r="P110" s="1">
         <f t="shared" si="38"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q110" s="1" t="e">
+        <v>-20.85</v>
+      </c>
+      <c r="Q110" s="1">
         <f t="shared" si="39"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R110" s="13"/>
+        <v>-86.916666666666671</v>
+      </c>
+      <c r="R110" s="13" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="111" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="3">

--- a/Ocorrências Literatura.xlsx
+++ b/Ocorrências Literatura.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faculdade\Laboratorio\lagostas_carapaca\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA36930-029B-40E9-8259-A5AF32AA04D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F921765-7979-4B94-9560-399387C6944E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Ocorrências Panulirus" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$B$1:$I$477</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ocorrências Panulirus'!$B$1:$I$477</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1032,7 +1032,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1108,13 +1108,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>

--- a/Ocorrências Literatura.xlsx
+++ b/Ocorrências Literatura.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faculdade\Laboratorio\lagostas_carapaca\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B1F738-5288-4031-8C8C-D6EEAF9BE16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DEC900-C0A2-4462-B6BE-81BAD4D6D2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Ocorrências Panulirus" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ocorrências Panulirus'!$B$1:$I$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ocorrências Panulirus'!$B$1:$I$222</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -1747,7 +1747,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1830,9 +1830,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1841,6 +1838,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2126,6 +2129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:R466"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2146,7 +2150,7 @@
     <col min="19" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -2202,7 +2206,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="15.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2266,8 +2270,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34">
+    <row r="3" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="33">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -2330,8 +2334,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="34">
+    <row r="4" spans="1:18" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="33">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -2394,8 +2398,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="34">
+    <row r="5" spans="1:18" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="33">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -2458,8 +2462,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="34">
+    <row r="6" spans="1:18" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="33">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -2522,8 +2526,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="34">
+    <row r="7" spans="1:18" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="33">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -2586,8 +2590,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="34">
+    <row r="8" spans="1:18" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="33">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -2650,8 +2654,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="34">
+    <row r="9" spans="1:18" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="33">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -2714,8 +2718,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="34">
+    <row r="10" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="33">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -2778,8 +2782,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
+    <row r="11" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="33">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -2842,8 +2846,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="34">
+    <row r="12" spans="1:18" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="33">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -2906,8 +2910,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="34">
+    <row r="13" spans="1:18" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="33">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -2970,8 +2974,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="34">
+    <row r="14" spans="1:18" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="33">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -3034,8 +3038,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="34">
+    <row r="15" spans="1:18" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="33">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -3098,8 +3102,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="34">
+    <row r="16" spans="1:18" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="33">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -3163,7 +3167,7 @@
       </c>
     </row>
     <row r="17" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="34">
+      <c r="A17" s="33">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -3227,7 +3231,7 @@
       </c>
     </row>
     <row r="18" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="34">
+      <c r="A18" s="33">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -3290,8 +3294,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="34">
+    <row r="19" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="33">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -3354,8 +3358,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="34">
+    <row r="20" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="33">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -3418,8 +3422,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="34">
+    <row r="21" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="33">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -3482,8 +3486,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="34">
+    <row r="22" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="33">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -3546,8 +3550,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="34">
+    <row r="23" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="33">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -3610,8 +3614,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="34">
+    <row r="24" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="33">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -3674,8 +3678,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="34">
+    <row r="25" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="33">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -3738,8 +3742,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="34">
+    <row r="26" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="33">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -3802,8 +3806,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="34">
+    <row r="27" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="33">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -3866,8 +3870,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="34">
+    <row r="28" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="33">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -3931,7 +3935,7 @@
       </c>
     </row>
     <row r="29" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="34">
+      <c r="A29" s="33">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -3994,8 +3998,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="34">
+    <row r="30" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="33">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -4058,8 +4062,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="34">
+    <row r="31" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="33">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -4122,8 +4126,8 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="34">
+    <row r="32" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="33">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -4186,8 +4190,8 @@
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="34">
+    <row r="33" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="33">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -4250,8 +4254,8 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="34">
+    <row r="34" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="33">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -4314,8 +4318,8 @@
         <v>104</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="34">
+    <row r="35" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="33">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
@@ -4378,8 +4382,8 @@
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="34">
+    <row r="36" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="33">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -4442,8 +4446,8 @@
         <v>104</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="34">
+    <row r="37" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="33">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -4506,8 +4510,8 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="34">
+    <row r="38" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="33">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
@@ -4570,8 +4574,8 @@
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="34">
+    <row r="39" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="33">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -4634,8 +4638,8 @@
         <v>104</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="34">
+    <row r="40" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="33">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -4699,7 +4703,7 @@
       </c>
     </row>
     <row r="41" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="34">
+      <c r="A41" s="33">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
@@ -4762,8 +4766,8 @@
         <v>113</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="34">
+    <row r="42" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="33">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -4826,8 +4830,8 @@
         <v>113</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="34">
+    <row r="43" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="33">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
@@ -4891,7 +4895,7 @@
       </c>
     </row>
     <row r="44" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="34">
+      <c r="A44" s="33">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -4954,8 +4958,8 @@
         <v>119</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="34">
+    <row r="45" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="33">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
@@ -5018,8 +5022,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="34">
+    <row r="46" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="33">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
@@ -5082,8 +5086,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="34">
+    <row r="47" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="33">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
@@ -5146,8 +5150,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="34">
+    <row r="48" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="33">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
@@ -5210,8 +5214,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="34">
+    <row r="49" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="33">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
@@ -5274,8 +5278,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="34">
+    <row r="50" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="33">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -5338,8 +5342,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="34">
+    <row r="51" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="33">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
@@ -5402,8 +5406,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="34">
+    <row r="52" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="33">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
@@ -5466,8 +5470,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="34">
+    <row r="53" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="33">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
@@ -5530,8 +5534,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="34">
+    <row r="54" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="33">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
@@ -5594,8 +5598,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="34">
+    <row r="55" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="33">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
@@ -5658,8 +5662,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="34">
+    <row r="56" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="33">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
@@ -5722,8 +5726,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="34">
+    <row r="57" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="33">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
@@ -5786,8 +5790,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="34">
+    <row r="58" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="33">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -5850,8 +5854,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="34">
+    <row r="59" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="33">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
@@ -5914,8 +5918,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="34">
+    <row r="60" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="33">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
@@ -5978,8 +5982,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="34">
+    <row r="61" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="33">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
@@ -6042,8 +6046,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="34">
+    <row r="62" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="33">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
@@ -6106,8 +6110,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="34">
+    <row r="63" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="33">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
@@ -6170,8 +6174,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="34">
+    <row r="64" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="33">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -6234,8 +6238,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="34">
+    <row r="65" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="33">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
@@ -6298,8 +6302,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="34">
+    <row r="66" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="33">
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -6362,8 +6366,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="34">
+    <row r="67" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="33">
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
@@ -6426,8 +6430,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="34">
+    <row r="68" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="33">
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
@@ -6490,8 +6494,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="34">
+    <row r="69" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="33">
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
@@ -6554,8 +6558,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="34">
+    <row r="70" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="33">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
@@ -6618,8 +6622,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="34">
+    <row r="71" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="33">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -6682,8 +6686,8 @@
         <v>170</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="34">
+    <row r="72" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="33">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
@@ -6746,8 +6750,8 @@
         <v>170</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="34">
+    <row r="73" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="33">
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
@@ -6810,8 +6814,8 @@
         <v>170</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="34">
+    <row r="74" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="33">
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
@@ -6874,8 +6878,8 @@
         <v>174</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="34">
+    <row r="75" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="33">
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
@@ -6938,8 +6942,8 @@
         <v>174</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="34">
+    <row r="76" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="33">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
@@ -7002,8 +7006,8 @@
         <v>174</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="34">
+    <row r="77" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="33">
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
@@ -7066,8 +7070,8 @@
         <v>179</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" s="34">
+    <row r="78" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="33">
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
@@ -7130,8 +7134,8 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="34">
+    <row r="79" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="33">
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
@@ -7194,8 +7198,8 @@
         <v>185</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="34">
+    <row r="80" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="33">
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
@@ -7258,8 +7262,8 @@
         <v>191</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="34">
+    <row r="81" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="33">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
@@ -7322,8 +7326,8 @@
         <v>191</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="34">
+    <row r="82" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="33">
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
@@ -7386,8 +7390,8 @@
         <v>192</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="34">
+    <row r="83" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="33">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
@@ -7450,8 +7454,8 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="34">
+    <row r="84" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="33">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
@@ -7514,8 +7518,8 @@
         <v>193</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="34">
+    <row r="85" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="33">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
@@ -7578,8 +7582,8 @@
         <v>193</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" s="34">
+    <row r="86" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="33">
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
@@ -7642,8 +7646,8 @@
         <v>193</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="34">
+    <row r="87" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="33">
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
@@ -7706,8 +7710,8 @@
         <v>193</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="34">
+    <row r="88" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="33">
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
@@ -7770,8 +7774,8 @@
         <v>193</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="34">
+    <row r="89" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="33">
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
@@ -7834,8 +7838,8 @@
         <v>213</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="34">
+    <row r="90" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="33">
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
@@ -7898,8 +7902,8 @@
         <v>213</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="34">
+    <row r="91" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="33">
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
@@ -7962,8 +7966,8 @@
         <v>223</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="34">
+    <row r="92" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="33">
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
@@ -8026,8 +8030,8 @@
         <v>224</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="34">
+    <row r="93" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="33">
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
@@ -8090,8 +8094,8 @@
         <v>227</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" s="34">
+    <row r="94" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="33">
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
@@ -8154,8 +8158,8 @@
         <v>233</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="34">
+    <row r="95" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="33">
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
@@ -8218,8 +8222,8 @@
         <v>238</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="34">
+    <row r="96" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="33">
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
@@ -8282,8 +8286,8 @@
         <v>243</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="34">
+    <row r="97" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="33">
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
@@ -8346,8 +8350,8 @@
         <v>244</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="34">
+    <row r="98" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="33">
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
@@ -8410,8 +8414,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="34">
+    <row r="99" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="33">
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
@@ -8474,8 +8478,8 @@
         <v>254</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="34">
+    <row r="100" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="33">
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
@@ -8538,8 +8542,8 @@
         <v>263</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="34">
+    <row r="101" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="33">
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
@@ -8602,8 +8606,8 @@
         <v>263</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" s="34">
+    <row r="102" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="33">
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
@@ -8666,8 +8670,8 @@
         <v>263</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="34">
+    <row r="103" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="33">
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
@@ -8730,8 +8734,8 @@
         <v>263</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="34">
+    <row r="104" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="33">
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
@@ -8794,1032 +8798,1032 @@
         <v>266</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="34">
+    <row r="105" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="33">
         <v>104</v>
       </c>
-      <c r="B105" s="34" t="s">
+      <c r="B105" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C105" s="34" t="s">
+      <c r="C105" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D105" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E105" s="32" t="s">
+      <c r="D105" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E105" s="31" t="s">
         <v>441</v>
       </c>
-      <c r="F105" s="32" t="s">
+      <c r="F105" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="G105" s="32" t="s">
+      <c r="G105" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="H105" s="34" t="s">
+      <c r="H105" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I105" s="34" t="s">
+      <c r="I105" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="J105" s="34" t="str">
+      <c r="J105" s="33" t="str">
         <f t="shared" si="32"/>
         <v>02</v>
       </c>
-      <c r="K105" s="34" t="str">
+      <c r="K105" s="33" t="str">
         <f t="shared" si="33"/>
         <v>53</v>
       </c>
-      <c r="L105" s="34" t="str">
+      <c r="L105" s="33" t="str">
         <f t="shared" si="34"/>
         <v>22</v>
       </c>
-      <c r="M105" s="34" t="str">
+      <c r="M105" s="33" t="str">
         <f t="shared" si="35"/>
         <v>41</v>
       </c>
-      <c r="N105" s="34" t="str">
+      <c r="N105" s="33" t="str">
         <f t="shared" si="36"/>
         <v>13</v>
       </c>
-      <c r="O105" s="34" t="str">
+      <c r="O105" s="33" t="str">
         <f t="shared" si="37"/>
         <v>46</v>
       </c>
-      <c r="P105" s="33">
+      <c r="P105" s="32">
         <f t="shared" si="38"/>
         <v>-2.8894444444444445</v>
       </c>
-      <c r="Q105" s="33">
+      <c r="Q105" s="32">
         <f t="shared" si="39"/>
         <v>-41.229444444444447</v>
       </c>
-      <c r="R105" s="35" t="s">
+      <c r="R105" s="36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="34">
+    <row r="106" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="33">
         <v>105</v>
       </c>
-      <c r="B106" s="34" t="s">
+      <c r="B106" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C106" s="34" t="s">
+      <c r="C106" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D106" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E106" s="32" t="s">
+      <c r="D106" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E106" s="31" t="s">
         <v>442</v>
       </c>
-      <c r="F106" s="32" t="s">
+      <c r="F106" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="G106" s="32" t="s">
+      <c r="G106" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="H106" s="34" t="s">
+      <c r="H106" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I106" s="34" t="s">
+      <c r="I106" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="J106" s="34" t="str">
+      <c r="J106" s="33" t="str">
         <f t="shared" si="32"/>
         <v>04</v>
       </c>
-      <c r="K106" s="34" t="str">
+      <c r="K106" s="33" t="str">
         <f t="shared" si="33"/>
         <v>06</v>
       </c>
-      <c r="L106" s="34" t="str">
+      <c r="L106" s="33" t="str">
         <f t="shared" si="34"/>
         <v>06</v>
       </c>
-      <c r="M106" s="34" t="str">
+      <c r="M106" s="33" t="str">
         <f t="shared" si="35"/>
         <v>38</v>
       </c>
-      <c r="N106" s="34" t="str">
+      <c r="N106" s="33" t="str">
         <f t="shared" si="36"/>
         <v>08</v>
       </c>
-      <c r="O106" s="34" t="str">
+      <c r="O106" s="33" t="str">
         <f t="shared" si="37"/>
         <v>56</v>
       </c>
-      <c r="P106" s="33">
+      <c r="P106" s="32">
         <f t="shared" si="38"/>
         <v>-4.1016666666666666</v>
       </c>
-      <c r="Q106" s="33">
+      <c r="Q106" s="32">
         <f t="shared" si="39"/>
         <v>-38.148888888888891</v>
       </c>
-      <c r="R106" s="35" t="s">
+      <c r="R106" s="36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="34">
+    <row r="107" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="33">
         <v>106</v>
       </c>
-      <c r="B107" s="34" t="s">
+      <c r="B107" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C107" s="34" t="s">
+      <c r="C107" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D107" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E107" s="32" t="s">
+      <c r="D107" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E107" s="31" t="s">
         <v>443</v>
       </c>
-      <c r="F107" s="32" t="s">
+      <c r="F107" s="31" t="s">
         <v>447</v>
       </c>
-      <c r="G107" s="32" t="s">
+      <c r="G107" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="H107" s="34" t="s">
+      <c r="H107" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I107" s="34" t="s">
+      <c r="I107" s="33" t="s">
         <v>444</v>
       </c>
-      <c r="J107" s="34" t="str">
+      <c r="J107" s="33" t="str">
         <f t="shared" si="32"/>
         <v>04</v>
       </c>
-      <c r="K107" s="34" t="str">
+      <c r="K107" s="33" t="str">
         <f t="shared" si="33"/>
         <v>53</v>
       </c>
-      <c r="L107" s="34" t="str">
+      <c r="L107" s="33" t="str">
         <f t="shared" si="34"/>
         <v>26</v>
       </c>
-      <c r="M107" s="34" t="str">
+      <c r="M107" s="33" t="str">
         <f t="shared" si="35"/>
         <v>37</v>
       </c>
-      <c r="N107" s="34" t="str">
+      <c r="N107" s="33" t="str">
         <f t="shared" si="36"/>
         <v>14</v>
       </c>
-      <c r="O107" s="34" t="str">
+      <c r="O107" s="33" t="str">
         <f t="shared" si="37"/>
         <v>37</v>
       </c>
-      <c r="P107" s="33">
+      <c r="P107" s="32">
         <f t="shared" si="38"/>
         <v>-4.8905555555555553</v>
       </c>
-      <c r="Q107" s="33">
+      <c r="Q107" s="32">
         <f t="shared" si="39"/>
         <v>-37.243611111111115</v>
       </c>
-      <c r="R107" s="35" t="s">
+      <c r="R107" s="36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="34">
+    <row r="108" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="33">
         <v>107</v>
       </c>
-      <c r="B108" s="34" t="s">
+      <c r="B108" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C108" s="34" t="s">
+      <c r="C108" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D108" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E108" s="32" t="s">
+      <c r="D108" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E108" s="31" t="s">
         <v>448</v>
       </c>
-      <c r="F108" s="32" t="s">
+      <c r="F108" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="G108" s="32" t="s">
+      <c r="G108" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="H108" s="34" t="s">
+      <c r="H108" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I108" s="34" t="s">
+      <c r="I108" s="33" t="s">
         <v>444</v>
       </c>
-      <c r="J108" s="34" t="str">
+      <c r="J108" s="33" t="str">
         <f t="shared" si="32"/>
         <v>05</v>
       </c>
-      <c r="K108" s="34" t="str">
+      <c r="K108" s="33" t="str">
         <f t="shared" si="33"/>
         <v>12</v>
       </c>
-      <c r="L108" s="34" t="str">
+      <c r="L108" s="33" t="str">
         <f t="shared" si="34"/>
         <v>06</v>
       </c>
-      <c r="M108" s="34" t="str">
+      <c r="M108" s="33" t="str">
         <f t="shared" si="35"/>
         <v>35</v>
       </c>
-      <c r="N108" s="34" t="str">
+      <c r="N108" s="33" t="str">
         <f t="shared" si="36"/>
         <v>27</v>
       </c>
-      <c r="O108" s="34" t="str">
+      <c r="O108" s="33" t="str">
         <f t="shared" si="37"/>
         <v>27</v>
       </c>
-      <c r="P108" s="33">
+      <c r="P108" s="32">
         <f t="shared" si="38"/>
         <v>-5.2016666666666662</v>
       </c>
-      <c r="Q108" s="33">
+      <c r="Q108" s="32">
         <f t="shared" si="39"/>
         <v>-35.457500000000003</v>
       </c>
-      <c r="R108" s="35" t="s">
+      <c r="R108" s="36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="34">
+    <row r="109" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="33">
         <v>108</v>
       </c>
-      <c r="B109" s="34" t="s">
+      <c r="B109" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C109" s="34" t="s">
+      <c r="C109" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D109" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E109" s="32" t="s">
+      <c r="D109" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E109" s="31" t="s">
         <v>450</v>
       </c>
-      <c r="F109" s="32" t="s">
+      <c r="F109" s="31" t="s">
         <v>452</v>
       </c>
-      <c r="G109" s="32" t="s">
+      <c r="G109" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="H109" s="34" t="s">
+      <c r="H109" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I109" s="34" t="s">
+      <c r="I109" s="33" t="s">
         <v>445</v>
       </c>
-      <c r="J109" s="34" t="str">
+      <c r="J109" s="33" t="str">
         <f t="shared" si="32"/>
         <v>06</v>
       </c>
-      <c r="K109" s="34" t="str">
+      <c r="K109" s="33" t="str">
         <f t="shared" si="33"/>
         <v>30</v>
       </c>
-      <c r="L109" s="34" t="str">
+      <c r="L109" s="33" t="str">
         <f t="shared" si="34"/>
         <v>11</v>
       </c>
-      <c r="M109" s="34" t="str">
+      <c r="M109" s="33" t="str">
         <f t="shared" si="35"/>
         <v>34</v>
       </c>
-      <c r="N109" s="34" t="str">
+      <c r="N109" s="33" t="str">
         <f t="shared" si="36"/>
         <v>57</v>
       </c>
-      <c r="O109" s="34" t="str">
+      <c r="O109" s="33" t="str">
         <f t="shared" si="37"/>
         <v>30</v>
       </c>
-      <c r="P109" s="33">
+      <c r="P109" s="32">
         <f t="shared" si="38"/>
         <v>-6.5030555555555551</v>
       </c>
-      <c r="Q109" s="33">
+      <c r="Q109" s="32">
         <f t="shared" si="39"/>
         <v>-34.958333333333336</v>
       </c>
-      <c r="R109" s="35" t="s">
+      <c r="R109" s="36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="34">
+    <row r="110" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="33">
         <v>109</v>
       </c>
-      <c r="B110" s="34" t="s">
+      <c r="B110" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C110" s="34" t="s">
+      <c r="C110" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D110" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E110" s="32" t="s">
+      <c r="D110" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E110" s="31" t="s">
         <v>451</v>
       </c>
-      <c r="F110" s="32" t="s">
+      <c r="F110" s="31" t="s">
         <v>453</v>
       </c>
-      <c r="G110" s="32" t="s">
+      <c r="G110" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="H110" s="34" t="s">
+      <c r="H110" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I110" s="34" t="s">
+      <c r="I110" s="33" t="s">
         <v>445</v>
       </c>
-      <c r="J110" s="34" t="str">
+      <c r="J110" s="33" t="str">
         <f t="shared" si="32"/>
         <v>06</v>
       </c>
-      <c r="K110" s="34" t="str">
+      <c r="K110" s="33" t="str">
         <f t="shared" si="33"/>
         <v>57</v>
       </c>
-      <c r="L110" s="34" t="str">
+      <c r="L110" s="33" t="str">
         <f t="shared" si="34"/>
         <v>57</v>
       </c>
-      <c r="M110" s="34" t="str">
+      <c r="M110" s="33" t="str">
         <f t="shared" si="35"/>
         <v>34</v>
       </c>
-      <c r="N110" s="34" t="str">
+      <c r="N110" s="33" t="str">
         <f t="shared" si="36"/>
         <v>51</v>
       </c>
-      <c r="O110" s="34" t="str">
+      <c r="O110" s="33" t="str">
         <f t="shared" si="37"/>
         <v>22</v>
       </c>
-      <c r="P110" s="33">
+      <c r="P110" s="32">
         <f t="shared" si="38"/>
         <v>-6.9658333333333333</v>
       </c>
-      <c r="Q110" s="33">
+      <c r="Q110" s="32">
         <f t="shared" si="39"/>
         <v>-34.856111111111112</v>
       </c>
-      <c r="R110" s="35" t="s">
+      <c r="R110" s="36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="34">
+    <row r="111" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="33">
         <v>110</v>
       </c>
-      <c r="B111" s="34" t="s">
+      <c r="B111" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C111" s="34" t="s">
+      <c r="C111" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D111" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E111" s="32" t="s">
+      <c r="D111" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E111" s="31" t="s">
         <v>454</v>
       </c>
-      <c r="F111" s="32" t="s">
+      <c r="F111" s="31" t="s">
         <v>457</v>
       </c>
-      <c r="G111" s="32" t="s">
+      <c r="G111" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="H111" s="34" t="s">
+      <c r="H111" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I111" s="34" t="s">
+      <c r="I111" s="33" t="s">
         <v>446</v>
       </c>
-      <c r="J111" s="34" t="str">
+      <c r="J111" s="33" t="str">
         <f t="shared" si="32"/>
         <v>07</v>
       </c>
-      <c r="K111" s="34" t="str">
+      <c r="K111" s="33" t="str">
         <f t="shared" si="33"/>
         <v>33</v>
       </c>
-      <c r="L111" s="34" t="str">
+      <c r="L111" s="33" t="str">
         <f t="shared" si="34"/>
         <v>07</v>
       </c>
-      <c r="M111" s="34" t="str">
+      <c r="M111" s="33" t="str">
         <f t="shared" si="35"/>
         <v>34</v>
       </c>
-      <c r="N111" s="34" t="str">
+      <c r="N111" s="33" t="str">
         <f t="shared" si="36"/>
         <v>50</v>
       </c>
-      <c r="O111" s="34" t="str">
+      <c r="O111" s="33" t="str">
         <f t="shared" si="37"/>
         <v>39</v>
       </c>
-      <c r="P111" s="33">
+      <c r="P111" s="32">
         <f t="shared" si="38"/>
         <v>-7.5519444444444446</v>
       </c>
-      <c r="Q111" s="33">
+      <c r="Q111" s="32">
         <f t="shared" si="39"/>
         <v>-34.844166666666666</v>
       </c>
-      <c r="R111" s="35" t="s">
+      <c r="R111" s="36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="34">
+    <row r="112" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="33">
         <v>111</v>
       </c>
-      <c r="B112" s="34" t="s">
+      <c r="B112" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C112" s="34" t="s">
+      <c r="C112" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D112" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E112" s="32" t="s">
+      <c r="D112" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E112" s="31" t="s">
         <v>455</v>
       </c>
-      <c r="F112" s="32" t="s">
+      <c r="F112" s="31" t="s">
         <v>456</v>
       </c>
-      <c r="G112" s="32" t="s">
+      <c r="G112" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="H112" s="34" t="s">
+      <c r="H112" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I112" s="34" t="s">
+      <c r="I112" s="33" t="s">
         <v>446</v>
       </c>
-      <c r="J112" s="34" t="str">
+      <c r="J112" s="33" t="str">
         <f t="shared" si="32"/>
         <v>08</v>
       </c>
-      <c r="K112" s="34" t="str">
+      <c r="K112" s="33" t="str">
         <f t="shared" si="33"/>
         <v>02</v>
       </c>
-      <c r="L112" s="34" t="str">
+      <c r="L112" s="33" t="str">
         <f t="shared" si="34"/>
         <v>54</v>
       </c>
-      <c r="M112" s="34" t="str">
+      <c r="M112" s="33" t="str">
         <f t="shared" si="35"/>
         <v>34</v>
       </c>
-      <c r="N112" s="34" t="str">
+      <c r="N112" s="33" t="str">
         <f t="shared" si="36"/>
         <v>52</v>
       </c>
-      <c r="O112" s="34" t="str">
+      <c r="O112" s="33" t="str">
         <f t="shared" si="37"/>
         <v>42</v>
       </c>
-      <c r="P112" s="33">
+      <c r="P112" s="32">
         <f t="shared" si="38"/>
         <v>-8.0483333333333338</v>
       </c>
-      <c r="Q112" s="33">
+      <c r="Q112" s="32">
         <f t="shared" si="39"/>
         <v>-34.87833333333333</v>
       </c>
-      <c r="R112" s="35" t="s">
+      <c r="R112" s="36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="34">
+    <row r="113" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="33">
         <v>112</v>
       </c>
-      <c r="B113" s="34" t="s">
+      <c r="B113" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C113" s="34" t="s">
+      <c r="C113" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D113" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E113" s="32" t="s">
+      <c r="D113" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E113" s="31" t="s">
         <v>441</v>
       </c>
-      <c r="F113" s="32" t="s">
+      <c r="F113" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="G113" s="32" t="s">
+      <c r="G113" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="H113" s="34" t="s">
+      <c r="H113" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I113" s="34" t="s">
+      <c r="I113" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="J113" s="34" t="str">
+      <c r="J113" s="33" t="str">
         <f t="shared" si="32"/>
         <v>02</v>
       </c>
-      <c r="K113" s="34" t="str">
+      <c r="K113" s="33" t="str">
         <f t="shared" si="33"/>
         <v>53</v>
       </c>
-      <c r="L113" s="34" t="str">
+      <c r="L113" s="33" t="str">
         <f t="shared" si="34"/>
         <v>22</v>
       </c>
-      <c r="M113" s="34" t="str">
+      <c r="M113" s="33" t="str">
         <f t="shared" si="35"/>
         <v>41</v>
       </c>
-      <c r="N113" s="34" t="str">
+      <c r="N113" s="33" t="str">
         <f t="shared" si="36"/>
         <v>13</v>
       </c>
-      <c r="O113" s="34" t="str">
+      <c r="O113" s="33" t="str">
         <f t="shared" si="37"/>
         <v>46</v>
       </c>
-      <c r="P113" s="33">
+      <c r="P113" s="32">
         <f t="shared" si="38"/>
         <v>-2.8894444444444445</v>
       </c>
-      <c r="Q113" s="33">
+      <c r="Q113" s="32">
         <f t="shared" si="39"/>
         <v>-41.229444444444447</v>
       </c>
-      <c r="R113" s="35" t="s">
+      <c r="R113" s="36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="34">
+    <row r="114" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="33">
         <v>113</v>
       </c>
-      <c r="B114" s="34" t="s">
+      <c r="B114" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C114" s="34" t="s">
+      <c r="C114" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D114" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E114" s="32" t="s">
+      <c r="D114" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E114" s="31" t="s">
         <v>442</v>
       </c>
-      <c r="F114" s="32" t="s">
+      <c r="F114" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="G114" s="32" t="s">
+      <c r="G114" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="H114" s="34" t="s">
+      <c r="H114" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I114" s="34" t="s">
+      <c r="I114" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="J114" s="34" t="str">
+      <c r="J114" s="33" t="str">
         <f t="shared" si="32"/>
         <v>04</v>
       </c>
-      <c r="K114" s="34" t="str">
+      <c r="K114" s="33" t="str">
         <f t="shared" si="33"/>
         <v>06</v>
       </c>
-      <c r="L114" s="34" t="str">
+      <c r="L114" s="33" t="str">
         <f t="shared" si="34"/>
         <v>06</v>
       </c>
-      <c r="M114" s="34" t="str">
+      <c r="M114" s="33" t="str">
         <f t="shared" si="35"/>
         <v>38</v>
       </c>
-      <c r="N114" s="34" t="str">
+      <c r="N114" s="33" t="str">
         <f t="shared" si="36"/>
         <v>08</v>
       </c>
-      <c r="O114" s="34" t="str">
+      <c r="O114" s="33" t="str">
         <f t="shared" si="37"/>
         <v>56</v>
       </c>
-      <c r="P114" s="33">
+      <c r="P114" s="32">
         <f t="shared" si="38"/>
         <v>-4.1016666666666666</v>
       </c>
-      <c r="Q114" s="33">
+      <c r="Q114" s="32">
         <f t="shared" si="39"/>
         <v>-38.148888888888891</v>
       </c>
-      <c r="R114" s="35" t="s">
+      <c r="R114" s="36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="34">
+    <row r="115" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="33">
         <v>114</v>
       </c>
-      <c r="B115" s="34" t="s">
+      <c r="B115" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C115" s="34" t="s">
+      <c r="C115" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D115" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E115" s="32" t="s">
+      <c r="D115" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E115" s="31" t="s">
         <v>443</v>
       </c>
-      <c r="F115" s="32" t="s">
+      <c r="F115" s="31" t="s">
         <v>447</v>
       </c>
-      <c r="G115" s="32" t="s">
+      <c r="G115" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="H115" s="34" t="s">
+      <c r="H115" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I115" s="34" t="s">
+      <c r="I115" s="33" t="s">
         <v>444</v>
       </c>
-      <c r="J115" s="34" t="str">
+      <c r="J115" s="33" t="str">
         <f t="shared" si="32"/>
         <v>04</v>
       </c>
-      <c r="K115" s="34" t="str">
+      <c r="K115" s="33" t="str">
         <f t="shared" si="33"/>
         <v>53</v>
       </c>
-      <c r="L115" s="34" t="str">
+      <c r="L115" s="33" t="str">
         <f t="shared" si="34"/>
         <v>26</v>
       </c>
-      <c r="M115" s="34" t="str">
+      <c r="M115" s="33" t="str">
         <f t="shared" si="35"/>
         <v>37</v>
       </c>
-      <c r="N115" s="34" t="str">
+      <c r="N115" s="33" t="str">
         <f t="shared" si="36"/>
         <v>14</v>
       </c>
-      <c r="O115" s="34" t="str">
+      <c r="O115" s="33" t="str">
         <f t="shared" si="37"/>
         <v>37</v>
       </c>
-      <c r="P115" s="33">
+      <c r="P115" s="32">
         <f t="shared" si="38"/>
         <v>-4.8905555555555553</v>
       </c>
-      <c r="Q115" s="33">
+      <c r="Q115" s="32">
         <f t="shared" si="39"/>
         <v>-37.243611111111115</v>
       </c>
-      <c r="R115" s="35" t="s">
+      <c r="R115" s="36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="34">
+    <row r="116" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="33">
         <v>115</v>
       </c>
-      <c r="B116" s="34" t="s">
+      <c r="B116" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C116" s="34" t="s">
+      <c r="C116" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D116" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E116" s="32" t="s">
+      <c r="D116" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E116" s="31" t="s">
         <v>448</v>
       </c>
-      <c r="F116" s="32" t="s">
+      <c r="F116" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="G116" s="32" t="s">
+      <c r="G116" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="H116" s="34" t="s">
+      <c r="H116" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I116" s="34" t="s">
+      <c r="I116" s="33" t="s">
         <v>444</v>
       </c>
-      <c r="J116" s="34" t="str">
+      <c r="J116" s="33" t="str">
         <f t="shared" si="32"/>
         <v>05</v>
       </c>
-      <c r="K116" s="34" t="str">
+      <c r="K116" s="33" t="str">
         <f t="shared" si="33"/>
         <v>12</v>
       </c>
-      <c r="L116" s="34" t="str">
+      <c r="L116" s="33" t="str">
         <f t="shared" si="34"/>
         <v>06</v>
       </c>
-      <c r="M116" s="34" t="str">
+      <c r="M116" s="33" t="str">
         <f t="shared" si="35"/>
         <v>35</v>
       </c>
-      <c r="N116" s="34" t="str">
+      <c r="N116" s="33" t="str">
         <f t="shared" si="36"/>
         <v>27</v>
       </c>
-      <c r="O116" s="34" t="str">
+      <c r="O116" s="33" t="str">
         <f t="shared" si="37"/>
         <v>27</v>
       </c>
-      <c r="P116" s="33">
+      <c r="P116" s="32">
         <f t="shared" si="38"/>
         <v>-5.2016666666666662</v>
       </c>
-      <c r="Q116" s="33">
+      <c r="Q116" s="32">
         <f t="shared" si="39"/>
         <v>-35.457500000000003</v>
       </c>
-      <c r="R116" s="35" t="s">
+      <c r="R116" s="36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="34">
+    <row r="117" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="33">
         <v>116</v>
       </c>
-      <c r="B117" s="34" t="s">
+      <c r="B117" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C117" s="34" t="s">
+      <c r="C117" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D117" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E117" s="32" t="s">
+      <c r="D117" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E117" s="31" t="s">
         <v>450</v>
       </c>
-      <c r="F117" s="32" t="s">
+      <c r="F117" s="31" t="s">
         <v>452</v>
       </c>
-      <c r="G117" s="32" t="s">
+      <c r="G117" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="H117" s="34" t="s">
+      <c r="H117" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I117" s="34" t="s">
+      <c r="I117" s="33" t="s">
         <v>445</v>
       </c>
-      <c r="J117" s="34" t="str">
+      <c r="J117" s="33" t="str">
         <f t="shared" si="32"/>
         <v>06</v>
       </c>
-      <c r="K117" s="34" t="str">
+      <c r="K117" s="33" t="str">
         <f t="shared" si="33"/>
         <v>30</v>
       </c>
-      <c r="L117" s="34" t="str">
+      <c r="L117" s="33" t="str">
         <f t="shared" si="34"/>
         <v>11</v>
       </c>
-      <c r="M117" s="34" t="str">
+      <c r="M117" s="33" t="str">
         <f t="shared" si="35"/>
         <v>34</v>
       </c>
-      <c r="N117" s="34" t="str">
+      <c r="N117" s="33" t="str">
         <f t="shared" si="36"/>
         <v>57</v>
       </c>
-      <c r="O117" s="34" t="str">
+      <c r="O117" s="33" t="str">
         <f t="shared" si="37"/>
         <v>30</v>
       </c>
-      <c r="P117" s="33">
+      <c r="P117" s="32">
         <f t="shared" si="38"/>
         <v>-6.5030555555555551</v>
       </c>
-      <c r="Q117" s="33">
+      <c r="Q117" s="32">
         <f t="shared" si="39"/>
         <v>-34.958333333333336</v>
       </c>
-      <c r="R117" s="35" t="s">
+      <c r="R117" s="36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="34">
+    <row r="118" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="33">
         <v>117</v>
       </c>
-      <c r="B118" s="34" t="s">
+      <c r="B118" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C118" s="34" t="s">
+      <c r="C118" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D118" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E118" s="32" t="s">
+      <c r="D118" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E118" s="31" t="s">
         <v>451</v>
       </c>
-      <c r="F118" s="32" t="s">
+      <c r="F118" s="31" t="s">
         <v>453</v>
       </c>
-      <c r="G118" s="32" t="s">
+      <c r="G118" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="H118" s="34" t="s">
+      <c r="H118" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I118" s="34" t="s">
+      <c r="I118" s="33" t="s">
         <v>445</v>
       </c>
-      <c r="J118" s="34" t="str">
+      <c r="J118" s="33" t="str">
         <f t="shared" si="32"/>
         <v>06</v>
       </c>
-      <c r="K118" s="34" t="str">
+      <c r="K118" s="33" t="str">
         <f t="shared" si="33"/>
         <v>57</v>
       </c>
-      <c r="L118" s="34" t="str">
+      <c r="L118" s="33" t="str">
         <f t="shared" si="34"/>
         <v>57</v>
       </c>
-      <c r="M118" s="34" t="str">
+      <c r="M118" s="33" t="str">
         <f t="shared" si="35"/>
         <v>34</v>
       </c>
-      <c r="N118" s="34" t="str">
+      <c r="N118" s="33" t="str">
         <f t="shared" si="36"/>
         <v>51</v>
       </c>
-      <c r="O118" s="34" t="str">
+      <c r="O118" s="33" t="str">
         <f t="shared" si="37"/>
         <v>22</v>
       </c>
-      <c r="P118" s="33">
+      <c r="P118" s="32">
         <f t="shared" si="38"/>
         <v>-6.9658333333333333</v>
       </c>
-      <c r="Q118" s="33">
+      <c r="Q118" s="32">
         <f t="shared" si="39"/>
         <v>-34.856111111111112</v>
       </c>
-      <c r="R118" s="35" t="s">
+      <c r="R118" s="36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="34">
+    <row r="119" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="33">
         <v>118</v>
       </c>
-      <c r="B119" s="34" t="s">
+      <c r="B119" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C119" s="34" t="s">
+      <c r="C119" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D119" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E119" s="32" t="s">
+      <c r="D119" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E119" s="31" t="s">
         <v>454</v>
       </c>
-      <c r="F119" s="32" t="s">
+      <c r="F119" s="31" t="s">
         <v>457</v>
       </c>
-      <c r="G119" s="32" t="s">
+      <c r="G119" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="H119" s="34" t="s">
+      <c r="H119" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I119" s="34" t="s">
+      <c r="I119" s="33" t="s">
         <v>446</v>
       </c>
-      <c r="J119" s="34" t="str">
+      <c r="J119" s="33" t="str">
         <f t="shared" si="32"/>
         <v>07</v>
       </c>
-      <c r="K119" s="34" t="str">
+      <c r="K119" s="33" t="str">
         <f t="shared" si="33"/>
         <v>33</v>
       </c>
-      <c r="L119" s="34" t="str">
+      <c r="L119" s="33" t="str">
         <f t="shared" si="34"/>
         <v>07</v>
       </c>
-      <c r="M119" s="34" t="str">
+      <c r="M119" s="33" t="str">
         <f t="shared" si="35"/>
         <v>34</v>
       </c>
-      <c r="N119" s="34" t="str">
+      <c r="N119" s="33" t="str">
         <f t="shared" si="36"/>
         <v>50</v>
       </c>
-      <c r="O119" s="34" t="str">
+      <c r="O119" s="33" t="str">
         <f t="shared" si="37"/>
         <v>39</v>
       </c>
-      <c r="P119" s="33">
+      <c r="P119" s="32">
         <f t="shared" si="38"/>
         <v>-7.5519444444444446</v>
       </c>
-      <c r="Q119" s="33">
+      <c r="Q119" s="32">
         <f t="shared" si="39"/>
         <v>-34.844166666666666</v>
       </c>
-      <c r="R119" s="35" t="s">
+      <c r="R119" s="36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A120" s="34">
+    <row r="120" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="33">
         <v>119</v>
       </c>
-      <c r="B120" s="34" t="s">
+      <c r="B120" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C120" s="34" t="s">
+      <c r="C120" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D120" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E120" s="32" t="s">
+      <c r="D120" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E120" s="31" t="s">
         <v>455</v>
       </c>
-      <c r="F120" s="32" t="s">
+      <c r="F120" s="31" t="s">
         <v>456</v>
       </c>
-      <c r="G120" s="32" t="s">
+      <c r="G120" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="H120" s="34" t="s">
+      <c r="H120" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I120" s="34" t="s">
+      <c r="I120" s="33" t="s">
         <v>446</v>
       </c>
-      <c r="J120" s="34" t="str">
+      <c r="J120" s="33" t="str">
         <f t="shared" si="32"/>
         <v>08</v>
       </c>
-      <c r="K120" s="34" t="str">
+      <c r="K120" s="33" t="str">
         <f t="shared" si="33"/>
         <v>02</v>
       </c>
-      <c r="L120" s="34" t="str">
+      <c r="L120" s="33" t="str">
         <f t="shared" si="34"/>
         <v>54</v>
       </c>
-      <c r="M120" s="34" t="str">
+      <c r="M120" s="33" t="str">
         <f t="shared" si="35"/>
         <v>34</v>
       </c>
-      <c r="N120" s="34" t="str">
+      <c r="N120" s="33" t="str">
         <f t="shared" si="36"/>
         <v>52</v>
       </c>
-      <c r="O120" s="34" t="str">
+      <c r="O120" s="33" t="str">
         <f t="shared" si="37"/>
         <v>42</v>
       </c>
-      <c r="P120" s="33">
+      <c r="P120" s="32">
         <f t="shared" si="38"/>
         <v>-8.0483333333333338</v>
       </c>
-      <c r="Q120" s="33">
+      <c r="Q120" s="32">
         <f t="shared" si="39"/>
         <v>-34.87833333333333</v>
       </c>
-      <c r="R120" s="35" t="s">
+      <c r="R120" s="36" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="121" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A121" s="34">
+      <c r="A121" s="33">
         <v>120</v>
       </c>
       <c r="B121" s="3" t="s">
@@ -9837,13 +9841,13 @@
       <c r="F121" t="s">
         <v>315</v>
       </c>
-      <c r="G121" s="3" t="s">
+      <c r="G121" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="H121" s="3" t="s">
+      <c r="H121" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I121" s="3" t="s">
+      <c r="I121" s="33" t="s">
         <v>309</v>
       </c>
       <c r="J121" s="3" t="str">
@@ -9883,7 +9887,7 @@
       </c>
     </row>
     <row r="122" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A122" s="34">
+      <c r="A122" s="33">
         <v>121</v>
       </c>
       <c r="B122" s="3" t="s">
@@ -9901,13 +9905,13 @@
       <c r="F122" t="s">
         <v>316</v>
       </c>
-      <c r="G122" s="3" t="s">
+      <c r="G122" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="H122" s="3" t="s">
+      <c r="H122" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I122" s="3" t="s">
+      <c r="I122" s="33" t="s">
         <v>309</v>
       </c>
       <c r="J122" s="3" t="str">
@@ -9947,7 +9951,7 @@
       </c>
     </row>
     <row r="123" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A123" s="34">
+      <c r="A123" s="33">
         <v>122</v>
       </c>
       <c r="B123" s="3" t="s">
@@ -9965,13 +9969,13 @@
       <c r="F123" t="s">
         <v>317</v>
       </c>
-      <c r="G123" s="3" t="s">
+      <c r="G123" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="H123" s="3" t="s">
+      <c r="H123" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I123" s="3" t="s">
+      <c r="I123" s="33" t="s">
         <v>309</v>
       </c>
       <c r="J123" s="3" t="str">
@@ -10011,7 +10015,7 @@
       </c>
     </row>
     <row r="124" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="34">
+      <c r="A124" s="33">
         <v>123</v>
       </c>
       <c r="B124" s="3" t="s">
@@ -10029,13 +10033,13 @@
       <c r="F124" t="s">
         <v>318</v>
       </c>
-      <c r="G124" s="3" t="s">
+      <c r="G124" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="H124" s="3" t="s">
+      <c r="H124" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I124" s="3" t="s">
+      <c r="I124" s="33" t="s">
         <v>309</v>
       </c>
       <c r="J124" s="3" t="str">
@@ -10075,7 +10079,7 @@
       </c>
     </row>
     <row r="125" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A125" s="34">
+      <c r="A125" s="33">
         <v>124</v>
       </c>
       <c r="B125" s="3" t="s">
@@ -10093,13 +10097,13 @@
       <c r="F125" t="s">
         <v>319</v>
       </c>
-      <c r="G125" s="3" t="s">
+      <c r="G125" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="H125" s="3" t="s">
+      <c r="H125" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I125" s="3" t="s">
+      <c r="I125" s="33" t="s">
         <v>309</v>
       </c>
       <c r="J125" s="3" t="str">
@@ -10138,8 +10142,8 @@
         <v>320</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A126" s="34">
+    <row r="126" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="33">
         <v>125</v>
       </c>
       <c r="B126" s="3" t="s">
@@ -10157,13 +10161,13 @@
       <c r="F126" t="s">
         <v>326</v>
       </c>
-      <c r="G126" s="3" t="s">
+      <c r="G126" s="33" t="s">
         <v>321</v>
       </c>
-      <c r="H126" s="3" t="s">
+      <c r="H126" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I126" s="3" t="s">
+      <c r="I126" s="33" t="s">
         <v>322</v>
       </c>
       <c r="J126" s="3" t="str">
@@ -10202,8 +10206,8 @@
         <v>328</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A127" s="34">
+    <row r="127" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="33">
         <v>126</v>
       </c>
       <c r="B127" s="3" t="s">
@@ -10221,13 +10225,13 @@
       <c r="F127" t="s">
         <v>327</v>
       </c>
-      <c r="G127" s="3" t="s">
+      <c r="G127" s="33" t="s">
         <v>321</v>
       </c>
-      <c r="H127" s="3" t="s">
+      <c r="H127" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I127" s="3" t="s">
+      <c r="I127" s="33" t="s">
         <v>323</v>
       </c>
       <c r="J127" s="3" t="str">
@@ -10266,8 +10270,8 @@
         <v>328</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A128" s="34">
+    <row r="128" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="33">
         <v>127</v>
       </c>
       <c r="B128" s="3" t="s">
@@ -10285,13 +10289,13 @@
       <c r="F128" t="s">
         <v>326</v>
       </c>
-      <c r="G128" s="3" t="s">
+      <c r="G128" s="33" t="s">
         <v>321</v>
       </c>
-      <c r="H128" s="3" t="s">
+      <c r="H128" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I128" s="3" t="s">
+      <c r="I128" s="33" t="s">
         <v>322</v>
       </c>
       <c r="J128" s="3" t="str">
@@ -10330,8 +10334,8 @@
         <v>328</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A129" s="34">
+    <row r="129" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="33">
         <v>128</v>
       </c>
       <c r="B129" s="3" t="s">
@@ -10349,13 +10353,13 @@
       <c r="F129" t="s">
         <v>327</v>
       </c>
-      <c r="G129" s="3" t="s">
+      <c r="G129" s="33" t="s">
         <v>321</v>
       </c>
-      <c r="H129" s="3" t="s">
+      <c r="H129" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I129" s="3" t="s">
+      <c r="I129" s="33" t="s">
         <v>323</v>
       </c>
       <c r="J129" s="3" t="str">
@@ -10394,8 +10398,8 @@
         <v>328</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A130" s="34">
+    <row r="130" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="33">
         <v>129</v>
       </c>
       <c r="B130" s="3" t="s">
@@ -10413,13 +10417,13 @@
       <c r="F130" t="s">
         <v>326</v>
       </c>
-      <c r="G130" s="3" t="s">
+      <c r="G130" s="33" t="s">
         <v>321</v>
       </c>
-      <c r="H130" s="3" t="s">
+      <c r="H130" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I130" s="3" t="s">
+      <c r="I130" s="33" t="s">
         <v>322</v>
       </c>
       <c r="J130" s="3" t="str">
@@ -10458,8 +10462,8 @@
         <v>328</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A131" s="34">
+    <row r="131" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="33">
         <v>130</v>
       </c>
       <c r="B131" s="3" t="s">
@@ -10477,13 +10481,13 @@
       <c r="F131" t="s">
         <v>327</v>
       </c>
-      <c r="G131" s="3" t="s">
+      <c r="G131" s="33" t="s">
         <v>321</v>
       </c>
-      <c r="H131" s="3" t="s">
+      <c r="H131" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I131" s="3" t="s">
+      <c r="I131" s="33" t="s">
         <v>323</v>
       </c>
       <c r="J131" s="3" t="str">
@@ -10522,8 +10526,8 @@
         <v>328</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A132" s="34">
+    <row r="132" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="33">
         <v>131</v>
       </c>
       <c r="B132" s="3" t="s">
@@ -10541,13 +10545,13 @@
       <c r="F132" t="s">
         <v>335</v>
       </c>
-      <c r="G132" s="3" t="s">
+      <c r="G132" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H132" s="3" t="s">
+      <c r="H132" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I132" s="5" t="s">
+      <c r="I132" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J132" s="3" t="str">
@@ -10586,8 +10590,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A133" s="34">
+    <row r="133" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="33">
         <v>132</v>
       </c>
       <c r="B133" s="3" t="s">
@@ -10605,13 +10609,13 @@
       <c r="F133" t="s">
         <v>337</v>
       </c>
-      <c r="G133" s="3" t="s">
+      <c r="G133" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H133" s="3" t="s">
+      <c r="H133" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I133" s="5" t="s">
+      <c r="I133" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J133" s="3" t="str">
@@ -10650,8 +10654,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A134" s="34">
+    <row r="134" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="33">
         <v>133</v>
       </c>
       <c r="B134" s="3" t="s">
@@ -10669,13 +10673,13 @@
       <c r="F134" t="s">
         <v>339</v>
       </c>
-      <c r="G134" s="3" t="s">
+      <c r="G134" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H134" s="3" t="s">
+      <c r="H134" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I134" s="5" t="s">
+      <c r="I134" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J134" s="3" t="str">
@@ -10714,8 +10718,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A135" s="34">
+    <row r="135" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="33">
         <v>134</v>
       </c>
       <c r="B135" s="3" t="s">
@@ -10733,13 +10737,13 @@
       <c r="F135" t="s">
         <v>341</v>
       </c>
-      <c r="G135" s="3" t="s">
+      <c r="G135" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H135" s="3" t="s">
+      <c r="H135" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I135" s="5" t="s">
+      <c r="I135" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J135" s="3" t="str">
@@ -10778,8 +10782,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A136" s="34">
+    <row r="136" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="33">
         <v>135</v>
       </c>
       <c r="B136" s="3" t="s">
@@ -10797,13 +10801,13 @@
       <c r="F136" t="s">
         <v>343</v>
       </c>
-      <c r="G136" s="3" t="s">
+      <c r="G136" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H136" s="3" t="s">
+      <c r="H136" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I136" s="5" t="s">
+      <c r="I136" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J136" s="3" t="str">
@@ -10842,8 +10846,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A137" s="34">
+    <row r="137" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="33">
         <v>136</v>
       </c>
       <c r="B137" s="3" t="s">
@@ -10861,13 +10865,13 @@
       <c r="F137" t="s">
         <v>343</v>
       </c>
-      <c r="G137" s="3" t="s">
+      <c r="G137" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H137" s="3" t="s">
+      <c r="H137" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I137" s="5" t="s">
+      <c r="I137" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J137" s="3" t="str">
@@ -10906,8 +10910,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A138" s="34">
+    <row r="138" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="33">
         <v>137</v>
       </c>
       <c r="B138" s="3" t="s">
@@ -10925,13 +10929,13 @@
       <c r="F138" t="s">
         <v>345</v>
       </c>
-      <c r="G138" s="3" t="s">
+      <c r="G138" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H138" s="3" t="s">
+      <c r="H138" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I138" s="5" t="s">
+      <c r="I138" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J138" s="3" t="str">
@@ -10970,8 +10974,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A139" s="34">
+    <row r="139" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="33">
         <v>138</v>
       </c>
       <c r="B139" s="3" t="s">
@@ -10989,13 +10993,13 @@
       <c r="F139" t="s">
         <v>345</v>
       </c>
-      <c r="G139" s="3" t="s">
+      <c r="G139" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H139" s="3" t="s">
+      <c r="H139" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I139" s="5" t="s">
+      <c r="I139" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J139" s="3" t="str">
@@ -11034,8 +11038,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A140" s="34">
+    <row r="140" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="33">
         <v>139</v>
       </c>
       <c r="B140" s="3" t="s">
@@ -11053,13 +11057,13 @@
       <c r="F140" t="s">
         <v>341</v>
       </c>
-      <c r="G140" s="3" t="s">
+      <c r="G140" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H140" s="3" t="s">
+      <c r="H140" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I140" s="5" t="s">
+      <c r="I140" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J140" s="3" t="str">
@@ -11098,8 +11102,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A141" s="34">
+    <row r="141" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="33">
         <v>140</v>
       </c>
       <c r="B141" s="3" t="s">
@@ -11117,13 +11121,13 @@
       <c r="F141" t="s">
         <v>348</v>
       </c>
-      <c r="G141" s="3" t="s">
+      <c r="G141" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H141" s="3" t="s">
+      <c r="H141" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I141" s="5" t="s">
+      <c r="I141" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J141" s="3" t="str">
@@ -11162,8 +11166,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A142" s="34">
+    <row r="142" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="33">
         <v>141</v>
       </c>
       <c r="B142" s="3" t="s">
@@ -11181,13 +11185,13 @@
       <c r="F142" t="s">
         <v>349</v>
       </c>
-      <c r="G142" s="3" t="s">
+      <c r="G142" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H142" s="3" t="s">
+      <c r="H142" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I142" s="5" t="s">
+      <c r="I142" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J142" s="3" t="str">
@@ -11226,8 +11230,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A143" s="34">
+    <row r="143" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="33">
         <v>142</v>
       </c>
       <c r="B143" s="3" t="s">
@@ -11245,13 +11249,13 @@
       <c r="F143" t="s">
         <v>349</v>
       </c>
-      <c r="G143" s="3" t="s">
+      <c r="G143" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H143" s="3" t="s">
+      <c r="H143" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I143" s="5" t="s">
+      <c r="I143" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J143" s="3" t="str">
@@ -11290,8 +11294,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A144" s="34">
+    <row r="144" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="33">
         <v>143</v>
       </c>
       <c r="B144" s="29" t="s">
@@ -11309,13 +11313,13 @@
       <c r="F144" s="27" t="s">
         <v>335</v>
       </c>
-      <c r="G144" s="29" t="s">
+      <c r="G144" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H144" s="29" t="s">
+      <c r="H144" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I144" s="30" t="s">
+      <c r="I144" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J144" s="29" t="str">
@@ -11350,12 +11354,12 @@
         <f t="shared" ref="Q144:Q167" si="55">((((O144/60)+N144)/60)+M144)*IF(D144="W",-1, 1)</f>
         <v>-35.000555555555557</v>
       </c>
-      <c r="R144" s="31" t="s">
+      <c r="R144" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A145" s="34">
+    <row r="145" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="33">
         <v>144</v>
       </c>
       <c r="B145" s="29" t="s">
@@ -11373,13 +11377,13 @@
       <c r="F145" s="27" t="s">
         <v>337</v>
       </c>
-      <c r="G145" s="29" t="s">
+      <c r="G145" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H145" s="29" t="s">
+      <c r="H145" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I145" s="30" t="s">
+      <c r="I145" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J145" s="29" t="str">
@@ -11414,12 +11418,12 @@
         <f t="shared" si="55"/>
         <v>-34.999444444444443</v>
       </c>
-      <c r="R145" s="31" t="s">
+      <c r="R145" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="34">
+    <row r="146" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="33">
         <v>145</v>
       </c>
       <c r="B146" s="29" t="s">
@@ -11437,13 +11441,13 @@
       <c r="F146" s="27" t="s">
         <v>339</v>
       </c>
-      <c r="G146" s="29" t="s">
+      <c r="G146" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H146" s="29" t="s">
+      <c r="H146" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I146" s="30" t="s">
+      <c r="I146" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J146" s="29" t="str">
@@ -11478,12 +11482,12 @@
         <f t="shared" si="55"/>
         <v>-34.999166666666667</v>
       </c>
-      <c r="R146" s="31" t="s">
+      <c r="R146" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A147" s="34">
+    <row r="147" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="33">
         <v>146</v>
       </c>
       <c r="B147" s="29" t="s">
@@ -11501,13 +11505,13 @@
       <c r="F147" s="27" t="s">
         <v>341</v>
       </c>
-      <c r="G147" s="29" t="s">
+      <c r="G147" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H147" s="29" t="s">
+      <c r="H147" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I147" s="30" t="s">
+      <c r="I147" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J147" s="29" t="str">
@@ -11542,12 +11546,12 @@
         <f t="shared" si="55"/>
         <v>-34.998888888888892</v>
       </c>
-      <c r="R147" s="31" t="s">
+      <c r="R147" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A148" s="34">
+    <row r="148" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="33">
         <v>147</v>
       </c>
       <c r="B148" s="29" t="s">
@@ -11565,13 +11569,13 @@
       <c r="F148" s="27" t="s">
         <v>343</v>
       </c>
-      <c r="G148" s="29" t="s">
+      <c r="G148" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H148" s="29" t="s">
+      <c r="H148" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I148" s="30" t="s">
+      <c r="I148" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J148" s="29" t="str">
@@ -11606,12 +11610,12 @@
         <f t="shared" si="55"/>
         <v>-34.998333333333335</v>
       </c>
-      <c r="R148" s="31" t="s">
+      <c r="R148" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A149" s="34">
+    <row r="149" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="33">
         <v>148</v>
       </c>
       <c r="B149" s="29" t="s">
@@ -11629,13 +11633,13 @@
       <c r="F149" s="27" t="s">
         <v>343</v>
       </c>
-      <c r="G149" s="29" t="s">
+      <c r="G149" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H149" s="29" t="s">
+      <c r="H149" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I149" s="30" t="s">
+      <c r="I149" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J149" s="29" t="str">
@@ -11670,12 +11674,12 @@
         <f t="shared" si="55"/>
         <v>-34.998333333333335</v>
       </c>
-      <c r="R149" s="31" t="s">
+      <c r="R149" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A150" s="34">
+    <row r="150" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="33">
         <v>149</v>
       </c>
       <c r="B150" s="29" t="s">
@@ -11693,13 +11697,13 @@
       <c r="F150" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="G150" s="29" t="s">
+      <c r="G150" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H150" s="29" t="s">
+      <c r="H150" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I150" s="30" t="s">
+      <c r="I150" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J150" s="29" t="str">
@@ -11734,12 +11738,12 @@
         <f t="shared" si="55"/>
         <v>-34.997777777777777</v>
       </c>
-      <c r="R150" s="31" t="s">
+      <c r="R150" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A151" s="34">
+    <row r="151" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="33">
         <v>150</v>
       </c>
       <c r="B151" s="29" t="s">
@@ -11757,13 +11761,13 @@
       <c r="F151" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="G151" s="29" t="s">
+      <c r="G151" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H151" s="29" t="s">
+      <c r="H151" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I151" s="30" t="s">
+      <c r="I151" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J151" s="29" t="str">
@@ -11798,12 +11802,12 @@
         <f t="shared" si="55"/>
         <v>-34.997777777777777</v>
       </c>
-      <c r="R151" s="31" t="s">
+      <c r="R151" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A152" s="34">
+    <row r="152" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="33">
         <v>151</v>
       </c>
       <c r="B152" s="29" t="s">
@@ -11821,13 +11825,13 @@
       <c r="F152" s="27" t="s">
         <v>341</v>
       </c>
-      <c r="G152" s="29" t="s">
+      <c r="G152" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H152" s="29" t="s">
+      <c r="H152" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I152" s="30" t="s">
+      <c r="I152" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J152" s="29" t="str">
@@ -11862,12 +11866,12 @@
         <f t="shared" si="55"/>
         <v>-34.998888888888892</v>
       </c>
-      <c r="R152" s="31" t="s">
+      <c r="R152" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A153" s="34">
+    <row r="153" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="33">
         <v>152</v>
       </c>
       <c r="B153" s="29" t="s">
@@ -11885,13 +11889,13 @@
       <c r="F153" s="27" t="s">
         <v>348</v>
       </c>
-      <c r="G153" s="29" t="s">
+      <c r="G153" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H153" s="29" t="s">
+      <c r="H153" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I153" s="30" t="s">
+      <c r="I153" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J153" s="29" t="str">
@@ -11926,12 +11930,12 @@
         <f t="shared" si="55"/>
         <v>-34.99861111111111</v>
       </c>
-      <c r="R153" s="31" t="s">
+      <c r="R153" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A154" s="34">
+    <row r="154" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="33">
         <v>153</v>
       </c>
       <c r="B154" s="29" t="s">
@@ -11949,13 +11953,13 @@
       <c r="F154" s="27" t="s">
         <v>349</v>
       </c>
-      <c r="G154" s="29" t="s">
+      <c r="G154" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H154" s="29" t="s">
+      <c r="H154" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I154" s="30" t="s">
+      <c r="I154" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J154" s="29" t="str">
@@ -11990,12 +11994,12 @@
         <f t="shared" si="55"/>
         <v>-34.998055555555553</v>
       </c>
-      <c r="R154" s="31" t="s">
+      <c r="R154" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A155" s="34">
+    <row r="155" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="33">
         <v>154</v>
       </c>
       <c r="B155" s="29" t="s">
@@ -12013,13 +12017,13 @@
       <c r="F155" s="27" t="s">
         <v>349</v>
       </c>
-      <c r="G155" s="29" t="s">
+      <c r="G155" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H155" s="29" t="s">
+      <c r="H155" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I155" s="30" t="s">
+      <c r="I155" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J155" s="29" t="str">
@@ -12054,12 +12058,12 @@
         <f t="shared" si="55"/>
         <v>-34.998055555555553</v>
       </c>
-      <c r="R155" s="31" t="s">
+      <c r="R155" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A156" s="34">
+    <row r="156" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="33">
         <v>155</v>
       </c>
       <c r="B156" s="29" t="s">
@@ -12077,13 +12081,13 @@
       <c r="F156" s="27" t="s">
         <v>335</v>
       </c>
-      <c r="G156" s="29" t="s">
+      <c r="G156" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H156" s="29" t="s">
+      <c r="H156" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I156" s="30" t="s">
+      <c r="I156" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J156" s="29" t="str">
@@ -12118,12 +12122,12 @@
         <f t="shared" si="55"/>
         <v>-35.000555555555557</v>
       </c>
-      <c r="R156" s="31" t="s">
+      <c r="R156" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A157" s="34">
+    <row r="157" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="33">
         <v>156</v>
       </c>
       <c r="B157" s="29" t="s">
@@ -12141,13 +12145,13 @@
       <c r="F157" s="27" t="s">
         <v>337</v>
       </c>
-      <c r="G157" s="29" t="s">
+      <c r="G157" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H157" s="29" t="s">
+      <c r="H157" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I157" s="30" t="s">
+      <c r="I157" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J157" s="29" t="str">
@@ -12182,12 +12186,12 @@
         <f t="shared" si="55"/>
         <v>-34.999444444444443</v>
       </c>
-      <c r="R157" s="31" t="s">
+      <c r="R157" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A158" s="34">
+    <row r="158" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="33">
         <v>157</v>
       </c>
       <c r="B158" s="29" t="s">
@@ -12205,13 +12209,13 @@
       <c r="F158" s="27" t="s">
         <v>339</v>
       </c>
-      <c r="G158" s="29" t="s">
+      <c r="G158" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H158" s="29" t="s">
+      <c r="H158" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I158" s="30" t="s">
+      <c r="I158" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J158" s="29" t="str">
@@ -12246,12 +12250,12 @@
         <f t="shared" si="55"/>
         <v>-34.999166666666667</v>
       </c>
-      <c r="R158" s="31" t="s">
+      <c r="R158" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A159" s="34">
+    <row r="159" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="33">
         <v>158</v>
       </c>
       <c r="B159" s="29" t="s">
@@ -12269,13 +12273,13 @@
       <c r="F159" s="27" t="s">
         <v>341</v>
       </c>
-      <c r="G159" s="29" t="s">
+      <c r="G159" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H159" s="29" t="s">
+      <c r="H159" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I159" s="30" t="s">
+      <c r="I159" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J159" s="29" t="str">
@@ -12310,12 +12314,12 @@
         <f t="shared" si="55"/>
         <v>-34.998888888888892</v>
       </c>
-      <c r="R159" s="31" t="s">
+      <c r="R159" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A160" s="34">
+    <row r="160" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="33">
         <v>159</v>
       </c>
       <c r="B160" s="29" t="s">
@@ -12333,13 +12337,13 @@
       <c r="F160" s="27" t="s">
         <v>343</v>
       </c>
-      <c r="G160" s="29" t="s">
+      <c r="G160" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H160" s="29" t="s">
+      <c r="H160" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I160" s="30" t="s">
+      <c r="I160" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J160" s="29" t="str">
@@ -12374,12 +12378,12 @@
         <f t="shared" si="55"/>
         <v>-34.998333333333335</v>
       </c>
-      <c r="R160" s="31" t="s">
+      <c r="R160" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A161" s="34">
+    <row r="161" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="33">
         <v>160</v>
       </c>
       <c r="B161" s="29" t="s">
@@ -12397,13 +12401,13 @@
       <c r="F161" s="27" t="s">
         <v>343</v>
       </c>
-      <c r="G161" s="29" t="s">
+      <c r="G161" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H161" s="29" t="s">
+      <c r="H161" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I161" s="30" t="s">
+      <c r="I161" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J161" s="29" t="str">
@@ -12438,12 +12442,12 @@
         <f t="shared" si="55"/>
         <v>-34.998333333333335</v>
       </c>
-      <c r="R161" s="31" t="s">
+      <c r="R161" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A162" s="34">
+    <row r="162" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="33">
         <v>161</v>
       </c>
       <c r="B162" s="29" t="s">
@@ -12461,13 +12465,13 @@
       <c r="F162" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="G162" s="29" t="s">
+      <c r="G162" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H162" s="29" t="s">
+      <c r="H162" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I162" s="30" t="s">
+      <c r="I162" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J162" s="29" t="str">
@@ -12502,12 +12506,12 @@
         <f t="shared" si="55"/>
         <v>-34.997777777777777</v>
       </c>
-      <c r="R162" s="31" t="s">
+      <c r="R162" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A163" s="34">
+    <row r="163" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="33">
         <v>162</v>
       </c>
       <c r="B163" s="29" t="s">
@@ -12525,13 +12529,13 @@
       <c r="F163" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="G163" s="29" t="s">
+      <c r="G163" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H163" s="29" t="s">
+      <c r="H163" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I163" s="30" t="s">
+      <c r="I163" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J163" s="29" t="str">
@@ -12566,12 +12570,12 @@
         <f t="shared" si="55"/>
         <v>-34.997777777777777</v>
       </c>
-      <c r="R163" s="31" t="s">
+      <c r="R163" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A164" s="34">
+    <row r="164" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="33">
         <v>163</v>
       </c>
       <c r="B164" s="29" t="s">
@@ -12589,13 +12593,13 @@
       <c r="F164" s="27" t="s">
         <v>341</v>
       </c>
-      <c r="G164" s="29" t="s">
+      <c r="G164" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H164" s="29" t="s">
+      <c r="H164" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I164" s="30" t="s">
+      <c r="I164" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J164" s="29" t="str">
@@ -12630,12 +12634,12 @@
         <f t="shared" si="55"/>
         <v>-34.998888888888892</v>
       </c>
-      <c r="R164" s="31" t="s">
+      <c r="R164" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A165" s="34">
+    <row r="165" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="33">
         <v>164</v>
       </c>
       <c r="B165" s="29" t="s">
@@ -12653,13 +12657,13 @@
       <c r="F165" s="27" t="s">
         <v>348</v>
       </c>
-      <c r="G165" s="29" t="s">
+      <c r="G165" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H165" s="29" t="s">
+      <c r="H165" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I165" s="30" t="s">
+      <c r="I165" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J165" s="29" t="str">
@@ -12694,12 +12698,12 @@
         <f t="shared" si="55"/>
         <v>-34.99861111111111</v>
       </c>
-      <c r="R165" s="31" t="s">
+      <c r="R165" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A166" s="34">
+    <row r="166" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="33">
         <v>165</v>
       </c>
       <c r="B166" s="29" t="s">
@@ -12717,13 +12721,13 @@
       <c r="F166" s="27" t="s">
         <v>349</v>
       </c>
-      <c r="G166" s="29" t="s">
+      <c r="G166" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H166" s="29" t="s">
+      <c r="H166" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I166" s="30" t="s">
+      <c r="I166" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J166" s="29" t="str">
@@ -12758,12 +12762,12 @@
         <f t="shared" si="55"/>
         <v>-34.998055555555553</v>
       </c>
-      <c r="R166" s="31" t="s">
+      <c r="R166" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A167" s="34">
+    <row r="167" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="33">
         <v>166</v>
       </c>
       <c r="B167" s="29" t="s">
@@ -12781,13 +12785,13 @@
       <c r="F167" s="27" t="s">
         <v>349</v>
       </c>
-      <c r="G167" s="29" t="s">
+      <c r="G167" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="H167" s="29" t="s">
+      <c r="H167" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I167" s="30" t="s">
+      <c r="I167" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J167" s="29" t="str">
@@ -12822,12 +12826,12 @@
         <f t="shared" si="55"/>
         <v>-34.998055555555553</v>
       </c>
-      <c r="R167" s="31" t="s">
+      <c r="R167" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A168" s="34">
+    <row r="168" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="33">
         <v>167</v>
       </c>
       <c r="B168" s="3" t="s">
@@ -12845,13 +12849,13 @@
       <c r="F168" t="s">
         <v>357</v>
       </c>
-      <c r="G168" t="s">
+      <c r="G168" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="H168" s="3" t="s">
+      <c r="H168" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I168" s="3" t="s">
+      <c r="I168" s="33" t="s">
         <v>363</v>
       </c>
       <c r="J168" s="3" t="str">
@@ -12890,8 +12894,8 @@
         <v>369</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A169" s="34">
+    <row r="169" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="33">
         <v>168</v>
       </c>
       <c r="B169" s="3" t="s">
@@ -12909,13 +12913,13 @@
       <c r="F169" t="s">
         <v>358</v>
       </c>
-      <c r="G169" t="s">
+      <c r="G169" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="H169" s="3" t="s">
+      <c r="H169" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I169" s="3" t="s">
+      <c r="I169" s="33" t="s">
         <v>364</v>
       </c>
       <c r="J169" s="3" t="str">
@@ -12954,8 +12958,8 @@
         <v>369</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A170" s="34">
+    <row r="170" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="33">
         <v>169</v>
       </c>
       <c r="B170" s="3" t="s">
@@ -12973,13 +12977,13 @@
       <c r="F170" t="s">
         <v>359</v>
       </c>
-      <c r="G170" t="s">
+      <c r="G170" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="H170" s="3" t="s">
+      <c r="H170" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I170" s="3" t="s">
+      <c r="I170" s="33" t="s">
         <v>366</v>
       </c>
       <c r="J170" s="3" t="str">
@@ -13018,8 +13022,8 @@
         <v>369</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A171" s="34">
+    <row r="171" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="33">
         <v>170</v>
       </c>
       <c r="B171" s="3" t="s">
@@ -13037,13 +13041,13 @@
       <c r="F171" t="s">
         <v>360</v>
       </c>
-      <c r="G171" t="s">
+      <c r="G171" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="H171" s="3" t="s">
+      <c r="H171" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I171" s="3" t="s">
+      <c r="I171" s="33" t="s">
         <v>365</v>
       </c>
       <c r="J171" s="3" t="str">
@@ -13082,8 +13086,8 @@
         <v>369</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A172" s="34">
+    <row r="172" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="33">
         <v>171</v>
       </c>
       <c r="B172" s="3" t="s">
@@ -13101,13 +13105,13 @@
       <c r="F172" t="s">
         <v>361</v>
       </c>
-      <c r="G172" t="s">
+      <c r="G172" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="H172" s="3" t="s">
+      <c r="H172" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I172" s="3" t="s">
+      <c r="I172" s="33" t="s">
         <v>367</v>
       </c>
       <c r="J172" s="3" t="str">
@@ -13146,8 +13150,8 @@
         <v>369</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A173" s="34">
+    <row r="173" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="33">
         <v>172</v>
       </c>
       <c r="B173" s="3" t="s">
@@ -13165,13 +13169,13 @@
       <c r="F173" t="s">
         <v>362</v>
       </c>
-      <c r="G173" t="s">
+      <c r="G173" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="H173" s="3" t="s">
+      <c r="H173" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I173" s="3" t="s">
+      <c r="I173" s="33" t="s">
         <v>368</v>
       </c>
       <c r="J173" s="3" t="str">
@@ -13210,8 +13214,8 @@
         <v>369</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A174" s="34">
+    <row r="174" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="33">
         <v>173</v>
       </c>
       <c r="B174" s="3" t="s">
@@ -13229,13 +13233,13 @@
       <c r="F174" t="s">
         <v>374</v>
       </c>
-      <c r="G174" t="s">
+      <c r="G174" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H174" s="3" t="s">
+      <c r="H174" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I174" t="s">
+      <c r="I174" s="35" t="s">
         <v>372</v>
       </c>
       <c r="J174" s="3" t="str">
@@ -13274,8 +13278,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A175" s="34">
+    <row r="175" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="33">
         <v>174</v>
       </c>
       <c r="B175" s="3" t="s">
@@ -13293,13 +13297,13 @@
       <c r="F175" t="s">
         <v>379</v>
       </c>
-      <c r="G175" t="s">
+      <c r="G175" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H175" s="3" t="s">
+      <c r="H175" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I175" t="s">
+      <c r="I175" s="35" t="s">
         <v>372</v>
       </c>
       <c r="J175" s="3" t="str">
@@ -13338,8 +13342,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A176" s="34">
+    <row r="176" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="33">
         <v>175</v>
       </c>
       <c r="B176" s="3" t="s">
@@ -13357,13 +13361,13 @@
       <c r="F176" t="s">
         <v>380</v>
       </c>
-      <c r="G176" t="s">
+      <c r="G176" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H176" s="3" t="s">
+      <c r="H176" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I176" t="s">
+      <c r="I176" s="35" t="s">
         <v>372</v>
       </c>
       <c r="J176" s="3" t="str">
@@ -13402,8 +13406,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A177" s="34">
+    <row r="177" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="33">
         <v>176</v>
       </c>
       <c r="B177" s="3" t="s">
@@ -13421,13 +13425,13 @@
       <c r="F177" t="s">
         <v>381</v>
       </c>
-      <c r="G177" t="s">
+      <c r="G177" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H177" s="3" t="s">
+      <c r="H177" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I177" t="s">
+      <c r="I177" s="35" t="s">
         <v>372</v>
       </c>
       <c r="J177" s="3" t="str">
@@ -13466,8 +13470,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A178" s="34">
+    <row r="178" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="33">
         <v>177</v>
       </c>
       <c r="B178" s="3" t="s">
@@ -13485,13 +13489,13 @@
       <c r="F178" t="s">
         <v>382</v>
       </c>
-      <c r="G178" t="s">
+      <c r="G178" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H178" s="3" t="s">
+      <c r="H178" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I178" t="s">
+      <c r="I178" s="35" t="s">
         <v>372</v>
       </c>
       <c r="J178" s="3" t="str">
@@ -13530,8 +13534,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A179" s="34">
+    <row r="179" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="33">
         <v>178</v>
       </c>
       <c r="B179" s="3" t="s">
@@ -13549,13 +13553,13 @@
       <c r="F179" t="s">
         <v>385</v>
       </c>
-      <c r="G179" t="s">
+      <c r="G179" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H179" s="3" t="s">
+      <c r="H179" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I179" t="s">
+      <c r="I179" s="35" t="s">
         <v>383</v>
       </c>
       <c r="J179" s="3" t="str">
@@ -13594,8 +13598,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A180" s="34">
+    <row r="180" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="33">
         <v>179</v>
       </c>
       <c r="B180" s="3" t="s">
@@ -13613,13 +13617,13 @@
       <c r="F180" t="s">
         <v>387</v>
       </c>
-      <c r="G180" t="s">
+      <c r="G180" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H180" s="3" t="s">
+      <c r="H180" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I180" t="s">
+      <c r="I180" s="35" t="s">
         <v>383</v>
       </c>
       <c r="J180" s="3" t="str">
@@ -13658,8 +13662,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A181" s="34">
+    <row r="181" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="33">
         <v>180</v>
       </c>
       <c r="B181" s="3" t="s">
@@ -13677,13 +13681,13 @@
       <c r="F181" t="s">
         <v>389</v>
       </c>
-      <c r="G181" t="s">
+      <c r="G181" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H181" s="3" t="s">
+      <c r="H181" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I181" t="s">
+      <c r="I181" s="35" t="s">
         <v>383</v>
       </c>
       <c r="J181" s="3" t="str">
@@ -13722,8 +13726,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A182" s="34">
+    <row r="182" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="33">
         <v>181</v>
       </c>
       <c r="B182" s="3" t="s">
@@ -13741,13 +13745,13 @@
       <c r="F182" t="s">
         <v>391</v>
       </c>
-      <c r="G182" t="s">
+      <c r="G182" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H182" s="3" t="s">
+      <c r="H182" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I182" t="s">
+      <c r="I182" s="35" t="s">
         <v>383</v>
       </c>
       <c r="J182" s="3" t="str">
@@ -13786,8 +13790,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A183" s="34">
+    <row r="183" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="33">
         <v>182</v>
       </c>
       <c r="B183" s="3" t="s">
@@ -13805,13 +13809,13 @@
       <c r="F183" t="s">
         <v>393</v>
       </c>
-      <c r="G183" t="s">
+      <c r="G183" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H183" s="3" t="s">
+      <c r="H183" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I183" t="s">
+      <c r="I183" s="35" t="s">
         <v>383</v>
       </c>
       <c r="J183" s="3" t="str">
@@ -13850,8 +13854,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A184" s="34">
+    <row r="184" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="33">
         <v>183</v>
       </c>
       <c r="B184" s="3" t="s">
@@ -13869,13 +13873,13 @@
       <c r="F184" t="s">
         <v>396</v>
       </c>
-      <c r="G184" t="s">
+      <c r="G184" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H184" s="3" t="s">
+      <c r="H184" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I184" t="s">
+      <c r="I184" s="35" t="s">
         <v>383</v>
       </c>
       <c r="J184" s="3" t="str">
@@ -13914,8 +13918,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A185" s="34">
+    <row r="185" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="33">
         <v>184</v>
       </c>
       <c r="B185" s="3" t="s">
@@ -13933,13 +13937,13 @@
       <c r="F185" t="s">
         <v>397</v>
       </c>
-      <c r="G185" t="s">
+      <c r="G185" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H185" s="3" t="s">
+      <c r="H185" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I185" t="s">
+      <c r="I185" s="35" t="s">
         <v>383</v>
       </c>
       <c r="J185" s="3" t="str">
@@ -13978,8 +13982,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A186" s="34">
+    <row r="186" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="33">
         <v>185</v>
       </c>
       <c r="B186" s="3" t="s">
@@ -13997,13 +14001,13 @@
       <c r="F186" t="s">
         <v>406</v>
       </c>
-      <c r="G186" t="s">
+      <c r="G186" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H186" s="3" t="s">
+      <c r="H186" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I186" t="s">
+      <c r="I186" s="35" t="s">
         <v>398</v>
       </c>
       <c r="J186" s="3" t="str">
@@ -14042,8 +14046,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A187" s="34">
+    <row r="187" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="33">
         <v>186</v>
       </c>
       <c r="B187" s="3" t="s">
@@ -14061,13 +14065,13 @@
       <c r="F187" t="s">
         <v>405</v>
       </c>
-      <c r="G187" t="s">
+      <c r="G187" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H187" s="3" t="s">
+      <c r="H187" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I187" t="s">
+      <c r="I187" s="35" t="s">
         <v>398</v>
       </c>
       <c r="J187" s="3" t="str">
@@ -14106,8 +14110,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A188" s="34">
+    <row r="188" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="33">
         <v>187</v>
       </c>
       <c r="B188" s="3" t="s">
@@ -14125,13 +14129,13 @@
       <c r="F188" t="s">
         <v>404</v>
       </c>
-      <c r="G188" t="s">
+      <c r="G188" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H188" s="3" t="s">
+      <c r="H188" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I188" t="s">
+      <c r="I188" s="35" t="s">
         <v>398</v>
       </c>
       <c r="J188" s="3" t="str">
@@ -14170,8 +14174,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A189" s="34">
+    <row r="189" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="33">
         <v>188</v>
       </c>
       <c r="B189" s="3" t="s">
@@ -14189,13 +14193,13 @@
       <c r="F189" t="s">
         <v>403</v>
       </c>
-      <c r="G189" t="s">
+      <c r="G189" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H189" s="3" t="s">
+      <c r="H189" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I189" t="s">
+      <c r="I189" s="35" t="s">
         <v>398</v>
       </c>
       <c r="J189" s="3" t="str">
@@ -14234,8 +14238,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A190" s="34">
+    <row r="190" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="33">
         <v>189</v>
       </c>
       <c r="B190" s="3" t="s">
@@ -14253,13 +14257,13 @@
       <c r="F190" t="s">
         <v>410</v>
       </c>
-      <c r="G190" t="s">
+      <c r="G190" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H190" s="3" t="s">
+      <c r="H190" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I190" t="s">
+      <c r="I190" s="35" t="s">
         <v>398</v>
       </c>
       <c r="J190" s="3" t="str">
@@ -14298,8 +14302,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A191" s="34">
+    <row r="191" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="33">
         <v>190</v>
       </c>
       <c r="B191" s="3" t="s">
@@ -14317,13 +14321,13 @@
       <c r="F191" t="s">
         <v>409</v>
       </c>
-      <c r="G191" t="s">
+      <c r="G191" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H191" s="3" t="s">
+      <c r="H191" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I191" t="s">
+      <c r="I191" s="35" t="s">
         <v>398</v>
       </c>
       <c r="J191" s="3" t="str">
@@ -14362,8 +14366,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A192" s="34">
+    <row r="192" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="33">
         <v>191</v>
       </c>
       <c r="B192" s="3" t="s">
@@ -14381,13 +14385,13 @@
       <c r="F192" t="s">
         <v>425</v>
       </c>
-      <c r="G192" t="s">
+      <c r="G192" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H192" s="3" t="s">
+      <c r="H192" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I192" t="s">
+      <c r="I192" s="35" t="s">
         <v>411</v>
       </c>
       <c r="J192" s="3" t="str">
@@ -14426,8 +14430,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A193" s="34">
+    <row r="193" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="33">
         <v>192</v>
       </c>
       <c r="B193" s="3" t="s">
@@ -14445,13 +14449,13 @@
       <c r="F193" t="s">
         <v>424</v>
       </c>
-      <c r="G193" t="s">
+      <c r="G193" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H193" s="3" t="s">
+      <c r="H193" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I193" t="s">
+      <c r="I193" s="35" t="s">
         <v>411</v>
       </c>
       <c r="J193" s="3" t="str">
@@ -14490,8 +14494,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A194" s="34">
+    <row r="194" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="33">
         <v>193</v>
       </c>
       <c r="B194" s="3" t="s">
@@ -14509,13 +14513,13 @@
       <c r="F194" t="s">
         <v>423</v>
       </c>
-      <c r="G194" t="s">
+      <c r="G194" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H194" s="3" t="s">
+      <c r="H194" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I194" t="s">
+      <c r="I194" s="35" t="s">
         <v>411</v>
       </c>
       <c r="J194" s="3" t="str">
@@ -14554,8 +14558,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A195" s="34">
+    <row r="195" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="33">
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
@@ -14573,13 +14577,13 @@
       <c r="F195" t="s">
         <v>422</v>
       </c>
-      <c r="G195" t="s">
+      <c r="G195" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H195" s="3" t="s">
+      <c r="H195" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I195" t="s">
+      <c r="I195" s="35" t="s">
         <v>411</v>
       </c>
       <c r="J195" s="3" t="str">
@@ -14618,8 +14622,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A196" s="34">
+    <row r="196" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="33">
         <v>195</v>
       </c>
       <c r="B196" s="3" t="s">
@@ -14637,13 +14641,13 @@
       <c r="F196" t="s">
         <v>420</v>
       </c>
-      <c r="G196" t="s">
+      <c r="G196" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H196" s="3" t="s">
+      <c r="H196" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I196" t="s">
+      <c r="I196" s="35" t="s">
         <v>411</v>
       </c>
       <c r="J196" s="3" t="str">
@@ -14682,8 +14686,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A197" s="34">
+    <row r="197" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="33">
         <v>196</v>
       </c>
       <c r="B197" s="3" t="s">
@@ -14701,13 +14705,13 @@
       <c r="F197" t="s">
         <v>421</v>
       </c>
-      <c r="G197" t="s">
+      <c r="G197" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H197" s="3" t="s">
+      <c r="H197" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I197" t="s">
+      <c r="I197" s="35" t="s">
         <v>411</v>
       </c>
       <c r="J197" s="3" t="str">
@@ -14746,8 +14750,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A198" s="34">
+    <row r="198" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="33">
         <v>197</v>
       </c>
       <c r="B198" s="3" t="s">
@@ -14765,13 +14769,13 @@
       <c r="F198" t="s">
         <v>419</v>
       </c>
-      <c r="G198" t="s">
+      <c r="G198" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="H198" s="3" t="s">
+      <c r="H198" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I198" t="s">
+      <c r="I198" s="35" t="s">
         <v>411</v>
       </c>
       <c r="J198" s="3" t="str">
@@ -14810,8 +14814,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A199" s="34">
+    <row r="199" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="33">
         <v>198</v>
       </c>
       <c r="B199" s="3" t="s">
@@ -14829,13 +14833,13 @@
       <c r="F199" t="s">
         <v>439</v>
       </c>
-      <c r="G199" t="s">
+      <c r="G199" s="35" t="s">
         <v>426</v>
       </c>
-      <c r="H199" s="3" t="s">
+      <c r="H199" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I199" t="s">
+      <c r="I199" s="35" t="s">
         <v>427</v>
       </c>
       <c r="J199" s="3" t="str">
@@ -14874,8 +14878,8 @@
         <v>440</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A200" s="34">
+    <row r="200" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="33">
         <v>199</v>
       </c>
       <c r="B200" s="3" t="s">
@@ -14893,13 +14897,13 @@
       <c r="F200" t="s">
         <v>438</v>
       </c>
-      <c r="G200" t="s">
+      <c r="G200" s="35" t="s">
         <v>426</v>
       </c>
-      <c r="H200" s="3" t="s">
+      <c r="H200" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I200" t="s">
+      <c r="I200" s="35" t="s">
         <v>427</v>
       </c>
       <c r="J200" s="3" t="str">
@@ -14938,8 +14942,8 @@
         <v>440</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A201" s="34">
+    <row r="201" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="33">
         <v>200</v>
       </c>
       <c r="B201" s="3" t="s">
@@ -14957,13 +14961,13 @@
       <c r="F201" t="s">
         <v>437</v>
       </c>
-      <c r="G201" t="s">
+      <c r="G201" s="35" t="s">
         <v>426</v>
       </c>
-      <c r="H201" s="3" t="s">
+      <c r="H201" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I201" t="s">
+      <c r="I201" s="35" t="s">
         <v>427</v>
       </c>
       <c r="J201" s="3" t="str">
@@ -15002,8 +15006,8 @@
         <v>440</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A202" s="34">
+    <row r="202" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="33">
         <v>201</v>
       </c>
       <c r="B202" s="3" t="s">
@@ -15021,13 +15025,13 @@
       <c r="F202" t="s">
         <v>436</v>
       </c>
-      <c r="G202" t="s">
+      <c r="G202" s="35" t="s">
         <v>426</v>
       </c>
-      <c r="H202" s="3" t="s">
+      <c r="H202" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I202" t="s">
+      <c r="I202" s="35" t="s">
         <v>427</v>
       </c>
       <c r="J202" s="3" t="str">
@@ -15066,8 +15070,8 @@
         <v>440</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A203" s="34">
+    <row r="203" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="33">
         <v>202</v>
       </c>
       <c r="B203" s="3" t="s">
@@ -15085,13 +15089,13 @@
       <c r="F203" t="s">
         <v>435</v>
       </c>
-      <c r="G203" t="s">
+      <c r="G203" s="35" t="s">
         <v>426</v>
       </c>
-      <c r="H203" s="3" t="s">
+      <c r="H203" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I203" t="s">
+      <c r="I203" s="35" t="s">
         <v>427</v>
       </c>
       <c r="J203" s="3" t="str">
@@ -15130,8 +15134,8 @@
         <v>440</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A204" s="34">
+    <row r="204" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="33">
         <v>203</v>
       </c>
       <c r="B204" s="3" t="s">
@@ -15149,13 +15153,13 @@
       <c r="F204" t="s">
         <v>434</v>
       </c>
-      <c r="G204" t="s">
+      <c r="G204" s="35" t="s">
         <v>426</v>
       </c>
-      <c r="H204" s="3" t="s">
+      <c r="H204" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I204" t="s">
+      <c r="I204" s="35" t="s">
         <v>427</v>
       </c>
       <c r="J204" s="3" t="str">
@@ -15194,8 +15198,8 @@
         <v>440</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A205" s="34">
+    <row r="205" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="33">
         <v>204</v>
       </c>
       <c r="B205" s="3" t="s">
@@ -15213,13 +15217,13 @@
       <c r="F205" t="s">
         <v>271</v>
       </c>
-      <c r="G205" t="s">
+      <c r="G205" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="H205" s="3" t="s">
+      <c r="H205" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I205" s="3" t="s">
+      <c r="I205" s="33" t="s">
         <v>268</v>
       </c>
       <c r="J205" s="3" t="str">
@@ -15258,8 +15262,8 @@
         <v>269</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A206" s="34">
+    <row r="206" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="33">
         <v>205</v>
       </c>
       <c r="B206" s="3" t="s">
@@ -15277,13 +15281,13 @@
       <c r="F206" t="s">
         <v>283</v>
       </c>
-      <c r="G206" t="s">
+      <c r="G206" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="H206" s="3" t="s">
+      <c r="H206" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I206" s="3" t="s">
+      <c r="I206" s="33" t="s">
         <v>268</v>
       </c>
       <c r="J206" s="3" t="str">
@@ -15322,8 +15326,8 @@
         <v>269</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A207" s="34">
+    <row r="207" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="33">
         <v>206</v>
       </c>
       <c r="B207" s="3" t="s">
@@ -15341,13 +15345,13 @@
       <c r="F207" t="s">
         <v>284</v>
       </c>
-      <c r="G207" t="s">
+      <c r="G207" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="H207" s="3" t="s">
+      <c r="H207" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I207" s="3" t="s">
+      <c r="I207" s="33" t="s">
         <v>268</v>
       </c>
       <c r="J207" s="3" t="str">
@@ -15386,8 +15390,8 @@
         <v>269</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A208" s="34">
+    <row r="208" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="33">
         <v>207</v>
       </c>
       <c r="B208" s="3" t="s">
@@ -15405,13 +15409,13 @@
       <c r="F208" t="s">
         <v>285</v>
       </c>
-      <c r="G208" t="s">
+      <c r="G208" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="H208" s="3" t="s">
+      <c r="H208" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I208" s="3" t="s">
+      <c r="I208" s="33" t="s">
         <v>268</v>
       </c>
       <c r="J208" s="3" t="str">
@@ -15450,8 +15454,8 @@
         <v>269</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A209" s="34">
+    <row r="209" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="33">
         <v>208</v>
       </c>
       <c r="B209" s="3" t="s">
@@ -15469,13 +15473,13 @@
       <c r="F209" t="s">
         <v>286</v>
       </c>
-      <c r="G209" t="s">
+      <c r="G209" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="H209" s="3" t="s">
+      <c r="H209" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I209" s="3" t="s">
+      <c r="I209" s="33" t="s">
         <v>268</v>
       </c>
       <c r="J209" s="3" t="str">
@@ -15514,8 +15518,8 @@
         <v>269</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A210" s="34">
+    <row r="210" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="33">
         <v>209</v>
       </c>
       <c r="B210" s="3" t="s">
@@ -15533,13 +15537,13 @@
       <c r="F210" t="s">
         <v>287</v>
       </c>
-      <c r="G210" t="s">
+      <c r="G210" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="H210" s="3" t="s">
+      <c r="H210" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I210" s="3" t="s">
+      <c r="I210" s="33" t="s">
         <v>268</v>
       </c>
       <c r="J210" s="3" t="str">
@@ -15578,8 +15582,8 @@
         <v>269</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A211" s="34">
+    <row r="211" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="33">
         <v>210</v>
       </c>
       <c r="B211" s="3" t="s">
@@ -15597,13 +15601,13 @@
       <c r="F211" t="s">
         <v>288</v>
       </c>
-      <c r="G211" t="s">
+      <c r="G211" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="H211" s="3" t="s">
+      <c r="H211" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I211" s="3" t="s">
+      <c r="I211" s="33" t="s">
         <v>268</v>
       </c>
       <c r="J211" s="3" t="str">
@@ -15642,8 +15646,8 @@
         <v>269</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A212" s="34">
+    <row r="212" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="33">
         <v>211</v>
       </c>
       <c r="B212" s="3" t="s">
@@ -15661,13 +15665,13 @@
       <c r="F212" t="s">
         <v>289</v>
       </c>
-      <c r="G212" t="s">
+      <c r="G212" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="H212" s="3" t="s">
+      <c r="H212" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I212" s="3" t="s">
+      <c r="I212" s="33" t="s">
         <v>268</v>
       </c>
       <c r="J212" s="3" t="str">
@@ -15706,8 +15710,8 @@
         <v>269</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A213" s="34">
+    <row r="213" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="33">
         <v>212</v>
       </c>
       <c r="B213" s="3" t="s">
@@ -15725,13 +15729,13 @@
       <c r="F213" t="s">
         <v>290</v>
       </c>
-      <c r="G213" t="s">
+      <c r="G213" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="H213" s="3" t="s">
+      <c r="H213" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I213" s="3" t="s">
+      <c r="I213" s="33" t="s">
         <v>268</v>
       </c>
       <c r="J213" s="3" t="str">
@@ -15770,8 +15774,8 @@
         <v>269</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A214" s="34">
+    <row r="214" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="33">
         <v>213</v>
       </c>
       <c r="B214" s="3" t="s">
@@ -15789,13 +15793,13 @@
       <c r="F214" t="s">
         <v>291</v>
       </c>
-      <c r="G214" t="s">
+      <c r="G214" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="H214" s="3" t="s">
+      <c r="H214" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I214" s="3" t="s">
+      <c r="I214" s="33" t="s">
         <v>268</v>
       </c>
       <c r="J214" s="3" t="str">
@@ -15834,8 +15838,8 @@
         <v>269</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A215" s="34">
+    <row r="215" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="33">
         <v>214</v>
       </c>
       <c r="B215" s="3" t="s">
@@ -15853,13 +15857,13 @@
       <c r="F215" t="s">
         <v>292</v>
       </c>
-      <c r="G215" t="s">
+      <c r="G215" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="H215" s="3" t="s">
+      <c r="H215" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I215" s="3" t="s">
+      <c r="I215" s="33" t="s">
         <v>268</v>
       </c>
       <c r="J215" s="3" t="str">
@@ -15898,8 +15902,8 @@
         <v>269</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A216" s="34">
+    <row r="216" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A216" s="33">
         <v>215</v>
       </c>
       <c r="B216" s="3" t="s">
@@ -15917,13 +15921,13 @@
       <c r="F216" t="s">
         <v>293</v>
       </c>
-      <c r="G216" t="s">
+      <c r="G216" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="H216" s="3" t="s">
+      <c r="H216" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I216" s="3" t="s">
+      <c r="I216" s="33" t="s">
         <v>268</v>
       </c>
       <c r="J216" s="3" t="str">
@@ -15963,7 +15967,7 @@
       </c>
     </row>
     <row r="217" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A217" s="34">
+      <c r="A217" s="33">
         <v>216</v>
       </c>
       <c r="B217" s="3" t="s">
@@ -15981,13 +15985,13 @@
       <c r="F217" t="s">
         <v>298</v>
       </c>
-      <c r="G217" s="3" t="s">
+      <c r="G217" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="H217" s="3" t="s">
+      <c r="H217" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I217" s="3" t="s">
+      <c r="I217" s="33" t="s">
         <v>295</v>
       </c>
       <c r="J217" s="3" t="str">
@@ -16027,7 +16031,7 @@
       </c>
     </row>
     <row r="218" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A218" s="34">
+      <c r="A218" s="33">
         <v>217</v>
       </c>
       <c r="B218" s="3" t="s">
@@ -16045,13 +16049,13 @@
       <c r="F218" t="s">
         <v>299</v>
       </c>
-      <c r="G218" s="3" t="s">
+      <c r="G218" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="H218" s="3" t="s">
+      <c r="H218" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I218" s="3" t="s">
+      <c r="I218" s="33" t="s">
         <v>295</v>
       </c>
       <c r="J218" s="3" t="str">
@@ -16090,8 +16094,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A219" s="34">
+    <row r="219" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="33">
         <v>218</v>
       </c>
       <c r="B219" s="3" t="s">
@@ -16109,13 +16113,13 @@
       <c r="F219" t="s">
         <v>304</v>
       </c>
-      <c r="G219" s="3" t="s">
+      <c r="G219" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="H219" s="3" t="s">
+      <c r="H219" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I219" s="3" t="s">
+      <c r="I219" s="33" t="s">
         <v>295</v>
       </c>
       <c r="J219" s="3" t="str">
@@ -16154,8 +16158,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A220" s="34">
+    <row r="220" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A220" s="33">
         <v>219</v>
       </c>
       <c r="B220" s="3" t="s">
@@ -16173,13 +16177,13 @@
       <c r="F220" t="s">
         <v>305</v>
       </c>
-      <c r="G220" s="3" t="s">
+      <c r="G220" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="H220" s="3" t="s">
+      <c r="H220" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I220" s="3" t="s">
+      <c r="I220" s="33" t="s">
         <v>295</v>
       </c>
       <c r="J220" s="3" t="str">
@@ -16218,8 +16222,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A221" s="34">
+    <row r="221" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="33">
         <v>220</v>
       </c>
       <c r="B221" s="3" t="s">
@@ -16237,13 +16241,13 @@
       <c r="F221" t="s">
         <v>306</v>
       </c>
-      <c r="G221" s="3" t="s">
+      <c r="G221" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="H221" s="3" t="s">
+      <c r="H221" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I221" s="3" t="s">
+      <c r="I221" s="33" t="s">
         <v>295</v>
       </c>
       <c r="J221" s="3" t="str">
@@ -16282,8 +16286,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A222" s="34">
+    <row r="222" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="33">
         <v>221</v>
       </c>
       <c r="B222" s="3" t="s">
@@ -16301,13 +16305,13 @@
       <c r="F222" t="s">
         <v>307</v>
       </c>
-      <c r="G222" s="3" t="s">
+      <c r="G222" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="H222" s="3" t="s">
+      <c r="H222" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I222" s="3" t="s">
+      <c r="I222" s="33" t="s">
         <v>295</v>
       </c>
       <c r="J222" s="3" t="str">
@@ -17821,7 +17825,13 @@
       <c r="Q466" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:I196" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="B1:I222" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Panulirus meripurpuratus"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Ocorrências Literatura.xlsx
+++ b/Ocorrências Literatura.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faculdade\Laboratorio\lagostas_carapaca\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DEC900-C0A2-4462-B6BE-81BAD4D6D2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074B4B81-D42B-4B22-B984-4BA5AC186470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2129,7 +2129,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:R466"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2150,7 +2149,7 @@
     <col min="19" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -2206,7 +2205,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2270,7 +2269,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33">
         <v>2</v>
       </c>
@@ -2334,7 +2333,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33">
         <v>3</v>
       </c>
@@ -2398,7 +2397,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>4</v>
       </c>
@@ -2462,7 +2461,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="33">
         <v>5</v>
       </c>
@@ -2526,7 +2525,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>6</v>
       </c>
@@ -2590,7 +2589,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="33">
         <v>7</v>
       </c>
@@ -2654,7 +2653,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>8</v>
       </c>
@@ -2718,7 +2717,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <v>9</v>
       </c>
@@ -2782,7 +2781,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
         <v>10</v>
       </c>
@@ -2846,7 +2845,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="33">
         <v>11</v>
       </c>
@@ -2910,7 +2909,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>12</v>
       </c>
@@ -2974,7 +2973,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="33">
         <v>13</v>
       </c>
@@ -3038,7 +3037,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>14</v>
       </c>
@@ -3102,7 +3101,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="16.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="33">
         <v>15</v>
       </c>
@@ -3294,7 +3293,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="33">
         <v>18</v>
       </c>
@@ -3358,7 +3357,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="33">
         <v>19</v>
       </c>
@@ -3422,7 +3421,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="33">
         <v>20</v>
       </c>
@@ -3486,7 +3485,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="33">
         <v>21</v>
       </c>
@@ -3550,7 +3549,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="33">
         <v>22</v>
       </c>
@@ -3614,7 +3613,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="33">
         <v>23</v>
       </c>
@@ -3678,7 +3677,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="33">
         <v>24</v>
       </c>
@@ -3742,7 +3741,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="33">
         <v>25</v>
       </c>
@@ -3806,7 +3805,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="33">
         <v>26</v>
       </c>
@@ -3870,7 +3869,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="33">
         <v>27</v>
       </c>
@@ -3998,7 +3997,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="33">
         <v>29</v>
       </c>
@@ -4062,7 +4061,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="33">
         <v>30</v>
       </c>
@@ -4126,7 +4125,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="33">
         <v>31</v>
       </c>
@@ -4190,7 +4189,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="33">
         <v>32</v>
       </c>
@@ -4254,7 +4253,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="33">
         <v>33</v>
       </c>
@@ -4318,7 +4317,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="33">
         <v>34</v>
       </c>
@@ -4382,7 +4381,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="33">
         <v>35</v>
       </c>
@@ -4446,7 +4445,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="33">
         <v>36</v>
       </c>
@@ -4510,7 +4509,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="33">
         <v>37</v>
       </c>
@@ -4574,7 +4573,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="33">
         <v>38</v>
       </c>
@@ -4638,7 +4637,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="33">
         <v>39</v>
       </c>
@@ -4766,7 +4765,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="33">
         <v>41</v>
       </c>
@@ -4830,7 +4829,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="33">
         <v>42</v>
       </c>
@@ -4958,7 +4957,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="33">
         <v>44</v>
       </c>
@@ -5022,7 +5021,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="33">
         <v>45</v>
       </c>
@@ -5086,7 +5085,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="33">
         <v>46</v>
       </c>
@@ -5150,7 +5149,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="33">
         <v>47</v>
       </c>
@@ -5214,7 +5213,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="33">
         <v>48</v>
       </c>
@@ -5278,7 +5277,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="33">
         <v>49</v>
       </c>
@@ -5342,7 +5341,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="33">
         <v>50</v>
       </c>
@@ -5406,7 +5405,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="33">
         <v>51</v>
       </c>
@@ -5470,7 +5469,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="33">
         <v>52</v>
       </c>
@@ -5534,7 +5533,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="33">
         <v>53</v>
       </c>
@@ -5598,7 +5597,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="33">
         <v>54</v>
       </c>
@@ -5662,7 +5661,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="33">
         <v>55</v>
       </c>
@@ -5726,7 +5725,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="33">
         <v>56</v>
       </c>
@@ -5790,7 +5789,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="33">
         <v>57</v>
       </c>
@@ -5854,7 +5853,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="33">
         <v>58</v>
       </c>
@@ -5918,7 +5917,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="33">
         <v>59</v>
       </c>
@@ -5982,7 +5981,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="33">
         <v>60</v>
       </c>
@@ -6046,7 +6045,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="33">
         <v>61</v>
       </c>
@@ -6110,7 +6109,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="33">
         <v>62</v>
       </c>
@@ -6174,7 +6173,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="33">
         <v>63</v>
       </c>
@@ -6238,7 +6237,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="33">
         <v>64</v>
       </c>
@@ -6302,7 +6301,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="33">
         <v>65</v>
       </c>
@@ -6366,7 +6365,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="33">
         <v>66</v>
       </c>
@@ -6430,7 +6429,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="33">
         <v>67</v>
       </c>
@@ -6494,7 +6493,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="33">
         <v>68</v>
       </c>
@@ -6558,7 +6557,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="33">
         <v>69</v>
       </c>
@@ -6622,7 +6621,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="33">
         <v>70</v>
       </c>
@@ -6686,7 +6685,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="33">
         <v>71</v>
       </c>
@@ -6750,7 +6749,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="33">
         <v>72</v>
       </c>
@@ -6814,7 +6813,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="33">
         <v>73</v>
       </c>
@@ -6878,7 +6877,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="33">
         <v>74</v>
       </c>
@@ -6942,7 +6941,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="33">
         <v>75</v>
       </c>
@@ -7006,7 +7005,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="33">
         <v>76</v>
       </c>
@@ -7070,7 +7069,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="33">
         <v>77</v>
       </c>
@@ -7134,7 +7133,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="33">
         <v>78</v>
       </c>
@@ -7198,7 +7197,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="33">
         <v>79</v>
       </c>
@@ -7262,7 +7261,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="33">
         <v>80</v>
       </c>
@@ -7326,7 +7325,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="33">
         <v>81</v>
       </c>
@@ -7390,7 +7389,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="33">
         <v>82</v>
       </c>
@@ -7454,7 +7453,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="33">
         <v>83</v>
       </c>
@@ -7518,7 +7517,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="33">
         <v>84</v>
       </c>
@@ -7582,7 +7581,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="33">
         <v>85</v>
       </c>
@@ -7646,7 +7645,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="33">
         <v>86</v>
       </c>
@@ -7710,7 +7709,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="33">
         <v>87</v>
       </c>
@@ -7774,7 +7773,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="33">
         <v>88</v>
       </c>
@@ -7838,7 +7837,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="33">
         <v>89</v>
       </c>
@@ -7902,7 +7901,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="33">
         <v>90</v>
       </c>
@@ -7966,7 +7965,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="33">
         <v>91</v>
       </c>
@@ -8030,7 +8029,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="33">
         <v>92</v>
       </c>
@@ -8094,7 +8093,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="33">
         <v>93</v>
       </c>
@@ -8158,7 +8157,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="33">
         <v>94</v>
       </c>
@@ -8222,7 +8221,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="33">
         <v>95</v>
       </c>
@@ -8286,7 +8285,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="33">
         <v>96</v>
       </c>
@@ -8350,7 +8349,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="33">
         <v>97</v>
       </c>
@@ -8414,7 +8413,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="33">
         <v>98</v>
       </c>
@@ -8478,7 +8477,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="33">
         <v>99</v>
       </c>
@@ -8542,7 +8541,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="33">
         <v>100</v>
       </c>
@@ -8606,7 +8605,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="33">
         <v>101</v>
       </c>
@@ -8670,7 +8669,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="33">
         <v>102</v>
       </c>
@@ -8734,7 +8733,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="33">
         <v>103</v>
       </c>
@@ -8798,7 +8797,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="33">
         <v>104</v>
       </c>
@@ -8862,7 +8861,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="33">
         <v>105</v>
       </c>
@@ -8926,7 +8925,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="33">
         <v>106</v>
       </c>
@@ -8990,7 +8989,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="33">
         <v>107</v>
       </c>
@@ -9054,7 +9053,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="33">
         <v>108</v>
       </c>
@@ -9118,7 +9117,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="33">
         <v>109</v>
       </c>
@@ -9182,7 +9181,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="33">
         <v>110</v>
       </c>
@@ -9246,7 +9245,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="33">
         <v>111</v>
       </c>
@@ -9310,7 +9309,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="33">
         <v>112</v>
       </c>
@@ -9374,7 +9373,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="33">
         <v>113</v>
       </c>
@@ -9438,7 +9437,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="33">
         <v>114</v>
       </c>
@@ -9502,7 +9501,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="33">
         <v>115</v>
       </c>
@@ -9566,7 +9565,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="33">
         <v>116</v>
       </c>
@@ -9630,7 +9629,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="33">
         <v>117</v>
       </c>
@@ -9694,7 +9693,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="33">
         <v>118</v>
       </c>
@@ -9758,7 +9757,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="33">
         <v>119</v>
       </c>
@@ -10142,7 +10141,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="33">
         <v>125</v>
       </c>
@@ -10206,7 +10205,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="33">
         <v>126</v>
       </c>
@@ -10270,7 +10269,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="33">
         <v>127</v>
       </c>
@@ -10334,7 +10333,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="33">
         <v>128</v>
       </c>
@@ -10398,7 +10397,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="33">
         <v>129</v>
       </c>
@@ -10462,7 +10461,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="33">
         <v>130</v>
       </c>
@@ -10526,7 +10525,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="33">
         <v>131</v>
       </c>
@@ -10590,7 +10589,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="33">
         <v>132</v>
       </c>
@@ -10654,7 +10653,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="33">
         <v>133</v>
       </c>
@@ -10718,7 +10717,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="33">
         <v>134</v>
       </c>
@@ -10782,7 +10781,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="33">
         <v>135</v>
       </c>
@@ -10846,7 +10845,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="33">
         <v>136</v>
       </c>
@@ -10910,7 +10909,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="33">
         <v>137</v>
       </c>
@@ -10974,7 +10973,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="33">
         <v>138</v>
       </c>
@@ -11038,7 +11037,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="33">
         <v>139</v>
       </c>
@@ -11102,7 +11101,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="33">
         <v>140</v>
       </c>
@@ -11166,7 +11165,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="33">
         <v>141</v>
       </c>
@@ -11230,7 +11229,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="33">
         <v>142</v>
       </c>
@@ -11294,7 +11293,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="33">
         <v>143</v>
       </c>
@@ -11358,7 +11357,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="33">
         <v>144</v>
       </c>
@@ -11422,7 +11421,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="33">
         <v>145</v>
       </c>
@@ -11486,7 +11485,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="33">
         <v>146</v>
       </c>
@@ -11550,7 +11549,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="33">
         <v>147</v>
       </c>
@@ -11614,7 +11613,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="33">
         <v>148</v>
       </c>
@@ -11678,7 +11677,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="33">
         <v>149</v>
       </c>
@@ -11742,7 +11741,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="33">
         <v>150</v>
       </c>
@@ -11806,7 +11805,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="33">
         <v>151</v>
       </c>
@@ -11870,7 +11869,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="33">
         <v>152</v>
       </c>
@@ -11934,7 +11933,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="33">
         <v>153</v>
       </c>
@@ -11998,7 +11997,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="33">
         <v>154</v>
       </c>
@@ -12062,7 +12061,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="33">
         <v>155</v>
       </c>
@@ -12126,7 +12125,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="33">
         <v>156</v>
       </c>
@@ -12190,7 +12189,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="33">
         <v>157</v>
       </c>
@@ -12254,7 +12253,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" s="33">
         <v>158</v>
       </c>
@@ -12318,7 +12317,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" s="33">
         <v>159</v>
       </c>
@@ -12382,7 +12381,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" s="33">
         <v>160</v>
       </c>
@@ -12446,7 +12445,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="33">
         <v>161</v>
       </c>
@@ -12510,7 +12509,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="33">
         <v>162</v>
       </c>
@@ -12574,7 +12573,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="33">
         <v>163</v>
       </c>
@@ -12638,7 +12637,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="33">
         <v>164</v>
       </c>
@@ -12702,7 +12701,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="33">
         <v>165</v>
       </c>
@@ -12766,7 +12765,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="33">
         <v>166</v>
       </c>
@@ -12830,7 +12829,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="33">
         <v>167</v>
       </c>
@@ -12894,7 +12893,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="33">
         <v>168</v>
       </c>
@@ -12958,7 +12957,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="33">
         <v>169</v>
       </c>
@@ -13022,7 +13021,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="33">
         <v>170</v>
       </c>
@@ -13086,7 +13085,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="33">
         <v>171</v>
       </c>
@@ -13150,7 +13149,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="33">
         <v>172</v>
       </c>
@@ -13214,7 +13213,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="33">
         <v>173</v>
       </c>
@@ -13278,7 +13277,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="33">
         <v>174</v>
       </c>
@@ -13342,7 +13341,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="33">
         <v>175</v>
       </c>
@@ -13406,7 +13405,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="33">
         <v>176</v>
       </c>
@@ -13470,7 +13469,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="33">
         <v>177</v>
       </c>
@@ -13534,7 +13533,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="33">
         <v>178</v>
       </c>
@@ -13598,7 +13597,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="33">
         <v>179</v>
       </c>
@@ -13662,7 +13661,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="33">
         <v>180</v>
       </c>
@@ -13726,7 +13725,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="33">
         <v>181</v>
       </c>
@@ -13790,7 +13789,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="33">
         <v>182</v>
       </c>
@@ -13854,7 +13853,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="33">
         <v>183</v>
       </c>
@@ -13918,7 +13917,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="33">
         <v>184</v>
       </c>
@@ -13982,7 +13981,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="33">
         <v>185</v>
       </c>
@@ -14046,7 +14045,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="33">
         <v>186</v>
       </c>
@@ -14110,7 +14109,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="33">
         <v>187</v>
       </c>
@@ -14174,7 +14173,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="33">
         <v>188</v>
       </c>
@@ -14238,7 +14237,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="33">
         <v>189</v>
       </c>
@@ -14302,7 +14301,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" s="33">
         <v>190</v>
       </c>
@@ -14366,7 +14365,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="33">
         <v>191</v>
       </c>
@@ -14430,7 +14429,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="33">
         <v>192</v>
       </c>
@@ -14494,7 +14493,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="33">
         <v>193</v>
       </c>
@@ -14558,7 +14557,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="33">
         <v>194</v>
       </c>
@@ -14622,7 +14621,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="33">
         <v>195</v>
       </c>
@@ -14686,7 +14685,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="33">
         <v>196</v>
       </c>
@@ -14750,7 +14749,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="33">
         <v>197</v>
       </c>
@@ -14814,7 +14813,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" s="33">
         <v>198</v>
       </c>
@@ -14878,7 +14877,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" s="33">
         <v>199</v>
       </c>
@@ -14942,7 +14941,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="33">
         <v>200</v>
       </c>
@@ -15006,7 +15005,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="33">
         <v>201</v>
       </c>
@@ -15070,7 +15069,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" s="33">
         <v>202</v>
       </c>
@@ -15134,7 +15133,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" s="33">
         <v>203</v>
       </c>
@@ -15198,7 +15197,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" s="33">
         <v>204</v>
       </c>
@@ -15262,7 +15261,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" s="33">
         <v>205</v>
       </c>
@@ -15326,7 +15325,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="33">
         <v>206</v>
       </c>
@@ -15390,7 +15389,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="33">
         <v>207</v>
       </c>
@@ -15454,7 +15453,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" s="33">
         <v>208</v>
       </c>
@@ -15518,7 +15517,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="33">
         <v>209</v>
       </c>
@@ -15582,7 +15581,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" s="33">
         <v>210</v>
       </c>
@@ -15646,7 +15645,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" s="33">
         <v>211</v>
       </c>
@@ -15710,7 +15709,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" s="33">
         <v>212</v>
       </c>
@@ -15774,7 +15773,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" s="33">
         <v>213</v>
       </c>
@@ -15838,7 +15837,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" s="33">
         <v>214</v>
       </c>
@@ -15902,7 +15901,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" s="33">
         <v>215</v>
       </c>
@@ -16094,7 +16093,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" s="33">
         <v>218</v>
       </c>
@@ -16158,7 +16157,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" s="33">
         <v>219</v>
       </c>
@@ -16222,7 +16221,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" s="33">
         <v>220</v>
       </c>
@@ -16286,7 +16285,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="33">
         <v>221</v>
       </c>
@@ -17825,13 +17824,7 @@
       <c r="Q466" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:I222" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Panulirus meripurpuratus"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B1:I222" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Ocorrências Literatura.xlsx
+++ b/Ocorrências Literatura.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faculdade\Laboratorio\lagostas_carapaca\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3610A36-3191-4973-B000-CA7AAD9FA4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF239299-B919-482E-844E-8E4D950A8FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ocorrências Panulirus'!$B$1:$I$252</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ocorrências Panulirus'!$B$1:$I$268</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="584">
   <si>
     <t>origem</t>
   </si>
@@ -1723,6 +1723,231 @@
   </si>
   <si>
     <t>34°57′</t>
+  </si>
+  <si>
+    <t>LOPEZTEGUI CASTILLO, Alexander; (2021)</t>
+  </si>
+  <si>
+    <t>22°13′21″</t>
+  </si>
+  <si>
+    <t>22°20′56″</t>
+  </si>
+  <si>
+    <t>22°18′23″</t>
+  </si>
+  <si>
+    <t>22°10′42″</t>
+  </si>
+  <si>
+    <t>22°03′43″</t>
+  </si>
+  <si>
+    <t>21°55′27″</t>
+  </si>
+  <si>
+    <t>21°45′33″</t>
+  </si>
+  <si>
+    <t>21°35′36″</t>
+  </si>
+  <si>
+    <t>21°43′01″</t>
+  </si>
+  <si>
+    <t>21°52′06″</t>
+  </si>
+  <si>
+    <t>22°02′00″</t>
+  </si>
+  <si>
+    <t>81°35′18″</t>
+  </si>
+  <si>
+    <t>81°49′32″</t>
+  </si>
+  <si>
+    <t>82°03′38″</t>
+  </si>
+  <si>
+    <t>82°20′44″</t>
+  </si>
+  <si>
+    <t>82°29′48″</t>
+  </si>
+  <si>
+    <t>82°47′22″</t>
+  </si>
+  <si>
+    <t>83°04′22″</t>
+  </si>
+  <si>
+    <t>83°12′51″</t>
+  </si>
+  <si>
+    <t>83°04′41″</t>
+  </si>
+  <si>
+    <t>82°45′03″</t>
+  </si>
+  <si>
+    <t>82°22′28″</t>
+  </si>
+  <si>
+    <t>82°20′09″</t>
+  </si>
+  <si>
+    <t>0034-7744-rbt-68-04-1346</t>
+  </si>
+  <si>
+    <t>0034-7744-rbt-68-04-1347</t>
+  </si>
+  <si>
+    <t>0034-7744-rbt-68-04-1348</t>
+  </si>
+  <si>
+    <t>0034-7744-rbt-68-04-1349</t>
+  </si>
+  <si>
+    <t>0034-7744-rbt-68-04-1350</t>
+  </si>
+  <si>
+    <t>0034-7744-rbt-68-04-1351</t>
+  </si>
+  <si>
+    <t>0034-7744-rbt-68-04-1352</t>
+  </si>
+  <si>
+    <t>0034-7744-rbt-68-04-1353</t>
+  </si>
+  <si>
+    <t>0034-7744-rbt-68-04-1354</t>
+  </si>
+  <si>
+    <t>0034-7744-rbt-68-04-1355</t>
+  </si>
+  <si>
+    <t>0034-7744-rbt-68-04-1356</t>
+  </si>
+  <si>
+    <t>0034-7744-rbt-68-04-1357</t>
+  </si>
+  <si>
+    <t>0718-1957-revbiolmar-57-01-34</t>
+  </si>
+  <si>
+    <t>MARTÍNEZ-COELLO, Diana (2022)</t>
+  </si>
+  <si>
+    <t>Santa cruz del sur</t>
+  </si>
+  <si>
+    <t>0718-1957-revbiolmar-57-01-35</t>
+  </si>
+  <si>
+    <t>0718-1957-revbiolmar-57-01-36</t>
+  </si>
+  <si>
+    <t>0718-1957-revbiolmar-57-01-37</t>
+  </si>
+  <si>
+    <t>0718-1957-revbiolmar-57-01-38</t>
+  </si>
+  <si>
+    <t>0718-1957-revbiolmar-57-01-39</t>
+  </si>
+  <si>
+    <t>20°32′36″</t>
+  </si>
+  <si>
+    <t>20°40′14″</t>
+  </si>
+  <si>
+    <t>21°01′12″</t>
+  </si>
+  <si>
+    <t>79°11′32″</t>
+  </si>
+  <si>
+    <t>78°41′15″</t>
+  </si>
+  <si>
+    <t>78°21′00″</t>
+  </si>
+  <si>
+    <t>22°02′36″</t>
+  </si>
+  <si>
+    <t>22°05′54″</t>
+  </si>
+  <si>
+    <t>22°01′07″</t>
+  </si>
+  <si>
+    <t>81°21′43″</t>
+  </si>
+  <si>
+    <t>81°33′56″</t>
+  </si>
+  <si>
+    <t>81°38′11″</t>
+  </si>
+  <si>
+    <t>GONZÁLEZ, Oscar(2011)</t>
+  </si>
+  <si>
+    <t>Coast of Costa Rica</t>
+  </si>
+  <si>
+    <t>art17</t>
+  </si>
+  <si>
+    <t>art18</t>
+  </si>
+  <si>
+    <t>art19</t>
+  </si>
+  <si>
+    <t>art20</t>
+  </si>
+  <si>
+    <t>art21</t>
+  </si>
+  <si>
+    <t>art22</t>
+  </si>
+  <si>
+    <t>09°44′15″</t>
+  </si>
+  <si>
+    <t>09°44′48″</t>
+  </si>
+  <si>
+    <t>09°44′36″</t>
+  </si>
+  <si>
+    <t>09°44′29″</t>
+  </si>
+  <si>
+    <t>09°44′16″</t>
+  </si>
+  <si>
+    <t>82°49′28″</t>
+  </si>
+  <si>
+    <t>82°49′19″</t>
+  </si>
+  <si>
+    <t>82°49′08″</t>
+  </si>
+  <si>
+    <t>82°48′23″</t>
+  </si>
+  <si>
+    <t>82°48′32″</t>
+  </si>
+  <si>
+    <t>82°48′30″</t>
   </si>
 </sst>
 </file>
@@ -1868,7 +2093,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1944,9 +2169,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7325,35 +7547,35 @@
         <v>196</v>
       </c>
       <c r="J80" s="22" t="str">
-        <f t="shared" ref="J80:J109" si="24">MID(E80,1,FIND("°",E80,1)-1)</f>
+        <f t="shared" ref="J80:J100" si="24">MID(E80,1,FIND("°",E80,1)-1)</f>
         <v>03</v>
       </c>
       <c r="K80" s="22" t="str">
-        <f t="shared" ref="K80:K109" si="25">MID(E80,FIND("°",E80,1)+1,(FIND("′",E80,1)-FIND("°",E80,1))-1)</f>
+        <f t="shared" ref="K80:K100" si="25">MID(E80,FIND("°",E80,1)+1,(FIND("′",E80,1)-FIND("°",E80,1))-1)</f>
         <v>38</v>
       </c>
       <c r="L80" s="22" t="e">
-        <f t="shared" ref="L80:L109" si="26">MID(E80,FIND("′",E80,1)+1,(FIND("″",E80,1)-FIND("′",E80,1))-1)</f>
+        <f t="shared" ref="L80:L100" si="26">MID(E80,FIND("′",E80,1)+1,(FIND("″",E80,1)-FIND("′",E80,1))-1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="M80" s="22" t="str">
-        <f t="shared" ref="M80:M109" si="27">MID(F80,1,FIND("°",F80,1)-1)</f>
+        <f t="shared" ref="M80:M100" si="27">MID(F80,1,FIND("°",F80,1)-1)</f>
         <v>38</v>
       </c>
       <c r="N80" s="22" t="str">
-        <f t="shared" ref="N80:N109" si="28">MID(F80,FIND("°",F80,1)+1,(FIND("′",F80,1)-FIND("°",F80,1))-1)</f>
+        <f t="shared" ref="N80:N100" si="28">MID(F80,FIND("°",F80,1)+1,(FIND("′",F80,1)-FIND("°",F80,1))-1)</f>
         <v>13</v>
       </c>
       <c r="O80" s="22" t="e">
-        <f t="shared" ref="O80:O109" si="29">MID(F80,FIND("′",F80,1)+1,(FIND("″",F80,1)-FIND("′",F80,1))-1)</f>
+        <f t="shared" ref="O80:O100" si="29">MID(F80,FIND("′",F80,1)+1,(FIND("″",F80,1)-FIND("′",F80,1))-1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="P80" s="21" t="e">
-        <f t="shared" ref="P80:P109" si="30">((((L80/60)+K80)/60)+J80)*IF(C80="S",-1, 1)</f>
+        <f t="shared" ref="P80:P100" si="30">((((L80/60)+K80)/60)+J80)*IF(C80="S",-1, 1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="Q80" s="21" t="e">
-        <f t="shared" ref="Q80:Q109" si="31">((((O80/60)+N80)/60)+M80)*IF(D80="W",-1, 1)</f>
+        <f t="shared" ref="Q80:Q100" si="31">((((O80/60)+N80)/60)+M80)*IF(D80="W",-1, 1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="R80" s="25" t="s">
@@ -9949,35 +10171,35 @@
         <v>72</v>
       </c>
       <c r="J121" s="22" t="str">
-        <f>MID(E121,1,FIND("°",E121,1)-1)</f>
+        <f t="shared" ref="J121:J145" si="40">MID(E121,1,FIND("°",E121,1)-1)</f>
         <v>21</v>
       </c>
       <c r="K121" s="22" t="str">
-        <f>MID(E121,FIND("°",E121,1)+1,(FIND("′",E121,1)-FIND("°",E121,1))-1)</f>
+        <f t="shared" ref="K121:K145" si="41">MID(E121,FIND("°",E121,1)+1,(FIND("′",E121,1)-FIND("°",E121,1))-1)</f>
         <v>34</v>
       </c>
       <c r="L121" s="22" t="e">
-        <f>MID(E121,FIND("′",E121,1)+1,(FIND("″",E121,1)-FIND("′",E121,1))-1)</f>
+        <f t="shared" ref="L121:L145" si="42">MID(E121,FIND("′",E121,1)+1,(FIND("″",E121,1)-FIND("′",E121,1))-1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="M121" s="22" t="str">
-        <f>MID(F121,1,FIND("°",F121,1)-1)</f>
+        <f t="shared" ref="M121:M145" si="43">MID(F121,1,FIND("°",F121,1)-1)</f>
         <v>83</v>
       </c>
       <c r="N121" s="22" t="str">
-        <f>MID(F121,FIND("°",F121,1)+1,(FIND("′",F121,1)-FIND("°",F121,1))-1)</f>
+        <f t="shared" ref="N121:N145" si="44">MID(F121,FIND("°",F121,1)+1,(FIND("′",F121,1)-FIND("°",F121,1))-1)</f>
         <v>31</v>
       </c>
       <c r="O121" s="22" t="e">
-        <f>MID(F121,FIND("′",F121,1)+1,(FIND("″",F121,1)-FIND("′",F121,1))-1)</f>
+        <f t="shared" ref="O121:O145" si="45">MID(F121,FIND("′",F121,1)+1,(FIND("″",F121,1)-FIND("′",F121,1))-1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="P121" s="21" t="e">
-        <f>((((L121/60)+K121)/60)+J121)*IF(C121="S",-1, 1)</f>
+        <f t="shared" ref="P121:P145" si="46">((((L121/60)+K121)/60)+J121)*IF(C121="S",-1, 1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="Q121" s="21" t="e">
-        <f>((((O121/60)+N121)/60)+M121)*IF(D121="W",-1, 1)</f>
+        <f t="shared" ref="Q121:Q145" si="47">((((O121/60)+N121)/60)+M121)*IF(D121="W",-1, 1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="R121" s="25" t="s">
@@ -10013,35 +10235,35 @@
         <v>72</v>
       </c>
       <c r="J122" s="22" t="str">
-        <f>MID(E122,1,FIND("°",E122,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>3</v>
       </c>
       <c r="K122" s="22" t="str">
-        <f>MID(E122,FIND("°",E122,1)+1,(FIND("′",E122,1)-FIND("°",E122,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>32,981</v>
       </c>
       <c r="L122" s="22" t="e">
-        <f>MID(E122,FIND("′",E122,1)+1,(FIND("″",E122,1)-FIND("′",E122,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>#VALUE!</v>
       </c>
       <c r="M122" s="22" t="str">
-        <f>MID(F122,1,FIND("°",F122,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>38</v>
       </c>
       <c r="N122" s="22" t="str">
-        <f>MID(F122,FIND("°",F122,1)+1,(FIND("′",F122,1)-FIND("°",F122,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>48.669</v>
       </c>
       <c r="O122" s="22" t="e">
-        <f>MID(F122,FIND("′",F122,1)+1,(FIND("″",F122,1)-FIND("′",F122,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>#VALUE!</v>
       </c>
       <c r="P122" s="21" t="e">
-        <f>((((L122/60)+K122)/60)+J122)*IF(C122="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>#VALUE!</v>
       </c>
       <c r="Q122" s="21" t="e">
-        <f>((((O122/60)+N122)/60)+M122)*IF(D122="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>#VALUE!</v>
       </c>
       <c r="R122" s="25" t="s">
@@ -10077,35 +10299,35 @@
         <v>186</v>
       </c>
       <c r="J123" s="22" t="str">
-        <f>MID(E123,1,FIND("°",E123,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>02</v>
       </c>
       <c r="K123" s="22" t="str">
-        <f>MID(E123,FIND("°",E123,1)+1,(FIND("′",E123,1)-FIND("°",E123,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>53</v>
       </c>
       <c r="L123" s="22" t="str">
-        <f>MID(E123,FIND("′",E123,1)+1,(FIND("″",E123,1)-FIND("′",E123,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>22</v>
       </c>
       <c r="M123" s="22" t="str">
-        <f>MID(F123,1,FIND("°",F123,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>41</v>
       </c>
       <c r="N123" s="22" t="str">
-        <f>MID(F123,FIND("°",F123,1)+1,(FIND("′",F123,1)-FIND("°",F123,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>13</v>
       </c>
       <c r="O123" s="22" t="str">
-        <f>MID(F123,FIND("′",F123,1)+1,(FIND("″",F123,1)-FIND("′",F123,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>46</v>
       </c>
       <c r="P123" s="21">
-        <f>((((L123/60)+K123)/60)+J123)*IF(C123="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-2.8894444444444445</v>
       </c>
       <c r="Q123" s="21">
-        <f>((((O123/60)+N123)/60)+M123)*IF(D123="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-41.229444444444447</v>
       </c>
       <c r="R123" s="25" t="s">
@@ -10141,35 +10363,35 @@
         <v>186</v>
       </c>
       <c r="J124" s="22" t="str">
-        <f>MID(E124,1,FIND("°",E124,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>04</v>
       </c>
       <c r="K124" s="22" t="str">
-        <f>MID(E124,FIND("°",E124,1)+1,(FIND("′",E124,1)-FIND("°",E124,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>06</v>
       </c>
       <c r="L124" s="22" t="str">
-        <f>MID(E124,FIND("′",E124,1)+1,(FIND("″",E124,1)-FIND("′",E124,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>06</v>
       </c>
       <c r="M124" s="22" t="str">
-        <f>MID(F124,1,FIND("°",F124,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>38</v>
       </c>
       <c r="N124" s="22" t="str">
-        <f>MID(F124,FIND("°",F124,1)+1,(FIND("′",F124,1)-FIND("°",F124,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>08</v>
       </c>
       <c r="O124" s="22" t="str">
-        <f>MID(F124,FIND("′",F124,1)+1,(FIND("″",F124,1)-FIND("′",F124,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>56</v>
       </c>
       <c r="P124" s="21">
-        <f>((((L124/60)+K124)/60)+J124)*IF(C124="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-4.1016666666666666</v>
       </c>
       <c r="Q124" s="21">
-        <f>((((O124/60)+N124)/60)+M124)*IF(D124="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-38.148888888888891</v>
       </c>
       <c r="R124" s="25" t="s">
@@ -10205,35 +10427,35 @@
         <v>442</v>
       </c>
       <c r="J125" s="22" t="str">
-        <f>MID(E125,1,FIND("°",E125,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>04</v>
       </c>
       <c r="K125" s="22" t="str">
-        <f>MID(E125,FIND("°",E125,1)+1,(FIND("′",E125,1)-FIND("°",E125,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>53</v>
       </c>
       <c r="L125" s="22" t="str">
-        <f>MID(E125,FIND("′",E125,1)+1,(FIND("″",E125,1)-FIND("′",E125,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>26</v>
       </c>
       <c r="M125" s="22" t="str">
-        <f>MID(F125,1,FIND("°",F125,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>37</v>
       </c>
       <c r="N125" s="22" t="str">
-        <f>MID(F125,FIND("°",F125,1)+1,(FIND("′",F125,1)-FIND("°",F125,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>14</v>
       </c>
       <c r="O125" s="22" t="str">
-        <f>MID(F125,FIND("′",F125,1)+1,(FIND("″",F125,1)-FIND("′",F125,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>37</v>
       </c>
       <c r="P125" s="21">
-        <f>((((L125/60)+K125)/60)+J125)*IF(C125="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-4.8905555555555553</v>
       </c>
       <c r="Q125" s="21">
-        <f>((((O125/60)+N125)/60)+M125)*IF(D125="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-37.243611111111115</v>
       </c>
       <c r="R125" s="25" t="s">
@@ -10269,35 +10491,35 @@
         <v>442</v>
       </c>
       <c r="J126" s="22" t="str">
-        <f>MID(E126,1,FIND("°",E126,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>05</v>
       </c>
       <c r="K126" s="22" t="str">
-        <f>MID(E126,FIND("°",E126,1)+1,(FIND("′",E126,1)-FIND("°",E126,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>12</v>
       </c>
       <c r="L126" s="22" t="str">
-        <f>MID(E126,FIND("′",E126,1)+1,(FIND("″",E126,1)-FIND("′",E126,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>06</v>
       </c>
       <c r="M126" s="22" t="str">
-        <f>MID(F126,1,FIND("°",F126,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>35</v>
       </c>
       <c r="N126" s="22" t="str">
-        <f>MID(F126,FIND("°",F126,1)+1,(FIND("′",F126,1)-FIND("°",F126,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>27</v>
       </c>
       <c r="O126" s="22" t="str">
-        <f>MID(F126,FIND("′",F126,1)+1,(FIND("″",F126,1)-FIND("′",F126,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>27</v>
       </c>
       <c r="P126" s="21">
-        <f>((((L126/60)+K126)/60)+J126)*IF(C126="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-5.2016666666666662</v>
       </c>
       <c r="Q126" s="21">
-        <f>((((O126/60)+N126)/60)+M126)*IF(D126="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-35.457500000000003</v>
       </c>
       <c r="R126" s="25" t="s">
@@ -10333,35 +10555,35 @@
         <v>443</v>
       </c>
       <c r="J127" s="22" t="str">
-        <f>MID(E127,1,FIND("°",E127,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>06</v>
       </c>
       <c r="K127" s="22" t="str">
-        <f>MID(E127,FIND("°",E127,1)+1,(FIND("′",E127,1)-FIND("°",E127,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>30</v>
       </c>
       <c r="L127" s="22" t="str">
-        <f>MID(E127,FIND("′",E127,1)+1,(FIND("″",E127,1)-FIND("′",E127,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>11</v>
       </c>
       <c r="M127" s="22" t="str">
-        <f>MID(F127,1,FIND("°",F127,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>34</v>
       </c>
       <c r="N127" s="22" t="str">
-        <f>MID(F127,FIND("°",F127,1)+1,(FIND("′",F127,1)-FIND("°",F127,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>57</v>
       </c>
       <c r="O127" s="22" t="str">
-        <f>MID(F127,FIND("′",F127,1)+1,(FIND("″",F127,1)-FIND("′",F127,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>30</v>
       </c>
       <c r="P127" s="21">
-        <f>((((L127/60)+K127)/60)+J127)*IF(C127="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-6.5030555555555551</v>
       </c>
       <c r="Q127" s="21">
-        <f>((((O127/60)+N127)/60)+M127)*IF(D127="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-34.958333333333336</v>
       </c>
       <c r="R127" s="25" t="s">
@@ -10397,35 +10619,35 @@
         <v>443</v>
       </c>
       <c r="J128" s="22" t="str">
-        <f>MID(E128,1,FIND("°",E128,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>06</v>
       </c>
       <c r="K128" s="22" t="str">
-        <f>MID(E128,FIND("°",E128,1)+1,(FIND("′",E128,1)-FIND("°",E128,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>57</v>
       </c>
       <c r="L128" s="22" t="str">
-        <f>MID(E128,FIND("′",E128,1)+1,(FIND("″",E128,1)-FIND("′",E128,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>57</v>
       </c>
       <c r="M128" s="22" t="str">
-        <f>MID(F128,1,FIND("°",F128,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>34</v>
       </c>
       <c r="N128" s="22" t="str">
-        <f>MID(F128,FIND("°",F128,1)+1,(FIND("′",F128,1)-FIND("°",F128,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>51</v>
       </c>
       <c r="O128" s="22" t="str">
-        <f>MID(F128,FIND("′",F128,1)+1,(FIND("″",F128,1)-FIND("′",F128,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>22</v>
       </c>
       <c r="P128" s="21">
-        <f>((((L128/60)+K128)/60)+J128)*IF(C128="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-6.9658333333333333</v>
       </c>
       <c r="Q128" s="21">
-        <f>((((O128/60)+N128)/60)+M128)*IF(D128="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-34.856111111111112</v>
       </c>
       <c r="R128" s="25" t="s">
@@ -10461,35 +10683,35 @@
         <v>444</v>
       </c>
       <c r="J129" s="22" t="str">
-        <f>MID(E129,1,FIND("°",E129,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>07</v>
       </c>
       <c r="K129" s="22" t="str">
-        <f>MID(E129,FIND("°",E129,1)+1,(FIND("′",E129,1)-FIND("°",E129,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>33</v>
       </c>
       <c r="L129" s="22" t="str">
-        <f>MID(E129,FIND("′",E129,1)+1,(FIND("″",E129,1)-FIND("′",E129,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>07</v>
       </c>
       <c r="M129" s="22" t="str">
-        <f>MID(F129,1,FIND("°",F129,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>34</v>
       </c>
       <c r="N129" s="22" t="str">
-        <f>MID(F129,FIND("°",F129,1)+1,(FIND("′",F129,1)-FIND("°",F129,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>50</v>
       </c>
       <c r="O129" s="22" t="str">
-        <f>MID(F129,FIND("′",F129,1)+1,(FIND("″",F129,1)-FIND("′",F129,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>39</v>
       </c>
       <c r="P129" s="21">
-        <f>((((L129/60)+K129)/60)+J129)*IF(C129="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-7.5519444444444446</v>
       </c>
       <c r="Q129" s="21">
-        <f>((((O129/60)+N129)/60)+M129)*IF(D129="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-34.844166666666666</v>
       </c>
       <c r="R129" s="25" t="s">
@@ -10525,35 +10747,35 @@
         <v>444</v>
       </c>
       <c r="J130" s="22" t="str">
-        <f>MID(E130,1,FIND("°",E130,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>08</v>
       </c>
       <c r="K130" s="22" t="str">
-        <f>MID(E130,FIND("°",E130,1)+1,(FIND("′",E130,1)-FIND("°",E130,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>02</v>
       </c>
       <c r="L130" s="22" t="str">
-        <f>MID(E130,FIND("′",E130,1)+1,(FIND("″",E130,1)-FIND("′",E130,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>54</v>
       </c>
       <c r="M130" s="22" t="str">
-        <f>MID(F130,1,FIND("°",F130,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>34</v>
       </c>
       <c r="N130" s="22" t="str">
-        <f>MID(F130,FIND("°",F130,1)+1,(FIND("′",F130,1)-FIND("°",F130,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>52</v>
       </c>
       <c r="O130" s="22" t="str">
-        <f>MID(F130,FIND("′",F130,1)+1,(FIND("″",F130,1)-FIND("′",F130,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>42</v>
       </c>
       <c r="P130" s="21">
-        <f>((((L130/60)+K130)/60)+J130)*IF(C130="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-8.0483333333333338</v>
       </c>
       <c r="Q130" s="21">
-        <f>((((O130/60)+N130)/60)+M130)*IF(D130="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-34.87833333333333</v>
       </c>
       <c r="R130" s="25" t="s">
@@ -10589,35 +10811,35 @@
         <v>186</v>
       </c>
       <c r="J131" s="22" t="str">
-        <f>MID(E131,1,FIND("°",E131,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>02</v>
       </c>
       <c r="K131" s="22" t="str">
-        <f>MID(E131,FIND("°",E131,1)+1,(FIND("′",E131,1)-FIND("°",E131,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>53</v>
       </c>
       <c r="L131" s="22" t="str">
-        <f>MID(E131,FIND("′",E131,1)+1,(FIND("″",E131,1)-FIND("′",E131,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>22</v>
       </c>
       <c r="M131" s="22" t="str">
-        <f>MID(F131,1,FIND("°",F131,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>41</v>
       </c>
       <c r="N131" s="22" t="str">
-        <f>MID(F131,FIND("°",F131,1)+1,(FIND("′",F131,1)-FIND("°",F131,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>13</v>
       </c>
       <c r="O131" s="22" t="str">
-        <f>MID(F131,FIND("′",F131,1)+1,(FIND("″",F131,1)-FIND("′",F131,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>46</v>
       </c>
       <c r="P131" s="21">
-        <f>((((L131/60)+K131)/60)+J131)*IF(C131="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-2.8894444444444445</v>
       </c>
       <c r="Q131" s="21">
-        <f>((((O131/60)+N131)/60)+M131)*IF(D131="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-41.229444444444447</v>
       </c>
       <c r="R131" s="25" t="s">
@@ -10653,35 +10875,35 @@
         <v>186</v>
       </c>
       <c r="J132" s="22" t="str">
-        <f>MID(E132,1,FIND("°",E132,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>04</v>
       </c>
       <c r="K132" s="22" t="str">
-        <f>MID(E132,FIND("°",E132,1)+1,(FIND("′",E132,1)-FIND("°",E132,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>06</v>
       </c>
       <c r="L132" s="22" t="str">
-        <f>MID(E132,FIND("′",E132,1)+1,(FIND("″",E132,1)-FIND("′",E132,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>06</v>
       </c>
       <c r="M132" s="22" t="str">
-        <f>MID(F132,1,FIND("°",F132,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>38</v>
       </c>
       <c r="N132" s="22" t="str">
-        <f>MID(F132,FIND("°",F132,1)+1,(FIND("′",F132,1)-FIND("°",F132,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>08</v>
       </c>
       <c r="O132" s="22" t="str">
-        <f>MID(F132,FIND("′",F132,1)+1,(FIND("″",F132,1)-FIND("′",F132,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>56</v>
       </c>
       <c r="P132" s="21">
-        <f>((((L132/60)+K132)/60)+J132)*IF(C132="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-4.1016666666666666</v>
       </c>
       <c r="Q132" s="21">
-        <f>((((O132/60)+N132)/60)+M132)*IF(D132="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-38.148888888888891</v>
       </c>
       <c r="R132" s="25" t="s">
@@ -10717,35 +10939,35 @@
         <v>442</v>
       </c>
       <c r="J133" s="22" t="str">
-        <f>MID(E133,1,FIND("°",E133,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>04</v>
       </c>
       <c r="K133" s="22" t="str">
-        <f>MID(E133,FIND("°",E133,1)+1,(FIND("′",E133,1)-FIND("°",E133,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>53</v>
       </c>
       <c r="L133" s="22" t="str">
-        <f>MID(E133,FIND("′",E133,1)+1,(FIND("″",E133,1)-FIND("′",E133,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>26</v>
       </c>
       <c r="M133" s="22" t="str">
-        <f>MID(F133,1,FIND("°",F133,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>37</v>
       </c>
       <c r="N133" s="22" t="str">
-        <f>MID(F133,FIND("°",F133,1)+1,(FIND("′",F133,1)-FIND("°",F133,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>14</v>
       </c>
       <c r="O133" s="22" t="str">
-        <f>MID(F133,FIND("′",F133,1)+1,(FIND("″",F133,1)-FIND("′",F133,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>37</v>
       </c>
       <c r="P133" s="21">
-        <f>((((L133/60)+K133)/60)+J133)*IF(C133="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-4.8905555555555553</v>
       </c>
       <c r="Q133" s="21">
-        <f>((((O133/60)+N133)/60)+M133)*IF(D133="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-37.243611111111115</v>
       </c>
       <c r="R133" s="25" t="s">
@@ -10781,35 +11003,35 @@
         <v>442</v>
       </c>
       <c r="J134" s="22" t="str">
-        <f>MID(E134,1,FIND("°",E134,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>05</v>
       </c>
       <c r="K134" s="22" t="str">
-        <f>MID(E134,FIND("°",E134,1)+1,(FIND("′",E134,1)-FIND("°",E134,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>12</v>
       </c>
       <c r="L134" s="22" t="str">
-        <f>MID(E134,FIND("′",E134,1)+1,(FIND("″",E134,1)-FIND("′",E134,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>06</v>
       </c>
       <c r="M134" s="22" t="str">
-        <f>MID(F134,1,FIND("°",F134,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>35</v>
       </c>
       <c r="N134" s="22" t="str">
-        <f>MID(F134,FIND("°",F134,1)+1,(FIND("′",F134,1)-FIND("°",F134,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>27</v>
       </c>
       <c r="O134" s="22" t="str">
-        <f>MID(F134,FIND("′",F134,1)+1,(FIND("″",F134,1)-FIND("′",F134,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>27</v>
       </c>
       <c r="P134" s="21">
-        <f>((((L134/60)+K134)/60)+J134)*IF(C134="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-5.2016666666666662</v>
       </c>
       <c r="Q134" s="21">
-        <f>((((O134/60)+N134)/60)+M134)*IF(D134="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-35.457500000000003</v>
       </c>
       <c r="R134" s="25" t="s">
@@ -10845,35 +11067,35 @@
         <v>443</v>
       </c>
       <c r="J135" s="22" t="str">
-        <f>MID(E135,1,FIND("°",E135,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>06</v>
       </c>
       <c r="K135" s="22" t="str">
-        <f>MID(E135,FIND("°",E135,1)+1,(FIND("′",E135,1)-FIND("°",E135,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>30</v>
       </c>
       <c r="L135" s="22" t="str">
-        <f>MID(E135,FIND("′",E135,1)+1,(FIND("″",E135,1)-FIND("′",E135,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>11</v>
       </c>
       <c r="M135" s="22" t="str">
-        <f>MID(F135,1,FIND("°",F135,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>34</v>
       </c>
       <c r="N135" s="22" t="str">
-        <f>MID(F135,FIND("°",F135,1)+1,(FIND("′",F135,1)-FIND("°",F135,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>57</v>
       </c>
       <c r="O135" s="22" t="str">
-        <f>MID(F135,FIND("′",F135,1)+1,(FIND("″",F135,1)-FIND("′",F135,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>30</v>
       </c>
       <c r="P135" s="21">
-        <f>((((L135/60)+K135)/60)+J135)*IF(C135="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-6.5030555555555551</v>
       </c>
       <c r="Q135" s="21">
-        <f>((((O135/60)+N135)/60)+M135)*IF(D135="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-34.958333333333336</v>
       </c>
       <c r="R135" s="25" t="s">
@@ -10909,35 +11131,35 @@
         <v>443</v>
       </c>
       <c r="J136" s="22" t="str">
-        <f>MID(E136,1,FIND("°",E136,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>06</v>
       </c>
       <c r="K136" s="22" t="str">
-        <f>MID(E136,FIND("°",E136,1)+1,(FIND("′",E136,1)-FIND("°",E136,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>57</v>
       </c>
       <c r="L136" s="22" t="str">
-        <f>MID(E136,FIND("′",E136,1)+1,(FIND("″",E136,1)-FIND("′",E136,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>57</v>
       </c>
       <c r="M136" s="22" t="str">
-        <f>MID(F136,1,FIND("°",F136,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>34</v>
       </c>
       <c r="N136" s="22" t="str">
-        <f>MID(F136,FIND("°",F136,1)+1,(FIND("′",F136,1)-FIND("°",F136,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>51</v>
       </c>
       <c r="O136" s="22" t="str">
-        <f>MID(F136,FIND("′",F136,1)+1,(FIND("″",F136,1)-FIND("′",F136,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>22</v>
       </c>
       <c r="P136" s="21">
-        <f>((((L136/60)+K136)/60)+J136)*IF(C136="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-6.9658333333333333</v>
       </c>
       <c r="Q136" s="21">
-        <f>((((O136/60)+N136)/60)+M136)*IF(D136="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-34.856111111111112</v>
       </c>
       <c r="R136" s="25" t="s">
@@ -10973,35 +11195,35 @@
         <v>444</v>
       </c>
       <c r="J137" s="22" t="str">
-        <f>MID(E137,1,FIND("°",E137,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>07</v>
       </c>
       <c r="K137" s="22" t="str">
-        <f>MID(E137,FIND("°",E137,1)+1,(FIND("′",E137,1)-FIND("°",E137,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>33</v>
       </c>
       <c r="L137" s="22" t="str">
-        <f>MID(E137,FIND("′",E137,1)+1,(FIND("″",E137,1)-FIND("′",E137,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>07</v>
       </c>
       <c r="M137" s="22" t="str">
-        <f>MID(F137,1,FIND("°",F137,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>34</v>
       </c>
       <c r="N137" s="22" t="str">
-        <f>MID(F137,FIND("°",F137,1)+1,(FIND("′",F137,1)-FIND("°",F137,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>50</v>
       </c>
       <c r="O137" s="22" t="str">
-        <f>MID(F137,FIND("′",F137,1)+1,(FIND("″",F137,1)-FIND("′",F137,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>39</v>
       </c>
       <c r="P137" s="21">
-        <f>((((L137/60)+K137)/60)+J137)*IF(C137="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-7.5519444444444446</v>
       </c>
       <c r="Q137" s="21">
-        <f>((((O137/60)+N137)/60)+M137)*IF(D137="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-34.844166666666666</v>
       </c>
       <c r="R137" s="25" t="s">
@@ -11037,35 +11259,35 @@
         <v>444</v>
       </c>
       <c r="J138" s="22" t="str">
-        <f>MID(E138,1,FIND("°",E138,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>08</v>
       </c>
       <c r="K138" s="22" t="str">
-        <f>MID(E138,FIND("°",E138,1)+1,(FIND("′",E138,1)-FIND("°",E138,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>02</v>
       </c>
       <c r="L138" s="22" t="str">
-        <f>MID(E138,FIND("′",E138,1)+1,(FIND("″",E138,1)-FIND("′",E138,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>54</v>
       </c>
       <c r="M138" s="22" t="str">
-        <f>MID(F138,1,FIND("°",F138,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>34</v>
       </c>
       <c r="N138" s="22" t="str">
-        <f>MID(F138,FIND("°",F138,1)+1,(FIND("′",F138,1)-FIND("°",F138,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>52</v>
       </c>
       <c r="O138" s="22" t="str">
-        <f>MID(F138,FIND("′",F138,1)+1,(FIND("″",F138,1)-FIND("′",F138,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>42</v>
       </c>
       <c r="P138" s="21">
-        <f>((((L138/60)+K138)/60)+J138)*IF(C138="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-8.0483333333333338</v>
       </c>
       <c r="Q138" s="21">
-        <f>((((O138/60)+N138)/60)+M138)*IF(D138="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-34.87833333333333</v>
       </c>
       <c r="R138" s="25" t="s">
@@ -11101,35 +11323,35 @@
         <v>307</v>
       </c>
       <c r="J139" s="22" t="str">
-        <f>MID(E139,1,FIND("°",E139,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>01</v>
       </c>
       <c r="K139" s="22" t="str">
-        <f>MID(E139,FIND("°",E139,1)+1,(FIND("′",E139,1)-FIND("°",E139,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>45</v>
       </c>
       <c r="L139" s="22" t="str">
-        <f>MID(E139,FIND("′",E139,1)+1,(FIND("″",E139,1)-FIND("′",E139,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>10</v>
       </c>
       <c r="M139" s="22" t="str">
-        <f>MID(F139,1,FIND("°",F139,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>48</v>
       </c>
       <c r="N139" s="22" t="str">
-        <f>MID(F139,FIND("°",F139,1)+1,(FIND("′",F139,1)-FIND("°",F139,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>12</v>
       </c>
       <c r="O139" s="22" t="str">
-        <f>MID(F139,FIND("′",F139,1)+1,(FIND("″",F139,1)-FIND("′",F139,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>56</v>
       </c>
       <c r="P139" s="21">
-        <f>((((L139/60)+K139)/60)+J139)*IF(C139="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>1.7527777777777778</v>
       </c>
       <c r="Q139" s="21">
-        <f>((((O139/60)+N139)/60)+M139)*IF(D139="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-48.215555555555554</v>
       </c>
       <c r="R139" s="25" t="s">
@@ -11165,35 +11387,35 @@
         <v>307</v>
       </c>
       <c r="J140" s="22" t="str">
-        <f>MID(E140,1,FIND("°",E140,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>01</v>
       </c>
       <c r="K140" s="22" t="str">
-        <f>MID(E140,FIND("°",E140,1)+1,(FIND("′",E140,1)-FIND("°",E140,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>43</v>
       </c>
       <c r="L140" s="22" t="str">
-        <f>MID(E140,FIND("′",E140,1)+1,(FIND("″",E140,1)-FIND("′",E140,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>38</v>
       </c>
       <c r="M140" s="22" t="str">
-        <f>MID(F140,1,FIND("°",F140,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>48</v>
       </c>
       <c r="N140" s="22" t="str">
-        <f>MID(F140,FIND("°",F140,1)+1,(FIND("′",F140,1)-FIND("°",F140,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>26</v>
       </c>
       <c r="O140" s="22" t="str">
-        <f>MID(F140,FIND("′",F140,1)+1,(FIND("″",F140,1)-FIND("′",F140,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>22</v>
       </c>
       <c r="P140" s="21">
-        <f>((((L140/60)+K140)/60)+J140)*IF(C140="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>1.7272222222222222</v>
       </c>
       <c r="Q140" s="21">
-        <f>((((O140/60)+N140)/60)+M140)*IF(D140="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-48.439444444444447</v>
       </c>
       <c r="R140" s="25" t="s">
@@ -11229,35 +11451,35 @@
         <v>307</v>
       </c>
       <c r="J141" s="22" t="str">
-        <f>MID(E141,1,FIND("°",E141,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>02</v>
       </c>
       <c r="K141" s="22" t="str">
-        <f>MID(E141,FIND("°",E141,1)+1,(FIND("′",E141,1)-FIND("°",E141,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>00</v>
       </c>
       <c r="L141" s="22" t="str">
-        <f>MID(E141,FIND("′",E141,1)+1,(FIND("″",E141,1)-FIND("′",E141,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>35</v>
       </c>
       <c r="M141" s="22" t="str">
-        <f>MID(F141,1,FIND("°",F141,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>48</v>
       </c>
       <c r="N141" s="22" t="str">
-        <f>MID(F141,FIND("°",F141,1)+1,(FIND("′",F141,1)-FIND("°",F141,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>12</v>
       </c>
       <c r="O141" s="22" t="str">
-        <f>MID(F141,FIND("′",F141,1)+1,(FIND("″",F141,1)-FIND("′",F141,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>39</v>
       </c>
       <c r="P141" s="21">
-        <f>((((L141/60)+K141)/60)+J141)*IF(C141="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>2.0097222222222224</v>
       </c>
       <c r="Q141" s="21">
-        <f>((((O141/60)+N141)/60)+M141)*IF(D141="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-48.210833333333333</v>
       </c>
       <c r="R141" s="25" t="s">
@@ -11293,35 +11515,35 @@
         <v>307</v>
       </c>
       <c r="J142" s="22" t="str">
-        <f>MID(E142,1,FIND("°",E142,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>02</v>
       </c>
       <c r="K142" s="22" t="str">
-        <f>MID(E142,FIND("°",E142,1)+1,(FIND("′",E142,1)-FIND("°",E142,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>39</v>
       </c>
       <c r="L142" s="22" t="str">
-        <f>MID(E142,FIND("′",E142,1)+1,(FIND("″",E142,1)-FIND("′",E142,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>44</v>
       </c>
       <c r="M142" s="22" t="str">
-        <f>MID(F142,1,FIND("°",F142,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>49</v>
       </c>
       <c r="N142" s="22" t="str">
-        <f>MID(F142,FIND("°",F142,1)+1,(FIND("′",F142,1)-FIND("°",F142,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>08</v>
       </c>
       <c r="O142" s="22" t="str">
-        <f>MID(F142,FIND("′",F142,1)+1,(FIND("″",F142,1)-FIND("′",F142,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>56</v>
       </c>
       <c r="P142" s="21">
-        <f>((((L142/60)+K142)/60)+J142)*IF(C142="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>2.6622222222222223</v>
       </c>
       <c r="Q142" s="21">
-        <f>((((O142/60)+N142)/60)+M142)*IF(D142="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-49.148888888888891</v>
       </c>
       <c r="R142" s="25" t="s">
@@ -11357,35 +11579,35 @@
         <v>307</v>
       </c>
       <c r="J143" s="22" t="str">
-        <f>MID(E143,1,FIND("°",E143,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>03</v>
       </c>
       <c r="K143" s="22" t="str">
-        <f>MID(E143,FIND("°",E143,1)+1,(FIND("′",E143,1)-FIND("°",E143,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>29</v>
       </c>
       <c r="L143" s="22" t="str">
-        <f>MID(E143,FIND("′",E143,1)+1,(FIND("″",E143,1)-FIND("′",E143,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>13</v>
       </c>
       <c r="M143" s="22" t="str">
-        <f>MID(F143,1,FIND("°",F143,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>49</v>
       </c>
       <c r="N143" s="22" t="str">
-        <f>MID(F143,FIND("°",F143,1)+1,(FIND("′",F143,1)-FIND("°",F143,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>47</v>
       </c>
       <c r="O143" s="22" t="str">
-        <f>MID(F143,FIND("′",F143,1)+1,(FIND("″",F143,1)-FIND("′",F143,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>04</v>
       </c>
       <c r="P143" s="21">
-        <f>((((L143/60)+K143)/60)+J143)*IF(C143="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>3.4869444444444442</v>
       </c>
       <c r="Q143" s="21">
-        <f>((((O143/60)+N143)/60)+M143)*IF(D143="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-49.784444444444446</v>
       </c>
       <c r="R143" s="25" t="s">
@@ -11421,35 +11643,35 @@
         <v>320</v>
       </c>
       <c r="J144" s="22" t="str">
-        <f>MID(E144,1,FIND("°",E144,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>07</v>
       </c>
       <c r="K144" s="22" t="str">
-        <f>MID(E144,FIND("°",E144,1)+1,(FIND("′",E144,1)-FIND("°",E144,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>09</v>
       </c>
       <c r="L144" s="22" t="str">
-        <f>MID(E144,FIND("′",E144,1)+1,(FIND("″",E144,1)-FIND("′",E144,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>33</v>
       </c>
       <c r="M144" s="22" t="str">
-        <f>MID(F144,1,FIND("°",F144,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>34</v>
       </c>
       <c r="N144" s="22" t="str">
-        <f>MID(F144,FIND("°",F144,1)+1,(FIND("′",F144,1)-FIND("°",F144,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>47</v>
       </c>
       <c r="O144" s="22" t="str">
-        <f>MID(F144,FIND("′",F144,1)+1,(FIND("″",F144,1)-FIND("′",F144,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>08</v>
       </c>
       <c r="P144" s="21">
-        <f>((((L144/60)+K144)/60)+J144)*IF(C144="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-7.1591666666666667</v>
       </c>
       <c r="Q144" s="21">
-        <f>((((O144/60)+N144)/60)+M144)*IF(D144="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-34.785555555555554</v>
       </c>
       <c r="R144" s="25" t="s">
@@ -11485,35 +11707,35 @@
         <v>321</v>
       </c>
       <c r="J145" s="22" t="str">
-        <f>MID(E145,1,FIND("°",E145,1)-1)</f>
+        <f t="shared" si="40"/>
         <v>07</v>
       </c>
       <c r="K145" s="22" t="str">
-        <f>MID(E145,FIND("°",E145,1)+1,(FIND("′",E145,1)-FIND("°",E145,1))-1)</f>
+        <f t="shared" si="41"/>
         <v>10</v>
       </c>
       <c r="L145" s="22" t="str">
-        <f>MID(E145,FIND("′",E145,1)+1,(FIND("″",E145,1)-FIND("′",E145,1))-1)</f>
+        <f t="shared" si="42"/>
         <v>47</v>
       </c>
       <c r="M145" s="22" t="str">
-        <f>MID(F145,1,FIND("°",F145,1)-1)</f>
+        <f t="shared" si="43"/>
         <v>34</v>
       </c>
       <c r="N145" s="22" t="str">
-        <f>MID(F145,FIND("°",F145,1)+1,(FIND("′",F145,1)-FIND("°",F145,1))-1)</f>
+        <f t="shared" si="44"/>
         <v>46</v>
       </c>
       <c r="O145" s="22" t="str">
-        <f>MID(F145,FIND("′",F145,1)+1,(FIND("″",F145,1)-FIND("′",F145,1))-1)</f>
+        <f t="shared" si="45"/>
         <v>56</v>
       </c>
       <c r="P145" s="21">
-        <f>((((L145/60)+K145)/60)+J145)*IF(C145="S",-1, 1)</f>
+        <f t="shared" si="46"/>
         <v>-7.1797222222222219</v>
       </c>
       <c r="Q145" s="21">
-        <f>((((O145/60)+N145)/60)+M145)*IF(D145="W",-1, 1)</f>
+        <f t="shared" si="47"/>
         <v>-34.782222222222224</v>
       </c>
       <c r="R145" s="25" t="s">
@@ -11549,35 +11771,35 @@
         <v>320</v>
       </c>
       <c r="J146" s="22" t="str">
-        <f t="shared" ref="J146:J161" si="40">MID(E146,1,FIND("°",E146,1)-1)</f>
+        <f t="shared" ref="J146:J161" si="48">MID(E146,1,FIND("°",E146,1)-1)</f>
         <v>07</v>
       </c>
       <c r="K146" s="22" t="str">
-        <f t="shared" ref="K146:K161" si="41">MID(E146,FIND("°",E146,1)+1,(FIND("′",E146,1)-FIND("°",E146,1))-1)</f>
+        <f t="shared" ref="K146:K161" si="49">MID(E146,FIND("°",E146,1)+1,(FIND("′",E146,1)-FIND("°",E146,1))-1)</f>
         <v>09</v>
       </c>
       <c r="L146" s="22" t="str">
-        <f t="shared" ref="L146:L161" si="42">MID(E146,FIND("′",E146,1)+1,(FIND("″",E146,1)-FIND("′",E146,1))-1)</f>
+        <f t="shared" ref="L146:L161" si="50">MID(E146,FIND("′",E146,1)+1,(FIND("″",E146,1)-FIND("′",E146,1))-1)</f>
         <v>33</v>
       </c>
       <c r="M146" s="22" t="str">
-        <f t="shared" ref="M146:M161" si="43">MID(F146,1,FIND("°",F146,1)-1)</f>
+        <f t="shared" ref="M146:M161" si="51">MID(F146,1,FIND("°",F146,1)-1)</f>
         <v>34</v>
       </c>
       <c r="N146" s="22" t="str">
-        <f t="shared" ref="N146:N161" si="44">MID(F146,FIND("°",F146,1)+1,(FIND("′",F146,1)-FIND("°",F146,1))-1)</f>
+        <f t="shared" ref="N146:N161" si="52">MID(F146,FIND("°",F146,1)+1,(FIND("′",F146,1)-FIND("°",F146,1))-1)</f>
         <v>47</v>
       </c>
       <c r="O146" s="22" t="str">
-        <f t="shared" ref="O146:O161" si="45">MID(F146,FIND("′",F146,1)+1,(FIND("″",F146,1)-FIND("′",F146,1))-1)</f>
+        <f t="shared" ref="O146:O161" si="53">MID(F146,FIND("′",F146,1)+1,(FIND("″",F146,1)-FIND("′",F146,1))-1)</f>
         <v>08</v>
       </c>
       <c r="P146" s="21">
-        <f t="shared" ref="P146:P161" si="46">((((L146/60)+K146)/60)+J146)*IF(C146="S",-1, 1)</f>
+        <f t="shared" ref="P146:P161" si="54">((((L146/60)+K146)/60)+J146)*IF(C146="S",-1, 1)</f>
         <v>-7.1591666666666667</v>
       </c>
       <c r="Q146" s="21">
-        <f t="shared" ref="Q146:Q161" si="47">((((O146/60)+N146)/60)+M146)*IF(D146="W",-1, 1)</f>
+        <f t="shared" ref="Q146:Q161" si="55">((((O146/60)+N146)/60)+M146)*IF(D146="W",-1, 1)</f>
         <v>-34.785555555555554</v>
       </c>
       <c r="R146" s="25" t="s">
@@ -11613,35 +11835,35 @@
         <v>321</v>
       </c>
       <c r="J147" s="22" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>07</v>
       </c>
       <c r="K147" s="22" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>10</v>
       </c>
       <c r="L147" s="22" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>47</v>
       </c>
       <c r="M147" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>34</v>
       </c>
       <c r="N147" s="22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>46</v>
       </c>
       <c r="O147" s="22" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>56</v>
       </c>
       <c r="P147" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>-7.1797222222222219</v>
       </c>
       <c r="Q147" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>-34.782222222222224</v>
       </c>
       <c r="R147" s="25" t="s">
@@ -11677,35 +11899,35 @@
         <v>320</v>
       </c>
       <c r="J148" s="22" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>07</v>
       </c>
       <c r="K148" s="22" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>09</v>
       </c>
       <c r="L148" s="22" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>33</v>
       </c>
       <c r="M148" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>34</v>
       </c>
       <c r="N148" s="22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>47</v>
       </c>
       <c r="O148" s="22" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>08</v>
       </c>
       <c r="P148" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>-7.1591666666666667</v>
       </c>
       <c r="Q148" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>-34.785555555555554</v>
       </c>
       <c r="R148" s="25" t="s">
@@ -11741,35 +11963,35 @@
         <v>321</v>
       </c>
       <c r="J149" s="22" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>07</v>
       </c>
       <c r="K149" s="22" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>10</v>
       </c>
       <c r="L149" s="22" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>47</v>
       </c>
       <c r="M149" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>34</v>
       </c>
       <c r="N149" s="22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>46</v>
       </c>
       <c r="O149" s="22" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>56</v>
       </c>
       <c r="P149" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>-7.1797222222222219</v>
       </c>
       <c r="Q149" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>-34.782222222222224</v>
       </c>
       <c r="R149" s="25" t="s">
@@ -11805,35 +12027,35 @@
         <v>80</v>
       </c>
       <c r="J150" s="22" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>08</v>
       </c>
       <c r="K150" s="22" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>30</v>
       </c>
       <c r="L150" s="22" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>41</v>
       </c>
       <c r="M150" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>35</v>
       </c>
       <c r="N150" s="22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>00</v>
       </c>
       <c r="O150" s="22" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>02</v>
       </c>
       <c r="P150" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>-8.511388888888888</v>
       </c>
       <c r="Q150" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>-35.000555555555557</v>
       </c>
       <c r="R150" s="25" t="s">
@@ -11869,35 +12091,35 @@
         <v>80</v>
       </c>
       <c r="J151" s="22" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>08</v>
       </c>
       <c r="K151" s="22" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>30</v>
       </c>
       <c r="L151" s="22" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>31</v>
       </c>
       <c r="M151" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>34</v>
       </c>
       <c r="N151" s="22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>59</v>
       </c>
       <c r="O151" s="22" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>58</v>
       </c>
       <c r="P151" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>-8.5086111111111116</v>
       </c>
       <c r="Q151" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>-34.999444444444443</v>
       </c>
       <c r="R151" s="25" t="s">
@@ -11933,35 +12155,35 @@
         <v>80</v>
       </c>
       <c r="J152" s="22" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>08</v>
       </c>
       <c r="K152" s="22" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>30</v>
       </c>
       <c r="L152" s="22" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>23</v>
       </c>
       <c r="M152" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>34</v>
       </c>
       <c r="N152" s="22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>59</v>
       </c>
       <c r="O152" s="22" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>57</v>
       </c>
       <c r="P152" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>-8.506388888888889</v>
       </c>
       <c r="Q152" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>-34.999166666666667</v>
       </c>
       <c r="R152" s="25" t="s">
@@ -11997,35 +12219,35 @@
         <v>80</v>
       </c>
       <c r="J153" s="22" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>08</v>
       </c>
       <c r="K153" s="22" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>30</v>
       </c>
       <c r="L153" s="22" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>32</v>
       </c>
       <c r="M153" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>34</v>
       </c>
       <c r="N153" s="22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>59</v>
       </c>
       <c r="O153" s="22" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>56</v>
       </c>
       <c r="P153" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>-8.5088888888888885</v>
       </c>
       <c r="Q153" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>-34.998888888888892</v>
       </c>
       <c r="R153" s="25" t="s">
@@ -12061,35 +12283,35 @@
         <v>80</v>
       </c>
       <c r="J154" s="22" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>08</v>
       </c>
       <c r="K154" s="22" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>30</v>
       </c>
       <c r="L154" s="22" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>25</v>
       </c>
       <c r="M154" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>34</v>
       </c>
       <c r="N154" s="22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>59</v>
       </c>
       <c r="O154" s="22" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>54</v>
       </c>
       <c r="P154" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>-8.5069444444444446</v>
       </c>
       <c r="Q154" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>-34.998333333333335</v>
       </c>
       <c r="R154" s="25" t="s">
@@ -12125,35 +12347,35 @@
         <v>80</v>
       </c>
       <c r="J155" s="22" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>08</v>
       </c>
       <c r="K155" s="22" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>30</v>
       </c>
       <c r="L155" s="22" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>23</v>
       </c>
       <c r="M155" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>34</v>
       </c>
       <c r="N155" s="22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>59</v>
       </c>
       <c r="O155" s="22" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>54</v>
       </c>
       <c r="P155" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>-8.506388888888889</v>
       </c>
       <c r="Q155" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>-34.998333333333335</v>
       </c>
       <c r="R155" s="25" t="s">
@@ -12189,35 +12411,35 @@
         <v>80</v>
       </c>
       <c r="J156" s="22" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>08</v>
       </c>
       <c r="K156" s="22" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>30</v>
       </c>
       <c r="L156" s="22" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>21</v>
       </c>
       <c r="M156" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>34</v>
       </c>
       <c r="N156" s="22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>59</v>
       </c>
       <c r="O156" s="22" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>52</v>
       </c>
       <c r="P156" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>-8.5058333333333334</v>
       </c>
       <c r="Q156" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>-34.997777777777777</v>
       </c>
       <c r="R156" s="25" t="s">
@@ -12253,35 +12475,35 @@
         <v>80</v>
       </c>
       <c r="J157" s="22" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>08</v>
       </c>
       <c r="K157" s="22" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>30</v>
       </c>
       <c r="L157" s="22" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>24</v>
       </c>
       <c r="M157" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>34</v>
       </c>
       <c r="N157" s="22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>59</v>
       </c>
       <c r="O157" s="22" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>52</v>
       </c>
       <c r="P157" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>-8.5066666666666659</v>
       </c>
       <c r="Q157" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>-34.997777777777777</v>
       </c>
       <c r="R157" s="25" t="s">
@@ -12317,35 +12539,35 @@
         <v>80</v>
       </c>
       <c r="J158" s="22" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>08</v>
       </c>
       <c r="K158" s="22" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>30</v>
       </c>
       <c r="L158" s="22" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>41</v>
       </c>
       <c r="M158" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>34</v>
       </c>
       <c r="N158" s="22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>59</v>
       </c>
       <c r="O158" s="22" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>56</v>
       </c>
       <c r="P158" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>-8.511388888888888</v>
       </c>
       <c r="Q158" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>-34.998888888888892</v>
       </c>
       <c r="R158" s="25" t="s">
@@ -12381,35 +12603,35 @@
         <v>80</v>
       </c>
       <c r="J159" s="22" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>08</v>
       </c>
       <c r="K159" s="22" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>30</v>
       </c>
       <c r="L159" s="22" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>42</v>
       </c>
       <c r="M159" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>34</v>
       </c>
       <c r="N159" s="22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>59</v>
       </c>
       <c r="O159" s="22" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>55</v>
       </c>
       <c r="P159" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>-8.5116666666666667</v>
       </c>
       <c r="Q159" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>-34.99861111111111</v>
       </c>
       <c r="R159" s="25" t="s">
@@ -12445,35 +12667,35 @@
         <v>80</v>
       </c>
       <c r="J160" s="22" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>08</v>
       </c>
       <c r="K160" s="22" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>30</v>
       </c>
       <c r="L160" s="22" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>41</v>
       </c>
       <c r="M160" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>34</v>
       </c>
       <c r="N160" s="22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>59</v>
       </c>
       <c r="O160" s="22" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>53</v>
       </c>
       <c r="P160" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>-8.511388888888888</v>
       </c>
       <c r="Q160" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>-34.998055555555553</v>
       </c>
       <c r="R160" s="25" t="s">
@@ -12509,35 +12731,35 @@
         <v>80</v>
       </c>
       <c r="J161" s="22" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>08</v>
       </c>
       <c r="K161" s="22" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>30</v>
       </c>
       <c r="L161" s="22" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>42</v>
       </c>
       <c r="M161" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>34</v>
       </c>
       <c r="N161" s="22" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>59</v>
       </c>
       <c r="O161" s="22" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>53</v>
       </c>
       <c r="P161" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>-8.5116666666666667</v>
       </c>
       <c r="Q161" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>-34.998055555555553</v>
       </c>
       <c r="R161" s="25" t="s">
@@ -12573,35 +12795,35 @@
         <v>80</v>
       </c>
       <c r="J162" s="22" t="str">
-        <f t="shared" ref="J162:J185" si="48">MID(E162,1,FIND("°",E162,1)-1)</f>
+        <f t="shared" ref="J162:J185" si="56">MID(E162,1,FIND("°",E162,1)-1)</f>
         <v>08</v>
       </c>
       <c r="K162" s="22" t="str">
-        <f t="shared" ref="K162:K185" si="49">MID(E162,FIND("°",E162,1)+1,(FIND("′",E162,1)-FIND("°",E162,1))-1)</f>
+        <f t="shared" ref="K162:K185" si="57">MID(E162,FIND("°",E162,1)+1,(FIND("′",E162,1)-FIND("°",E162,1))-1)</f>
         <v>30</v>
       </c>
       <c r="L162" s="22" t="str">
-        <f t="shared" ref="L162:L185" si="50">MID(E162,FIND("′",E162,1)+1,(FIND("″",E162,1)-FIND("′",E162,1))-1)</f>
+        <f t="shared" ref="L162:L185" si="58">MID(E162,FIND("′",E162,1)+1,(FIND("″",E162,1)-FIND("′",E162,1))-1)</f>
         <v>41</v>
       </c>
       <c r="M162" s="22" t="str">
-        <f t="shared" ref="M162:M185" si="51">MID(F162,1,FIND("°",F162,1)-1)</f>
+        <f t="shared" ref="M162:M185" si="59">MID(F162,1,FIND("°",F162,1)-1)</f>
         <v>35</v>
       </c>
       <c r="N162" s="22" t="str">
-        <f t="shared" ref="N162:N185" si="52">MID(F162,FIND("°",F162,1)+1,(FIND("′",F162,1)-FIND("°",F162,1))-1)</f>
+        <f t="shared" ref="N162:N185" si="60">MID(F162,FIND("°",F162,1)+1,(FIND("′",F162,1)-FIND("°",F162,1))-1)</f>
         <v>00</v>
       </c>
       <c r="O162" s="22" t="str">
-        <f t="shared" ref="O162:O185" si="53">MID(F162,FIND("′",F162,1)+1,(FIND("″",F162,1)-FIND("′",F162,1))-1)</f>
+        <f t="shared" ref="O162:O185" si="61">MID(F162,FIND("′",F162,1)+1,(FIND("″",F162,1)-FIND("′",F162,1))-1)</f>
         <v>02</v>
       </c>
       <c r="P162" s="21">
-        <f t="shared" ref="P162:P185" si="54">((((L162/60)+K162)/60)+J162)*IF(C162="S",-1, 1)</f>
+        <f t="shared" ref="P162:P185" si="62">((((L162/60)+K162)/60)+J162)*IF(C162="S",-1, 1)</f>
         <v>-8.511388888888888</v>
       </c>
       <c r="Q162" s="21">
-        <f t="shared" ref="Q162:Q185" si="55">((((O162/60)+N162)/60)+M162)*IF(D162="W",-1, 1)</f>
+        <f t="shared" ref="Q162:Q185" si="63">((((O162/60)+N162)/60)+M162)*IF(D162="W",-1, 1)</f>
         <v>-35.000555555555557</v>
       </c>
       <c r="R162" s="25" t="s">
@@ -12637,35 +12859,35 @@
         <v>80</v>
       </c>
       <c r="J163" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K163" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L163" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>31</v>
       </c>
       <c r="M163" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N163" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O163" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>58</v>
       </c>
       <c r="P163" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.5086111111111116</v>
       </c>
       <c r="Q163" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.999444444444443</v>
       </c>
       <c r="R163" s="25" t="s">
@@ -12701,35 +12923,35 @@
         <v>80</v>
       </c>
       <c r="J164" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K164" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L164" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>23</v>
       </c>
       <c r="M164" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N164" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O164" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>57</v>
       </c>
       <c r="P164" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.506388888888889</v>
       </c>
       <c r="Q164" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.999166666666667</v>
       </c>
       <c r="R164" s="25" t="s">
@@ -12765,35 +12987,35 @@
         <v>80</v>
       </c>
       <c r="J165" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K165" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L165" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>32</v>
       </c>
       <c r="M165" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N165" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O165" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>56</v>
       </c>
       <c r="P165" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.5088888888888885</v>
       </c>
       <c r="Q165" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.998888888888892</v>
       </c>
       <c r="R165" s="25" t="s">
@@ -12829,35 +13051,35 @@
         <v>80</v>
       </c>
       <c r="J166" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K166" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L166" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>25</v>
       </c>
       <c r="M166" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N166" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O166" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>54</v>
       </c>
       <c r="P166" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.5069444444444446</v>
       </c>
       <c r="Q166" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.998333333333335</v>
       </c>
       <c r="R166" s="25" t="s">
@@ -12893,35 +13115,35 @@
         <v>80</v>
       </c>
       <c r="J167" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K167" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L167" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>23</v>
       </c>
       <c r="M167" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N167" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O167" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>54</v>
       </c>
       <c r="P167" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.506388888888889</v>
       </c>
       <c r="Q167" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.998333333333335</v>
       </c>
       <c r="R167" s="25" t="s">
@@ -12957,35 +13179,35 @@
         <v>80</v>
       </c>
       <c r="J168" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K168" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L168" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>21</v>
       </c>
       <c r="M168" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N168" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O168" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>52</v>
       </c>
       <c r="P168" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.5058333333333334</v>
       </c>
       <c r="Q168" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.997777777777777</v>
       </c>
       <c r="R168" s="25" t="s">
@@ -13021,35 +13243,35 @@
         <v>80</v>
       </c>
       <c r="J169" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K169" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L169" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>24</v>
       </c>
       <c r="M169" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N169" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O169" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>52</v>
       </c>
       <c r="P169" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.5066666666666659</v>
       </c>
       <c r="Q169" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.997777777777777</v>
       </c>
       <c r="R169" s="25" t="s">
@@ -13085,35 +13307,35 @@
         <v>80</v>
       </c>
       <c r="J170" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K170" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L170" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>41</v>
       </c>
       <c r="M170" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N170" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O170" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>56</v>
       </c>
       <c r="P170" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.511388888888888</v>
       </c>
       <c r="Q170" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.998888888888892</v>
       </c>
       <c r="R170" s="25" t="s">
@@ -13149,35 +13371,35 @@
         <v>80</v>
       </c>
       <c r="J171" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K171" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L171" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>42</v>
       </c>
       <c r="M171" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N171" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O171" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>55</v>
       </c>
       <c r="P171" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.5116666666666667</v>
       </c>
       <c r="Q171" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.99861111111111</v>
       </c>
       <c r="R171" s="25" t="s">
@@ -13213,35 +13435,35 @@
         <v>80</v>
       </c>
       <c r="J172" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K172" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L172" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>41</v>
       </c>
       <c r="M172" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N172" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O172" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>53</v>
       </c>
       <c r="P172" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.511388888888888</v>
       </c>
       <c r="Q172" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.998055555555553</v>
       </c>
       <c r="R172" s="25" t="s">
@@ -13277,35 +13499,35 @@
         <v>80</v>
       </c>
       <c r="J173" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K173" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L173" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>42</v>
       </c>
       <c r="M173" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N173" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O173" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>53</v>
       </c>
       <c r="P173" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.5116666666666667</v>
       </c>
       <c r="Q173" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.998055555555553</v>
       </c>
       <c r="R173" s="25" t="s">
@@ -13341,35 +13563,35 @@
         <v>80</v>
       </c>
       <c r="J174" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K174" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L174" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>41</v>
       </c>
       <c r="M174" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>35</v>
       </c>
       <c r="N174" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>00</v>
       </c>
       <c r="O174" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>02</v>
       </c>
       <c r="P174" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.511388888888888</v>
       </c>
       <c r="Q174" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-35.000555555555557</v>
       </c>
       <c r="R174" s="25" t="s">
@@ -13405,35 +13627,35 @@
         <v>80</v>
       </c>
       <c r="J175" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K175" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L175" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>31</v>
       </c>
       <c r="M175" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N175" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O175" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>58</v>
       </c>
       <c r="P175" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.5086111111111116</v>
       </c>
       <c r="Q175" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.999444444444443</v>
       </c>
       <c r="R175" s="25" t="s">
@@ -13469,35 +13691,35 @@
         <v>80</v>
       </c>
       <c r="J176" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K176" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L176" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>23</v>
       </c>
       <c r="M176" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N176" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O176" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>57</v>
       </c>
       <c r="P176" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.506388888888889</v>
       </c>
       <c r="Q176" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.999166666666667</v>
       </c>
       <c r="R176" s="25" t="s">
@@ -13533,35 +13755,35 @@
         <v>80</v>
       </c>
       <c r="J177" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K177" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L177" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>32</v>
       </c>
       <c r="M177" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N177" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O177" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>56</v>
       </c>
       <c r="P177" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.5088888888888885</v>
       </c>
       <c r="Q177" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.998888888888892</v>
       </c>
       <c r="R177" s="25" t="s">
@@ -13597,35 +13819,35 @@
         <v>80</v>
       </c>
       <c r="J178" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K178" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L178" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>25</v>
       </c>
       <c r="M178" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N178" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O178" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>54</v>
       </c>
       <c r="P178" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.5069444444444446</v>
       </c>
       <c r="Q178" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.998333333333335</v>
       </c>
       <c r="R178" s="25" t="s">
@@ -13661,35 +13883,35 @@
         <v>80</v>
       </c>
       <c r="J179" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K179" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L179" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>23</v>
       </c>
       <c r="M179" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N179" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O179" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>54</v>
       </c>
       <c r="P179" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.506388888888889</v>
       </c>
       <c r="Q179" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.998333333333335</v>
       </c>
       <c r="R179" s="25" t="s">
@@ -13725,35 +13947,35 @@
         <v>80</v>
       </c>
       <c r="J180" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K180" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L180" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>21</v>
       </c>
       <c r="M180" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N180" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O180" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>52</v>
       </c>
       <c r="P180" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.5058333333333334</v>
       </c>
       <c r="Q180" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.997777777777777</v>
       </c>
       <c r="R180" s="25" t="s">
@@ -13789,35 +14011,35 @@
         <v>80</v>
       </c>
       <c r="J181" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K181" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L181" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>24</v>
       </c>
       <c r="M181" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N181" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O181" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>52</v>
       </c>
       <c r="P181" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.5066666666666659</v>
       </c>
       <c r="Q181" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.997777777777777</v>
       </c>
       <c r="R181" s="25" t="s">
@@ -13853,35 +14075,35 @@
         <v>80</v>
       </c>
       <c r="J182" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K182" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L182" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>41</v>
       </c>
       <c r="M182" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N182" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O182" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>56</v>
       </c>
       <c r="P182" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.511388888888888</v>
       </c>
       <c r="Q182" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.998888888888892</v>
       </c>
       <c r="R182" s="25" t="s">
@@ -13917,35 +14139,35 @@
         <v>80</v>
       </c>
       <c r="J183" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K183" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L183" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>42</v>
       </c>
       <c r="M183" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N183" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O183" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>55</v>
       </c>
       <c r="P183" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.5116666666666667</v>
       </c>
       <c r="Q183" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.99861111111111</v>
       </c>
       <c r="R183" s="25" t="s">
@@ -13981,35 +14203,35 @@
         <v>80</v>
       </c>
       <c r="J184" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K184" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L184" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>41</v>
       </c>
       <c r="M184" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N184" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O184" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>53</v>
       </c>
       <c r="P184" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.511388888888888</v>
       </c>
       <c r="Q184" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.998055555555553</v>
       </c>
       <c r="R184" s="25" t="s">
@@ -14045,35 +14267,35 @@
         <v>80</v>
       </c>
       <c r="J185" s="22" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>08</v>
       </c>
       <c r="K185" s="22" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>30</v>
       </c>
       <c r="L185" s="22" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>42</v>
       </c>
       <c r="M185" s="22" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>34</v>
       </c>
       <c r="N185" s="22" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>59</v>
       </c>
       <c r="O185" s="22" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>53</v>
       </c>
       <c r="P185" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>-8.5116666666666667</v>
       </c>
       <c r="Q185" s="21">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>-34.998055555555553</v>
       </c>
       <c r="R185" s="25" t="s">
@@ -14109,35 +14331,35 @@
         <v>361</v>
       </c>
       <c r="J186" s="22" t="str">
-        <f t="shared" ref="J186:J217" si="56">MID(E186,1,FIND("°",E186,1)-1)</f>
+        <f t="shared" ref="J186:J217" si="64">MID(E186,1,FIND("°",E186,1)-1)</f>
         <v>16</v>
       </c>
       <c r="K186" s="22" t="str">
-        <f t="shared" ref="K186:K217" si="57">MID(E186,FIND("°",E186,1)+1,(FIND("′",E186,1)-FIND("°",E186,1))-1)</f>
+        <f t="shared" ref="K186:K217" si="65">MID(E186,FIND("°",E186,1)+1,(FIND("′",E186,1)-FIND("°",E186,1))-1)</f>
         <v>24</v>
       </c>
       <c r="L186" s="22" t="str">
-        <f t="shared" ref="L186:L217" si="58">MID(E186,FIND("′",E186,1)+1,(FIND("″",E186,1)-FIND("′",E186,1))-1)</f>
+        <f t="shared" ref="L186:L217" si="66">MID(E186,FIND("′",E186,1)+1,(FIND("″",E186,1)-FIND("′",E186,1))-1)</f>
         <v>18</v>
       </c>
       <c r="M186" s="22" t="str">
-        <f t="shared" ref="M186:M217" si="59">MID(F186,1,FIND("°",F186,1)-1)</f>
+        <f t="shared" ref="M186:M217" si="67">MID(F186,1,FIND("°",F186,1)-1)</f>
         <v>88</v>
       </c>
       <c r="N186" s="22" t="str">
-        <f t="shared" ref="N186:N217" si="60">MID(F186,FIND("°",F186,1)+1,(FIND("′",F186,1)-FIND("°",F186,1))-1)</f>
+        <f t="shared" ref="N186:N217" si="68">MID(F186,FIND("°",F186,1)+1,(FIND("′",F186,1)-FIND("°",F186,1))-1)</f>
         <v>10</v>
       </c>
       <c r="O186" s="22" t="str">
-        <f t="shared" ref="O186:O217" si="61">MID(F186,FIND("′",F186,1)+1,(FIND("″",F186,1)-FIND("′",F186,1))-1)</f>
+        <f t="shared" ref="O186:O217" si="69">MID(F186,FIND("′",F186,1)+1,(FIND("″",F186,1)-FIND("′",F186,1))-1)</f>
         <v>42</v>
       </c>
       <c r="P186" s="21">
-        <f t="shared" ref="P186:P217" si="62">((((L186/60)+K186)/60)+J186)*IF(C186="S",-1, 1)</f>
+        <f t="shared" ref="P186:P217" si="70">((((L186/60)+K186)/60)+J186)*IF(C186="S",-1, 1)</f>
         <v>16.405000000000001</v>
       </c>
       <c r="Q186" s="21">
-        <f t="shared" ref="Q186:Q217" si="63">((((O186/60)+N186)/60)+M186)*IF(D186="W",-1, 1)</f>
+        <f t="shared" ref="Q186:Q217" si="71">((((O186/60)+N186)/60)+M186)*IF(D186="W",-1, 1)</f>
         <v>-88.178333333333327</v>
       </c>
       <c r="R186" s="25" t="s">
@@ -14173,35 +14395,35 @@
         <v>362</v>
       </c>
       <c r="J187" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>19</v>
       </c>
       <c r="K187" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>09</v>
       </c>
       <c r="L187" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>17</v>
       </c>
       <c r="M187" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>87</v>
       </c>
       <c r="N187" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>11</v>
       </c>
       <c r="O187" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>43</v>
       </c>
       <c r="P187" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>19.154722222222222</v>
       </c>
       <c r="Q187" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-87.195277777777775</v>
       </c>
       <c r="R187" s="25" t="s">
@@ -14237,35 +14459,35 @@
         <v>364</v>
       </c>
       <c r="J188" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>21</v>
       </c>
       <c r="K188" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>53</v>
       </c>
       <c r="L188" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>01</v>
       </c>
       <c r="M188" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>81</v>
       </c>
       <c r="N188" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>42</v>
       </c>
       <c r="O188" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>21</v>
       </c>
       <c r="P188" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>21.883611111111112</v>
       </c>
       <c r="Q188" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-81.705833333333331</v>
       </c>
       <c r="R188" s="25" t="s">
@@ -14301,35 +14523,35 @@
         <v>363</v>
       </c>
       <c r="J189" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>17</v>
       </c>
       <c r="K189" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>46</v>
       </c>
       <c r="L189" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>53</v>
       </c>
       <c r="M189" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>65</v>
       </c>
       <c r="N189" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>07</v>
       </c>
       <c r="O189" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>50</v>
       </c>
       <c r="P189" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>17.781388888888888</v>
       </c>
       <c r="Q189" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-65.13055555555556</v>
       </c>
       <c r="R189" s="25" t="s">
@@ -14365,35 +14587,35 @@
         <v>365</v>
       </c>
       <c r="J190" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>15</v>
       </c>
       <c r="K190" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>49</v>
       </c>
       <c r="L190" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>37</v>
       </c>
       <c r="M190" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>62</v>
       </c>
       <c r="N190" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>10</v>
       </c>
       <c r="O190" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>49</v>
       </c>
       <c r="P190" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>15.826944444444445</v>
       </c>
       <c r="Q190" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-62.180277777777775</v>
       </c>
       <c r="R190" s="25" t="s">
@@ -14429,35 +14651,35 @@
         <v>366</v>
       </c>
       <c r="J191" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>24</v>
       </c>
       <c r="K191" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>28</v>
       </c>
       <c r="L191" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>24</v>
       </c>
       <c r="M191" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>81</v>
       </c>
       <c r="N191" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>03</v>
       </c>
       <c r="O191" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>19</v>
       </c>
       <c r="P191" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>24.473333333333333</v>
       </c>
       <c r="Q191" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-81.055277777777775</v>
       </c>
       <c r="R191" s="25" t="s">
@@ -14493,35 +14715,35 @@
         <v>370</v>
       </c>
       <c r="J192" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>12</v>
       </c>
       <c r="K192" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>11</v>
       </c>
       <c r="L192" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>35</v>
       </c>
       <c r="M192" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>83</v>
       </c>
       <c r="N192" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>25</v>
       </c>
       <c r="O192" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>46</v>
       </c>
       <c r="P192" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>12.193055555555556</v>
       </c>
       <c r="Q192" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-83.429444444444442</v>
       </c>
       <c r="R192" s="25" t="s">
@@ -14557,35 +14779,35 @@
         <v>370</v>
       </c>
       <c r="J193" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>15</v>
       </c>
       <c r="K193" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>27</v>
       </c>
       <c r="L193" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>28</v>
       </c>
       <c r="M193" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>83</v>
       </c>
       <c r="N193" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>42</v>
       </c>
       <c r="O193" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>30</v>
       </c>
       <c r="P193" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>15.457777777777778</v>
       </c>
       <c r="Q193" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-83.708333333333329</v>
       </c>
       <c r="R193" s="25" t="s">
@@ -14621,35 +14843,35 @@
         <v>370</v>
       </c>
       <c r="J194" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>16</v>
       </c>
       <c r="K194" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>06</v>
       </c>
       <c r="L194" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>27</v>
       </c>
       <c r="M194" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>86</v>
       </c>
       <c r="N194" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>00</v>
       </c>
       <c r="O194" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>39</v>
       </c>
       <c r="P194" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>16.107500000000002</v>
       </c>
       <c r="Q194" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-86.010833333333338</v>
       </c>
       <c r="R194" s="25" t="s">
@@ -14685,35 +14907,35 @@
         <v>370</v>
       </c>
       <c r="J195" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>15</v>
       </c>
       <c r="K195" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>58</v>
       </c>
       <c r="L195" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>47</v>
       </c>
       <c r="M195" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>87</v>
       </c>
       <c r="N195" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>42</v>
       </c>
       <c r="O195" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>42</v>
       </c>
       <c r="P195" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>15.979722222222222</v>
       </c>
       <c r="Q195" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-87.711666666666673</v>
       </c>
       <c r="R195" s="25" t="s">
@@ -14749,35 +14971,35 @@
         <v>370</v>
       </c>
       <c r="J196" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>16</v>
       </c>
       <c r="K196" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>54</v>
       </c>
       <c r="L196" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>33</v>
       </c>
       <c r="M196" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>88</v>
       </c>
       <c r="N196" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>02</v>
       </c>
       <c r="O196" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>54</v>
       </c>
       <c r="P196" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>16.909166666666668</v>
       </c>
       <c r="Q196" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-88.048333333333332</v>
       </c>
       <c r="R196" s="25" t="s">
@@ -14813,35 +15035,35 @@
         <v>381</v>
       </c>
       <c r="J197" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>21</v>
       </c>
       <c r="K197" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>36</v>
       </c>
       <c r="L197" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>45</v>
       </c>
       <c r="M197" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>89</v>
       </c>
       <c r="N197" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>31</v>
       </c>
       <c r="O197" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>40</v>
       </c>
       <c r="P197" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>21.612500000000001</v>
       </c>
       <c r="Q197" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-89.527777777777771</v>
       </c>
       <c r="R197" s="25" t="s">
@@ -14877,35 +15099,35 @@
         <v>381</v>
       </c>
       <c r="J198" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>19</v>
       </c>
       <c r="K198" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>16</v>
       </c>
       <c r="L198" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>24</v>
       </c>
       <c r="M198" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>81</v>
       </c>
       <c r="N198" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>14</v>
       </c>
       <c r="O198" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>12</v>
       </c>
       <c r="P198" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>19.273333333333333</v>
       </c>
       <c r="Q198" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-81.236666666666665</v>
       </c>
       <c r="R198" s="25" t="s">
@@ -14941,35 +15163,35 @@
         <v>381</v>
       </c>
       <c r="J199" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>19</v>
       </c>
       <c r="K199" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>40</v>
       </c>
       <c r="L199" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>37</v>
       </c>
       <c r="M199" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>80</v>
       </c>
       <c r="N199" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>01</v>
       </c>
       <c r="O199" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>17</v>
       </c>
       <c r="P199" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>19.676944444444445</v>
       </c>
       <c r="Q199" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-80.021388888888893</v>
       </c>
       <c r="R199" s="25" t="s">
@@ -15005,35 +15227,35 @@
         <v>381</v>
       </c>
       <c r="J200" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>19</v>
       </c>
       <c r="K200" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>53</v>
       </c>
       <c r="L200" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>57</v>
       </c>
       <c r="M200" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>75</v>
       </c>
       <c r="N200" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>00</v>
       </c>
       <c r="O200" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>52</v>
       </c>
       <c r="P200" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>19.899166666666666</v>
       </c>
       <c r="Q200" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-75.01444444444445</v>
       </c>
       <c r="R200" s="25" t="s">
@@ -15069,35 +15291,35 @@
         <v>381</v>
       </c>
       <c r="J201" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>18</v>
       </c>
       <c r="K201" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>21</v>
       </c>
       <c r="L201" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>10</v>
       </c>
       <c r="M201" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>69</v>
       </c>
       <c r="N201" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>52</v>
       </c>
       <c r="O201" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>10</v>
       </c>
       <c r="P201" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>18.352777777777778</v>
       </c>
       <c r="Q201" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-69.86944444444444</v>
       </c>
       <c r="R201" s="25" t="s">
@@ -15133,35 +15355,35 @@
         <v>381</v>
       </c>
       <c r="J202" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>19</v>
       </c>
       <c r="K202" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>42</v>
       </c>
       <c r="L202" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>37</v>
       </c>
       <c r="M202" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>70</v>
       </c>
       <c r="N202" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>03</v>
       </c>
       <c r="O202" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>14</v>
       </c>
       <c r="P202" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>19.710277777777776</v>
       </c>
       <c r="Q202" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-70.053888888888892</v>
       </c>
       <c r="R202" s="25" t="s">
@@ -15197,35 +15419,35 @@
         <v>381</v>
       </c>
       <c r="J203" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>17</v>
       </c>
       <c r="K203" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>55</v>
       </c>
       <c r="L203" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>50</v>
       </c>
       <c r="M203" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>66</v>
       </c>
       <c r="N203" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>21</v>
       </c>
       <c r="O203" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>14</v>
       </c>
       <c r="P203" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>17.930555555555557</v>
       </c>
       <c r="Q203" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-66.353888888888889</v>
       </c>
       <c r="R203" s="25" t="s">
@@ -15261,35 +15483,35 @@
         <v>396</v>
       </c>
       <c r="J204" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>17</v>
       </c>
       <c r="K204" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>15</v>
       </c>
       <c r="L204" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>20</v>
       </c>
       <c r="M204" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>62</v>
       </c>
       <c r="N204" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>42</v>
       </c>
       <c r="O204" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>40</v>
       </c>
       <c r="P204" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>17.255555555555556</v>
       </c>
       <c r="Q204" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-62.711111111111109</v>
       </c>
       <c r="R204" s="25" t="s">
@@ -15325,35 +15547,35 @@
         <v>396</v>
       </c>
       <c r="J205" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>14</v>
       </c>
       <c r="K205" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>33</v>
       </c>
       <c r="L205" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>56</v>
       </c>
       <c r="M205" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>61</v>
       </c>
       <c r="N205" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>03</v>
       </c>
       <c r="O205" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>00</v>
       </c>
       <c r="P205" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>14.565555555555555</v>
       </c>
       <c r="Q205" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-61.05</v>
       </c>
       <c r="R205" s="25" t="s">
@@ -15389,35 +15611,35 @@
         <v>396</v>
       </c>
       <c r="J206" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>11</v>
       </c>
       <c r="K206" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>03</v>
       </c>
       <c r="L206" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>46</v>
       </c>
       <c r="M206" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>64</v>
       </c>
       <c r="N206" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>01</v>
       </c>
       <c r="O206" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>30</v>
       </c>
       <c r="P206" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>11.062777777777777</v>
       </c>
       <c r="Q206" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-64.025000000000006</v>
       </c>
       <c r="R206" s="25" t="s">
@@ -15453,35 +15675,35 @@
         <v>396</v>
       </c>
       <c r="J207" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>10</v>
       </c>
       <c r="K207" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>57</v>
       </c>
       <c r="L207" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>51</v>
       </c>
       <c r="M207" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>65</v>
       </c>
       <c r="N207" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>15</v>
       </c>
       <c r="O207" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>53</v>
       </c>
       <c r="P207" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>10.964166666666667</v>
       </c>
       <c r="Q207" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-65.264722222222218</v>
       </c>
       <c r="R207" s="25" t="s">
@@ -15517,35 +15739,35 @@
         <v>396</v>
       </c>
       <c r="J208" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>12</v>
       </c>
       <c r="K208" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>02</v>
       </c>
       <c r="L208" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>08</v>
       </c>
       <c r="M208" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>68</v>
       </c>
       <c r="N208" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>49</v>
       </c>
       <c r="O208" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>30</v>
       </c>
       <c r="P208" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>12.035555555555556</v>
       </c>
       <c r="Q208" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-68.825000000000003</v>
       </c>
       <c r="R208" s="25" t="s">
@@ -15581,35 +15803,35 @@
         <v>396</v>
       </c>
       <c r="J209" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>12</v>
       </c>
       <c r="K209" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>22</v>
       </c>
       <c r="L209" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>32</v>
       </c>
       <c r="M209" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>69</v>
       </c>
       <c r="N209" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>06</v>
       </c>
       <c r="O209" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>45</v>
       </c>
       <c r="P209" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>12.375555555555556</v>
       </c>
       <c r="Q209" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-69.112499999999997</v>
       </c>
       <c r="R209" s="25" t="s">
@@ -15645,35 +15867,35 @@
         <v>409</v>
       </c>
       <c r="J210" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>23</v>
       </c>
       <c r="K210" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>10</v>
       </c>
       <c r="L210" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>42</v>
       </c>
       <c r="M210" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>75</v>
       </c>
       <c r="N210" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>04</v>
       </c>
       <c r="O210" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>08</v>
       </c>
       <c r="P210" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>23.178333333333335</v>
       </c>
       <c r="Q210" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-75.068888888888893</v>
       </c>
       <c r="R210" s="25" t="s">
@@ -15709,35 +15931,35 @@
         <v>409</v>
       </c>
       <c r="J211" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>25</v>
       </c>
       <c r="K211" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>09</v>
       </c>
       <c r="L211" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>08</v>
       </c>
       <c r="M211" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>76</v>
       </c>
       <c r="N211" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>07</v>
       </c>
       <c r="O211" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>55</v>
       </c>
       <c r="P211" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>25.152222222222221</v>
       </c>
       <c r="Q211" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-76.131944444444443</v>
       </c>
       <c r="R211" s="25" t="s">
@@ -15773,35 +15995,35 @@
         <v>409</v>
       </c>
       <c r="J212" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>23</v>
       </c>
       <c r="K212" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>37</v>
       </c>
       <c r="L212" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>51</v>
       </c>
       <c r="M212" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>77</v>
       </c>
       <c r="N212" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>40</v>
       </c>
       <c r="O212" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>56</v>
       </c>
       <c r="P212" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>23.630833333333335</v>
       </c>
       <c r="Q212" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-77.682222222222222</v>
       </c>
       <c r="R212" s="25" t="s">
@@ -15837,35 +16059,35 @@
         <v>409</v>
       </c>
       <c r="J213" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>24</v>
       </c>
       <c r="K213" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>22</v>
       </c>
       <c r="L213" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>23</v>
       </c>
       <c r="M213" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>78</v>
       </c>
       <c r="N213" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>08</v>
       </c>
       <c r="O213" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>46</v>
       </c>
       <c r="P213" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>24.373055555555556</v>
       </c>
       <c r="Q213" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-78.146111111111111</v>
       </c>
       <c r="R213" s="25" t="s">
@@ -15901,35 +16123,35 @@
         <v>409</v>
       </c>
       <c r="J214" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>24</v>
       </c>
       <c r="K214" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>38</v>
       </c>
       <c r="L214" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>59</v>
       </c>
       <c r="M214" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>78</v>
       </c>
       <c r="N214" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>29</v>
       </c>
       <c r="O214" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>17</v>
       </c>
       <c r="P214" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>24.649722222222223</v>
       </c>
       <c r="Q214" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-78.488055555555562</v>
       </c>
       <c r="R214" s="25" t="s">
@@ -15965,35 +16187,35 @@
         <v>409</v>
       </c>
       <c r="J215" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>25</v>
       </c>
       <c r="K215" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>45</v>
       </c>
       <c r="L215" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>28</v>
       </c>
       <c r="M215" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>77</v>
       </c>
       <c r="N215" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>52</v>
       </c>
       <c r="O215" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>41</v>
       </c>
       <c r="P215" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>25.757777777777779</v>
       </c>
       <c r="Q215" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-77.878055555555562</v>
       </c>
       <c r="R215" s="25" t="s">
@@ -16029,35 +16251,35 @@
         <v>409</v>
       </c>
       <c r="J216" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>26</v>
       </c>
       <c r="K216" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>35</v>
       </c>
       <c r="L216" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>20</v>
       </c>
       <c r="M216" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>78</v>
       </c>
       <c r="N216" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>43</v>
       </c>
       <c r="O216" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>54</v>
       </c>
       <c r="P216" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>26.588888888888889</v>
       </c>
       <c r="Q216" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-78.731666666666669</v>
       </c>
       <c r="R216" s="25" t="s">
@@ -16093,35 +16315,35 @@
         <v>425</v>
       </c>
       <c r="J217" s="22" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>25</v>
       </c>
       <c r="K217" s="22" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>32</v>
       </c>
       <c r="L217" s="22" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>00</v>
       </c>
       <c r="M217" s="22" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>79</v>
       </c>
       <c r="N217" s="22" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>17</v>
       </c>
       <c r="O217" s="22" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>00</v>
       </c>
       <c r="P217" s="21">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>25.533333333333335</v>
       </c>
       <c r="Q217" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>-79.283333333333331</v>
       </c>
       <c r="R217" s="25" t="s">
@@ -16157,35 +16379,35 @@
         <v>425</v>
       </c>
       <c r="J218" s="22" t="str">
-        <f t="shared" ref="J218:J222" si="64">MID(E218,1,FIND("°",E218,1)-1)</f>
+        <f t="shared" ref="J218:J222" si="72">MID(E218,1,FIND("°",E218,1)-1)</f>
         <v>25</v>
       </c>
       <c r="K218" s="22" t="str">
-        <f t="shared" ref="K218:K222" si="65">MID(E218,FIND("°",E218,1)+1,(FIND("′",E218,1)-FIND("°",E218,1))-1)</f>
+        <f t="shared" ref="K218:K222" si="73">MID(E218,FIND("°",E218,1)+1,(FIND("′",E218,1)-FIND("°",E218,1))-1)</f>
         <v>40</v>
       </c>
       <c r="L218" s="22" t="str">
-        <f t="shared" ref="L218:L222" si="66">MID(E218,FIND("′",E218,1)+1,(FIND("″",E218,1)-FIND("′",E218,1))-1)</f>
+        <f t="shared" ref="L218:L222" si="74">MID(E218,FIND("′",E218,1)+1,(FIND("″",E218,1)-FIND("′",E218,1))-1)</f>
         <v>15</v>
       </c>
       <c r="M218" s="22" t="str">
-        <f t="shared" ref="M218:M222" si="67">MID(F218,1,FIND("°",F218,1)-1)</f>
+        <f t="shared" ref="M218:M222" si="75">MID(F218,1,FIND("°",F218,1)-1)</f>
         <v>79</v>
       </c>
       <c r="N218" s="22" t="str">
-        <f t="shared" ref="N218:N222" si="68">MID(F218,FIND("°",F218,1)+1,(FIND("′",F218,1)-FIND("°",F218,1))-1)</f>
+        <f t="shared" ref="N218:N222" si="76">MID(F218,FIND("°",F218,1)+1,(FIND("′",F218,1)-FIND("°",F218,1))-1)</f>
         <v>18</v>
       </c>
       <c r="O218" s="22" t="str">
-        <f t="shared" ref="O218:O222" si="69">MID(F218,FIND("′",F218,1)+1,(FIND("″",F218,1)-FIND("′",F218,1))-1)</f>
+        <f t="shared" ref="O218:O222" si="77">MID(F218,FIND("′",F218,1)+1,(FIND("″",F218,1)-FIND("′",F218,1))-1)</f>
         <v>30</v>
       </c>
       <c r="P218" s="21">
-        <f t="shared" ref="P218:P222" si="70">((((L218/60)+K218)/60)+J218)*IF(C218="S",-1, 1)</f>
+        <f t="shared" ref="P218:P222" si="78">((((L218/60)+K218)/60)+J218)*IF(C218="S",-1, 1)</f>
         <v>25.670833333333334</v>
       </c>
       <c r="Q218" s="21">
-        <f t="shared" ref="Q218:Q222" si="71">((((O218/60)+N218)/60)+M218)*IF(D218="W",-1, 1)</f>
+        <f t="shared" ref="Q218:Q222" si="79">((((O218/60)+N218)/60)+M218)*IF(D218="W",-1, 1)</f>
         <v>-79.308333333333337</v>
       </c>
       <c r="R218" s="25" t="s">
@@ -16221,35 +16443,35 @@
         <v>425</v>
       </c>
       <c r="J219" s="22" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="72"/>
         <v>25</v>
       </c>
       <c r="K219" s="22" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="73"/>
         <v>44</v>
       </c>
       <c r="L219" s="22" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="74"/>
         <v>51</v>
       </c>
       <c r="M219" s="22" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="75"/>
         <v>79</v>
       </c>
       <c r="N219" s="22" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="76"/>
         <v>17</v>
       </c>
       <c r="O219" s="22" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>49</v>
       </c>
       <c r="P219" s="21">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>25.747499999999999</v>
       </c>
       <c r="Q219" s="21">
-        <f t="shared" si="71"/>
+        <f t="shared" si="79"/>
         <v>-79.296944444444449</v>
       </c>
       <c r="R219" s="25" t="s">
@@ -16285,35 +16507,35 @@
         <v>425</v>
       </c>
       <c r="J220" s="22" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="72"/>
         <v>25</v>
       </c>
       <c r="K220" s="22" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="73"/>
         <v>47</v>
       </c>
       <c r="L220" s="22" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="74"/>
         <v>19</v>
       </c>
       <c r="M220" s="22" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="75"/>
         <v>79</v>
       </c>
       <c r="N220" s="22" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="76"/>
         <v>15</v>
       </c>
       <c r="O220" s="22" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>34</v>
       </c>
       <c r="P220" s="21">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>25.788611111111113</v>
       </c>
       <c r="Q220" s="21">
-        <f t="shared" si="71"/>
+        <f t="shared" si="79"/>
         <v>-79.259444444444441</v>
       </c>
       <c r="R220" s="25" t="s">
@@ -16349,35 +16571,35 @@
         <v>425</v>
       </c>
       <c r="J221" s="22" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="72"/>
         <v>25</v>
       </c>
       <c r="K221" s="22" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="73"/>
         <v>39</v>
       </c>
       <c r="L221" s="22" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="74"/>
         <v>02</v>
       </c>
       <c r="M221" s="22" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="75"/>
         <v>79</v>
       </c>
       <c r="N221" s="22" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="76"/>
         <v>17</v>
       </c>
       <c r="O221" s="22" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>36</v>
       </c>
       <c r="P221" s="21">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>25.650555555555556</v>
       </c>
       <c r="Q221" s="21">
-        <f t="shared" si="71"/>
+        <f t="shared" si="79"/>
         <v>-79.293333333333337</v>
       </c>
       <c r="R221" s="25" t="s">
@@ -16413,35 +16635,35 @@
         <v>425</v>
       </c>
       <c r="J222" s="22" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="72"/>
         <v>26</v>
       </c>
       <c r="K222" s="22" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="73"/>
         <v>02</v>
       </c>
       <c r="L222" s="22" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="74"/>
         <v>00</v>
       </c>
       <c r="M222" s="22" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="75"/>
         <v>79</v>
       </c>
       <c r="N222" s="22" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="76"/>
         <v>06</v>
       </c>
       <c r="O222" s="22" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>00</v>
       </c>
       <c r="P222" s="21">
-        <f t="shared" si="70"/>
+        <f t="shared" si="78"/>
         <v>26.033333333333335</v>
       </c>
       <c r="Q222" s="21">
-        <f t="shared" si="71"/>
+        <f t="shared" si="79"/>
         <v>-79.099999999999994</v>
       </c>
       <c r="R222" s="25" t="s">
@@ -16477,35 +16699,35 @@
         <v>266</v>
       </c>
       <c r="J223" s="22" t="str">
-        <f t="shared" ref="J223:J240" si="72">MID(E223,1,FIND("°",E223,1)-1)</f>
+        <f t="shared" ref="J223:J240" si="80">MID(E223,1,FIND("°",E223,1)-1)</f>
         <v>24</v>
       </c>
       <c r="K223" s="22" t="str">
-        <f t="shared" ref="K223:K240" si="73">MID(E223,FIND("°",E223,1)+1,(FIND("′",E223,1)-FIND("°",E223,1))-1)</f>
+        <f t="shared" ref="K223:K240" si="81">MID(E223,FIND("°",E223,1)+1,(FIND("′",E223,1)-FIND("°",E223,1))-1)</f>
         <v>43</v>
       </c>
       <c r="L223" s="22" t="str">
-        <f t="shared" ref="L223:L240" si="74">MID(E223,FIND("′",E223,1)+1,(FIND("″",E223,1)-FIND("′",E223,1))-1)</f>
+        <f t="shared" ref="L223:L240" si="82">MID(E223,FIND("′",E223,1)+1,(FIND("″",E223,1)-FIND("′",E223,1))-1)</f>
         <v>57</v>
       </c>
       <c r="M223" s="22" t="str">
-        <f t="shared" ref="M223:M240" si="75">MID(F223,1,FIND("°",F223,1)-1)</f>
+        <f t="shared" ref="M223:M240" si="83">MID(F223,1,FIND("°",F223,1)-1)</f>
         <v>81</v>
       </c>
       <c r="N223" s="22" t="str">
-        <f t="shared" ref="N223:N240" si="76">MID(F223,FIND("°",F223,1)+1,(FIND("′",F223,1)-FIND("°",F223,1))-1)</f>
+        <f t="shared" ref="N223:N240" si="84">MID(F223,FIND("°",F223,1)+1,(FIND("′",F223,1)-FIND("°",F223,1))-1)</f>
         <v>05</v>
       </c>
       <c r="O223" s="22" t="str">
-        <f t="shared" ref="O223:O240" si="77">MID(F223,FIND("′",F223,1)+1,(FIND("″",F223,1)-FIND("′",F223,1))-1)</f>
+        <f t="shared" ref="O223:O240" si="85">MID(F223,FIND("′",F223,1)+1,(FIND("″",F223,1)-FIND("′",F223,1))-1)</f>
         <v>38</v>
       </c>
       <c r="P223" s="21">
-        <f t="shared" ref="P223:P240" si="78">((((L223/60)+K223)/60)+J223)*IF(C223="S",-1, 1)</f>
+        <f t="shared" ref="P223:P240" si="86">((((L223/60)+K223)/60)+J223)*IF(C223="S",-1, 1)</f>
         <v>24.732500000000002</v>
       </c>
       <c r="Q223" s="21">
-        <f t="shared" ref="Q223:Q240" si="79">((((O223/60)+N223)/60)+M223)*IF(D223="W",-1, 1)</f>
+        <f t="shared" ref="Q223:Q240" si="87">((((O223/60)+N223)/60)+M223)*IF(D223="W",-1, 1)</f>
         <v>-81.093888888888884</v>
       </c>
       <c r="R223" s="25" t="s">
@@ -16541,35 +16763,35 @@
         <v>266</v>
       </c>
       <c r="J224" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>24</v>
       </c>
       <c r="K224" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>44</v>
       </c>
       <c r="L224" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>56</v>
       </c>
       <c r="M224" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>81</v>
       </c>
       <c r="N224" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>02</v>
       </c>
       <c r="O224" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>50</v>
       </c>
       <c r="P224" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>24.748888888888889</v>
       </c>
       <c r="Q224" s="21">
-        <f t="shared" si="79"/>
+        <f t="shared" si="87"/>
         <v>-81.047222222222217</v>
       </c>
       <c r="R224" s="25" t="s">
@@ -16605,35 +16827,35 @@
         <v>266</v>
       </c>
       <c r="J225" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>24</v>
       </c>
       <c r="K225" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>46</v>
       </c>
       <c r="L225" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>10</v>
       </c>
       <c r="M225" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>80</v>
       </c>
       <c r="N225" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>58</v>
       </c>
       <c r="O225" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>45</v>
       </c>
       <c r="P225" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>24.769444444444446</v>
       </c>
       <c r="Q225" s="21">
-        <f t="shared" si="79"/>
+        <f t="shared" si="87"/>
         <v>-80.979166666666671</v>
       </c>
       <c r="R225" s="25" t="s">
@@ -16669,35 +16891,35 @@
         <v>266</v>
       </c>
       <c r="J226" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>24</v>
       </c>
       <c r="K226" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>47</v>
       </c>
       <c r="L226" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>50</v>
       </c>
       <c r="M226" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>81</v>
       </c>
       <c r="N226" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>01</v>
       </c>
       <c r="O226" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>35</v>
       </c>
       <c r="P226" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>24.797222222222221</v>
       </c>
       <c r="Q226" s="21">
-        <f t="shared" si="79"/>
+        <f t="shared" si="87"/>
         <v>-81.026388888888889</v>
       </c>
       <c r="R226" s="25" t="s">
@@ -16733,35 +16955,35 @@
         <v>266</v>
       </c>
       <c r="J227" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>24</v>
       </c>
       <c r="K227" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>49</v>
       </c>
       <c r="L227" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>35</v>
       </c>
       <c r="M227" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>80</v>
       </c>
       <c r="N227" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>58</v>
       </c>
       <c r="O227" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>55</v>
       </c>
       <c r="P227" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>24.826388888888889</v>
       </c>
       <c r="Q227" s="21">
-        <f t="shared" si="79"/>
+        <f t="shared" si="87"/>
         <v>-80.981944444444451</v>
       </c>
       <c r="R227" s="25" t="s">
@@ -16797,35 +17019,35 @@
         <v>266</v>
       </c>
       <c r="J228" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>24</v>
       </c>
       <c r="K228" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>49</v>
       </c>
       <c r="L228" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>15</v>
       </c>
       <c r="M228" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>80</v>
       </c>
       <c r="N228" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>55</v>
       </c>
       <c r="O228" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>21</v>
       </c>
       <c r="P228" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>24.820833333333333</v>
       </c>
       <c r="Q228" s="21">
-        <f t="shared" si="79"/>
+        <f t="shared" si="87"/>
         <v>-80.922499999999999</v>
       </c>
       <c r="R228" s="25" t="s">
@@ -16861,35 +17083,35 @@
         <v>266</v>
       </c>
       <c r="J229" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>24</v>
       </c>
       <c r="K229" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>49</v>
       </c>
       <c r="L229" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>05</v>
       </c>
       <c r="M229" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>80</v>
       </c>
       <c r="N229" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>52</v>
       </c>
       <c r="O229" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>01</v>
       </c>
       <c r="P229" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>24.818055555555556</v>
       </c>
       <c r="Q229" s="21">
-        <f t="shared" si="79"/>
+        <f t="shared" si="87"/>
         <v>-80.866944444444442</v>
       </c>
       <c r="R229" s="25" t="s">
@@ -16925,35 +17147,35 @@
         <v>266</v>
       </c>
       <c r="J230" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>24</v>
       </c>
       <c r="K230" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>52</v>
       </c>
       <c r="L230" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>08</v>
       </c>
       <c r="M230" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>80</v>
       </c>
       <c r="N230" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>50</v>
       </c>
       <c r="O230" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>48</v>
       </c>
       <c r="P230" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>24.86888888888889</v>
       </c>
       <c r="Q230" s="21">
-        <f t="shared" si="79"/>
+        <f t="shared" si="87"/>
         <v>-80.846666666666664</v>
       </c>
       <c r="R230" s="25" t="s">
@@ -16989,35 +17211,35 @@
         <v>266</v>
       </c>
       <c r="J231" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>24</v>
       </c>
       <c r="K231" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>51</v>
       </c>
       <c r="L231" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>13</v>
       </c>
       <c r="M231" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>80</v>
       </c>
       <c r="N231" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>46</v>
       </c>
       <c r="O231" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>57</v>
       </c>
       <c r="P231" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>24.85361111111111</v>
       </c>
       <c r="Q231" s="21">
-        <f t="shared" si="79"/>
+        <f t="shared" si="87"/>
         <v>-80.782499999999999</v>
       </c>
       <c r="R231" s="25" t="s">
@@ -17053,35 +17275,35 @@
         <v>266</v>
       </c>
       <c r="J232" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>24</v>
       </c>
       <c r="K232" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>53</v>
       </c>
       <c r="L232" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>06</v>
       </c>
       <c r="M232" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>80</v>
       </c>
       <c r="N232" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>45</v>
       </c>
       <c r="O232" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>27</v>
       </c>
       <c r="P232" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>24.885000000000002</v>
       </c>
       <c r="Q232" s="21">
-        <f t="shared" si="79"/>
+        <f t="shared" si="87"/>
         <v>-80.757499999999993</v>
       </c>
       <c r="R232" s="25" t="s">
@@ -17117,35 +17339,35 @@
         <v>266</v>
       </c>
       <c r="J233" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>24</v>
       </c>
       <c r="K233" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>41</v>
       </c>
       <c r="L233" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>55</v>
       </c>
       <c r="M233" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>81</v>
       </c>
       <c r="N233" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>23</v>
       </c>
       <c r="O233" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>50</v>
       </c>
       <c r="P233" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>24.698611111111113</v>
       </c>
       <c r="Q233" s="21">
-        <f t="shared" si="79"/>
+        <f t="shared" si="87"/>
         <v>-81.397222222222226</v>
       </c>
       <c r="R233" s="25" t="s">
@@ -17181,35 +17403,35 @@
         <v>266</v>
       </c>
       <c r="J234" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>24</v>
       </c>
       <c r="K234" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>44</v>
       </c>
       <c r="L234" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>45</v>
       </c>
       <c r="M234" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>81</v>
       </c>
       <c r="N234" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>26</v>
       </c>
       <c r="O234" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>07</v>
       </c>
       <c r="P234" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>24.745833333333334</v>
       </c>
       <c r="Q234" s="21">
-        <f t="shared" si="79"/>
+        <f t="shared" si="87"/>
         <v>-81.435277777777785</v>
       </c>
       <c r="R234" s="25" t="s">
@@ -17245,35 +17467,35 @@
         <v>293</v>
       </c>
       <c r="J235" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>19</v>
       </c>
       <c r="K235" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>41</v>
       </c>
       <c r="L235" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>54</v>
       </c>
       <c r="M235" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>87</v>
       </c>
       <c r="N235" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>27</v>
       </c>
       <c r="O235" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>43</v>
       </c>
       <c r="P235" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>19.698333333333334</v>
       </c>
       <c r="Q235" s="21">
-        <f t="shared" si="79"/>
+        <f t="shared" si="87"/>
         <v>-87.461944444444441</v>
       </c>
       <c r="R235" s="25" t="s">
@@ -17309,35 +17531,35 @@
         <v>293</v>
       </c>
       <c r="J236" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>19</v>
       </c>
       <c r="K236" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>43</v>
       </c>
       <c r="L236" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>35</v>
       </c>
       <c r="M236" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>87</v>
       </c>
       <c r="N236" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>25</v>
       </c>
       <c r="O236" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>06</v>
       </c>
       <c r="P236" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>19.726388888888888</v>
       </c>
       <c r="Q236" s="21">
-        <f t="shared" si="79"/>
+        <f t="shared" si="87"/>
         <v>-87.418333333333337</v>
       </c>
       <c r="R236" s="25" t="s">
@@ -17373,35 +17595,35 @@
         <v>293</v>
       </c>
       <c r="J237" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>19</v>
       </c>
       <c r="K237" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>44</v>
       </c>
       <c r="L237" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>04</v>
       </c>
       <c r="M237" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>87</v>
       </c>
       <c r="N237" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>25</v>
       </c>
       <c r="O237" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>23</v>
       </c>
       <c r="P237" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>19.734444444444446</v>
       </c>
       <c r="Q237" s="21">
-        <f t="shared" si="79"/>
+        <f t="shared" si="87"/>
         <v>-87.42305555555555</v>
       </c>
       <c r="R237" s="25" t="s">
@@ -17437,35 +17659,35 @@
         <v>293</v>
       </c>
       <c r="J238" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>19</v>
       </c>
       <c r="K238" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>46</v>
       </c>
       <c r="L238" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>33</v>
       </c>
       <c r="M238" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>87</v>
       </c>
       <c r="N238" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>28</v>
       </c>
       <c r="O238" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>37</v>
       </c>
       <c r="P238" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>19.775833333333335</v>
       </c>
       <c r="Q238" s="21">
-        <f t="shared" si="79"/>
+        <f t="shared" si="87"/>
         <v>-87.476944444444442</v>
       </c>
       <c r="R238" s="25" t="s">
@@ -17501,35 +17723,35 @@
         <v>293</v>
       </c>
       <c r="J239" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>19</v>
       </c>
       <c r="K239" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>38</v>
       </c>
       <c r="L239" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>59</v>
       </c>
       <c r="M239" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>87</v>
       </c>
       <c r="N239" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>27</v>
       </c>
       <c r="O239" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>21</v>
       </c>
       <c r="P239" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>19.649722222222223</v>
       </c>
       <c r="Q239" s="21">
-        <f t="shared" si="79"/>
+        <f t="shared" si="87"/>
         <v>-87.455833333333331</v>
       </c>
       <c r="R239" s="25" t="s">
@@ -17565,202 +17787,1749 @@
         <v>293</v>
       </c>
       <c r="J240" s="22" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="80"/>
         <v>19</v>
       </c>
       <c r="K240" s="22" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="81"/>
         <v>38</v>
       </c>
       <c r="L240" s="22" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="82"/>
         <v>36</v>
       </c>
       <c r="M240" s="22" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="83"/>
         <v>87</v>
       </c>
       <c r="N240" s="22" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="84"/>
         <v>27</v>
       </c>
       <c r="O240" s="22" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="85"/>
         <v>36</v>
       </c>
       <c r="P240" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="86"/>
         <v>19.643333333333334</v>
       </c>
       <c r="Q240" s="21">
-        <f t="shared" si="79"/>
+        <f>((((O240/60)+N240)/60)+M240)*IF(D241="W",-1, 1)</f>
         <v>-87.46</v>
       </c>
       <c r="R240" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="241" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E241" s="3"/>
-      <c r="F241" s="3"/>
-    </row>
-    <row r="242" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E242" s="3"/>
-      <c r="F242" s="3"/>
-    </row>
-    <row r="243" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E243" s="3"/>
-      <c r="F243" s="3"/>
-    </row>
-    <row r="244" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E244" s="3"/>
-      <c r="F244" s="3"/>
-    </row>
-    <row r="245" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E245" s="3"/>
-      <c r="F245" s="3"/>
-    </row>
-    <row r="246" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E246" s="3"/>
-      <c r="F246" s="3"/>
-    </row>
-    <row r="247" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E247" s="3"/>
-      <c r="F247" s="3"/>
-    </row>
-    <row r="248" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E248" s="3"/>
-      <c r="F248" s="3"/>
-    </row>
-    <row r="249" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E249" s="3"/>
-      <c r="F249" s="3"/>
-    </row>
-    <row r="250" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E250" s="3"/>
-      <c r="F250" s="3"/>
-    </row>
-    <row r="251" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E251" s="3"/>
-      <c r="F251" s="3"/>
-    </row>
-    <row r="252" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E252" s="3"/>
-      <c r="F252" s="3"/>
-    </row>
-    <row r="253" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E253" s="3"/>
-      <c r="F253" s="3"/>
-    </row>
-    <row r="254" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E254" s="2"/>
-      <c r="F254" s="2"/>
-      <c r="P254" s="1"/>
-      <c r="Q254" s="1"/>
-      <c r="R254" s="26"/>
-    </row>
-    <row r="255" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E255" s="2"/>
-      <c r="P255" s="1"/>
-      <c r="Q255" s="1"/>
-      <c r="R255" s="26"/>
-    </row>
-    <row r="256" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E256" s="2"/>
-      <c r="F256" s="2"/>
-      <c r="P256" s="1"/>
-      <c r="Q256" s="1"/>
-    </row>
-    <row r="257" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E257" s="2"/>
-      <c r="F257" s="2"/>
-      <c r="P257" s="1"/>
-      <c r="Q257" s="1"/>
-    </row>
-    <row r="258" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E258" s="2"/>
-      <c r="F258" s="2"/>
-      <c r="P258" s="1"/>
-      <c r="Q258" s="1"/>
-    </row>
-    <row r="259" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E259" s="2"/>
-      <c r="F259" s="2"/>
-      <c r="P259" s="1"/>
-      <c r="Q259" s="1"/>
-    </row>
-    <row r="260" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E260" s="2"/>
-      <c r="F260" s="2"/>
-      <c r="P260" s="1"/>
-      <c r="Q260" s="1"/>
-    </row>
-    <row r="261" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E261" s="2"/>
-      <c r="F261" s="2"/>
-      <c r="P261" s="1"/>
-      <c r="Q261" s="1"/>
-    </row>
-    <row r="262" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E262" s="2"/>
-      <c r="F262" s="2"/>
-      <c r="P262" s="1"/>
-      <c r="Q262" s="1"/>
-    </row>
-    <row r="263" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E263" s="2"/>
-      <c r="F263" s="2"/>
-      <c r="P263" s="1"/>
-      <c r="Q263" s="1"/>
-    </row>
-    <row r="264" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E264" s="2"/>
-      <c r="F264" s="2"/>
-      <c r="P264" s="1"/>
-      <c r="Q264" s="1"/>
-    </row>
-    <row r="265" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A241" s="22">
+        <v>240</v>
+      </c>
+      <c r="B241" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C241" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D241" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E241" s="24" t="s">
+        <v>511</v>
+      </c>
+      <c r="F241" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="G241" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="H241" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I241" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="J241" s="22" t="str">
+        <f t="shared" ref="J241:J252" si="88">MID(E241,1,FIND("°",E241,1)-1)</f>
+        <v>22</v>
+      </c>
+      <c r="K241" s="22" t="str">
+        <f t="shared" ref="K241:K252" si="89">MID(E241,FIND("°",E241,1)+1,(FIND("′",E241,1)-FIND("°",E241,1))-1)</f>
+        <v>20</v>
+      </c>
+      <c r="L241" s="22" t="str">
+        <f t="shared" ref="L241:L252" si="90">MID(E241,FIND("′",E241,1)+1,(FIND("″",E241,1)-FIND("′",E241,1))-1)</f>
+        <v>56</v>
+      </c>
+      <c r="M241" s="22" t="str">
+        <f t="shared" ref="M241:M252" si="91">MID(F241,1,FIND("°",F241,1)-1)</f>
+        <v>82</v>
+      </c>
+      <c r="N241" s="22" t="str">
+        <f t="shared" ref="N241:N252" si="92">MID(F241,FIND("°",F241,1)+1,(FIND("′",F241,1)-FIND("°",F241,1))-1)</f>
+        <v>20</v>
+      </c>
+      <c r="O241" s="22" t="str">
+        <f t="shared" ref="O241:O252" si="93">MID(F241,FIND("′",F241,1)+1,(FIND("″",F241,1)-FIND("′",F241,1))-1)</f>
+        <v>09</v>
+      </c>
+      <c r="P241" s="21">
+        <f t="shared" ref="P241:P252" si="94">((((L241/60)+K241)/60)+J241)*IF(C241="S",-1, 1)</f>
+        <v>22.34888888888889</v>
+      </c>
+      <c r="Q241" s="21">
+        <f t="shared" ref="Q241:Q252" si="95">((((O241/60)+N241)/60)+M241)*IF(D242="W",-1, 1)</f>
+        <v>-82.335833333333326</v>
+      </c>
+      <c r="R241" s="25" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="242" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A242" s="22">
+        <v>241</v>
+      </c>
+      <c r="B242" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C242" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D242" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E242" s="24" t="s">
+        <v>510</v>
+      </c>
+      <c r="F242" s="24" t="s">
+        <v>531</v>
+      </c>
+      <c r="G242" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="H242" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I242" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="J242" s="22" t="str">
+        <f t="shared" si="88"/>
+        <v>22</v>
+      </c>
+      <c r="K242" s="22" t="str">
+        <f t="shared" si="89"/>
+        <v>13</v>
+      </c>
+      <c r="L242" s="22" t="str">
+        <f t="shared" si="90"/>
+        <v>21</v>
+      </c>
+      <c r="M242" s="22" t="str">
+        <f t="shared" si="91"/>
+        <v>82</v>
+      </c>
+      <c r="N242" s="22" t="str">
+        <f t="shared" si="92"/>
+        <v>22</v>
+      </c>
+      <c r="O242" s="22" t="str">
+        <f t="shared" si="93"/>
+        <v>28</v>
+      </c>
+      <c r="P242" s="21">
+        <f t="shared" si="94"/>
+        <v>22.2225</v>
+      </c>
+      <c r="Q242" s="21">
+        <f t="shared" si="95"/>
+        <v>-82.37444444444445</v>
+      </c>
+      <c r="R242" s="25" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="243" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A243" s="22">
+        <v>242</v>
+      </c>
+      <c r="B243" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C243" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D243" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E243" s="24" t="s">
+        <v>512</v>
+      </c>
+      <c r="F243" s="24" t="s">
+        <v>530</v>
+      </c>
+      <c r="G243" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="H243" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I243" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="J243" s="22" t="str">
+        <f t="shared" si="88"/>
+        <v>22</v>
+      </c>
+      <c r="K243" s="22" t="str">
+        <f t="shared" si="89"/>
+        <v>18</v>
+      </c>
+      <c r="L243" s="22" t="str">
+        <f t="shared" si="90"/>
+        <v>23</v>
+      </c>
+      <c r="M243" s="22" t="str">
+        <f t="shared" si="91"/>
+        <v>82</v>
+      </c>
+      <c r="N243" s="22" t="str">
+        <f t="shared" si="92"/>
+        <v>45</v>
+      </c>
+      <c r="O243" s="22" t="str">
+        <f t="shared" si="93"/>
+        <v>03</v>
+      </c>
+      <c r="P243" s="21">
+        <f t="shared" si="94"/>
+        <v>22.30638888888889</v>
+      </c>
+      <c r="Q243" s="21">
+        <f t="shared" si="95"/>
+        <v>-82.750833333333333</v>
+      </c>
+      <c r="R243" s="25" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="244" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A244" s="22">
+        <v>243</v>
+      </c>
+      <c r="B244" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C244" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D244" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E244" s="24" t="s">
+        <v>512</v>
+      </c>
+      <c r="F244" s="24" t="s">
+        <v>529</v>
+      </c>
+      <c r="G244" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="H244" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I244" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="J244" s="22" t="str">
+        <f t="shared" si="88"/>
+        <v>22</v>
+      </c>
+      <c r="K244" s="22" t="str">
+        <f t="shared" si="89"/>
+        <v>18</v>
+      </c>
+      <c r="L244" s="22" t="str">
+        <f t="shared" si="90"/>
+        <v>23</v>
+      </c>
+      <c r="M244" s="22" t="str">
+        <f t="shared" si="91"/>
+        <v>83</v>
+      </c>
+      <c r="N244" s="22" t="str">
+        <f t="shared" si="92"/>
+        <v>04</v>
+      </c>
+      <c r="O244" s="22" t="str">
+        <f t="shared" si="93"/>
+        <v>41</v>
+      </c>
+      <c r="P244" s="21">
+        <f t="shared" si="94"/>
+        <v>22.30638888888889</v>
+      </c>
+      <c r="Q244" s="21">
+        <f t="shared" si="95"/>
+        <v>-83.078055555555551</v>
+      </c>
+      <c r="R244" s="25" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="245" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A245" s="22">
+        <v>244</v>
+      </c>
+      <c r="B245" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C245" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D245" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E245" s="24" t="s">
+        <v>513</v>
+      </c>
+      <c r="F245" s="24" t="s">
+        <v>528</v>
+      </c>
+      <c r="G245" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="H245" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I245" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="J245" s="22" t="str">
+        <f t="shared" si="88"/>
+        <v>22</v>
+      </c>
+      <c r="K245" s="22" t="str">
+        <f t="shared" si="89"/>
+        <v>10</v>
+      </c>
+      <c r="L245" s="22" t="str">
+        <f t="shared" si="90"/>
+        <v>42</v>
+      </c>
+      <c r="M245" s="22" t="str">
+        <f t="shared" si="91"/>
+        <v>83</v>
+      </c>
+      <c r="N245" s="22" t="str">
+        <f t="shared" si="92"/>
+        <v>12</v>
+      </c>
+      <c r="O245" s="22" t="str">
+        <f t="shared" si="93"/>
+        <v>51</v>
+      </c>
+      <c r="P245" s="21">
+        <f t="shared" si="94"/>
+        <v>22.178333333333335</v>
+      </c>
+      <c r="Q245" s="21">
+        <f t="shared" si="95"/>
+        <v>-83.214166666666671</v>
+      </c>
+      <c r="R245" s="25" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="246" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A246" s="22">
+        <v>245</v>
+      </c>
+      <c r="B246" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C246" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D246" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E246" s="24" t="s">
+        <v>514</v>
+      </c>
+      <c r="F246" s="24" t="s">
+        <v>527</v>
+      </c>
+      <c r="G246" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="H246" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I246" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="J246" s="22" t="str">
+        <f t="shared" si="88"/>
+        <v>22</v>
+      </c>
+      <c r="K246" s="22" t="str">
+        <f t="shared" si="89"/>
+        <v>03</v>
+      </c>
+      <c r="L246" s="22" t="str">
+        <f t="shared" si="90"/>
+        <v>43</v>
+      </c>
+      <c r="M246" s="22" t="str">
+        <f t="shared" si="91"/>
+        <v>83</v>
+      </c>
+      <c r="N246" s="22" t="str">
+        <f t="shared" si="92"/>
+        <v>04</v>
+      </c>
+      <c r="O246" s="22" t="str">
+        <f t="shared" si="93"/>
+        <v>22</v>
+      </c>
+      <c r="P246" s="21">
+        <f t="shared" si="94"/>
+        <v>22.061944444444446</v>
+      </c>
+      <c r="Q246" s="21">
+        <f t="shared" si="95"/>
+        <v>-83.072777777777773</v>
+      </c>
+      <c r="R246" s="25" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="247" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A247" s="22">
+        <v>246</v>
+      </c>
+      <c r="B247" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C247" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D247" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E247" s="24" t="s">
+        <v>515</v>
+      </c>
+      <c r="F247" s="24" t="s">
+        <v>526</v>
+      </c>
+      <c r="G247" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="H247" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I247" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="J247" s="22" t="str">
+        <f t="shared" si="88"/>
+        <v>21</v>
+      </c>
+      <c r="K247" s="22" t="str">
+        <f t="shared" si="89"/>
+        <v>55</v>
+      </c>
+      <c r="L247" s="22" t="str">
+        <f t="shared" si="90"/>
+        <v>27</v>
+      </c>
+      <c r="M247" s="22" t="str">
+        <f t="shared" si="91"/>
+        <v>82</v>
+      </c>
+      <c r="N247" s="22" t="str">
+        <f t="shared" si="92"/>
+        <v>47</v>
+      </c>
+      <c r="O247" s="22" t="str">
+        <f t="shared" si="93"/>
+        <v>22</v>
+      </c>
+      <c r="P247" s="21">
+        <f t="shared" si="94"/>
+        <v>21.924166666666668</v>
+      </c>
+      <c r="Q247" s="21">
+        <f t="shared" si="95"/>
+        <v>-82.789444444444442</v>
+      </c>
+      <c r="R247" s="25" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="248" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A248" s="22">
+        <v>247</v>
+      </c>
+      <c r="B248" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C248" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D248" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E248" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="F248" s="24" t="s">
+        <v>525</v>
+      </c>
+      <c r="G248" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="H248" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I248" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="J248" s="22" t="str">
+        <f t="shared" si="88"/>
+        <v>21</v>
+      </c>
+      <c r="K248" s="22" t="str">
+        <f t="shared" si="89"/>
+        <v>45</v>
+      </c>
+      <c r="L248" s="22" t="str">
+        <f t="shared" si="90"/>
+        <v>33</v>
+      </c>
+      <c r="M248" s="22" t="str">
+        <f t="shared" si="91"/>
+        <v>82</v>
+      </c>
+      <c r="N248" s="22" t="str">
+        <f t="shared" si="92"/>
+        <v>29</v>
+      </c>
+      <c r="O248" s="22" t="str">
+        <f t="shared" si="93"/>
+        <v>48</v>
+      </c>
+      <c r="P248" s="21">
+        <f t="shared" si="94"/>
+        <v>21.759166666666665</v>
+      </c>
+      <c r="Q248" s="21">
+        <f t="shared" si="95"/>
+        <v>-82.49666666666667</v>
+      </c>
+      <c r="R248" s="25" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="249" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A249" s="22">
+        <v>248</v>
+      </c>
+      <c r="B249" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C249" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D249" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E249" s="24" t="s">
+        <v>517</v>
+      </c>
+      <c r="F249" s="24" t="s">
+        <v>524</v>
+      </c>
+      <c r="G249" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="H249" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I249" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="J249" s="22" t="str">
+        <f t="shared" si="88"/>
+        <v>21</v>
+      </c>
+      <c r="K249" s="22" t="str">
+        <f t="shared" si="89"/>
+        <v>35</v>
+      </c>
+      <c r="L249" s="22" t="str">
+        <f t="shared" si="90"/>
+        <v>36</v>
+      </c>
+      <c r="M249" s="22" t="str">
+        <f t="shared" si="91"/>
+        <v>82</v>
+      </c>
+      <c r="N249" s="22" t="str">
+        <f t="shared" si="92"/>
+        <v>20</v>
+      </c>
+      <c r="O249" s="22" t="str">
+        <f t="shared" si="93"/>
+        <v>44</v>
+      </c>
+      <c r="P249" s="21">
+        <f t="shared" si="94"/>
+        <v>21.593333333333334</v>
+      </c>
+      <c r="Q249" s="21">
+        <f t="shared" si="95"/>
+        <v>-82.345555555555549</v>
+      </c>
+      <c r="R249" s="25" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="250" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A250" s="22">
+        <v>249</v>
+      </c>
+      <c r="B250" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C250" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D250" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E250" s="24" t="s">
+        <v>518</v>
+      </c>
+      <c r="F250" s="24" t="s">
+        <v>523</v>
+      </c>
+      <c r="G250" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="H250" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I250" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="J250" s="22" t="str">
+        <f t="shared" si="88"/>
+        <v>21</v>
+      </c>
+      <c r="K250" s="22" t="str">
+        <f t="shared" si="89"/>
+        <v>43</v>
+      </c>
+      <c r="L250" s="22" t="str">
+        <f t="shared" si="90"/>
+        <v>01</v>
+      </c>
+      <c r="M250" s="22" t="str">
+        <f t="shared" si="91"/>
+        <v>82</v>
+      </c>
+      <c r="N250" s="22" t="str">
+        <f t="shared" si="92"/>
+        <v>03</v>
+      </c>
+      <c r="O250" s="22" t="str">
+        <f t="shared" si="93"/>
+        <v>38</v>
+      </c>
+      <c r="P250" s="21">
+        <f t="shared" si="94"/>
+        <v>21.716944444444444</v>
+      </c>
+      <c r="Q250" s="21">
+        <f t="shared" si="95"/>
+        <v>-82.060555555555553</v>
+      </c>
+      <c r="R250" s="25" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="251" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A251" s="22">
+        <v>250</v>
+      </c>
+      <c r="B251" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C251" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D251" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E251" s="24" t="s">
+        <v>519</v>
+      </c>
+      <c r="F251" s="24" t="s">
+        <v>522</v>
+      </c>
+      <c r="G251" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="H251" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I251" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="J251" s="22" t="str">
+        <f t="shared" si="88"/>
+        <v>21</v>
+      </c>
+      <c r="K251" s="22" t="str">
+        <f t="shared" si="89"/>
+        <v>52</v>
+      </c>
+      <c r="L251" s="22" t="str">
+        <f t="shared" si="90"/>
+        <v>06</v>
+      </c>
+      <c r="M251" s="22" t="str">
+        <f t="shared" si="91"/>
+        <v>81</v>
+      </c>
+      <c r="N251" s="22" t="str">
+        <f t="shared" si="92"/>
+        <v>49</v>
+      </c>
+      <c r="O251" s="22" t="str">
+        <f t="shared" si="93"/>
+        <v>32</v>
+      </c>
+      <c r="P251" s="21">
+        <f t="shared" si="94"/>
+        <v>21.868333333333332</v>
+      </c>
+      <c r="Q251" s="21">
+        <f t="shared" si="95"/>
+        <v>-81.825555555555553</v>
+      </c>
+      <c r="R251" s="25" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="252" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A252" s="22">
+        <v>251</v>
+      </c>
+      <c r="B252" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C252" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D252" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E252" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="F252" s="24" t="s">
+        <v>521</v>
+      </c>
+      <c r="G252" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="H252" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I252" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="J252" s="22" t="str">
+        <f t="shared" si="88"/>
+        <v>22</v>
+      </c>
+      <c r="K252" s="22" t="str">
+        <f t="shared" si="89"/>
+        <v>02</v>
+      </c>
+      <c r="L252" s="22" t="str">
+        <f t="shared" si="90"/>
+        <v>00</v>
+      </c>
+      <c r="M252" s="22" t="str">
+        <f t="shared" si="91"/>
+        <v>81</v>
+      </c>
+      <c r="N252" s="22" t="str">
+        <f t="shared" si="92"/>
+        <v>35</v>
+      </c>
+      <c r="O252" s="22" t="str">
+        <f t="shared" si="93"/>
+        <v>18</v>
+      </c>
+      <c r="P252" s="21">
+        <f t="shared" si="94"/>
+        <v>22.033333333333335</v>
+      </c>
+      <c r="Q252" s="21">
+        <f t="shared" si="95"/>
+        <v>-81.588333333333338</v>
+      </c>
+      <c r="R252" s="25" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="253" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A253" s="22">
+        <v>252</v>
+      </c>
+      <c r="B253" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C253" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D253" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E253" s="24" t="s">
+        <v>553</v>
+      </c>
+      <c r="F253" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="G253" s="24" t="s">
+        <v>546</v>
+      </c>
+      <c r="H253" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I253" s="22" t="s">
+        <v>547</v>
+      </c>
+      <c r="J253" s="22" t="str">
+        <f t="shared" ref="J253:J268" si="96">MID(E253,1,FIND("°",E253,1)-1)</f>
+        <v>20</v>
+      </c>
+      <c r="K253" s="22" t="str">
+        <f t="shared" ref="K253:K268" si="97">MID(E253,FIND("°",E253,1)+1,(FIND("′",E253,1)-FIND("°",E253,1))-1)</f>
+        <v>32</v>
+      </c>
+      <c r="L253" s="22" t="str">
+        <f t="shared" ref="L253:L268" si="98">MID(E253,FIND("′",E253,1)+1,(FIND("″",E253,1)-FIND("′",E253,1))-1)</f>
+        <v>36</v>
+      </c>
+      <c r="M253" s="22" t="str">
+        <f t="shared" ref="M253:M268" si="99">MID(F253,1,FIND("°",F253,1)-1)</f>
+        <v>78</v>
+      </c>
+      <c r="N253" s="22" t="str">
+        <f t="shared" ref="N253:N268" si="100">MID(F253,FIND("°",F253,1)+1,(FIND("′",F253,1)-FIND("°",F253,1))-1)</f>
+        <v>21</v>
+      </c>
+      <c r="O253" s="22" t="str">
+        <f t="shared" ref="O253:O268" si="101">MID(F253,FIND("′",F253,1)+1,(FIND("″",F253,1)-FIND("′",F253,1))-1)</f>
+        <v>00</v>
+      </c>
+      <c r="P253" s="21">
+        <f t="shared" ref="P253:P268" si="102">((((L253/60)+K253)/60)+J253)*IF(C253="S",-1, 1)</f>
+        <v>20.543333333333333</v>
+      </c>
+      <c r="Q253" s="21">
+        <f t="shared" ref="Q253:Q268" si="103">((((O253/60)+N253)/60)+M253)*IF(D254="W",-1, 1)</f>
+        <v>-78.349999999999994</v>
+      </c>
+      <c r="R253" s="25" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="254" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A254" s="22">
+        <v>253</v>
+      </c>
+      <c r="B254" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C254" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D254" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E254" s="24" t="s">
+        <v>554</v>
+      </c>
+      <c r="F254" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="G254" s="24" t="s">
+        <v>546</v>
+      </c>
+      <c r="H254" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I254" s="22" t="s">
+        <v>547</v>
+      </c>
+      <c r="J254" s="22" t="str">
+        <f t="shared" si="96"/>
+        <v>20</v>
+      </c>
+      <c r="K254" s="22" t="str">
+        <f t="shared" si="97"/>
+        <v>40</v>
+      </c>
+      <c r="L254" s="22" t="str">
+        <f t="shared" si="98"/>
+        <v>14</v>
+      </c>
+      <c r="M254" s="22" t="str">
+        <f t="shared" si="99"/>
+        <v>78</v>
+      </c>
+      <c r="N254" s="22" t="str">
+        <f t="shared" si="100"/>
+        <v>41</v>
+      </c>
+      <c r="O254" s="22" t="str">
+        <f t="shared" si="101"/>
+        <v>15</v>
+      </c>
+      <c r="P254" s="21">
+        <f t="shared" si="102"/>
+        <v>20.670555555555556</v>
+      </c>
+      <c r="Q254" s="21">
+        <f t="shared" si="103"/>
+        <v>-78.6875</v>
+      </c>
+      <c r="R254" s="25" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="255" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A255" s="22">
+        <v>254</v>
+      </c>
+      <c r="B255" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C255" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D255" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E255" s="24" t="s">
+        <v>555</v>
+      </c>
+      <c r="F255" s="24" t="s">
+        <v>556</v>
+      </c>
+      <c r="G255" s="24" t="s">
+        <v>546</v>
+      </c>
+      <c r="H255" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I255" s="22" t="s">
+        <v>547</v>
+      </c>
+      <c r="J255" s="22" t="str">
+        <f t="shared" si="96"/>
+        <v>21</v>
+      </c>
+      <c r="K255" s="22" t="str">
+        <f t="shared" si="97"/>
+        <v>01</v>
+      </c>
+      <c r="L255" s="22" t="str">
+        <f t="shared" si="98"/>
+        <v>12</v>
+      </c>
+      <c r="M255" s="22" t="str">
+        <f t="shared" si="99"/>
+        <v>79</v>
+      </c>
+      <c r="N255" s="22" t="str">
+        <f t="shared" si="100"/>
+        <v>11</v>
+      </c>
+      <c r="O255" s="22" t="str">
+        <f t="shared" si="101"/>
+        <v>32</v>
+      </c>
+      <c r="P255" s="21">
+        <f t="shared" si="102"/>
+        <v>21.02</v>
+      </c>
+      <c r="Q255" s="21">
+        <f t="shared" si="103"/>
+        <v>-79.192222222222227</v>
+      </c>
+      <c r="R255" s="25" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="256" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A256" s="22">
+        <v>255</v>
+      </c>
+      <c r="B256" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C256" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D256" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E256" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="F256" s="24" t="s">
+        <v>564</v>
+      </c>
+      <c r="G256" s="24" t="s">
+        <v>546</v>
+      </c>
+      <c r="H256" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I256" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="J256" s="22" t="str">
+        <f t="shared" si="96"/>
+        <v>22</v>
+      </c>
+      <c r="K256" s="22" t="str">
+        <f t="shared" si="97"/>
+        <v>02</v>
+      </c>
+      <c r="L256" s="22" t="str">
+        <f t="shared" si="98"/>
+        <v>36</v>
+      </c>
+      <c r="M256" s="22" t="str">
+        <f t="shared" si="99"/>
+        <v>81</v>
+      </c>
+      <c r="N256" s="22" t="str">
+        <f t="shared" si="100"/>
+        <v>38</v>
+      </c>
+      <c r="O256" s="22" t="str">
+        <f t="shared" si="101"/>
+        <v>11</v>
+      </c>
+      <c r="P256" s="21">
+        <f t="shared" si="102"/>
+        <v>22.043333333333333</v>
+      </c>
+      <c r="Q256" s="21">
+        <f t="shared" si="103"/>
+        <v>-81.636388888888888</v>
+      </c>
+      <c r="R256" s="25" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="257" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A257" s="22">
+        <v>256</v>
+      </c>
+      <c r="B257" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C257" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D257" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E257" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="F257" s="24" t="s">
+        <v>563</v>
+      </c>
+      <c r="G257" s="24" t="s">
+        <v>546</v>
+      </c>
+      <c r="H257" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I257" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="J257" s="22" t="str">
+        <f t="shared" si="96"/>
+        <v>22</v>
+      </c>
+      <c r="K257" s="22" t="str">
+        <f t="shared" si="97"/>
+        <v>05</v>
+      </c>
+      <c r="L257" s="22" t="str">
+        <f t="shared" si="98"/>
+        <v>54</v>
+      </c>
+      <c r="M257" s="22" t="str">
+        <f t="shared" si="99"/>
+        <v>81</v>
+      </c>
+      <c r="N257" s="22" t="str">
+        <f t="shared" si="100"/>
+        <v>33</v>
+      </c>
+      <c r="O257" s="22" t="str">
+        <f t="shared" si="101"/>
+        <v>56</v>
+      </c>
+      <c r="P257" s="21">
+        <f t="shared" si="102"/>
+        <v>22.098333333333333</v>
+      </c>
+      <c r="Q257" s="21">
+        <f t="shared" si="103"/>
+        <v>-81.565555555555562</v>
+      </c>
+      <c r="R257" s="25" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="258" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A258" s="22">
+        <v>257</v>
+      </c>
+      <c r="B258" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C258" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D258" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E258" s="24" t="s">
+        <v>561</v>
+      </c>
+      <c r="F258" s="24" t="s">
+        <v>562</v>
+      </c>
+      <c r="G258" s="24" t="s">
+        <v>546</v>
+      </c>
+      <c r="H258" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I258" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="J258" s="22" t="str">
+        <f t="shared" si="96"/>
+        <v>22</v>
+      </c>
+      <c r="K258" s="22" t="str">
+        <f t="shared" si="97"/>
+        <v>01</v>
+      </c>
+      <c r="L258" s="22" t="str">
+        <f t="shared" si="98"/>
+        <v>07</v>
+      </c>
+      <c r="M258" s="22" t="str">
+        <f t="shared" si="99"/>
+        <v>81</v>
+      </c>
+      <c r="N258" s="22" t="str">
+        <f t="shared" si="100"/>
+        <v>21</v>
+      </c>
+      <c r="O258" s="22" t="str">
+        <f t="shared" si="101"/>
+        <v>43</v>
+      </c>
+      <c r="P258" s="21">
+        <f t="shared" si="102"/>
+        <v>22.01861111111111</v>
+      </c>
+      <c r="Q258" s="21">
+        <f t="shared" si="103"/>
+        <v>-81.361944444444447</v>
+      </c>
+      <c r="R258" s="25" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="259" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A259" s="22">
+        <v>258</v>
+      </c>
+      <c r="B259" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C259" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D259" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E259" s="24" t="s">
+        <v>573</v>
+      </c>
+      <c r="F259" s="24" t="s">
+        <v>578</v>
+      </c>
+      <c r="G259" s="22" t="s">
+        <v>565</v>
+      </c>
+      <c r="H259" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I259" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="J259" s="22" t="str">
+        <f t="shared" si="96"/>
+        <v>09</v>
+      </c>
+      <c r="K259" s="22" t="str">
+        <f t="shared" si="97"/>
+        <v>44</v>
+      </c>
+      <c r="L259" s="22" t="str">
+        <f t="shared" si="98"/>
+        <v>15</v>
+      </c>
+      <c r="M259" s="22" t="str">
+        <f t="shared" si="99"/>
+        <v>82</v>
+      </c>
+      <c r="N259" s="22" t="str">
+        <f t="shared" si="100"/>
+        <v>49</v>
+      </c>
+      <c r="O259" s="22" t="str">
+        <f t="shared" si="101"/>
+        <v>28</v>
+      </c>
+      <c r="P259" s="21">
+        <f t="shared" si="102"/>
+        <v>9.7375000000000007</v>
+      </c>
+      <c r="Q259" s="21">
+        <f t="shared" si="103"/>
+        <v>-82.824444444444438</v>
+      </c>
+      <c r="R259" s="25" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="260" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A260" s="22">
+        <v>259</v>
+      </c>
+      <c r="B260" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C260" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D260" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E260" s="24" t="s">
+        <v>477</v>
+      </c>
+      <c r="F260" s="24" t="s">
+        <v>579</v>
+      </c>
+      <c r="G260" s="22" t="s">
+        <v>565</v>
+      </c>
+      <c r="H260" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I260" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="J260" s="22" t="str">
+        <f t="shared" si="96"/>
+        <v>09</v>
+      </c>
+      <c r="K260" s="22" t="str">
+        <f t="shared" si="97"/>
+        <v>44</v>
+      </c>
+      <c r="L260" s="22" t="str">
+        <f t="shared" si="98"/>
+        <v>24</v>
+      </c>
+      <c r="M260" s="22" t="str">
+        <f t="shared" si="99"/>
+        <v>82</v>
+      </c>
+      <c r="N260" s="22" t="str">
+        <f t="shared" si="100"/>
+        <v>49</v>
+      </c>
+      <c r="O260" s="22" t="str">
+        <f t="shared" si="101"/>
+        <v>19</v>
+      </c>
+      <c r="P260" s="21">
+        <f t="shared" si="102"/>
+        <v>9.74</v>
+      </c>
+      <c r="Q260" s="21">
+        <f t="shared" si="103"/>
+        <v>-82.821944444444441</v>
+      </c>
+      <c r="R260" s="25" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="261" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A261" s="22">
+        <v>260</v>
+      </c>
+      <c r="B261" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C261" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D261" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E261" s="24" t="s">
+        <v>574</v>
+      </c>
+      <c r="F261" s="24" t="s">
+        <v>580</v>
+      </c>
+      <c r="G261" s="22" t="s">
+        <v>565</v>
+      </c>
+      <c r="H261" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I261" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="J261" s="22" t="str">
+        <f t="shared" si="96"/>
+        <v>09</v>
+      </c>
+      <c r="K261" s="22" t="str">
+        <f t="shared" si="97"/>
+        <v>44</v>
+      </c>
+      <c r="L261" s="22" t="str">
+        <f t="shared" si="98"/>
+        <v>48</v>
+      </c>
+      <c r="M261" s="22" t="str">
+        <f t="shared" si="99"/>
+        <v>82</v>
+      </c>
+      <c r="N261" s="22" t="str">
+        <f t="shared" si="100"/>
+        <v>49</v>
+      </c>
+      <c r="O261" s="22" t="str">
+        <f t="shared" si="101"/>
+        <v>08</v>
+      </c>
+      <c r="P261" s="21">
+        <f t="shared" si="102"/>
+        <v>9.7466666666666661</v>
+      </c>
+      <c r="Q261" s="21">
+        <f t="shared" si="103"/>
+        <v>-82.818888888888893</v>
+      </c>
+      <c r="R261" s="25" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="262" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A262" s="22">
+        <v>261</v>
+      </c>
+      <c r="B262" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C262" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D262" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E262" s="24" t="s">
+        <v>575</v>
+      </c>
+      <c r="F262" s="24" t="s">
+        <v>581</v>
+      </c>
+      <c r="G262" s="22" t="s">
+        <v>565</v>
+      </c>
+      <c r="H262" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I262" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="J262" s="22" t="str">
+        <f t="shared" si="96"/>
+        <v>09</v>
+      </c>
+      <c r="K262" s="22" t="str">
+        <f t="shared" si="97"/>
+        <v>44</v>
+      </c>
+      <c r="L262" s="22" t="str">
+        <f t="shared" si="98"/>
+        <v>36</v>
+      </c>
+      <c r="M262" s="22" t="str">
+        <f t="shared" si="99"/>
+        <v>82</v>
+      </c>
+      <c r="N262" s="22" t="str">
+        <f t="shared" si="100"/>
+        <v>48</v>
+      </c>
+      <c r="O262" s="22" t="str">
+        <f t="shared" si="101"/>
+        <v>23</v>
+      </c>
+      <c r="P262" s="21">
+        <f t="shared" si="102"/>
+        <v>9.7433333333333341</v>
+      </c>
+      <c r="Q262" s="21">
+        <f t="shared" si="103"/>
+        <v>-82.80638888888889</v>
+      </c>
+      <c r="R262" s="25" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="263" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A263" s="22">
+        <v>262</v>
+      </c>
+      <c r="B263" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C263" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D263" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E263" s="24" t="s">
+        <v>576</v>
+      </c>
+      <c r="F263" s="24" t="s">
+        <v>582</v>
+      </c>
+      <c r="G263" s="22" t="s">
+        <v>565</v>
+      </c>
+      <c r="H263" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I263" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="J263" s="22" t="str">
+        <f t="shared" si="96"/>
+        <v>09</v>
+      </c>
+      <c r="K263" s="22" t="str">
+        <f t="shared" si="97"/>
+        <v>44</v>
+      </c>
+      <c r="L263" s="22" t="str">
+        <f t="shared" si="98"/>
+        <v>29</v>
+      </c>
+      <c r="M263" s="22" t="str">
+        <f t="shared" si="99"/>
+        <v>82</v>
+      </c>
+      <c r="N263" s="22" t="str">
+        <f t="shared" si="100"/>
+        <v>48</v>
+      </c>
+      <c r="O263" s="22" t="str">
+        <f t="shared" si="101"/>
+        <v>32</v>
+      </c>
+      <c r="P263" s="21">
+        <f t="shared" si="102"/>
+        <v>9.7413888888888884</v>
+      </c>
+      <c r="Q263" s="21">
+        <f t="shared" si="103"/>
+        <v>-82.808888888888887</v>
+      </c>
+      <c r="R263" s="25" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="264" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A264" s="22">
+        <v>263</v>
+      </c>
+      <c r="B264" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C264" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D264" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E264" s="24" t="s">
+        <v>577</v>
+      </c>
+      <c r="F264" s="24" t="s">
+        <v>583</v>
+      </c>
+      <c r="G264" s="22" t="s">
+        <v>565</v>
+      </c>
+      <c r="H264" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I264" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="J264" s="22" t="str">
+        <f t="shared" si="96"/>
+        <v>09</v>
+      </c>
+      <c r="K264" s="22" t="str">
+        <f t="shared" si="97"/>
+        <v>44</v>
+      </c>
+      <c r="L264" s="22" t="str">
+        <f t="shared" si="98"/>
+        <v>16</v>
+      </c>
+      <c r="M264" s="22" t="str">
+        <f t="shared" si="99"/>
+        <v>82</v>
+      </c>
+      <c r="N264" s="22" t="str">
+        <f t="shared" si="100"/>
+        <v>48</v>
+      </c>
+      <c r="O264" s="22" t="str">
+        <f t="shared" si="101"/>
+        <v>30</v>
+      </c>
+      <c r="P264" s="21">
+        <f t="shared" si="102"/>
+        <v>9.7377777777777776</v>
+      </c>
+      <c r="Q264" s="21">
+        <f t="shared" si="103"/>
+        <v>82.808333333333337</v>
+      </c>
+      <c r="R264" s="25" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="265" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B265" s="22"/>
+      <c r="C265" s="22"/>
+      <c r="D265" s="22"/>
       <c r="E265" s="2"/>
       <c r="F265" s="2"/>
-      <c r="P265" s="1"/>
-      <c r="Q265" s="1"/>
-    </row>
-    <row r="266" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="G265" s="22"/>
+      <c r="H265" s="22"/>
+      <c r="I265" s="22"/>
+      <c r="J265" s="22" t="e">
+        <f t="shared" si="96"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K265" s="22" t="e">
+        <f t="shared" si="97"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L265" s="22" t="e">
+        <f t="shared" si="98"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M265" s="22" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N265" s="22" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O265" s="22" t="e">
+        <f t="shared" si="101"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P265" s="21" t="e">
+        <f t="shared" si="102"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q265" s="21" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R265" s="25"/>
+    </row>
+    <row r="266" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
-      <c r="P266" s="1"/>
-      <c r="Q266" s="1"/>
-    </row>
-    <row r="267" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J266" s="22" t="e">
+        <f t="shared" si="96"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K266" s="22" t="e">
+        <f t="shared" si="97"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L266" s="22" t="e">
+        <f t="shared" si="98"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M266" s="22" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N266" s="22" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O266" s="22" t="e">
+        <f t="shared" si="101"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P266" s="21" t="e">
+        <f t="shared" si="102"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q266" s="21" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R266" s="25"/>
+    </row>
+    <row r="267" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
-      <c r="P267" s="1"/>
-      <c r="Q267" s="1"/>
-    </row>
-    <row r="268" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J267" s="22" t="e">
+        <f t="shared" si="96"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K267" s="22" t="e">
+        <f t="shared" si="97"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L267" s="22" t="e">
+        <f t="shared" si="98"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M267" s="22" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N267" s="22" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O267" s="22" t="e">
+        <f t="shared" si="101"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P267" s="21" t="e">
+        <f t="shared" si="102"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q267" s="21" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R267" s="25"/>
+    </row>
+    <row r="268" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
-      <c r="P268" s="1"/>
-      <c r="Q268" s="1"/>
-    </row>
-    <row r="269" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="J268" s="22" t="e">
+        <f t="shared" si="96"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K268" s="22" t="e">
+        <f t="shared" si="97"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L268" s="22" t="e">
+        <f t="shared" si="98"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M268" s="22" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N268" s="22" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O268" s="22" t="e">
+        <f t="shared" si="101"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P268" s="21" t="e">
+        <f t="shared" si="102"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q268" s="21" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R268" s="25"/>
+    </row>
+    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E269" s="2"/>
       <c r="P269" s="1"/>
       <c r="Q269" s="1"/>
     </row>
-    <row r="270" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
       <c r="P270" s="1"/>
       <c r="Q270" s="1"/>
     </row>
-    <row r="271" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E271" s="2"/>
       <c r="F271" s="2"/>
       <c r="P271" s="1"/>
       <c r="Q271" s="1"/>
     </row>
-    <row r="272" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E272" s="2"/>
       <c r="F272" s="2"/>
       <c r="P272" s="1"/>
@@ -18895,7 +20664,7 @@
       <c r="Q446" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:I252" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="B1:I268" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -20031,35 +21800,35 @@
         <v>72</v>
       </c>
       <c r="I19" s="22" t="str">
-        <f>MID(D19,1,FIND("°",D19,1)-1)</f>
+        <f t="shared" ref="I19:I36" si="8">MID(D19,1,FIND("°",D19,1)-1)</f>
         <v>21</v>
       </c>
       <c r="J19" s="22" t="str">
-        <f>MID(D19,FIND("°",D19,1)+1,(FIND("′",D19,1)-FIND("°",D19,1))-1)</f>
+        <f t="shared" ref="J19:J36" si="9">MID(D19,FIND("°",D19,1)+1,(FIND("′",D19,1)-FIND("°",D19,1))-1)</f>
         <v>34</v>
       </c>
       <c r="K19" s="22" t="e">
-        <f>MID(D19,FIND("′",D19,1)+1,(FIND("″",D19,1)-FIND("′",D19,1))-1)</f>
+        <f t="shared" ref="K19:K36" si="10">MID(D19,FIND("′",D19,1)+1,(FIND("″",D19,1)-FIND("′",D19,1))-1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L19" s="22" t="str">
-        <f>MID(E19,1,FIND("°",E19,1)-1)</f>
+        <f t="shared" ref="L19:L36" si="11">MID(E19,1,FIND("°",E19,1)-1)</f>
         <v>83</v>
       </c>
       <c r="M19" s="22" t="str">
-        <f>MID(E19,FIND("°",E19,1)+1,(FIND("′",E19,1)-FIND("°",E19,1))-1)</f>
+        <f t="shared" ref="M19:M36" si="12">MID(E19,FIND("°",E19,1)+1,(FIND("′",E19,1)-FIND("°",E19,1))-1)</f>
         <v>31</v>
       </c>
       <c r="N19" s="22" t="e">
-        <f>MID(E19,FIND("′",E19,1)+1,(FIND("″",E19,1)-FIND("′",E19,1))-1)</f>
+        <f t="shared" ref="N19:N36" si="13">MID(E19,FIND("′",E19,1)+1,(FIND("″",E19,1)-FIND("′",E19,1))-1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="O19" s="21" t="e">
-        <f>((((K19/60)+J19)/60)+I19)*IF(B19="S",-1, 1)</f>
+        <f t="shared" ref="O19:O36" si="14">((((K19/60)+J19)/60)+I19)*IF(B19="S",-1, 1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="P19" s="21" t="e">
-        <f>((((N19/60)+M19)/60)+L19)*IF(C19="W",-1, 1)</f>
+        <f t="shared" ref="P19:P36" si="15">((((N19/60)+M19)/60)+L19)*IF(C19="W",-1, 1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="Q19" s="25" t="s">
@@ -20092,35 +21861,35 @@
         <v>72</v>
       </c>
       <c r="I20" s="22" t="str">
-        <f>MID(D20,1,FIND("°",D20,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="J20" s="22" t="str">
-        <f>MID(D20,FIND("°",D20,1)+1,(FIND("′",D20,1)-FIND("°",D20,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>32,981</v>
       </c>
       <c r="K20" s="22" t="e">
-        <f>MID(D20,FIND("′",D20,1)+1,(FIND("″",D20,1)-FIND("′",D20,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="L20" s="22" t="str">
-        <f>MID(E20,1,FIND("°",E20,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>38</v>
       </c>
       <c r="M20" s="22" t="str">
-        <f>MID(E20,FIND("°",E20,1)+1,(FIND("′",E20,1)-FIND("°",E20,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>48.669</v>
       </c>
       <c r="N20" s="22" t="e">
-        <f>MID(E20,FIND("′",E20,1)+1,(FIND("″",E20,1)-FIND("′",E20,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="O20" s="21" t="e">
-        <f>((((K20/60)+J20)/60)+I20)*IF(B20="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>#VALUE!</v>
       </c>
       <c r="P20" s="21" t="e">
-        <f>((((N20/60)+M20)/60)+L20)*IF(C20="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="Q20" s="25" t="s">
@@ -20153,35 +21922,35 @@
         <v>186</v>
       </c>
       <c r="I21" s="22" t="str">
-        <f>MID(D21,1,FIND("°",D21,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>02</v>
       </c>
       <c r="J21" s="22" t="str">
-        <f>MID(D21,FIND("°",D21,1)+1,(FIND("′",D21,1)-FIND("°",D21,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>53</v>
       </c>
       <c r="K21" s="22" t="str">
-        <f>MID(D21,FIND("′",D21,1)+1,(FIND("″",D21,1)-FIND("′",D21,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>22</v>
       </c>
       <c r="L21" s="22" t="str">
-        <f>MID(E21,1,FIND("°",E21,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>41</v>
       </c>
       <c r="M21" s="22" t="str">
-        <f>MID(E21,FIND("°",E21,1)+1,(FIND("′",E21,1)-FIND("°",E21,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
       <c r="N21" s="22" t="str">
-        <f>MID(E21,FIND("′",E21,1)+1,(FIND("″",E21,1)-FIND("′",E21,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>46</v>
       </c>
       <c r="O21" s="21">
-        <f>((((K21/60)+J21)/60)+I21)*IF(B21="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>-2.8894444444444445</v>
       </c>
       <c r="P21" s="21">
-        <f>((((N21/60)+M21)/60)+L21)*IF(C21="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>-41.229444444444447</v>
       </c>
       <c r="Q21" s="25" t="s">
@@ -20214,35 +21983,35 @@
         <v>186</v>
       </c>
       <c r="I22" s="22" t="str">
-        <f>MID(D22,1,FIND("°",D22,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>04</v>
       </c>
       <c r="J22" s="22" t="str">
-        <f>MID(D22,FIND("°",D22,1)+1,(FIND("′",D22,1)-FIND("°",D22,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>06</v>
       </c>
       <c r="K22" s="22" t="str">
-        <f>MID(D22,FIND("′",D22,1)+1,(FIND("″",D22,1)-FIND("′",D22,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>06</v>
       </c>
       <c r="L22" s="22" t="str">
-        <f>MID(E22,1,FIND("°",E22,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>38</v>
       </c>
       <c r="M22" s="22" t="str">
-        <f>MID(E22,FIND("°",E22,1)+1,(FIND("′",E22,1)-FIND("°",E22,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>08</v>
       </c>
       <c r="N22" s="22" t="str">
-        <f>MID(E22,FIND("′",E22,1)+1,(FIND("″",E22,1)-FIND("′",E22,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>56</v>
       </c>
       <c r="O22" s="21">
-        <f>((((K22/60)+J22)/60)+I22)*IF(B22="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>-4.1016666666666666</v>
       </c>
       <c r="P22" s="21">
-        <f>((((N22/60)+M22)/60)+L22)*IF(C22="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>-38.148888888888891</v>
       </c>
       <c r="Q22" s="25" t="s">
@@ -20275,35 +22044,35 @@
         <v>442</v>
       </c>
       <c r="I23" s="22" t="str">
-        <f>MID(D23,1,FIND("°",D23,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>04</v>
       </c>
       <c r="J23" s="22" t="str">
-        <f>MID(D23,FIND("°",D23,1)+1,(FIND("′",D23,1)-FIND("°",D23,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>53</v>
       </c>
       <c r="K23" s="22" t="str">
-        <f>MID(D23,FIND("′",D23,1)+1,(FIND("″",D23,1)-FIND("′",D23,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>26</v>
       </c>
       <c r="L23" s="22" t="str">
-        <f>MID(E23,1,FIND("°",E23,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>37</v>
       </c>
       <c r="M23" s="22" t="str">
-        <f>MID(E23,FIND("°",E23,1)+1,(FIND("′",E23,1)-FIND("°",E23,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
       <c r="N23" s="22" t="str">
-        <f>MID(E23,FIND("′",E23,1)+1,(FIND("″",E23,1)-FIND("′",E23,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>37</v>
       </c>
       <c r="O23" s="21">
-        <f>((((K23/60)+J23)/60)+I23)*IF(B23="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>-4.8905555555555553</v>
       </c>
       <c r="P23" s="21">
-        <f>((((N23/60)+M23)/60)+L23)*IF(C23="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>-37.243611111111115</v>
       </c>
       <c r="Q23" s="25" t="s">
@@ -20336,35 +22105,35 @@
         <v>442</v>
       </c>
       <c r="I24" s="22" t="str">
-        <f>MID(D24,1,FIND("°",D24,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>05</v>
       </c>
       <c r="J24" s="22" t="str">
-        <f>MID(D24,FIND("°",D24,1)+1,(FIND("′",D24,1)-FIND("°",D24,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="K24" s="22" t="str">
-        <f>MID(D24,FIND("′",D24,1)+1,(FIND("″",D24,1)-FIND("′",D24,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>06</v>
       </c>
       <c r="L24" s="22" t="str">
-        <f>MID(E24,1,FIND("°",E24,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>35</v>
       </c>
       <c r="M24" s="22" t="str">
-        <f>MID(E24,FIND("°",E24,1)+1,(FIND("′",E24,1)-FIND("°",E24,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>27</v>
       </c>
       <c r="N24" s="22" t="str">
-        <f>MID(E24,FIND("′",E24,1)+1,(FIND("″",E24,1)-FIND("′",E24,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>27</v>
       </c>
       <c r="O24" s="21">
-        <f>((((K24/60)+J24)/60)+I24)*IF(B24="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>-5.2016666666666662</v>
       </c>
       <c r="P24" s="21">
-        <f>((((N24/60)+M24)/60)+L24)*IF(C24="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>-35.457500000000003</v>
       </c>
       <c r="Q24" s="25" t="s">
@@ -20397,35 +22166,35 @@
         <v>443</v>
       </c>
       <c r="I25" s="22" t="str">
-        <f>MID(D25,1,FIND("°",D25,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>06</v>
       </c>
       <c r="J25" s="22" t="str">
-        <f>MID(D25,FIND("°",D25,1)+1,(FIND("′",D25,1)-FIND("°",D25,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
       <c r="K25" s="22" t="str">
-        <f>MID(D25,FIND("′",D25,1)+1,(FIND("″",D25,1)-FIND("′",D25,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="L25" s="22" t="str">
-        <f>MID(E25,1,FIND("°",E25,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
       <c r="M25" s="22" t="str">
-        <f>MID(E25,FIND("°",E25,1)+1,(FIND("′",E25,1)-FIND("°",E25,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>57</v>
       </c>
       <c r="N25" s="22" t="str">
-        <f>MID(E25,FIND("′",E25,1)+1,(FIND("″",E25,1)-FIND("′",E25,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>30</v>
       </c>
       <c r="O25" s="21">
-        <f>((((K25/60)+J25)/60)+I25)*IF(B25="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>-6.5030555555555551</v>
       </c>
       <c r="P25" s="21">
-        <f>((((N25/60)+M25)/60)+L25)*IF(C25="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>-34.958333333333336</v>
       </c>
       <c r="Q25" s="25" t="s">
@@ -20458,35 +22227,35 @@
         <v>443</v>
       </c>
       <c r="I26" s="22" t="str">
-        <f>MID(D26,1,FIND("°",D26,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>06</v>
       </c>
       <c r="J26" s="22" t="str">
-        <f>MID(D26,FIND("°",D26,1)+1,(FIND("′",D26,1)-FIND("°",D26,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>57</v>
       </c>
       <c r="K26" s="22" t="str">
-        <f>MID(D26,FIND("′",D26,1)+1,(FIND("″",D26,1)-FIND("′",D26,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>57</v>
       </c>
       <c r="L26" s="22" t="str">
-        <f>MID(E26,1,FIND("°",E26,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
       <c r="M26" s="22" t="str">
-        <f>MID(E26,FIND("°",E26,1)+1,(FIND("′",E26,1)-FIND("°",E26,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>51</v>
       </c>
       <c r="N26" s="22" t="str">
-        <f>MID(E26,FIND("′",E26,1)+1,(FIND("″",E26,1)-FIND("′",E26,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>22</v>
       </c>
       <c r="O26" s="21">
-        <f>((((K26/60)+J26)/60)+I26)*IF(B26="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>-6.9658333333333333</v>
       </c>
       <c r="P26" s="21">
-        <f>((((N26/60)+M26)/60)+L26)*IF(C26="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>-34.856111111111112</v>
       </c>
       <c r="Q26" s="25" t="s">
@@ -20519,35 +22288,35 @@
         <v>444</v>
       </c>
       <c r="I27" s="22" t="str">
-        <f>MID(D27,1,FIND("°",D27,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>07</v>
       </c>
       <c r="J27" s="22" t="str">
-        <f>MID(D27,FIND("°",D27,1)+1,(FIND("′",D27,1)-FIND("°",D27,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>33</v>
       </c>
       <c r="K27" s="22" t="str">
-        <f>MID(D27,FIND("′",D27,1)+1,(FIND("″",D27,1)-FIND("′",D27,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>07</v>
       </c>
       <c r="L27" s="22" t="str">
-        <f>MID(E27,1,FIND("°",E27,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
       <c r="M27" s="22" t="str">
-        <f>MID(E27,FIND("°",E27,1)+1,(FIND("′",E27,1)-FIND("°",E27,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>50</v>
       </c>
       <c r="N27" s="22" t="str">
-        <f>MID(E27,FIND("′",E27,1)+1,(FIND("″",E27,1)-FIND("′",E27,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>39</v>
       </c>
       <c r="O27" s="21">
-        <f>((((K27/60)+J27)/60)+I27)*IF(B27="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>-7.5519444444444446</v>
       </c>
       <c r="P27" s="21">
-        <f>((((N27/60)+M27)/60)+L27)*IF(C27="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>-34.844166666666666</v>
       </c>
       <c r="Q27" s="25" t="s">
@@ -20580,35 +22349,35 @@
         <v>444</v>
       </c>
       <c r="I28" s="22" t="str">
-        <f>MID(D28,1,FIND("°",D28,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>08</v>
       </c>
       <c r="J28" s="22" t="str">
-        <f>MID(D28,FIND("°",D28,1)+1,(FIND("′",D28,1)-FIND("°",D28,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>02</v>
       </c>
       <c r="K28" s="22" t="str">
-        <f>MID(D28,FIND("′",D28,1)+1,(FIND("″",D28,1)-FIND("′",D28,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>54</v>
       </c>
       <c r="L28" s="22" t="str">
-        <f>MID(E28,1,FIND("°",E28,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
       <c r="M28" s="22" t="str">
-        <f>MID(E28,FIND("°",E28,1)+1,(FIND("′",E28,1)-FIND("°",E28,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>52</v>
       </c>
       <c r="N28" s="22" t="str">
-        <f>MID(E28,FIND("′",E28,1)+1,(FIND("″",E28,1)-FIND("′",E28,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>42</v>
       </c>
       <c r="O28" s="21">
-        <f>((((K28/60)+J28)/60)+I28)*IF(B28="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>-8.0483333333333338</v>
       </c>
       <c r="P28" s="21">
-        <f>((((N28/60)+M28)/60)+L28)*IF(C28="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>-34.87833333333333</v>
       </c>
       <c r="Q28" s="25" t="s">
@@ -20641,35 +22410,35 @@
         <v>186</v>
       </c>
       <c r="I29" s="22" t="str">
-        <f>MID(D29,1,FIND("°",D29,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>02</v>
       </c>
       <c r="J29" s="22" t="str">
-        <f>MID(D29,FIND("°",D29,1)+1,(FIND("′",D29,1)-FIND("°",D29,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>53</v>
       </c>
       <c r="K29" s="22" t="str">
-        <f>MID(D29,FIND("′",D29,1)+1,(FIND("″",D29,1)-FIND("′",D29,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>22</v>
       </c>
       <c r="L29" s="22" t="str">
-        <f>MID(E29,1,FIND("°",E29,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>41</v>
       </c>
       <c r="M29" s="22" t="str">
-        <f>MID(E29,FIND("°",E29,1)+1,(FIND("′",E29,1)-FIND("°",E29,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
       <c r="N29" s="22" t="str">
-        <f>MID(E29,FIND("′",E29,1)+1,(FIND("″",E29,1)-FIND("′",E29,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>46</v>
       </c>
       <c r="O29" s="21">
-        <f>((((K29/60)+J29)/60)+I29)*IF(B29="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>-2.8894444444444445</v>
       </c>
       <c r="P29" s="21">
-        <f>((((N29/60)+M29)/60)+L29)*IF(C29="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>-41.229444444444447</v>
       </c>
       <c r="Q29" s="25" t="s">
@@ -20702,35 +22471,35 @@
         <v>186</v>
       </c>
       <c r="I30" s="22" t="str">
-        <f>MID(D30,1,FIND("°",D30,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>04</v>
       </c>
       <c r="J30" s="22" t="str">
-        <f>MID(D30,FIND("°",D30,1)+1,(FIND("′",D30,1)-FIND("°",D30,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>06</v>
       </c>
       <c r="K30" s="22" t="str">
-        <f>MID(D30,FIND("′",D30,1)+1,(FIND("″",D30,1)-FIND("′",D30,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>06</v>
       </c>
       <c r="L30" s="22" t="str">
-        <f>MID(E30,1,FIND("°",E30,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>38</v>
       </c>
       <c r="M30" s="22" t="str">
-        <f>MID(E30,FIND("°",E30,1)+1,(FIND("′",E30,1)-FIND("°",E30,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>08</v>
       </c>
       <c r="N30" s="22" t="str">
-        <f>MID(E30,FIND("′",E30,1)+1,(FIND("″",E30,1)-FIND("′",E30,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>56</v>
       </c>
       <c r="O30" s="21">
-        <f>((((K30/60)+J30)/60)+I30)*IF(B30="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>-4.1016666666666666</v>
       </c>
       <c r="P30" s="21">
-        <f>((((N30/60)+M30)/60)+L30)*IF(C30="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>-38.148888888888891</v>
       </c>
       <c r="Q30" s="25" t="s">
@@ -20763,35 +22532,35 @@
         <v>442</v>
       </c>
       <c r="I31" s="22" t="str">
-        <f>MID(D31,1,FIND("°",D31,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>04</v>
       </c>
       <c r="J31" s="22" t="str">
-        <f>MID(D31,FIND("°",D31,1)+1,(FIND("′",D31,1)-FIND("°",D31,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>53</v>
       </c>
       <c r="K31" s="22" t="str">
-        <f>MID(D31,FIND("′",D31,1)+1,(FIND("″",D31,1)-FIND("′",D31,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>26</v>
       </c>
       <c r="L31" s="22" t="str">
-        <f>MID(E31,1,FIND("°",E31,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>37</v>
       </c>
       <c r="M31" s="22" t="str">
-        <f>MID(E31,FIND("°",E31,1)+1,(FIND("′",E31,1)-FIND("°",E31,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
       <c r="N31" s="22" t="str">
-        <f>MID(E31,FIND("′",E31,1)+1,(FIND("″",E31,1)-FIND("′",E31,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>37</v>
       </c>
       <c r="O31" s="21">
-        <f>((((K31/60)+J31)/60)+I31)*IF(B31="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>-4.8905555555555553</v>
       </c>
       <c r="P31" s="21">
-        <f>((((N31/60)+M31)/60)+L31)*IF(C31="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>-37.243611111111115</v>
       </c>
       <c r="Q31" s="25" t="s">
@@ -20824,35 +22593,35 @@
         <v>442</v>
       </c>
       <c r="I32" s="22" t="str">
-        <f>MID(D32,1,FIND("°",D32,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>05</v>
       </c>
       <c r="J32" s="22" t="str">
-        <f>MID(D32,FIND("°",D32,1)+1,(FIND("′",D32,1)-FIND("°",D32,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="K32" s="22" t="str">
-        <f>MID(D32,FIND("′",D32,1)+1,(FIND("″",D32,1)-FIND("′",D32,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>06</v>
       </c>
       <c r="L32" s="22" t="str">
-        <f>MID(E32,1,FIND("°",E32,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>35</v>
       </c>
       <c r="M32" s="22" t="str">
-        <f>MID(E32,FIND("°",E32,1)+1,(FIND("′",E32,1)-FIND("°",E32,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>27</v>
       </c>
       <c r="N32" s="22" t="str">
-        <f>MID(E32,FIND("′",E32,1)+1,(FIND("″",E32,1)-FIND("′",E32,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>27</v>
       </c>
       <c r="O32" s="21">
-        <f>((((K32/60)+J32)/60)+I32)*IF(B32="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>-5.2016666666666662</v>
       </c>
       <c r="P32" s="21">
-        <f>((((N32/60)+M32)/60)+L32)*IF(C32="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>-35.457500000000003</v>
       </c>
       <c r="Q32" s="25" t="s">
@@ -20885,35 +22654,35 @@
         <v>443</v>
       </c>
       <c r="I33" s="22" t="str">
-        <f>MID(D33,1,FIND("°",D33,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>06</v>
       </c>
       <c r="J33" s="22" t="str">
-        <f>MID(D33,FIND("°",D33,1)+1,(FIND("′",D33,1)-FIND("°",D33,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
       <c r="K33" s="22" t="str">
-        <f>MID(D33,FIND("′",D33,1)+1,(FIND("″",D33,1)-FIND("′",D33,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="L33" s="22" t="str">
-        <f>MID(E33,1,FIND("°",E33,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
       <c r="M33" s="22" t="str">
-        <f>MID(E33,FIND("°",E33,1)+1,(FIND("′",E33,1)-FIND("°",E33,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>57</v>
       </c>
       <c r="N33" s="22" t="str">
-        <f>MID(E33,FIND("′",E33,1)+1,(FIND("″",E33,1)-FIND("′",E33,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>30</v>
       </c>
       <c r="O33" s="21">
-        <f>((((K33/60)+J33)/60)+I33)*IF(B33="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>-6.5030555555555551</v>
       </c>
       <c r="P33" s="21">
-        <f>((((N33/60)+M33)/60)+L33)*IF(C33="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>-34.958333333333336</v>
       </c>
       <c r="Q33" s="25" t="s">
@@ -20946,35 +22715,35 @@
         <v>443</v>
       </c>
       <c r="I34" s="22" t="str">
-        <f>MID(D34,1,FIND("°",D34,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>06</v>
       </c>
       <c r="J34" s="22" t="str">
-        <f>MID(D34,FIND("°",D34,1)+1,(FIND("′",D34,1)-FIND("°",D34,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>57</v>
       </c>
       <c r="K34" s="22" t="str">
-        <f>MID(D34,FIND("′",D34,1)+1,(FIND("″",D34,1)-FIND("′",D34,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>57</v>
       </c>
       <c r="L34" s="22" t="str">
-        <f>MID(E34,1,FIND("°",E34,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
       <c r="M34" s="22" t="str">
-        <f>MID(E34,FIND("°",E34,1)+1,(FIND("′",E34,1)-FIND("°",E34,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>51</v>
       </c>
       <c r="N34" s="22" t="str">
-        <f>MID(E34,FIND("′",E34,1)+1,(FIND("″",E34,1)-FIND("′",E34,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>22</v>
       </c>
       <c r="O34" s="21">
-        <f>((((K34/60)+J34)/60)+I34)*IF(B34="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>-6.9658333333333333</v>
       </c>
       <c r="P34" s="21">
-        <f>((((N34/60)+M34)/60)+L34)*IF(C34="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>-34.856111111111112</v>
       </c>
       <c r="Q34" s="25" t="s">
@@ -21007,35 +22776,35 @@
         <v>444</v>
       </c>
       <c r="I35" s="22" t="str">
-        <f>MID(D35,1,FIND("°",D35,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>07</v>
       </c>
       <c r="J35" s="22" t="str">
-        <f>MID(D35,FIND("°",D35,1)+1,(FIND("′",D35,1)-FIND("°",D35,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>33</v>
       </c>
       <c r="K35" s="22" t="str">
-        <f>MID(D35,FIND("′",D35,1)+1,(FIND("″",D35,1)-FIND("′",D35,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>07</v>
       </c>
       <c r="L35" s="22" t="str">
-        <f>MID(E35,1,FIND("°",E35,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
       <c r="M35" s="22" t="str">
-        <f>MID(E35,FIND("°",E35,1)+1,(FIND("′",E35,1)-FIND("°",E35,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>50</v>
       </c>
       <c r="N35" s="22" t="str">
-        <f>MID(E35,FIND("′",E35,1)+1,(FIND("″",E35,1)-FIND("′",E35,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>39</v>
       </c>
       <c r="O35" s="21">
-        <f>((((K35/60)+J35)/60)+I35)*IF(B35="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>-7.5519444444444446</v>
       </c>
       <c r="P35" s="21">
-        <f>((((N35/60)+M35)/60)+L35)*IF(C35="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>-34.844166666666666</v>
       </c>
       <c r="Q35" s="25" t="s">
@@ -21068,35 +22837,35 @@
         <v>444</v>
       </c>
       <c r="I36" s="22" t="str">
-        <f>MID(D36,1,FIND("°",D36,1)-1)</f>
+        <f t="shared" si="8"/>
         <v>08</v>
       </c>
       <c r="J36" s="22" t="str">
-        <f>MID(D36,FIND("°",D36,1)+1,(FIND("′",D36,1)-FIND("°",D36,1))-1)</f>
+        <f t="shared" si="9"/>
         <v>02</v>
       </c>
       <c r="K36" s="22" t="str">
-        <f>MID(D36,FIND("′",D36,1)+1,(FIND("″",D36,1)-FIND("′",D36,1))-1)</f>
+        <f t="shared" si="10"/>
         <v>54</v>
       </c>
       <c r="L36" s="22" t="str">
-        <f>MID(E36,1,FIND("°",E36,1)-1)</f>
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
       <c r="M36" s="22" t="str">
-        <f>MID(E36,FIND("°",E36,1)+1,(FIND("′",E36,1)-FIND("°",E36,1))-1)</f>
+        <f t="shared" si="12"/>
         <v>52</v>
       </c>
       <c r="N36" s="22" t="str">
-        <f>MID(E36,FIND("′",E36,1)+1,(FIND("″",E36,1)-FIND("′",E36,1))-1)</f>
+        <f t="shared" si="13"/>
         <v>42</v>
       </c>
       <c r="O36" s="21">
-        <f>((((K36/60)+J36)/60)+I36)*IF(B36="S",-1, 1)</f>
+        <f t="shared" si="14"/>
         <v>-8.0483333333333338</v>
       </c>
       <c r="P36" s="21">
-        <f>((((N36/60)+M36)/60)+L36)*IF(C36="W",-1, 1)</f>
+        <f t="shared" si="15"/>
         <v>-34.87833333333333</v>
       </c>
       <c r="Q36" s="25" t="s">

--- a/Ocorrências Literatura.xlsx
+++ b/Ocorrências Literatura.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faculdade\Laboratorio\lagostas_carapaca\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1001575-B972-49BB-AAB6-A77DC7D8CE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBEC1AE-89BA-4CF7-827E-C6E5A438CA83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Ocorrências Literatura.xlsx
+++ b/Ocorrências Literatura.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faculdade\Laboratorio\lagostas_carapaca\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBEC1AE-89BA-4CF7-827E-C6E5A438CA83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52A23E7-CDBD-46DA-B734-EBC2597E977E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3158" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3239" uniqueCount="698">
   <si>
     <t>ID</t>
   </si>
@@ -2209,6 +2209,93 @@
   </si>
   <si>
     <t>19°48′21″</t>
+  </si>
+  <si>
+    <t>BOLAÑOS-CUBILLOS, Nacor (2016)</t>
+  </si>
+  <si>
+    <t>Cayo Bolivar</t>
+  </si>
+  <si>
+    <t>Serranilla </t>
+  </si>
+  <si>
+    <t>Serrana Bank</t>
+  </si>
+  <si>
+    <t>Alice Shoal</t>
+  </si>
+  <si>
+    <t>Bajo Nuevo</t>
+  </si>
+  <si>
+    <t>Roncador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Providencia </t>
+  </si>
+  <si>
+    <t>San Andrés</t>
+  </si>
+  <si>
+    <t>Cayos de Albuquerque</t>
+  </si>
+  <si>
+    <t>Variación fenotípica de la langosta espinosa Panulirus argus (Decapoda_ Paniluridae) en el Caribe Suroccidental</t>
+  </si>
+  <si>
+    <t>12°24′56″</t>
+  </si>
+  <si>
+    <t>81°28′28″</t>
+  </si>
+  <si>
+    <t>79°52′54″</t>
+  </si>
+  <si>
+    <t>79°22′00″</t>
+  </si>
+  <si>
+    <t>78°40′01″</t>
+  </si>
+  <si>
+    <t>80°16′00″</t>
+  </si>
+  <si>
+    <t>80°03′60″</t>
+  </si>
+  <si>
+    <t>81°21′13″</t>
+  </si>
+  <si>
+    <t>81°40′59″</t>
+  </si>
+  <si>
+    <t>81°51′00″</t>
+  </si>
+  <si>
+    <t>12°09′57″</t>
+  </si>
+  <si>
+    <t>12°34′38″</t>
+  </si>
+  <si>
+    <t>13°23′16″</t>
+  </si>
+  <si>
+    <t>13°33′57″</t>
+  </si>
+  <si>
+    <t>14°23′58″</t>
+  </si>
+  <si>
+    <t>15°52′08″</t>
+  </si>
+  <si>
+    <t>16°04′56″</t>
+  </si>
+  <si>
+    <t>15°51′53″</t>
   </si>
 </sst>
 </file>
@@ -22790,113 +22877,638 @@
       </c>
       <c r="Q314" s="2">
         <f t="shared" si="55"/>
-        <v>85.532777777777781</v>
+        <v>-85.532777777777781</v>
       </c>
       <c r="R314" s="16" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E315"/>
-      <c r="F315"/>
-      <c r="P315" s="2"/>
-      <c r="Q315" s="2"/>
-    </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E316" s="17"/>
-      <c r="F316" s="17"/>
-      <c r="P316" s="2"/>
-      <c r="Q316" s="2"/>
-    </row>
-    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E317" s="17"/>
-      <c r="F317" s="17"/>
-      <c r="P317" s="2"/>
-      <c r="Q317" s="2"/>
-    </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E318" s="17"/>
-      <c r="F318" s="17"/>
-      <c r="P318" s="2"/>
-      <c r="Q318" s="2"/>
-    </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E319" s="17"/>
-      <c r="F319" s="17"/>
-      <c r="P319" s="2"/>
-      <c r="Q319" s="2"/>
-    </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E320" s="17"/>
-      <c r="F320" s="17"/>
-      <c r="P320" s="2"/>
-      <c r="Q320" s="2"/>
-    </row>
-    <row r="321" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E321" s="17"/>
-      <c r="F321" s="17"/>
-      <c r="P321" s="2"/>
-      <c r="Q321" s="2"/>
-    </row>
-    <row r="322" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E322" s="17"/>
-      <c r="F322" s="17"/>
-      <c r="P322" s="2"/>
-      <c r="Q322" s="2"/>
-    </row>
-    <row r="323" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="P323" s="2"/>
-      <c r="Q323" s="2"/>
-    </row>
-    <row r="324" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A315" s="1">
+        <v>314</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E315" s="20" t="s">
+        <v>680</v>
+      </c>
+      <c r="F315" s="20" t="s">
+        <v>681</v>
+      </c>
+      <c r="G315" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="H315" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I315" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="J315" s="1" t="str">
+        <f t="shared" ref="J315:J323" si="56">MID(E315,1,FIND("°",E315,1)-1)</f>
+        <v>12</v>
+      </c>
+      <c r="K315" s="1" t="str">
+        <f t="shared" ref="K315:K323" si="57">MID(E315,FIND("°",E315,1)+1,(FIND("′",E315,1)-FIND("°",E315,1))-1)</f>
+        <v>24</v>
+      </c>
+      <c r="L315" s="1" t="str">
+        <f t="shared" ref="L315:L323" si="58">MID(E315,FIND("′",E315,1)+1,(FIND("″",E315,1)-FIND("′",E315,1))-1)</f>
+        <v>56</v>
+      </c>
+      <c r="M315" s="1" t="str">
+        <f t="shared" ref="M315:M323" si="59">MID(F315,1,FIND("°",F315,1)-1)</f>
+        <v>81</v>
+      </c>
+      <c r="N315" s="1" t="str">
+        <f t="shared" ref="N315:N323" si="60">MID(F315,FIND("°",F315,1)+1,(FIND("′",F315,1)-FIND("°",F315,1))-1)</f>
+        <v>28</v>
+      </c>
+      <c r="O315" s="1" t="str">
+        <f t="shared" ref="O315:O323" si="61">MID(F315,FIND("′",F315,1)+1,(FIND("″",F315,1)-FIND("′",F315,1))-1)</f>
+        <v>28</v>
+      </c>
+      <c r="P315" s="2">
+        <f t="shared" ref="P315:P323" si="62">((((L315/60)+K315)/60)+J315)*IF(C315="S",-1, 1)</f>
+        <v>12.415555555555555</v>
+      </c>
+      <c r="Q315" s="2">
+        <f t="shared" ref="Q315:Q323" si="63">((((O315/60)+N315)/60)+M315)*IF(D316="W",-1, 1)</f>
+        <v>-81.474444444444444</v>
+      </c>
+      <c r="R315" s="16" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="316" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A316" s="1">
+        <v>315</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E316" s="20" t="s">
+        <v>697</v>
+      </c>
+      <c r="F316" s="20" t="s">
+        <v>682</v>
+      </c>
+      <c r="G316" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="H316" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I316" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="J316" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>15</v>
+      </c>
+      <c r="K316" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>51</v>
+      </c>
+      <c r="L316" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>53</v>
+      </c>
+      <c r="M316" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>79</v>
+      </c>
+      <c r="N316" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>52</v>
+      </c>
+      <c r="O316" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>54</v>
+      </c>
+      <c r="P316" s="2">
+        <f t="shared" si="62"/>
+        <v>15.864722222222222</v>
+      </c>
+      <c r="Q316" s="2">
+        <f t="shared" si="63"/>
+        <v>-79.881666666666661</v>
+      </c>
+      <c r="R316" s="16" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="317" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A317" s="1">
+        <v>316</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E317" s="20" t="s">
+        <v>696</v>
+      </c>
+      <c r="F317" s="20" t="s">
+        <v>683</v>
+      </c>
+      <c r="G317" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="H317" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I317" s="20" t="s">
+        <v>673</v>
+      </c>
+      <c r="J317" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>16</v>
+      </c>
+      <c r="K317" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>04</v>
+      </c>
+      <c r="L317" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>56</v>
+      </c>
+      <c r="M317" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>79</v>
+      </c>
+      <c r="N317" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>22</v>
+      </c>
+      <c r="O317" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>00</v>
+      </c>
+      <c r="P317" s="2">
+        <f t="shared" si="62"/>
+        <v>16.082222222222221</v>
+      </c>
+      <c r="Q317" s="2">
+        <f t="shared" si="63"/>
+        <v>-79.36666666666666</v>
+      </c>
+      <c r="R317" s="16" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="318" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A318" s="1">
+        <v>317</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E318" s="20" t="s">
+        <v>695</v>
+      </c>
+      <c r="F318" s="20" t="s">
+        <v>684</v>
+      </c>
+      <c r="G318" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="H318" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I318" s="20" t="s">
+        <v>674</v>
+      </c>
+      <c r="J318" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>15</v>
+      </c>
+      <c r="K318" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>52</v>
+      </c>
+      <c r="L318" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>08</v>
+      </c>
+      <c r="M318" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>78</v>
+      </c>
+      <c r="N318" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>40</v>
+      </c>
+      <c r="O318" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>01</v>
+      </c>
+      <c r="P318" s="2">
+        <f t="shared" si="62"/>
+        <v>15.86888888888889</v>
+      </c>
+      <c r="Q318" s="2">
+        <f t="shared" si="63"/>
+        <v>-78.666944444444439</v>
+      </c>
+      <c r="R318" s="16" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="319" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A319" s="1">
+        <v>318</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E319" s="20" t="s">
+        <v>694</v>
+      </c>
+      <c r="F319" s="20" t="s">
+        <v>685</v>
+      </c>
+      <c r="G319" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="H319" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I319" s="20" t="s">
+        <v>672</v>
+      </c>
+      <c r="J319" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>14</v>
+      </c>
+      <c r="K319" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>23</v>
+      </c>
+      <c r="L319" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>58</v>
+      </c>
+      <c r="M319" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>80</v>
+      </c>
+      <c r="N319" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>16</v>
+      </c>
+      <c r="O319" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>00</v>
+      </c>
+      <c r="P319" s="2">
+        <f t="shared" si="62"/>
+        <v>14.399444444444445</v>
+      </c>
+      <c r="Q319" s="2">
+        <f t="shared" si="63"/>
+        <v>-80.266666666666666</v>
+      </c>
+      <c r="R319" s="16" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="320" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A320" s="1">
+        <v>319</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E320" s="20" t="s">
+        <v>693</v>
+      </c>
+      <c r="F320" s="20" t="s">
+        <v>686</v>
+      </c>
+      <c r="G320" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="H320" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I320" s="20" t="s">
+        <v>675</v>
+      </c>
+      <c r="J320" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>13</v>
+      </c>
+      <c r="K320" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>33</v>
+      </c>
+      <c r="L320" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>57</v>
+      </c>
+      <c r="M320" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>80</v>
+      </c>
+      <c r="N320" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>03</v>
+      </c>
+      <c r="O320" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>60</v>
+      </c>
+      <c r="P320" s="2">
+        <f t="shared" si="62"/>
+        <v>13.565833333333334</v>
+      </c>
+      <c r="Q320" s="2">
+        <f t="shared" si="63"/>
+        <v>-80.066666666666663</v>
+      </c>
+      <c r="R320" s="16" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="321" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A321" s="1">
+        <v>320</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E321" s="20" t="s">
+        <v>692</v>
+      </c>
+      <c r="F321" s="20" t="s">
+        <v>687</v>
+      </c>
+      <c r="G321" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="H321" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I321" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="J321" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>13</v>
+      </c>
+      <c r="K321" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>23</v>
+      </c>
+      <c r="L321" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>16</v>
+      </c>
+      <c r="M321" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>81</v>
+      </c>
+      <c r="N321" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>21</v>
+      </c>
+      <c r="O321" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>13</v>
+      </c>
+      <c r="P321" s="2">
+        <f t="shared" si="62"/>
+        <v>13.387777777777778</v>
+      </c>
+      <c r="Q321" s="2">
+        <f t="shared" si="63"/>
+        <v>-81.353611111111107</v>
+      </c>
+      <c r="R321" s="16" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="322" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A322" s="1">
+        <v>321</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E322" s="20" t="s">
+        <v>691</v>
+      </c>
+      <c r="F322" s="20" t="s">
+        <v>688</v>
+      </c>
+      <c r="G322" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="H322" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I322" s="20" t="s">
+        <v>677</v>
+      </c>
+      <c r="J322" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>12</v>
+      </c>
+      <c r="K322" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>34</v>
+      </c>
+      <c r="L322" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>38</v>
+      </c>
+      <c r="M322" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>81</v>
+      </c>
+      <c r="N322" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>40</v>
+      </c>
+      <c r="O322" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>59</v>
+      </c>
+      <c r="P322" s="2">
+        <f t="shared" si="62"/>
+        <v>12.577222222222222</v>
+      </c>
+      <c r="Q322" s="2">
+        <f t="shared" si="63"/>
+        <v>-81.683055555555555</v>
+      </c>
+      <c r="R322" s="16" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="323" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A323" s="1">
+        <v>322</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D323" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E323" s="20" t="s">
+        <v>690</v>
+      </c>
+      <c r="F323" s="20" t="s">
+        <v>689</v>
+      </c>
+      <c r="G323" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="H323" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I323" s="20" t="s">
+        <v>678</v>
+      </c>
+      <c r="J323" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>12</v>
+      </c>
+      <c r="K323" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>09</v>
+      </c>
+      <c r="L323" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>57</v>
+      </c>
+      <c r="M323" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>81</v>
+      </c>
+      <c r="N323" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>51</v>
+      </c>
+      <c r="O323" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>00</v>
+      </c>
+      <c r="P323" s="2">
+        <f t="shared" si="62"/>
+        <v>12.165833333333333</v>
+      </c>
+      <c r="Q323" s="2">
+        <f t="shared" si="63"/>
+        <v>81.849999999999994</v>
+      </c>
+      <c r="R323" s="16" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="324" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="P324" s="2"/>
       <c r="Q324" s="2"/>
-    </row>
-    <row r="325" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="R324" s="16"/>
+    </row>
+    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P325" s="2"/>
       <c r="Q325" s="2"/>
     </row>
-    <row r="326" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P326" s="2"/>
       <c r="Q326" s="2"/>
     </row>
-    <row r="327" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P327" s="2"/>
       <c r="Q327" s="2"/>
     </row>
-    <row r="328" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P328" s="2"/>
       <c r="Q328" s="2"/>
     </row>
-    <row r="329" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P329" s="2"/>
       <c r="Q329" s="2"/>
     </row>
-    <row r="330" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P330" s="2"/>
       <c r="Q330" s="2"/>
     </row>
-    <row r="331" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P331" s="2"/>
       <c r="Q331" s="2"/>
     </row>
-    <row r="332" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P332" s="2"/>
       <c r="Q332" s="2"/>
     </row>
-    <row r="333" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P333" s="2"/>
       <c r="Q333" s="2"/>
     </row>
-    <row r="334" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P334" s="2"/>
       <c r="Q334" s="2"/>
     </row>
-    <row r="335" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P335" s="2"/>
       <c r="Q335" s="2"/>
     </row>
-    <row r="336" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:18" x14ac:dyDescent="0.25">
       <c r="P336" s="2"/>
       <c r="Q336" s="2"/>
     </row>

--- a/Ocorrências Literatura.xlsx
+++ b/Ocorrências Literatura.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faculdade\Laboratorio\lagostas_carapaca\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cofres Obsidian\Mar Aberto\Laboratório\lagostas_carapaca\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52A23E7-CDBD-46DA-B734-EBC2597E977E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC19BE9-1E65-4CCB-9247-0BF9A3CE5693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ocorrências Panulirus'!$B$1:$I$314</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ocorrências Panulirus'!$A$1:$R$387</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3239" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3815" uniqueCount="699">
   <si>
     <t>ID</t>
   </si>
@@ -2296,6 +2296,9 @@
   </si>
   <si>
     <t>15°51′53″</t>
+  </si>
+  <si>
+    <t>Panulirus guttatus</t>
   </si>
 </sst>
 </file>
@@ -8811,7 +8814,7 @@
         <v>17</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>19</v>
@@ -8857,7 +8860,7 @@
       </c>
       <c r="P95" s="2">
         <f t="shared" si="14"/>
-        <v>-20.85</v>
+        <v>20.85</v>
       </c>
       <c r="Q95" s="2">
         <f t="shared" si="15"/>
@@ -22912,31 +22915,31 @@
         <v>670</v>
       </c>
       <c r="J315" s="1" t="str">
-        <f t="shared" ref="J315:J323" si="56">MID(E315,1,FIND("°",E315,1)-1)</f>
+        <f t="shared" ref="J315:J378" si="56">MID(E315,1,FIND("°",E315,1)-1)</f>
         <v>12</v>
       </c>
       <c r="K315" s="1" t="str">
-        <f t="shared" ref="K315:K323" si="57">MID(E315,FIND("°",E315,1)+1,(FIND("′",E315,1)-FIND("°",E315,1))-1)</f>
+        <f t="shared" ref="K315:K378" si="57">MID(E315,FIND("°",E315,1)+1,(FIND("′",E315,1)-FIND("°",E315,1))-1)</f>
         <v>24</v>
       </c>
       <c r="L315" s="1" t="str">
-        <f t="shared" ref="L315:L323" si="58">MID(E315,FIND("′",E315,1)+1,(FIND("″",E315,1)-FIND("′",E315,1))-1)</f>
+        <f t="shared" ref="L315:L378" si="58">MID(E315,FIND("′",E315,1)+1,(FIND("″",E315,1)-FIND("′",E315,1))-1)</f>
         <v>56</v>
       </c>
       <c r="M315" s="1" t="str">
-        <f t="shared" ref="M315:M323" si="59">MID(F315,1,FIND("°",F315,1)-1)</f>
+        <f t="shared" ref="M315:M378" si="59">MID(F315,1,FIND("°",F315,1)-1)</f>
         <v>81</v>
       </c>
       <c r="N315" s="1" t="str">
-        <f t="shared" ref="N315:N323" si="60">MID(F315,FIND("°",F315,1)+1,(FIND("′",F315,1)-FIND("°",F315,1))-1)</f>
+        <f t="shared" ref="N315:N378" si="60">MID(F315,FIND("°",F315,1)+1,(FIND("′",F315,1)-FIND("°",F315,1))-1)</f>
         <v>28</v>
       </c>
       <c r="O315" s="1" t="str">
-        <f t="shared" ref="O315:O323" si="61">MID(F315,FIND("′",F315,1)+1,(FIND("″",F315,1)-FIND("′",F315,1))-1)</f>
+        <f t="shared" ref="O315:O378" si="61">MID(F315,FIND("′",F315,1)+1,(FIND("″",F315,1)-FIND("′",F315,1))-1)</f>
         <v>28</v>
       </c>
       <c r="P315" s="2">
-        <f t="shared" ref="P315:P323" si="62">((((L315/60)+K315)/60)+J315)*IF(C315="S",-1, 1)</f>
+        <f t="shared" ref="P315:P378" si="62">((((L315/60)+K315)/60)+J315)*IF(C315="S",-1, 1)</f>
         <v>12.415555555555555</v>
       </c>
       <c r="Q315" s="2">
@@ -23453,315 +23456,4109 @@
       </c>
       <c r="Q323" s="2">
         <f t="shared" si="63"/>
-        <v>81.849999999999994</v>
+        <v>-81.849999999999994</v>
       </c>
       <c r="R323" s="16" t="s">
         <v>679</v>
       </c>
     </row>
     <row r="324" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P324" s="2"/>
-      <c r="Q324" s="2"/>
-      <c r="R324" s="16"/>
-    </row>
-    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P325" s="2"/>
-      <c r="Q325" s="2"/>
-    </row>
-    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P326" s="2"/>
-      <c r="Q326" s="2"/>
-    </row>
-    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P327" s="2"/>
-      <c r="Q327" s="2"/>
-    </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P328" s="2"/>
-      <c r="Q328" s="2"/>
-    </row>
-    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P329" s="2"/>
-      <c r="Q329" s="2"/>
-    </row>
-    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P330" s="2"/>
-      <c r="Q330" s="2"/>
-    </row>
-    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P331" s="2"/>
-      <c r="Q331" s="2"/>
-    </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P332" s="2"/>
-      <c r="Q332" s="2"/>
-    </row>
-    <row r="333" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P333" s="2"/>
-      <c r="Q333" s="2"/>
-    </row>
-    <row r="334" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P334" s="2"/>
-      <c r="Q334" s="2"/>
-    </row>
-    <row r="335" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P335" s="2"/>
-      <c r="Q335" s="2"/>
+      <c r="A324" s="1">
+        <v>323</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E324" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="F324" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="G324" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="H324" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I324" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="J324" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>21</v>
+      </c>
+      <c r="K324" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>31</v>
+      </c>
+      <c r="L324" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>12</v>
+      </c>
+      <c r="M324" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>80</v>
+      </c>
+      <c r="N324" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>39</v>
+      </c>
+      <c r="O324" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>00</v>
+      </c>
+      <c r="P324" s="2">
+        <f t="shared" si="62"/>
+        <v>21.52</v>
+      </c>
+      <c r="Q324" s="2">
+        <f t="shared" ref="Q324:Q335" si="64">((((O324/60)+N324)/60)+M324)*IF(D324="W",-1, 1)</f>
+        <v>-80.650000000000006</v>
+      </c>
+      <c r="R324" s="16" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="325" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A325" s="1">
+        <v>324</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E325" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="F325" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G325" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="H325" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I325" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="J325" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>21</v>
+      </c>
+      <c r="K325" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>24</v>
+      </c>
+      <c r="L325" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>36</v>
+      </c>
+      <c r="M325" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>, 82</v>
+      </c>
+      <c r="N325" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>19</v>
+      </c>
+      <c r="O325" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>12</v>
+      </c>
+      <c r="P325" s="2">
+        <f t="shared" si="62"/>
+        <v>21.41</v>
+      </c>
+      <c r="Q325" s="2" t="e">
+        <f t="shared" si="64"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R325" s="16" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="326" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A326" s="1">
+        <v>325</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D326" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E326" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="F326" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="G326" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="H326" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I326" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="J326" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>21</v>
+      </c>
+      <c r="K326" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>10</v>
+      </c>
+      <c r="L326" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>48</v>
+      </c>
+      <c r="M326" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>84</v>
+      </c>
+      <c r="N326" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>51</v>
+      </c>
+      <c r="O326" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>36</v>
+      </c>
+      <c r="P326" s="2">
+        <f t="shared" si="62"/>
+        <v>21.18</v>
+      </c>
+      <c r="Q326" s="2">
+        <f t="shared" si="64"/>
+        <v>-84.86</v>
+      </c>
+      <c r="R326" s="16" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="327" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A327" s="1">
+        <v>326</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E327" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="F327" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="G327" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="H327" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I327" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="J327" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K327" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>00</v>
+      </c>
+      <c r="L327" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>00</v>
+      </c>
+      <c r="M327" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>84</v>
+      </c>
+      <c r="N327" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>53</v>
+      </c>
+      <c r="O327" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>24</v>
+      </c>
+      <c r="P327" s="2">
+        <f t="shared" si="62"/>
+        <v>20</v>
+      </c>
+      <c r="Q327" s="2">
+        <f t="shared" si="64"/>
+        <v>-84.89</v>
+      </c>
+      <c r="R327" s="16" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="328" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A328" s="1">
+        <v>327</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E328" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="F328" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="G328" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="H328" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I328" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="J328" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K328" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>16</v>
+      </c>
+      <c r="L328" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>12</v>
+      </c>
+      <c r="M328" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>82</v>
+      </c>
+      <c r="N328" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>25</v>
+      </c>
+      <c r="O328" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>12</v>
+      </c>
+      <c r="P328" s="2">
+        <f t="shared" si="62"/>
+        <v>19.27</v>
+      </c>
+      <c r="Q328" s="2">
+        <f t="shared" si="64"/>
+        <v>-82.42</v>
+      </c>
+      <c r="R328" s="16" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="329" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A329" s="1">
+        <v>328</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E329" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="F329" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="G329" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="H329" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I329" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="J329" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K329" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>10</v>
+      </c>
+      <c r="L329" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>12</v>
+      </c>
+      <c r="M329" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>79</v>
+      </c>
+      <c r="N329" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>54</v>
+      </c>
+      <c r="O329" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>00</v>
+      </c>
+      <c r="P329" s="2">
+        <f t="shared" si="62"/>
+        <v>20.170000000000002</v>
+      </c>
+      <c r="Q329" s="2">
+        <f t="shared" si="64"/>
+        <v>-79.900000000000006</v>
+      </c>
+      <c r="R329" s="16" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="330" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A330" s="1">
+        <v>329</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E330" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="F330" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="G330" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="H330" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I330" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="J330" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>21</v>
+      </c>
+      <c r="K330" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>34</v>
+      </c>
+      <c r="L330" s="1" t="e">
+        <f t="shared" si="58"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M330" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>83</v>
+      </c>
+      <c r="N330" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>31</v>
+      </c>
+      <c r="O330" s="1" t="e">
+        <f t="shared" si="61"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P330" s="2" t="e">
+        <f t="shared" si="62"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q330" s="2" t="e">
+        <f t="shared" si="64"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R330" s="16" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="331" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A331" s="1">
+        <v>330</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E331" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="F331" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="G331" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="H331" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I331" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="J331" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K331" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>41</v>
+      </c>
+      <c r="L331" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>54</v>
+      </c>
+      <c r="M331" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N331" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>27</v>
+      </c>
+      <c r="O331" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>43</v>
+      </c>
+      <c r="P331" s="2">
+        <f t="shared" si="62"/>
+        <v>19.698333333333334</v>
+      </c>
+      <c r="Q331" s="2">
+        <f t="shared" si="64"/>
+        <v>-87.461944444444441</v>
+      </c>
+      <c r="R331" s="16" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="332" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A332" s="1">
+        <v>331</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E332" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="F332" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="G332" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="H332" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I332" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="J332" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K332" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>43</v>
+      </c>
+      <c r="L332" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>35</v>
+      </c>
+      <c r="M332" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N332" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>25</v>
+      </c>
+      <c r="O332" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>06</v>
+      </c>
+      <c r="P332" s="2">
+        <f t="shared" si="62"/>
+        <v>19.726388888888888</v>
+      </c>
+      <c r="Q332" s="2">
+        <f t="shared" si="64"/>
+        <v>-87.418333333333337</v>
+      </c>
+      <c r="R332" s="16" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="333" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A333" s="1">
+        <v>332</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E333" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="F333" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G333" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="H333" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I333" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="J333" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K333" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>44</v>
+      </c>
+      <c r="L333" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>04</v>
+      </c>
+      <c r="M333" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N333" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>25</v>
+      </c>
+      <c r="O333" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>23</v>
+      </c>
+      <c r="P333" s="2">
+        <f t="shared" si="62"/>
+        <v>19.734444444444446</v>
+      </c>
+      <c r="Q333" s="2">
+        <f t="shared" si="64"/>
+        <v>-87.42305555555555</v>
+      </c>
+      <c r="R333" s="16" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="334" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A334" s="1">
+        <v>333</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E334" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="F334" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="G334" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="H334" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I334" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="J334" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K334" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>46</v>
+      </c>
+      <c r="L334" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>33</v>
+      </c>
+      <c r="M334" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N334" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>28</v>
+      </c>
+      <c r="O334" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>37</v>
+      </c>
+      <c r="P334" s="2">
+        <f t="shared" si="62"/>
+        <v>19.775833333333335</v>
+      </c>
+      <c r="Q334" s="2">
+        <f t="shared" si="64"/>
+        <v>-87.476944444444442</v>
+      </c>
+      <c r="R334" s="16" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="335" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A335" s="1">
+        <v>334</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E335" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="F335" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="G335" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="H335" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I335" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="J335" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K335" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>38</v>
+      </c>
+      <c r="L335" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>59</v>
+      </c>
+      <c r="M335" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N335" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>27</v>
+      </c>
+      <c r="O335" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>21</v>
+      </c>
+      <c r="P335" s="2">
+        <f t="shared" si="62"/>
+        <v>19.649722222222223</v>
+      </c>
+      <c r="Q335" s="2">
+        <f t="shared" si="64"/>
+        <v>-87.455833333333331</v>
+      </c>
+      <c r="R335" s="16" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="336" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P336" s="2"/>
-      <c r="Q336" s="2"/>
-    </row>
-    <row r="337" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P337" s="2"/>
-      <c r="Q337" s="2"/>
-    </row>
-    <row r="338" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P338" s="2"/>
-      <c r="Q338" s="2"/>
-    </row>
-    <row r="339" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P339" s="2"/>
-      <c r="Q339" s="2"/>
-    </row>
-    <row r="340" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P340" s="2"/>
-      <c r="Q340" s="2"/>
-    </row>
-    <row r="341" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P341" s="2"/>
-      <c r="Q341" s="2"/>
-    </row>
-    <row r="342" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P342" s="2"/>
-      <c r="Q342" s="2"/>
-    </row>
-    <row r="343" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P343" s="2"/>
-      <c r="Q343" s="2"/>
-    </row>
-    <row r="344" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P344" s="2"/>
-      <c r="Q344" s="2"/>
-    </row>
-    <row r="345" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P345" s="2"/>
-      <c r="Q345" s="2"/>
-    </row>
-    <row r="346" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P346" s="2"/>
-      <c r="Q346" s="2"/>
-    </row>
-    <row r="347" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P347" s="2"/>
-      <c r="Q347" s="2"/>
-    </row>
-    <row r="348" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P348" s="2"/>
-      <c r="Q348" s="2"/>
-    </row>
-    <row r="349" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P349" s="2"/>
-      <c r="Q349" s="2"/>
-    </row>
-    <row r="350" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P350" s="2"/>
-      <c r="Q350" s="2"/>
-    </row>
-    <row r="351" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P351" s="2"/>
-      <c r="Q351" s="2"/>
-    </row>
-    <row r="352" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P352" s="2"/>
-      <c r="Q352" s="2"/>
-    </row>
-    <row r="353" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P353" s="2"/>
-      <c r="Q353" s="2"/>
-    </row>
-    <row r="354" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P354" s="2"/>
-      <c r="Q354" s="2"/>
-    </row>
-    <row r="355" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P355" s="2"/>
-      <c r="Q355" s="2"/>
-    </row>
-    <row r="356" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P356" s="2"/>
-      <c r="Q356" s="2"/>
-    </row>
-    <row r="357" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P357" s="2"/>
-      <c r="Q357" s="2"/>
-    </row>
-    <row r="358" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P358" s="2"/>
-      <c r="Q358" s="2"/>
-    </row>
-    <row r="359" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P359" s="2"/>
-      <c r="Q359" s="2"/>
-    </row>
-    <row r="360" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P360" s="2"/>
-      <c r="Q360" s="2"/>
-    </row>
-    <row r="361" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P361" s="2"/>
-      <c r="Q361" s="2"/>
-    </row>
-    <row r="362" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P362" s="2"/>
-      <c r="Q362" s="2"/>
-    </row>
-    <row r="363" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P363" s="2"/>
-      <c r="Q363" s="2"/>
-    </row>
-    <row r="364" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P364" s="2"/>
-      <c r="Q364" s="2"/>
-    </row>
-    <row r="365" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P365" s="2"/>
-      <c r="Q365" s="2"/>
-    </row>
-    <row r="366" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P366" s="2"/>
-      <c r="Q366" s="2"/>
-    </row>
-    <row r="367" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P367" s="2"/>
-      <c r="Q367" s="2"/>
-    </row>
-    <row r="368" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P368" s="2"/>
-      <c r="Q368" s="2"/>
-    </row>
-    <row r="369" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="P369" s="2"/>
-      <c r="Q369" s="2"/>
-    </row>
-    <row r="370" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="P370" s="2"/>
-      <c r="Q370" s="2"/>
-    </row>
-    <row r="371" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="P371" s="2"/>
-      <c r="Q371" s="2"/>
-    </row>
-    <row r="372" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="P372" s="2"/>
-      <c r="Q372" s="2"/>
-    </row>
-    <row r="373" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="P373" s="2"/>
-      <c r="Q373" s="2"/>
-    </row>
-    <row r="374" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="P374" s="2"/>
-      <c r="Q374" s="2"/>
-    </row>
-    <row r="375" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="P375" s="2"/>
-      <c r="Q375" s="2"/>
-    </row>
-    <row r="376" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="P376" s="2"/>
-      <c r="Q376" s="2"/>
-    </row>
-    <row r="377" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="P377" s="2"/>
-      <c r="Q377" s="2"/>
-    </row>
-    <row r="378" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="P378" s="2"/>
-      <c r="Q378" s="2"/>
-    </row>
-    <row r="379" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="P379" s="2"/>
-      <c r="Q379" s="2"/>
-    </row>
-    <row r="380" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B380" s="7"/>
-      <c r="G380" s="7"/>
-      <c r="H380" s="7"/>
-      <c r="P380" s="2"/>
-      <c r="Q380" s="2"/>
-    </row>
-    <row r="381" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B381" s="18"/>
-      <c r="E381" s="18"/>
-      <c r="F381" s="18"/>
-      <c r="G381" s="7"/>
-      <c r="H381" s="7"/>
-      <c r="I381" s="10"/>
-      <c r="P381" s="2"/>
-      <c r="Q381" s="2"/>
-    </row>
-    <row r="382" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B382" s="18"/>
-      <c r="E382" s="18"/>
-      <c r="F382" s="18"/>
-      <c r="G382" s="7"/>
-      <c r="H382" s="7"/>
-      <c r="I382" s="10"/>
-      <c r="P382" s="2"/>
-      <c r="Q382" s="2"/>
-    </row>
-    <row r="383" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B383" s="18"/>
-      <c r="E383" s="18"/>
-      <c r="F383" s="18"/>
-      <c r="G383" s="7"/>
-      <c r="H383" s="7"/>
-      <c r="I383" s="10"/>
-      <c r="P383" s="2"/>
-      <c r="Q383" s="2"/>
-    </row>
-    <row r="384" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B384" s="18"/>
-      <c r="E384" s="18"/>
-      <c r="F384" s="18"/>
-      <c r="G384" s="7"/>
-      <c r="H384" s="7"/>
-      <c r="I384" s="10"/>
-      <c r="P384" s="2"/>
-      <c r="Q384" s="2"/>
-    </row>
-    <row r="385" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B385" s="18"/>
-      <c r="E385" s="18"/>
-      <c r="F385" s="18"/>
-      <c r="G385" s="7"/>
-      <c r="H385" s="7"/>
-      <c r="I385" s="10"/>
-      <c r="P385" s="2"/>
-      <c r="Q385" s="2"/>
-    </row>
-    <row r="386" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B386" s="18"/>
-      <c r="E386" s="18"/>
-      <c r="F386" s="18"/>
-      <c r="G386" s="7"/>
-      <c r="H386" s="7"/>
-      <c r="I386" s="10"/>
-      <c r="P386" s="2"/>
-      <c r="Q386" s="2"/>
-    </row>
-    <row r="387" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B387" s="18"/>
-      <c r="E387" s="10"/>
-      <c r="F387" s="10"/>
-      <c r="G387" s="7"/>
-      <c r="H387" s="7"/>
-      <c r="I387" s="10"/>
-      <c r="P387" s="2"/>
-      <c r="Q387" s="2"/>
-    </row>
-    <row r="388" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="A336" s="1">
+        <v>335</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E336" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="F336" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="G336" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="H336" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I336" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="J336" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K336" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>38</v>
+      </c>
+      <c r="L336" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>36</v>
+      </c>
+      <c r="M336" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N336" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>27</v>
+      </c>
+      <c r="O336" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>36</v>
+      </c>
+      <c r="P336" s="2">
+        <f t="shared" si="62"/>
+        <v>19.643333333333334</v>
+      </c>
+      <c r="Q336" s="2">
+        <f t="shared" ref="Q336:Q384" si="65">((((O336/60)+N336)/60)+M336)*IF(D337="W",-1, 1)</f>
+        <v>-87.46</v>
+      </c>
+      <c r="R336" s="16" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="337" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A337" s="1">
+        <v>336</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E337" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="F337" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="G337" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="H337" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I337" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="J337" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>09</v>
+      </c>
+      <c r="K337" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>44</v>
+      </c>
+      <c r="L337" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>15</v>
+      </c>
+      <c r="M337" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>82</v>
+      </c>
+      <c r="N337" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>49</v>
+      </c>
+      <c r="O337" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>28</v>
+      </c>
+      <c r="P337" s="2">
+        <f t="shared" si="62"/>
+        <v>9.7375000000000007</v>
+      </c>
+      <c r="Q337" s="2">
+        <f t="shared" si="65"/>
+        <v>-82.824444444444438</v>
+      </c>
+      <c r="R337" s="16" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="338" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A338" s="1">
+        <v>337</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E338" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="F338" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="G338" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="H338" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I338" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="J338" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>09</v>
+      </c>
+      <c r="K338" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>44</v>
+      </c>
+      <c r="L338" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>24</v>
+      </c>
+      <c r="M338" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>82</v>
+      </c>
+      <c r="N338" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>49</v>
+      </c>
+      <c r="O338" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>19</v>
+      </c>
+      <c r="P338" s="2">
+        <f t="shared" si="62"/>
+        <v>9.74</v>
+      </c>
+      <c r="Q338" s="2">
+        <f t="shared" si="65"/>
+        <v>-82.821944444444441</v>
+      </c>
+      <c r="R338" s="16" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="339" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A339" s="1">
+        <v>338</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E339" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="F339" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="G339" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="H339" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I339" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="J339" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>09</v>
+      </c>
+      <c r="K339" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>44</v>
+      </c>
+      <c r="L339" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>48</v>
+      </c>
+      <c r="M339" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>82</v>
+      </c>
+      <c r="N339" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>49</v>
+      </c>
+      <c r="O339" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>08</v>
+      </c>
+      <c r="P339" s="2">
+        <f t="shared" si="62"/>
+        <v>9.7466666666666661</v>
+      </c>
+      <c r="Q339" s="2">
+        <f t="shared" si="65"/>
+        <v>-82.818888888888893</v>
+      </c>
+      <c r="R339" s="16" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="340" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A340" s="1">
+        <v>339</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E340" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="F340" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="G340" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="H340" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I340" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="J340" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>09</v>
+      </c>
+      <c r="K340" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>44</v>
+      </c>
+      <c r="L340" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>36</v>
+      </c>
+      <c r="M340" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>82</v>
+      </c>
+      <c r="N340" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>48</v>
+      </c>
+      <c r="O340" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>23</v>
+      </c>
+      <c r="P340" s="2">
+        <f t="shared" si="62"/>
+        <v>9.7433333333333341</v>
+      </c>
+      <c r="Q340" s="2">
+        <f t="shared" si="65"/>
+        <v>-82.80638888888889</v>
+      </c>
+      <c r="R340" s="16" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="341" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A341" s="1">
+        <v>340</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E341" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="F341" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="G341" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="H341" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I341" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="J341" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>09</v>
+      </c>
+      <c r="K341" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>44</v>
+      </c>
+      <c r="L341" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>29</v>
+      </c>
+      <c r="M341" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>82</v>
+      </c>
+      <c r="N341" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>48</v>
+      </c>
+      <c r="O341" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>32</v>
+      </c>
+      <c r="P341" s="2">
+        <f t="shared" si="62"/>
+        <v>9.7413888888888884</v>
+      </c>
+      <c r="Q341" s="2">
+        <f t="shared" si="65"/>
+        <v>-82.808888888888887</v>
+      </c>
+      <c r="R341" s="16" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="342" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A342" s="1">
+        <v>341</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E342" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="F342" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="G342" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="H342" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I342" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="J342" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>09</v>
+      </c>
+      <c r="K342" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>44</v>
+      </c>
+      <c r="L342" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>16</v>
+      </c>
+      <c r="M342" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>82</v>
+      </c>
+      <c r="N342" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>48</v>
+      </c>
+      <c r="O342" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>30</v>
+      </c>
+      <c r="P342" s="2">
+        <f t="shared" si="62"/>
+        <v>9.7377777777777776</v>
+      </c>
+      <c r="Q342" s="2">
+        <f t="shared" si="65"/>
+        <v>-82.808333333333337</v>
+      </c>
+      <c r="R342" s="16" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="343" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A343" s="1">
+        <v>342</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E343" s="20" t="s">
+        <v>584</v>
+      </c>
+      <c r="F343" s="20" t="s">
+        <v>603</v>
+      </c>
+      <c r="G343" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H343" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I343" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J343" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K343" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>05</v>
+      </c>
+      <c r="L343" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>44</v>
+      </c>
+      <c r="M343" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N343" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>23</v>
+      </c>
+      <c r="O343" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>22</v>
+      </c>
+      <c r="P343" s="2">
+        <f t="shared" si="62"/>
+        <v>19.095555555555556</v>
+      </c>
+      <c r="Q343" s="2">
+        <f t="shared" si="65"/>
+        <v>-87.38944444444445</v>
+      </c>
+      <c r="R343" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="344" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A344" s="1">
+        <v>343</v>
+      </c>
+      <c r="B344" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D344" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E344" s="20" t="s">
+        <v>585</v>
+      </c>
+      <c r="F344" s="20" t="s">
+        <v>602</v>
+      </c>
+      <c r="G344" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H344" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I344" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J344" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K344" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>01</v>
+      </c>
+      <c r="L344" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>25</v>
+      </c>
+      <c r="M344" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N344" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>11</v>
+      </c>
+      <c r="O344" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>20</v>
+      </c>
+      <c r="P344" s="2">
+        <f t="shared" si="62"/>
+        <v>19.023611111111112</v>
+      </c>
+      <c r="Q344" s="2">
+        <f t="shared" si="65"/>
+        <v>-87.188888888888883</v>
+      </c>
+      <c r="R344" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="345" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A345" s="1">
+        <v>344</v>
+      </c>
+      <c r="B345" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E345" s="20" t="s">
+        <v>586</v>
+      </c>
+      <c r="F345" s="20" t="s">
+        <v>601</v>
+      </c>
+      <c r="G345" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H345" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I345" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J345" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>18</v>
+      </c>
+      <c r="K345" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>57</v>
+      </c>
+      <c r="L345" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>22</v>
+      </c>
+      <c r="M345" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N345" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>57</v>
+      </c>
+      <c r="O345" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>43</v>
+      </c>
+      <c r="P345" s="2">
+        <f t="shared" si="62"/>
+        <v>18.95611111111111</v>
+      </c>
+      <c r="Q345" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.961944444444441</v>
+      </c>
+      <c r="R345" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="346" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A346" s="1">
+        <v>345</v>
+      </c>
+      <c r="B346" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E346" s="20" t="s">
+        <v>587</v>
+      </c>
+      <c r="F346" s="20" t="s">
+        <v>600</v>
+      </c>
+      <c r="G346" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H346" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I346" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J346" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>18</v>
+      </c>
+      <c r="K346" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>51</v>
+      </c>
+      <c r="L346" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>45</v>
+      </c>
+      <c r="M346" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N346" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>42</v>
+      </c>
+      <c r="O346" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>33</v>
+      </c>
+      <c r="P346" s="2">
+        <f t="shared" si="62"/>
+        <v>18.862500000000001</v>
+      </c>
+      <c r="Q346" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.709166666666661</v>
+      </c>
+      <c r="R346" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="347" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A347" s="1">
+        <v>346</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E347" s="20" t="s">
+        <v>588</v>
+      </c>
+      <c r="F347" s="20" t="s">
+        <v>599</v>
+      </c>
+      <c r="G347" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H347" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I347" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J347" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K347" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>26</v>
+      </c>
+      <c r="L347" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>27</v>
+      </c>
+      <c r="M347" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N347" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>14</v>
+      </c>
+      <c r="O347" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>30</v>
+      </c>
+      <c r="P347" s="2">
+        <f t="shared" si="62"/>
+        <v>19.440833333333334</v>
+      </c>
+      <c r="Q347" s="2">
+        <f t="shared" si="65"/>
+        <v>-87.24166666666666</v>
+      </c>
+      <c r="R347" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="348" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A348" s="1">
+        <v>347</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D348" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E348" s="20" t="s">
+        <v>589</v>
+      </c>
+      <c r="F348" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="G348" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H348" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I348" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J348" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K348" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>24</v>
+      </c>
+      <c r="L348" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>32</v>
+      </c>
+      <c r="M348" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N348" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>02</v>
+      </c>
+      <c r="O348" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>45</v>
+      </c>
+      <c r="P348" s="2">
+        <f t="shared" si="62"/>
+        <v>19.408888888888889</v>
+      </c>
+      <c r="Q348" s="2">
+        <f t="shared" si="65"/>
+        <v>-87.045833333333334</v>
+      </c>
+      <c r="R348" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="349" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A349" s="1">
+        <v>348</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C349" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D349" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E349" s="20" t="s">
+        <v>590</v>
+      </c>
+      <c r="F349" s="20" t="s">
+        <v>597</v>
+      </c>
+      <c r="G349" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H349" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I349" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J349" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K349" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>22</v>
+      </c>
+      <c r="L349" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>01</v>
+      </c>
+      <c r="M349" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N349" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>51</v>
+      </c>
+      <c r="O349" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>20</v>
+      </c>
+      <c r="P349" s="2">
+        <f t="shared" si="62"/>
+        <v>19.366944444444446</v>
+      </c>
+      <c r="Q349" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.855555555555554</v>
+      </c>
+      <c r="R349" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="350" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A350" s="1">
+        <v>349</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D350" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E350" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="F350" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="G350" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H350" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I350" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J350" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K350" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>18</v>
+      </c>
+      <c r="L350" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>32</v>
+      </c>
+      <c r="M350" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N350" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>37</v>
+      </c>
+      <c r="O350" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>24</v>
+      </c>
+      <c r="P350" s="2">
+        <f t="shared" si="62"/>
+        <v>19.308888888888887</v>
+      </c>
+      <c r="Q350" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.623333333333335</v>
+      </c>
+      <c r="R350" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="351" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A351" s="1">
+        <v>350</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D351" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E351" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="F351" s="20" t="s">
+        <v>595</v>
+      </c>
+      <c r="G351" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H351" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I351" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J351" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K351" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>14</v>
+      </c>
+      <c r="L351" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>28</v>
+      </c>
+      <c r="M351" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N351" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>25</v>
+      </c>
+      <c r="O351" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>23</v>
+      </c>
+      <c r="P351" s="2">
+        <f t="shared" si="62"/>
+        <v>19.24111111111111</v>
+      </c>
+      <c r="Q351" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.42305555555555</v>
+      </c>
+      <c r="R351" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="352" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A352" s="1">
+        <v>351</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E352" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F352" s="20" t="s">
+        <v>594</v>
+      </c>
+      <c r="G352" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H352" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I352" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J352" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K352" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>11</v>
+      </c>
+      <c r="L352" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>54</v>
+      </c>
+      <c r="M352" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N352" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>15</v>
+      </c>
+      <c r="O352" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>33</v>
+      </c>
+      <c r="P352" s="2">
+        <f t="shared" si="62"/>
+        <v>19.198333333333334</v>
+      </c>
+      <c r="Q352" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.259166666666673</v>
+      </c>
+      <c r="R352" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="353" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A353" s="1">
+        <v>352</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E353" s="20" t="s">
+        <v>605</v>
+      </c>
+      <c r="F353" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="G353" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H353" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I353" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J353" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K353" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>49</v>
+      </c>
+      <c r="L353" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>18</v>
+      </c>
+      <c r="M353" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N353" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>24</v>
+      </c>
+      <c r="O353" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>21</v>
+      </c>
+      <c r="P353" s="2">
+        <f t="shared" si="62"/>
+        <v>19.821666666666665</v>
+      </c>
+      <c r="Q353" s="2">
+        <f t="shared" si="65"/>
+        <v>-87.405833333333334</v>
+      </c>
+      <c r="R353" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="354" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A354" s="1">
+        <v>353</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E354" s="20" t="s">
+        <v>606</v>
+      </c>
+      <c r="F354" s="20" t="s">
+        <v>630</v>
+      </c>
+      <c r="G354" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H354" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I354" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J354" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K354" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>45</v>
+      </c>
+      <c r="L354" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>51</v>
+      </c>
+      <c r="M354" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N354" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>12</v>
+      </c>
+      <c r="O354" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>24</v>
+      </c>
+      <c r="P354" s="2">
+        <f t="shared" si="62"/>
+        <v>19.764166666666668</v>
+      </c>
+      <c r="Q354" s="2">
+        <f t="shared" si="65"/>
+        <v>-87.206666666666663</v>
+      </c>
+      <c r="R354" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="355" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A355" s="1">
+        <v>354</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E355" s="20" t="s">
+        <v>668</v>
+      </c>
+      <c r="F355" s="20" t="s">
+        <v>629</v>
+      </c>
+      <c r="G355" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H355" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I355" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J355" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K355" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>48</v>
+      </c>
+      <c r="L355" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>21</v>
+      </c>
+      <c r="M355" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N355" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>59</v>
+      </c>
+      <c r="O355" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>06</v>
+      </c>
+      <c r="P355" s="2">
+        <f t="shared" si="62"/>
+        <v>19.805833333333332</v>
+      </c>
+      <c r="Q355" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.984999999999999</v>
+      </c>
+      <c r="R355" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="356" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A356" s="1">
+        <v>355</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E356" s="20" t="s">
+        <v>607</v>
+      </c>
+      <c r="F356" s="20" t="s">
+        <v>628</v>
+      </c>
+      <c r="G356" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H356" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I356" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J356" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K356" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>59</v>
+      </c>
+      <c r="L356" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>09</v>
+      </c>
+      <c r="M356" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N356" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>26</v>
+      </c>
+      <c r="O356" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>19</v>
+      </c>
+      <c r="P356" s="2">
+        <f t="shared" si="62"/>
+        <v>19.985833333333332</v>
+      </c>
+      <c r="Q356" s="2">
+        <f t="shared" si="65"/>
+        <v>-87.438611111111115</v>
+      </c>
+      <c r="R356" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="357" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A357" s="1">
+        <v>356</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C357" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E357" s="20" t="s">
+        <v>608</v>
+      </c>
+      <c r="F357" s="20" t="s">
+        <v>627</v>
+      </c>
+      <c r="G357" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H357" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I357" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J357" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K357" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>00</v>
+      </c>
+      <c r="L357" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>22</v>
+      </c>
+      <c r="M357" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N357" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>13</v>
+      </c>
+      <c r="O357" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>16</v>
+      </c>
+      <c r="P357" s="2">
+        <f t="shared" si="62"/>
+        <v>20.00611111111111</v>
+      </c>
+      <c r="Q357" s="2">
+        <f t="shared" si="65"/>
+        <v>-87.221111111111114</v>
+      </c>
+      <c r="R357" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="358" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A358" s="1">
+        <v>357</v>
+      </c>
+      <c r="B358" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E358" s="20" t="s">
+        <v>609</v>
+      </c>
+      <c r="F358" s="20" t="s">
+        <v>626</v>
+      </c>
+      <c r="G358" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H358" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I358" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J358" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>19</v>
+      </c>
+      <c r="K358" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>58</v>
+      </c>
+      <c r="L358" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>01</v>
+      </c>
+      <c r="M358" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N358" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>07</v>
+      </c>
+      <c r="O358" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>18</v>
+      </c>
+      <c r="P358" s="2">
+        <f t="shared" si="62"/>
+        <v>19.966944444444444</v>
+      </c>
+      <c r="Q358" s="2">
+        <f t="shared" si="65"/>
+        <v>-87.12166666666667</v>
+      </c>
+      <c r="R358" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="359" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A359" s="1">
+        <v>358</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E359" s="20" t="s">
+        <v>610</v>
+      </c>
+      <c r="F359" s="20" t="s">
+        <v>625</v>
+      </c>
+      <c r="G359" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H359" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I359" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J359" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K359" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>00</v>
+      </c>
+      <c r="L359" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>33</v>
+      </c>
+      <c r="M359" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N359" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>58</v>
+      </c>
+      <c r="O359" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>42</v>
+      </c>
+      <c r="P359" s="2">
+        <f t="shared" si="62"/>
+        <v>20.009166666666665</v>
+      </c>
+      <c r="Q359" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.978333333333339</v>
+      </c>
+      <c r="R359" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="360" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A360" s="1">
+        <v>359</v>
+      </c>
+      <c r="B360" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C360" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D360" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E360" s="20" t="s">
+        <v>611</v>
+      </c>
+      <c r="F360" s="20" t="s">
+        <v>624</v>
+      </c>
+      <c r="G360" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H360" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I360" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J360" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K360" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>02</v>
+      </c>
+      <c r="L360" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>16</v>
+      </c>
+      <c r="M360" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N360" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>41</v>
+      </c>
+      <c r="O360" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>19</v>
+      </c>
+      <c r="P360" s="2">
+        <f t="shared" si="62"/>
+        <v>20.037777777777777</v>
+      </c>
+      <c r="Q360" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.688611111111115</v>
+      </c>
+      <c r="R360" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="361" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A361" s="1">
+        <v>360</v>
+      </c>
+      <c r="B361" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C361" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D361" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E361" s="20" t="s">
+        <v>612</v>
+      </c>
+      <c r="F361" s="20" t="s">
+        <v>623</v>
+      </c>
+      <c r="G361" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H361" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I361" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J361" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K361" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>01</v>
+      </c>
+      <c r="L361" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>15</v>
+      </c>
+      <c r="M361" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N361" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>30</v>
+      </c>
+      <c r="O361" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>41</v>
+      </c>
+      <c r="P361" s="2">
+        <f t="shared" si="62"/>
+        <v>20.020833333333332</v>
+      </c>
+      <c r="Q361" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.511388888888888</v>
+      </c>
+      <c r="R361" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="362" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A362" s="1">
+        <v>361</v>
+      </c>
+      <c r="B362" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C362" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E362" s="20" t="s">
+        <v>613</v>
+      </c>
+      <c r="F362" s="20" t="s">
+        <v>622</v>
+      </c>
+      <c r="G362" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H362" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I362" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J362" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K362" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>14</v>
+      </c>
+      <c r="L362" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>26</v>
+      </c>
+      <c r="M362" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N362" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>16</v>
+      </c>
+      <c r="O362" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>43</v>
+      </c>
+      <c r="P362" s="2">
+        <f t="shared" si="62"/>
+        <v>20.240555555555556</v>
+      </c>
+      <c r="Q362" s="2">
+        <f t="shared" si="65"/>
+        <v>-87.278611111111104</v>
+      </c>
+      <c r="R362" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="363" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A363" s="1">
+        <v>362</v>
+      </c>
+      <c r="B363" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C363" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E363" s="20" t="s">
+        <v>614</v>
+      </c>
+      <c r="F363" s="20" t="s">
+        <v>621</v>
+      </c>
+      <c r="G363" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H363" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I363" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J363" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K363" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>13</v>
+      </c>
+      <c r="L363" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>06</v>
+      </c>
+      <c r="M363" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>87</v>
+      </c>
+      <c r="N363" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>08</v>
+      </c>
+      <c r="O363" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>06</v>
+      </c>
+      <c r="P363" s="2">
+        <f t="shared" si="62"/>
+        <v>20.218333333333334</v>
+      </c>
+      <c r="Q363" s="2">
+        <f t="shared" si="65"/>
+        <v>-87.135000000000005</v>
+      </c>
+      <c r="R363" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="364" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A364" s="1">
+        <v>363</v>
+      </c>
+      <c r="B364" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E364" s="20" t="s">
+        <v>615</v>
+      </c>
+      <c r="F364" s="20" t="s">
+        <v>620</v>
+      </c>
+      <c r="G364" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H364" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I364" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J364" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K364" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>08</v>
+      </c>
+      <c r="L364" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>38</v>
+      </c>
+      <c r="M364" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N364" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>59</v>
+      </c>
+      <c r="O364" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>43</v>
+      </c>
+      <c r="P364" s="2">
+        <f t="shared" si="62"/>
+        <v>20.143888888888888</v>
+      </c>
+      <c r="Q364" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.995277777777773</v>
+      </c>
+      <c r="R364" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="365" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A365" s="1">
+        <v>364</v>
+      </c>
+      <c r="B365" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C365" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D365" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E365" s="20" t="s">
+        <v>616</v>
+      </c>
+      <c r="F365" s="20" t="s">
+        <v>619</v>
+      </c>
+      <c r="G365" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H365" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I365" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J365" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K365" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>12</v>
+      </c>
+      <c r="L365" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>54</v>
+      </c>
+      <c r="M365" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N365" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>50</v>
+      </c>
+      <c r="O365" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>07</v>
+      </c>
+      <c r="P365" s="2">
+        <f t="shared" si="62"/>
+        <v>20.215</v>
+      </c>
+      <c r="Q365" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.835277777777776</v>
+      </c>
+      <c r="R365" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="366" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A366" s="1">
+        <v>365</v>
+      </c>
+      <c r="B366" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E366" s="20" t="s">
+        <v>617</v>
+      </c>
+      <c r="F366" s="20" t="s">
+        <v>618</v>
+      </c>
+      <c r="G366" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H366" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I366" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J366" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K366" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>13</v>
+      </c>
+      <c r="L366" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>16</v>
+      </c>
+      <c r="M366" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N366" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>37</v>
+      </c>
+      <c r="O366" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>47</v>
+      </c>
+      <c r="P366" s="2">
+        <f t="shared" si="62"/>
+        <v>20.22111111111111</v>
+      </c>
+      <c r="Q366" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.629722222222227</v>
+      </c>
+      <c r="R366" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="367" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A367" s="1">
+        <v>366</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E367" s="20" t="s">
+        <v>632</v>
+      </c>
+      <c r="F367" s="20" t="s">
+        <v>667</v>
+      </c>
+      <c r="G367" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H367" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I367" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J367" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K367" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>41</v>
+      </c>
+      <c r="L367" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>46</v>
+      </c>
+      <c r="M367" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N367" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>52</v>
+      </c>
+      <c r="O367" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>49</v>
+      </c>
+      <c r="P367" s="2">
+        <f t="shared" si="62"/>
+        <v>20.696111111111112</v>
+      </c>
+      <c r="Q367" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.880277777777778</v>
+      </c>
+      <c r="R367" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="368" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A368" s="1">
+        <v>367</v>
+      </c>
+      <c r="B368" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E368" s="20" t="s">
+        <v>633</v>
+      </c>
+      <c r="F368" s="20" t="s">
+        <v>666</v>
+      </c>
+      <c r="G368" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H368" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I368" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J368" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K368" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>32</v>
+      </c>
+      <c r="L368" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>40</v>
+      </c>
+      <c r="M368" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N368" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>29</v>
+      </c>
+      <c r="O368" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>49</v>
+      </c>
+      <c r="P368" s="2">
+        <f t="shared" si="62"/>
+        <v>20.544444444444444</v>
+      </c>
+      <c r="Q368" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.496944444444438</v>
+      </c>
+      <c r="R368" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="369" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A369" s="1">
+        <v>368</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E369" s="20" t="s">
+        <v>634</v>
+      </c>
+      <c r="F369" s="20" t="s">
+        <v>665</v>
+      </c>
+      <c r="G369" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H369" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I369" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J369" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K369" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>30</v>
+      </c>
+      <c r="L369" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>05</v>
+      </c>
+      <c r="M369" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N369" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>20</v>
+      </c>
+      <c r="O369" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>32</v>
+      </c>
+      <c r="P369" s="2">
+        <f t="shared" si="62"/>
+        <v>20.50138888888889</v>
+      </c>
+      <c r="Q369" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.342222222222219</v>
+      </c>
+      <c r="R369" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="370" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A370" s="1">
+        <v>369</v>
+      </c>
+      <c r="B370" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D370" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E370" s="20" t="s">
+        <v>635</v>
+      </c>
+      <c r="F370" s="20" t="s">
+        <v>664</v>
+      </c>
+      <c r="G370" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H370" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I370" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J370" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K370" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>31</v>
+      </c>
+      <c r="L370" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>51</v>
+      </c>
+      <c r="M370" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>85</v>
+      </c>
+      <c r="N370" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>59</v>
+      </c>
+      <c r="O370" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>29</v>
+      </c>
+      <c r="P370" s="2">
+        <f t="shared" si="62"/>
+        <v>20.530833333333334</v>
+      </c>
+      <c r="Q370" s="2">
+        <f t="shared" si="65"/>
+        <v>-85.991388888888892</v>
+      </c>
+      <c r="R370" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="371" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A371" s="1">
+        <v>370</v>
+      </c>
+      <c r="B371" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D371" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E371" s="20" t="s">
+        <v>636</v>
+      </c>
+      <c r="F371" s="20" t="s">
+        <v>663</v>
+      </c>
+      <c r="G371" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H371" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I371" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J371" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K371" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>47</v>
+      </c>
+      <c r="L371" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>18</v>
+      </c>
+      <c r="M371" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N371" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>45</v>
+      </c>
+      <c r="O371" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>57</v>
+      </c>
+      <c r="P371" s="2">
+        <f t="shared" si="62"/>
+        <v>20.788333333333334</v>
+      </c>
+      <c r="Q371" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.765833333333333</v>
+      </c>
+      <c r="R371" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="372" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A372" s="1">
+        <v>371</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D372" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E372" s="20" t="s">
+        <v>637</v>
+      </c>
+      <c r="F372" s="20" t="s">
+        <v>662</v>
+      </c>
+      <c r="G372" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H372" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I372" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J372" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>21</v>
+      </c>
+      <c r="K372" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>02</v>
+      </c>
+      <c r="L372" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>26</v>
+      </c>
+      <c r="M372" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N372" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>29</v>
+      </c>
+      <c r="O372" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>47</v>
+      </c>
+      <c r="P372" s="2">
+        <f t="shared" si="62"/>
+        <v>21.040555555555557</v>
+      </c>
+      <c r="Q372" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.496388888888887</v>
+      </c>
+      <c r="R372" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="373" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A373" s="1">
+        <v>372</v>
+      </c>
+      <c r="B373" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D373" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E373" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="F373" s="20" t="s">
+        <v>661</v>
+      </c>
+      <c r="G373" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H373" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I373" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J373" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K373" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>57</v>
+      </c>
+      <c r="L373" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>52</v>
+      </c>
+      <c r="M373" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N373" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>19</v>
+      </c>
+      <c r="O373" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>30</v>
+      </c>
+      <c r="P373" s="2">
+        <f t="shared" si="62"/>
+        <v>20.964444444444446</v>
+      </c>
+      <c r="Q373" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.325000000000003</v>
+      </c>
+      <c r="R373" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="374" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A374" s="1">
+        <v>373</v>
+      </c>
+      <c r="B374" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D374" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E374" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="F374" s="20" t="s">
+        <v>660</v>
+      </c>
+      <c r="G374" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H374" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I374" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J374" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K374" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>52</v>
+      </c>
+      <c r="L374" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>54</v>
+      </c>
+      <c r="M374" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N374" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>08</v>
+      </c>
+      <c r="O374" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>30</v>
+      </c>
+      <c r="P374" s="2">
+        <f t="shared" si="62"/>
+        <v>20.881666666666668</v>
+      </c>
+      <c r="Q374" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.141666666666666</v>
+      </c>
+      <c r="R374" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="375" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A375" s="1">
+        <v>374</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D375" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E375" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="F375" s="20" t="s">
+        <v>659</v>
+      </c>
+      <c r="G375" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H375" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I375" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J375" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K375" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>50</v>
+      </c>
+      <c r="L375" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>55</v>
+      </c>
+      <c r="M375" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>85</v>
+      </c>
+      <c r="N375" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>53</v>
+      </c>
+      <c r="O375" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>52</v>
+      </c>
+      <c r="P375" s="2">
+        <f t="shared" si="62"/>
+        <v>20.848611111111111</v>
+      </c>
+      <c r="Q375" s="2">
+        <f t="shared" si="65"/>
+        <v>-85.897777777777776</v>
+      </c>
+      <c r="R375" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="376" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A376" s="1">
+        <v>375</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D376" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E376" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="F376" s="20" t="s">
+        <v>658</v>
+      </c>
+      <c r="G376" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H376" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I376" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J376" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>20</v>
+      </c>
+      <c r="K376" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>47</v>
+      </c>
+      <c r="L376" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>16</v>
+      </c>
+      <c r="M376" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>85</v>
+      </c>
+      <c r="N376" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>46</v>
+      </c>
+      <c r="O376" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>28</v>
+      </c>
+      <c r="P376" s="2">
+        <f t="shared" si="62"/>
+        <v>20.787777777777777</v>
+      </c>
+      <c r="Q376" s="2">
+        <f t="shared" si="65"/>
+        <v>-85.774444444444441</v>
+      </c>
+      <c r="R376" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="377" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A377" s="1">
+        <v>376</v>
+      </c>
+      <c r="B377" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D377" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E377" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="F377" s="20" t="s">
+        <v>657</v>
+      </c>
+      <c r="G377" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H377" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I377" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J377" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>21</v>
+      </c>
+      <c r="K377" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>15</v>
+      </c>
+      <c r="L377" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>14</v>
+      </c>
+      <c r="M377" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N377" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>29</v>
+      </c>
+      <c r="O377" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>13</v>
+      </c>
+      <c r="P377" s="2">
+        <f t="shared" si="62"/>
+        <v>21.253888888888888</v>
+      </c>
+      <c r="Q377" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.486944444444447</v>
+      </c>
+      <c r="R377" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="378" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A378" s="1">
+        <v>377</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E378" s="20" t="s">
+        <v>643</v>
+      </c>
+      <c r="F378" s="20" t="s">
+        <v>656</v>
+      </c>
+      <c r="G378" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H378" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I378" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J378" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>21</v>
+      </c>
+      <c r="K378" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>12</v>
+      </c>
+      <c r="L378" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>57</v>
+      </c>
+      <c r="M378" s="1" t="str">
+        <f t="shared" si="59"/>
+        <v>86</v>
+      </c>
+      <c r="N378" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>16</v>
+      </c>
+      <c r="O378" s="1" t="str">
+        <f t="shared" si="61"/>
+        <v>38</v>
+      </c>
+      <c r="P378" s="2">
+        <f t="shared" si="62"/>
+        <v>21.215833333333332</v>
+      </c>
+      <c r="Q378" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.277222222222221</v>
+      </c>
+      <c r="R378" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="379" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A379" s="1">
+        <v>378</v>
+      </c>
+      <c r="B379" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C379" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D379" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E379" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="F379" s="20" t="s">
+        <v>655</v>
+      </c>
+      <c r="G379" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H379" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I379" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J379" s="1" t="str">
+        <f t="shared" ref="J379:J387" si="66">MID(E379,1,FIND("°",E379,1)-1)</f>
+        <v>21</v>
+      </c>
+      <c r="K379" s="1" t="str">
+        <f t="shared" ref="K379:K387" si="67">MID(E379,FIND("°",E379,1)+1,(FIND("′",E379,1)-FIND("°",E379,1))-1)</f>
+        <v>09</v>
+      </c>
+      <c r="L379" s="1" t="str">
+        <f t="shared" ref="L379:L387" si="68">MID(E379,FIND("′",E379,1)+1,(FIND("″",E379,1)-FIND("′",E379,1))-1)</f>
+        <v>28</v>
+      </c>
+      <c r="M379" s="1" t="str">
+        <f t="shared" ref="M379:M387" si="69">MID(F379,1,FIND("°",F379,1)-1)</f>
+        <v>86</v>
+      </c>
+      <c r="N379" s="1" t="str">
+        <f t="shared" ref="N379:N387" si="70">MID(F379,FIND("°",F379,1)+1,(FIND("′",F379,1)-FIND("°",F379,1))-1)</f>
+        <v>06</v>
+      </c>
+      <c r="O379" s="1" t="str">
+        <f t="shared" ref="O379:O387" si="71">MID(F379,FIND("′",F379,1)+1,(FIND("″",F379,1)-FIND("′",F379,1))-1)</f>
+        <v>54</v>
+      </c>
+      <c r="P379" s="2">
+        <f t="shared" ref="P379:P387" si="72">((((L379/60)+K379)/60)+J379)*IF(C379="S",-1, 1)</f>
+        <v>21.157777777777778</v>
+      </c>
+      <c r="Q379" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.114999999999995</v>
+      </c>
+      <c r="R379" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="380" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A380" s="1">
+        <v>379</v>
+      </c>
+      <c r="B380" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C380" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D380" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E380" s="20" t="s">
+        <v>645</v>
+      </c>
+      <c r="F380" s="20" t="s">
+        <v>654</v>
+      </c>
+      <c r="G380" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H380" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I380" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J380" s="1" t="str">
+        <f t="shared" si="66"/>
+        <v>21</v>
+      </c>
+      <c r="K380" s="1" t="str">
+        <f t="shared" si="67"/>
+        <v>05</v>
+      </c>
+      <c r="L380" s="1" t="str">
+        <f t="shared" si="68"/>
+        <v>58</v>
+      </c>
+      <c r="M380" s="1" t="str">
+        <f t="shared" si="69"/>
+        <v>85</v>
+      </c>
+      <c r="N380" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>45</v>
+      </c>
+      <c r="O380" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>38</v>
+      </c>
+      <c r="P380" s="2">
+        <f t="shared" si="72"/>
+        <v>21.099444444444444</v>
+      </c>
+      <c r="Q380" s="2">
+        <f t="shared" si="65"/>
+        <v>-85.760555555555555</v>
+      </c>
+      <c r="R380" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="381" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A381" s="1">
+        <v>380</v>
+      </c>
+      <c r="B381" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C381" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D381" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E381" s="20" t="s">
+        <v>646</v>
+      </c>
+      <c r="F381" s="20" t="s">
+        <v>653</v>
+      </c>
+      <c r="G381" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H381" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I381" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J381" s="1" t="str">
+        <f t="shared" si="66"/>
+        <v>21</v>
+      </c>
+      <c r="K381" s="1" t="str">
+        <f t="shared" si="67"/>
+        <v>36</v>
+      </c>
+      <c r="L381" s="1" t="str">
+        <f t="shared" si="68"/>
+        <v>50</v>
+      </c>
+      <c r="M381" s="1" t="str">
+        <f t="shared" si="69"/>
+        <v>86</v>
+      </c>
+      <c r="N381" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>17</v>
+      </c>
+      <c r="O381" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>07</v>
+      </c>
+      <c r="P381" s="2">
+        <f t="shared" si="72"/>
+        <v>21.613888888888887</v>
+      </c>
+      <c r="Q381" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.285277777777779</v>
+      </c>
+      <c r="R381" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="382" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A382" s="1">
+        <v>381</v>
+      </c>
+      <c r="B382" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C382" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D382" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E382" s="20" t="s">
+        <v>647</v>
+      </c>
+      <c r="F382" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G382" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H382" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I382" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J382" s="1" t="str">
+        <f t="shared" si="66"/>
+        <v>21</v>
+      </c>
+      <c r="K382" s="1" t="str">
+        <f t="shared" si="67"/>
+        <v>35</v>
+      </c>
+      <c r="L382" s="1" t="str">
+        <f t="shared" si="68"/>
+        <v>49</v>
+      </c>
+      <c r="M382" s="1" t="str">
+        <f t="shared" si="69"/>
+        <v>86</v>
+      </c>
+      <c r="N382" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>07</v>
+      </c>
+      <c r="O382" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>40</v>
+      </c>
+      <c r="P382" s="2">
+        <f t="shared" si="72"/>
+        <v>21.596944444444446</v>
+      </c>
+      <c r="Q382" s="2">
+        <f t="shared" si="65"/>
+        <v>-86.12777777777778</v>
+      </c>
+      <c r="R382" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="383" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A383" s="1">
+        <v>382</v>
+      </c>
+      <c r="B383" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C383" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D383" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E383" s="20" t="s">
+        <v>648</v>
+      </c>
+      <c r="F383" s="20" t="s">
+        <v>651</v>
+      </c>
+      <c r="G383" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H383" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I383" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J383" s="1" t="str">
+        <f t="shared" si="66"/>
+        <v>21</v>
+      </c>
+      <c r="K383" s="1" t="str">
+        <f t="shared" si="67"/>
+        <v>34</v>
+      </c>
+      <c r="L383" s="1" t="str">
+        <f t="shared" si="68"/>
+        <v>51</v>
+      </c>
+      <c r="M383" s="1" t="str">
+        <f t="shared" si="69"/>
+        <v>85</v>
+      </c>
+      <c r="N383" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>59</v>
+      </c>
+      <c r="O383" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>26</v>
+      </c>
+      <c r="P383" s="2">
+        <f t="shared" si="72"/>
+        <v>21.580833333333334</v>
+      </c>
+      <c r="Q383" s="2">
+        <f t="shared" si="65"/>
+        <v>-85.990555555555559</v>
+      </c>
+      <c r="R383" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="384" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A384" s="1">
+        <v>383</v>
+      </c>
+      <c r="B384" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C384" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D384" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E384" s="20" t="s">
+        <v>649</v>
+      </c>
+      <c r="F384" s="20" t="s">
+        <v>650</v>
+      </c>
+      <c r="G384" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="H384" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I384" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J384" s="1" t="str">
+        <f t="shared" si="66"/>
+        <v>21</v>
+      </c>
+      <c r="K384" s="1" t="str">
+        <f t="shared" si="67"/>
+        <v>29</v>
+      </c>
+      <c r="L384" s="1" t="str">
+        <f t="shared" si="68"/>
+        <v>14</v>
+      </c>
+      <c r="M384" s="1" t="str">
+        <f t="shared" si="69"/>
+        <v>85</v>
+      </c>
+      <c r="N384" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>31</v>
+      </c>
+      <c r="O384" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>58</v>
+      </c>
+      <c r="P384" s="2">
+        <f t="shared" si="72"/>
+        <v>21.487222222222222</v>
+      </c>
+      <c r="Q384" s="2">
+        <f t="shared" si="65"/>
+        <v>-85.532777777777781</v>
+      </c>
+      <c r="R384" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="385" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A385" s="1">
+        <v>384</v>
+      </c>
+      <c r="B385" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C385" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D385" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E385" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="F385" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G385" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="H385" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I385" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="J385" s="1" t="str">
+        <f t="shared" si="66"/>
+        <v>20</v>
+      </c>
+      <c r="K385" s="1" t="str">
+        <f t="shared" si="67"/>
+        <v>51</v>
+      </c>
+      <c r="L385" s="1" t="str">
+        <f t="shared" si="68"/>
+        <v>00</v>
+      </c>
+      <c r="M385" s="1" t="str">
+        <f t="shared" si="69"/>
+        <v>86</v>
+      </c>
+      <c r="N385" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>55</v>
+      </c>
+      <c r="O385" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>00</v>
+      </c>
+      <c r="P385" s="2">
+        <f t="shared" si="72"/>
+        <v>20.85</v>
+      </c>
+      <c r="Q385" s="2">
+        <f t="shared" ref="Q385:Q387" si="73">((((O385/60)+N385)/60)+M385)*IF(D385="W",-1, 1)</f>
+        <v>-86.916666666666671</v>
+      </c>
+      <c r="R385" s="16" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="386" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A386" s="1">
+        <v>385</v>
+      </c>
+      <c r="B386" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D386" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E386" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="F386" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G386" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="H386" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I386" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="J386" s="1" t="str">
+        <f t="shared" si="66"/>
+        <v>20</v>
+      </c>
+      <c r="K386" s="1" t="str">
+        <f t="shared" si="67"/>
+        <v>51</v>
+      </c>
+      <c r="L386" s="1" t="str">
+        <f t="shared" si="68"/>
+        <v>00</v>
+      </c>
+      <c r="M386" s="1" t="str">
+        <f t="shared" si="69"/>
+        <v>86</v>
+      </c>
+      <c r="N386" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>55</v>
+      </c>
+      <c r="O386" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>00</v>
+      </c>
+      <c r="P386" s="2">
+        <f t="shared" si="72"/>
+        <v>20.85</v>
+      </c>
+      <c r="Q386" s="2">
+        <f t="shared" si="73"/>
+        <v>-86.916666666666671</v>
+      </c>
+      <c r="R386" s="16" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="387" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A387" s="1">
+        <v>386</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D387" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E387" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F387" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G387" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="H387" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I387" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="J387" s="1" t="str">
+        <f t="shared" si="66"/>
+        <v>8</v>
+      </c>
+      <c r="K387" s="1" t="str">
+        <f t="shared" si="67"/>
+        <v>45</v>
+      </c>
+      <c r="L387" s="1" t="e">
+        <f t="shared" si="68"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M387" s="1" t="str">
+        <f t="shared" si="69"/>
+        <v>34</v>
+      </c>
+      <c r="N387" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>57</v>
+      </c>
+      <c r="O387" s="1" t="e">
+        <f t="shared" si="71"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P387" s="2" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q387" s="2" t="e">
+        <f t="shared" si="73"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R387" s="16" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="388" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B388" s="18"/>
       <c r="E388" s="10"/>
       <c r="F388" s="10"/>
@@ -23771,7 +27568,7 @@
       <c r="P388" s="2"/>
       <c r="Q388" s="2"/>
     </row>
-    <row r="389" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B389" s="18"/>
       <c r="E389" s="10"/>
       <c r="F389" s="10"/>
@@ -23781,7 +27578,7 @@
       <c r="P389" s="2"/>
       <c r="Q389" s="2"/>
     </row>
-    <row r="390" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B390" s="18"/>
       <c r="E390" s="10"/>
       <c r="F390" s="10"/>
@@ -23791,7 +27588,7 @@
       <c r="P390" s="2"/>
       <c r="Q390" s="2"/>
     </row>
-    <row r="391" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B391" s="18"/>
       <c r="E391" s="10"/>
       <c r="F391" s="10"/>
@@ -23801,7 +27598,7 @@
       <c r="P391" s="2"/>
       <c r="Q391" s="2"/>
     </row>
-    <row r="392" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B392" s="18"/>
       <c r="E392" s="10"/>
       <c r="F392" s="10"/>
@@ -23811,7 +27608,7 @@
       <c r="P392" s="2"/>
       <c r="Q392" s="2"/>
     </row>
-    <row r="393" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B393" s="18"/>
       <c r="E393" s="10"/>
       <c r="F393" s="10"/>
@@ -23821,7 +27618,7 @@
       <c r="P393" s="2"/>
       <c r="Q393" s="2"/>
     </row>
-    <row r="394" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B394" s="18"/>
       <c r="E394" s="10"/>
       <c r="F394" s="10"/>
@@ -23831,7 +27628,7 @@
       <c r="P394" s="2"/>
       <c r="Q394" s="2"/>
     </row>
-    <row r="395" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B395" s="18"/>
       <c r="E395" s="10"/>
       <c r="F395" s="10"/>
@@ -23841,7 +27638,7 @@
       <c r="P395" s="2"/>
       <c r="Q395" s="2"/>
     </row>
-    <row r="396" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B396" s="18"/>
       <c r="E396" s="10"/>
       <c r="F396" s="10"/>
@@ -23851,7 +27648,7 @@
       <c r="P396" s="2"/>
       <c r="Q396" s="2"/>
     </row>
-    <row r="397" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B397" s="18"/>
       <c r="E397" s="10"/>
       <c r="F397" s="10"/>
@@ -23861,7 +27658,7 @@
       <c r="P397" s="2"/>
       <c r="Q397" s="2"/>
     </row>
-    <row r="398" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B398" s="18"/>
       <c r="E398" s="10"/>
       <c r="F398" s="10"/>
@@ -23871,7 +27668,7 @@
       <c r="P398" s="2"/>
       <c r="Q398" s="2"/>
     </row>
-    <row r="399" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B399" s="18"/>
       <c r="E399" s="10"/>
       <c r="F399" s="10"/>
@@ -23881,7 +27678,7 @@
       <c r="P399" s="2"/>
       <c r="Q399" s="2"/>
     </row>
-    <row r="400" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B400" s="18"/>
       <c r="E400" s="10"/>
       <c r="F400" s="10"/>
@@ -24214,7 +28011,7 @@
       <c r="Q440" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:I314" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R387" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/Ocorrências Literatura.xlsx
+++ b/Ocorrências Literatura.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cofres Obsidian\Mar Aberto\Laboratório\lagostas_carapaca\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8400B9A1-B38A-4811-9329-6CAD12FB2954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BBFB1C-2FAC-448A-BBB6-16F75D7B2968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="135" yWindow="7830" windowWidth="16140" windowHeight="7515" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ocorrências Panulirus" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ocorrências Panulirus'!$A$1:$R$454</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ocorrências Panulirus'!$A$1:$R$481</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4095" uniqueCount="877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4185" uniqueCount="909">
   <si>
     <t>ID</t>
   </si>
@@ -2832,6 +2832,102 @@
   </si>
   <si>
     <t xml:space="preserve">64°47′42″ </t>
+  </si>
+  <si>
+    <t>LOZANO-ÁLVAREZ, E. (2017)</t>
+  </si>
+  <si>
+    <t>20°50′01″</t>
+  </si>
+  <si>
+    <t>86°52′36″</t>
+  </si>
+  <si>
+    <t>ROBERTSON, D. N. (2009)</t>
+  </si>
+  <si>
+    <t>24°43′39″</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24°42′43″ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24°42′48″ </t>
+  </si>
+  <si>
+    <t>24°55′35″</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24°56′29″ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24°57′36″ </t>
+  </si>
+  <si>
+    <t>25°01′34″</t>
+  </si>
+  <si>
+    <t>25°02′37″</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25°07′00″ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">80°21′10″ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 80°22′49″ </t>
+  </si>
+  <si>
+    <t>80°24′42″</t>
+  </si>
+  <si>
+    <t>80°33′12″</t>
+  </si>
+  <si>
+    <t>80°33′40″</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 80°35′30″ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 80°59′34″</t>
+  </si>
+  <si>
+    <t>80°57′08″</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 80°56′20″</t>
+  </si>
+  <si>
+    <t>Recifes "Jardines"</t>
+  </si>
+  <si>
+    <t>robertson2009</t>
+  </si>
+  <si>
+    <t>robertson2010</t>
+  </si>
+  <si>
+    <t>robertson2011</t>
+  </si>
+  <si>
+    <t>robertson2012</t>
+  </si>
+  <si>
+    <t>robertson2013</t>
+  </si>
+  <si>
+    <t>robertson2014</t>
+  </si>
+  <si>
+    <t>robertson2015</t>
+  </si>
+  <si>
+    <t>robertson2016</t>
+  </si>
+  <si>
+    <t>robertson2017</t>
   </si>
 </sst>
 </file>
@@ -2980,7 +3076,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3040,9 +3136,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3306,7 +3399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R454"/>
+  <dimension ref="A1:R481"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -28023,7 +28116,7 @@
       </c>
     </row>
     <row r="387" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A387" s="21">
+      <c r="A387" s="1">
         <v>386</v>
       </c>
       <c r="B387" s="1" t="s">
@@ -28087,7 +28180,7 @@
       </c>
     </row>
     <row r="388" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A388" s="21">
+      <c r="A388" s="1">
         <v>387</v>
       </c>
       <c r="B388" s="1" t="s">
@@ -28151,7 +28244,7 @@
       </c>
     </row>
     <row r="389" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A389" s="21">
+      <c r="A389" s="1">
         <v>388</v>
       </c>
       <c r="B389" s="1" t="s">
@@ -28179,35 +28272,35 @@
         <v>726</v>
       </c>
       <c r="J389" s="1" t="str">
-        <f t="shared" ref="J389:J437" si="85">MID(E389,1,FIND("°",E389,1)-1)</f>
+        <f t="shared" ref="J389:J412" si="85">MID(E389,1,FIND("°",E389,1)-1)</f>
         <v>18</v>
       </c>
       <c r="K389" s="1" t="str">
-        <f t="shared" ref="K389:K437" si="86">MID(E389,FIND("°",E389,1)+1,(FIND("′",E389,1)-FIND("°",E389,1))-1)</f>
+        <f t="shared" ref="K389:K412" si="86">MID(E389,FIND("°",E389,1)+1,(FIND("′",E389,1)-FIND("°",E389,1))-1)</f>
         <v>55</v>
       </c>
       <c r="L389" s="1" t="str">
-        <f t="shared" ref="L389:L437" si="87">MID(E389,FIND("′",E389,1)+1,(FIND("″",E389,1)-FIND("′",E389,1))-1)</f>
+        <f t="shared" ref="L389:L412" si="87">MID(E389,FIND("′",E389,1)+1,(FIND("″",E389,1)-FIND("′",E389,1))-1)</f>
         <v>00</v>
       </c>
       <c r="M389" s="1" t="str">
-        <f t="shared" ref="M389:M437" si="88">MID(F389,1,FIND("°",F389,1)-1)</f>
+        <f t="shared" ref="M389:M412" si="88">MID(F389,1,FIND("°",F389,1)-1)</f>
         <v>75</v>
       </c>
       <c r="N389" s="1" t="str">
-        <f t="shared" ref="N389:N437" si="89">MID(F389,FIND("°",F389,1)+1,(FIND("′",F389,1)-FIND("°",F389,1))-1)</f>
+        <f t="shared" ref="N389:N412" si="89">MID(F389,FIND("°",F389,1)+1,(FIND("′",F389,1)-FIND("°",F389,1))-1)</f>
         <v>20</v>
       </c>
       <c r="O389" s="1" t="str">
-        <f t="shared" ref="O389:O437" si="90">MID(F389,FIND("′",F389,1)+1,(FIND("″",F389,1)-FIND("′",F389,1))-1)</f>
+        <f t="shared" ref="O389:O412" si="90">MID(F389,FIND("′",F389,1)+1,(FIND("″",F389,1)-FIND("′",F389,1))-1)</f>
         <v>00</v>
       </c>
       <c r="P389" s="2">
-        <f t="shared" ref="P389:P437" si="91">((((L389/60)+K389)/60)+J389)*IF(C389="S",-1, 1)</f>
+        <f t="shared" ref="P389:P412" si="91">((((L389/60)+K389)/60)+J389)*IF(C389="S",-1, 1)</f>
         <v>18.916666666666668</v>
       </c>
       <c r="Q389" s="2">
-        <f t="shared" ref="Q389:Q437" si="92">((((O389/60)+N389)/60)+M389)*IF(D389="W",-1, 1)</f>
+        <f t="shared" ref="Q389:Q412" si="92">((((O389/60)+N389)/60)+M389)*IF(D389="W",-1, 1)</f>
         <v>-75.333333333333329</v>
       </c>
       <c r="R389" s="16" t="s">
@@ -28215,7 +28308,7 @@
       </c>
     </row>
     <row r="390" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A390" s="21">
+      <c r="A390" s="1">
         <v>389</v>
       </c>
       <c r="B390" s="1" t="s">
@@ -28279,7 +28372,7 @@
       </c>
     </row>
     <row r="391" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A391" s="21">
+      <c r="A391" s="1">
         <v>390</v>
       </c>
       <c r="B391" s="1" t="s">
@@ -28343,7 +28436,7 @@
       </c>
     </row>
     <row r="392" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A392" s="21">
+      <c r="A392" s="1">
         <v>391</v>
       </c>
       <c r="B392" s="1" t="s">
@@ -28407,7 +28500,7 @@
       </c>
     </row>
     <row r="393" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A393" s="21">
+      <c r="A393" s="1">
         <v>392</v>
       </c>
       <c r="B393" s="1" t="s">
@@ -28471,7 +28564,7 @@
       </c>
     </row>
     <row r="394" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A394" s="21">
+      <c r="A394" s="1">
         <v>393</v>
       </c>
       <c r="B394" s="1" t="s">
@@ -28535,7 +28628,7 @@
       </c>
     </row>
     <row r="395" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A395" s="21">
+      <c r="A395" s="1">
         <v>394</v>
       </c>
       <c r="B395" s="1" t="s">
@@ -28599,7 +28692,7 @@
       </c>
     </row>
     <row r="396" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A396" s="21">
+      <c r="A396" s="1">
         <v>395</v>
       </c>
       <c r="B396" s="1" t="s">
@@ -28663,7 +28756,7 @@
       </c>
     </row>
     <row r="397" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A397" s="21">
+      <c r="A397" s="1">
         <v>396</v>
       </c>
       <c r="B397" s="1" t="s">
@@ -28727,7 +28820,7 @@
       </c>
     </row>
     <row r="398" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A398" s="21">
+      <c r="A398" s="1">
         <v>397</v>
       </c>
       <c r="B398" s="1" t="s">
@@ -28791,7 +28884,7 @@
       </c>
     </row>
     <row r="399" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A399" s="21">
+      <c r="A399" s="1">
         <v>398</v>
       </c>
       <c r="B399" s="1" t="s">
@@ -28855,7 +28948,7 @@
       </c>
     </row>
     <row r="400" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A400" s="21">
+      <c r="A400" s="1">
         <v>399</v>
       </c>
       <c r="B400" s="1" t="s">
@@ -28919,7 +29012,7 @@
       </c>
     </row>
     <row r="401" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A401" s="21">
+      <c r="A401" s="1">
         <v>400</v>
       </c>
       <c r="B401" s="1" t="s">
@@ -28983,7 +29076,7 @@
       </c>
     </row>
     <row r="402" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A402" s="21">
+      <c r="A402" s="1">
         <v>401</v>
       </c>
       <c r="B402" s="1" t="s">
@@ -29047,7 +29140,7 @@
       </c>
     </row>
     <row r="403" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A403" s="21">
+      <c r="A403" s="1">
         <v>402</v>
       </c>
       <c r="B403" s="1" t="s">
@@ -29111,7 +29204,7 @@
       </c>
     </row>
     <row r="404" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A404" s="21">
+      <c r="A404" s="1">
         <v>403</v>
       </c>
       <c r="B404" s="1" t="s">
@@ -29175,7 +29268,7 @@
       </c>
     </row>
     <row r="405" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A405" s="21">
+      <c r="A405" s="1">
         <v>404</v>
       </c>
       <c r="B405" s="1" t="s">
@@ -29239,7 +29332,7 @@
       </c>
     </row>
     <row r="406" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A406" s="21">
+      <c r="A406" s="1">
         <v>405</v>
       </c>
       <c r="B406" s="1" t="s">
@@ -29303,7 +29396,7 @@
       </c>
     </row>
     <row r="407" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A407" s="21">
+      <c r="A407" s="1">
         <v>406</v>
       </c>
       <c r="B407" s="1" t="s">
@@ -29367,7 +29460,7 @@
       </c>
     </row>
     <row r="408" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A408" s="21">
+      <c r="A408" s="1">
         <v>407</v>
       </c>
       <c r="B408" s="1" t="s">
@@ -29431,7 +29524,7 @@
       </c>
     </row>
     <row r="409" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A409" s="21">
+      <c r="A409" s="1">
         <v>408</v>
       </c>
       <c r="B409" s="1" t="s">
@@ -29495,7 +29588,7 @@
       </c>
     </row>
     <row r="410" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A410" s="21">
+      <c r="A410" s="1">
         <v>409</v>
       </c>
       <c r="B410" s="1" t="s">
@@ -29559,7 +29652,7 @@
       </c>
     </row>
     <row r="411" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A411" s="21">
+      <c r="A411" s="1">
         <v>410</v>
       </c>
       <c r="B411" s="1" t="s">
@@ -29623,7 +29716,7 @@
       </c>
     </row>
     <row r="412" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A412" s="21">
+      <c r="A412" s="1">
         <v>411</v>
       </c>
       <c r="B412" s="1" t="s">
@@ -29687,7 +29780,7 @@
       </c>
     </row>
     <row r="413" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A413" s="21">
+      <c r="A413" s="1">
         <v>412</v>
       </c>
       <c r="B413" s="1" t="s">
@@ -29751,7 +29844,7 @@
       </c>
     </row>
     <row r="414" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A414" s="21">
+      <c r="A414" s="1">
         <v>413</v>
       </c>
       <c r="B414" s="1" t="s">
@@ -29815,7 +29908,7 @@
       </c>
     </row>
     <row r="415" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A415" s="21">
+      <c r="A415" s="1">
         <v>414</v>
       </c>
       <c r="B415" s="1" t="s">
@@ -29879,7 +29972,7 @@
       </c>
     </row>
     <row r="416" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A416" s="21">
+      <c r="A416" s="1">
         <v>415</v>
       </c>
       <c r="B416" s="1" t="s">
@@ -29943,7 +30036,7 @@
       </c>
     </row>
     <row r="417" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A417" s="21">
+      <c r="A417" s="1">
         <v>416</v>
       </c>
       <c r="B417" s="1" t="s">
@@ -30007,7 +30100,7 @@
       </c>
     </row>
     <row r="418" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A418" s="21">
+      <c r="A418" s="1">
         <v>417</v>
       </c>
       <c r="B418" s="1" t="s">
@@ -30071,7 +30164,7 @@
       </c>
     </row>
     <row r="419" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A419" s="21">
+      <c r="A419" s="1">
         <v>418</v>
       </c>
       <c r="B419" s="1" t="s">
@@ -30135,7 +30228,7 @@
       </c>
     </row>
     <row r="420" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A420" s="21">
+      <c r="A420" s="1">
         <v>419</v>
       </c>
       <c r="B420" s="1" t="s">
@@ -30199,7 +30292,7 @@
       </c>
     </row>
     <row r="421" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A421" s="21">
+      <c r="A421" s="1">
         <v>420</v>
       </c>
       <c r="B421" s="1" t="s">
@@ -30263,7 +30356,7 @@
       </c>
     </row>
     <row r="422" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A422" s="21">
+      <c r="A422" s="1">
         <v>421</v>
       </c>
       <c r="B422" s="1" t="s">
@@ -30327,7 +30420,7 @@
       </c>
     </row>
     <row r="423" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A423" s="21">
+      <c r="A423" s="1">
         <v>422</v>
       </c>
       <c r="B423" s="1" t="s">
@@ -30391,7 +30484,7 @@
       </c>
     </row>
     <row r="424" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A424" s="21">
+      <c r="A424" s="1">
         <v>423</v>
       </c>
       <c r="B424" s="1" t="s">
@@ -30455,7 +30548,7 @@
       </c>
     </row>
     <row r="425" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A425" s="21">
+      <c r="A425" s="1">
         <v>424</v>
       </c>
       <c r="B425" s="1" t="s">
@@ -30519,7 +30612,7 @@
       </c>
     </row>
     <row r="426" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A426" s="21">
+      <c r="A426" s="1">
         <v>425</v>
       </c>
       <c r="B426" s="1" t="s">
@@ -30583,7 +30676,7 @@
       </c>
     </row>
     <row r="427" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A427" s="21">
+      <c r="A427" s="1">
         <v>426</v>
       </c>
       <c r="B427" s="1" t="s">
@@ -30647,7 +30740,7 @@
       </c>
     </row>
     <row r="428" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A428" s="21">
+      <c r="A428" s="1">
         <v>427</v>
       </c>
       <c r="B428" s="1" t="s">
@@ -30711,7 +30804,7 @@
       </c>
     </row>
     <row r="429" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A429" s="21">
+      <c r="A429" s="1">
         <v>428</v>
       </c>
       <c r="B429" s="1" t="s">
@@ -30775,7 +30868,7 @@
       </c>
     </row>
     <row r="430" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A430" s="21">
+      <c r="A430" s="1">
         <v>429</v>
       </c>
       <c r="B430" s="1" t="s">
@@ -30839,7 +30932,7 @@
       </c>
     </row>
     <row r="431" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A431" s="21">
+      <c r="A431" s="1">
         <v>430</v>
       </c>
       <c r="B431" s="1" t="s">
@@ -30903,7 +30996,7 @@
       </c>
     </row>
     <row r="432" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A432" s="21">
+      <c r="A432" s="1">
         <v>431</v>
       </c>
       <c r="B432" s="1" t="s">
@@ -30967,7 +31060,7 @@
       </c>
     </row>
     <row r="433" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A433" s="21">
+      <c r="A433" s="1">
         <v>432</v>
       </c>
       <c r="B433" s="1" t="s">
@@ -31031,7 +31124,7 @@
       </c>
     </row>
     <row r="434" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A434" s="21">
+      <c r="A434" s="1">
         <v>433</v>
       </c>
       <c r="B434" s="1" t="s">
@@ -31095,7 +31188,7 @@
       </c>
     </row>
     <row r="435" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A435" s="21">
+      <c r="A435" s="1">
         <v>434</v>
       </c>
       <c r="B435" s="1" t="s">
@@ -31159,7 +31252,7 @@
       </c>
     </row>
     <row r="436" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A436" s="21">
+      <c r="A436" s="1">
         <v>435</v>
       </c>
       <c r="B436" s="1" t="s">
@@ -31223,7 +31316,7 @@
       </c>
     </row>
     <row r="437" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A437" s="21">
+      <c r="A437" s="1">
         <v>436</v>
       </c>
       <c r="B437" s="1" t="s">
@@ -31287,7 +31380,7 @@
       </c>
     </row>
     <row r="438" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A438" s="21">
+      <c r="A438" s="1">
         <v>437</v>
       </c>
       <c r="B438" s="1" t="s">
@@ -31351,7 +31444,7 @@
       </c>
     </row>
     <row r="439" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A439" s="21">
+      <c r="A439" s="1">
         <v>438</v>
       </c>
       <c r="B439" s="1" t="s">
@@ -31415,7 +31508,7 @@
       </c>
     </row>
     <row r="440" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A440" s="21">
+      <c r="A440" s="1">
         <v>439</v>
       </c>
       <c r="B440" s="1" t="s">
@@ -31479,7 +31572,7 @@
       </c>
     </row>
     <row r="441" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A441" s="21">
+      <c r="A441" s="1">
         <v>440</v>
       </c>
       <c r="B441" s="1" t="s">
@@ -31543,7 +31636,7 @@
       </c>
     </row>
     <row r="442" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A442" s="21">
+      <c r="A442" s="1">
         <v>441</v>
       </c>
       <c r="B442" s="1" t="s">
@@ -31607,7 +31700,7 @@
       </c>
     </row>
     <row r="443" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A443" s="21">
+      <c r="A443" s="1">
         <v>442</v>
       </c>
       <c r="B443" s="1" t="s">
@@ -31671,7 +31764,7 @@
       </c>
     </row>
     <row r="444" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A444" s="21">
+      <c r="A444" s="1">
         <v>443</v>
       </c>
       <c r="B444" s="1" t="s">
@@ -31735,7 +31828,7 @@
       </c>
     </row>
     <row r="445" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A445" s="21">
+      <c r="A445" s="1">
         <v>444</v>
       </c>
       <c r="B445" s="1" t="s">
@@ -31799,7 +31892,7 @@
       </c>
     </row>
     <row r="446" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A446" s="21">
+      <c r="A446" s="1">
         <v>445</v>
       </c>
       <c r="B446" s="1" t="s">
@@ -31863,7 +31956,7 @@
       </c>
     </row>
     <row r="447" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A447" s="21">
+      <c r="A447" s="1">
         <v>446</v>
       </c>
       <c r="B447" s="1" t="s">
@@ -31927,7 +32020,7 @@
       </c>
     </row>
     <row r="448" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A448" s="21">
+      <c r="A448" s="1">
         <v>447</v>
       </c>
       <c r="B448" s="1" t="s">
@@ -31991,7 +32084,7 @@
       </c>
     </row>
     <row r="449" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A449" s="21">
+      <c r="A449" s="1">
         <v>448</v>
       </c>
       <c r="B449" s="1" t="s">
@@ -32055,7 +32148,7 @@
       </c>
     </row>
     <row r="450" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A450" s="21">
+      <c r="A450" s="1">
         <v>449</v>
       </c>
       <c r="B450" s="1" t="s">
@@ -32119,7 +32212,7 @@
       </c>
     </row>
     <row r="451" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A451" s="21">
+      <c r="A451" s="1">
         <v>450</v>
       </c>
       <c r="B451" s="1" t="s">
@@ -32183,7 +32276,7 @@
       </c>
     </row>
     <row r="452" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A452" s="21">
+      <c r="A452" s="1">
         <v>451</v>
       </c>
       <c r="B452" s="1" t="s">
@@ -32247,7 +32340,7 @@
       </c>
     </row>
     <row r="453" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A453" s="21">
+      <c r="A453" s="1">
         <v>452</v>
       </c>
       <c r="B453" s="1" t="s">
@@ -32311,7 +32404,7 @@
       </c>
     </row>
     <row r="454" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A454" s="21">
+      <c r="A454" s="1">
         <v>453</v>
       </c>
       <c r="B454" s="1" t="s">
@@ -32374,8 +32467,1238 @@
         <v>796</v>
       </c>
     </row>
+    <row r="455" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A455" s="1">
+        <v>454</v>
+      </c>
+      <c r="B455" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="C455" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D455" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E455" s="19" t="s">
+        <v>878</v>
+      </c>
+      <c r="F455" s="19" t="s">
+        <v>879</v>
+      </c>
+      <c r="G455" s="19" t="s">
+        <v>877</v>
+      </c>
+      <c r="H455" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I455" s="19" t="s">
+        <v>899</v>
+      </c>
+      <c r="J455" s="1" t="str">
+        <f t="shared" ref="J455:J462" si="115">MID(E455,1,FIND("°",E455,1)-1)</f>
+        <v>20</v>
+      </c>
+      <c r="K455" s="1" t="str">
+        <f t="shared" ref="K455:K462" si="116">MID(E455,FIND("°",E455,1)+1,(FIND("′",E455,1)-FIND("°",E455,1))-1)</f>
+        <v>50</v>
+      </c>
+      <c r="L455" s="1" t="str">
+        <f t="shared" ref="L455:L462" si="117">MID(E455,FIND("′",E455,1)+1,(FIND("″",E455,1)-FIND("′",E455,1))-1)</f>
+        <v>01</v>
+      </c>
+      <c r="M455" s="1" t="str">
+        <f t="shared" ref="M455:M462" si="118">MID(F455,1,FIND("°",F455,1)-1)</f>
+        <v>86</v>
+      </c>
+      <c r="N455" s="1" t="str">
+        <f t="shared" ref="N455:N462" si="119">MID(F455,FIND("°",F455,1)+1,(FIND("′",F455,1)-FIND("°",F455,1))-1)</f>
+        <v>52</v>
+      </c>
+      <c r="O455" s="1" t="str">
+        <f t="shared" ref="O455:O462" si="120">MID(F455,FIND("′",F455,1)+1,(FIND("″",F455,1)-FIND("′",F455,1))-1)</f>
+        <v>36</v>
+      </c>
+      <c r="P455" s="2">
+        <f t="shared" ref="P455:P462" si="121">((((L455/60)+K455)/60)+J455)*IF(C455="S",-1, 1)</f>
+        <v>20.833611111111111</v>
+      </c>
+      <c r="Q455" s="2">
+        <f t="shared" ref="Q455:Q462" si="122">((((O455/60)+N455)/60)+M455)*IF(D455="W",-1, 1)</f>
+        <v>-86.876666666666665</v>
+      </c>
+      <c r="R455" s="16" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="456" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A456" s="1">
+        <v>455</v>
+      </c>
+      <c r="B456" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="C456" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D456" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E456" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="F456" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="G456" s="19" t="s">
+        <v>880</v>
+      </c>
+      <c r="H456" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="I456" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="J456" s="1" t="str">
+        <f t="shared" si="115"/>
+        <v>24</v>
+      </c>
+      <c r="K456" s="1" t="str">
+        <f t="shared" si="116"/>
+        <v>43</v>
+      </c>
+      <c r="L456" s="1" t="str">
+        <f t="shared" si="117"/>
+        <v>39</v>
+      </c>
+      <c r="M456" s="1" t="str">
+        <f t="shared" si="118"/>
+        <v xml:space="preserve"> 80</v>
+      </c>
+      <c r="N456" s="1" t="str">
+        <f t="shared" si="119"/>
+        <v>56</v>
+      </c>
+      <c r="O456" s="1" t="str">
+        <f t="shared" si="120"/>
+        <v>20</v>
+      </c>
+      <c r="P456" s="2">
+        <f t="shared" si="121"/>
+        <v>24.727499999999999</v>
+      </c>
+      <c r="Q456" s="2">
+        <f t="shared" si="122"/>
+        <v>-80.938888888888883</v>
+      </c>
+      <c r="R456" s="16" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="457" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A457" s="1">
+        <v>456</v>
+      </c>
+      <c r="B457" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="C457" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D457" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E457" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="F457" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="G457" s="19" t="s">
+        <v>880</v>
+      </c>
+      <c r="H457" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="I457" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="J457" s="1" t="str">
+        <f t="shared" si="115"/>
+        <v>24</v>
+      </c>
+      <c r="K457" s="1" t="str">
+        <f t="shared" si="116"/>
+        <v>42</v>
+      </c>
+      <c r="L457" s="1" t="str">
+        <f t="shared" si="117"/>
+        <v>43</v>
+      </c>
+      <c r="M457" s="1" t="str">
+        <f t="shared" si="118"/>
+        <v>80</v>
+      </c>
+      <c r="N457" s="1" t="str">
+        <f t="shared" si="119"/>
+        <v>57</v>
+      </c>
+      <c r="O457" s="1" t="str">
+        <f t="shared" si="120"/>
+        <v>08</v>
+      </c>
+      <c r="P457" s="2">
+        <f t="shared" si="121"/>
+        <v>24.711944444444445</v>
+      </c>
+      <c r="Q457" s="2">
+        <f t="shared" si="122"/>
+        <v>-80.952222222222218</v>
+      </c>
+      <c r="R457" s="16" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="458" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A458" s="1">
+        <v>457</v>
+      </c>
+      <c r="B458" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="C458" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D458" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E458" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="F458" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="G458" s="19" t="s">
+        <v>880</v>
+      </c>
+      <c r="H458" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="I458" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="J458" s="1" t="str">
+        <f t="shared" si="115"/>
+        <v>24</v>
+      </c>
+      <c r="K458" s="1" t="str">
+        <f t="shared" si="116"/>
+        <v>42</v>
+      </c>
+      <c r="L458" s="1" t="str">
+        <f t="shared" si="117"/>
+        <v>48</v>
+      </c>
+      <c r="M458" s="1" t="str">
+        <f t="shared" si="118"/>
+        <v xml:space="preserve"> 80</v>
+      </c>
+      <c r="N458" s="1" t="str">
+        <f t="shared" si="119"/>
+        <v>59</v>
+      </c>
+      <c r="O458" s="1" t="str">
+        <f t="shared" si="120"/>
+        <v>34</v>
+      </c>
+      <c r="P458" s="2">
+        <f t="shared" si="121"/>
+        <v>24.713333333333335</v>
+      </c>
+      <c r="Q458" s="2">
+        <f t="shared" si="122"/>
+        <v>-80.992777777777775</v>
+      </c>
+      <c r="R458" s="16" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="459" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A459" s="1">
+        <v>458</v>
+      </c>
+      <c r="B459" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="C459" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D459" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E459" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="F459" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="G459" s="19" t="s">
+        <v>880</v>
+      </c>
+      <c r="H459" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="I459" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="J459" s="1" t="str">
+        <f t="shared" si="115"/>
+        <v>24</v>
+      </c>
+      <c r="K459" s="1" t="str">
+        <f t="shared" si="116"/>
+        <v>55</v>
+      </c>
+      <c r="L459" s="1" t="str">
+        <f t="shared" si="117"/>
+        <v>35</v>
+      </c>
+      <c r="M459" s="1" t="str">
+        <f t="shared" si="118"/>
+        <v xml:space="preserve"> 80</v>
+      </c>
+      <c r="N459" s="1" t="str">
+        <f t="shared" si="119"/>
+        <v>35</v>
+      </c>
+      <c r="O459" s="1" t="str">
+        <f t="shared" si="120"/>
+        <v>30</v>
+      </c>
+      <c r="P459" s="2">
+        <f t="shared" si="121"/>
+        <v>24.926388888888887</v>
+      </c>
+      <c r="Q459" s="2">
+        <f t="shared" si="122"/>
+        <v>-80.591666666666669</v>
+      </c>
+      <c r="R459" s="16" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="460" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A460" s="1">
+        <v>459</v>
+      </c>
+      <c r="B460" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="C460" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D460" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E460" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="F460" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="G460" s="19" t="s">
+        <v>880</v>
+      </c>
+      <c r="H460" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="I460" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="J460" s="1" t="str">
+        <f t="shared" si="115"/>
+        <v>24</v>
+      </c>
+      <c r="K460" s="1" t="str">
+        <f t="shared" si="116"/>
+        <v>56</v>
+      </c>
+      <c r="L460" s="1" t="str">
+        <f t="shared" si="117"/>
+        <v>29</v>
+      </c>
+      <c r="M460" s="1" t="str">
+        <f t="shared" si="118"/>
+        <v>80</v>
+      </c>
+      <c r="N460" s="1" t="str">
+        <f t="shared" si="119"/>
+        <v>33</v>
+      </c>
+      <c r="O460" s="1" t="str">
+        <f t="shared" si="120"/>
+        <v>40</v>
+      </c>
+      <c r="P460" s="2">
+        <f t="shared" si="121"/>
+        <v>24.941388888888888</v>
+      </c>
+      <c r="Q460" s="2">
+        <f t="shared" si="122"/>
+        <v>-80.561111111111117</v>
+      </c>
+      <c r="R460" s="16" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="461" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A461" s="1">
+        <v>460</v>
+      </c>
+      <c r="B461" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="C461" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D461" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E461" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="F461" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="G461" s="19" t="s">
+        <v>880</v>
+      </c>
+      <c r="H461" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="I461" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="J461" s="1" t="str">
+        <f t="shared" si="115"/>
+        <v>24</v>
+      </c>
+      <c r="K461" s="1" t="str">
+        <f t="shared" si="116"/>
+        <v>57</v>
+      </c>
+      <c r="L461" s="1" t="str">
+        <f t="shared" si="117"/>
+        <v>36</v>
+      </c>
+      <c r="M461" s="1" t="str">
+        <f t="shared" si="118"/>
+        <v>80</v>
+      </c>
+      <c r="N461" s="1" t="str">
+        <f t="shared" si="119"/>
+        <v>33</v>
+      </c>
+      <c r="O461" s="1" t="str">
+        <f t="shared" si="120"/>
+        <v>12</v>
+      </c>
+      <c r="P461" s="2">
+        <f t="shared" si="121"/>
+        <v>24.96</v>
+      </c>
+      <c r="Q461" s="2">
+        <f t="shared" si="122"/>
+        <v>-80.553333333333327</v>
+      </c>
+      <c r="R461" s="16" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="462" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A462" s="1">
+        <v>461</v>
+      </c>
+      <c r="B462" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="C462" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D462" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E462" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="F462" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="G462" s="19" t="s">
+        <v>880</v>
+      </c>
+      <c r="H462" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="I462" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="J462" s="1" t="str">
+        <f t="shared" si="115"/>
+        <v>25</v>
+      </c>
+      <c r="K462" s="1" t="str">
+        <f t="shared" si="116"/>
+        <v>01</v>
+      </c>
+      <c r="L462" s="1" t="str">
+        <f t="shared" si="117"/>
+        <v>34</v>
+      </c>
+      <c r="M462" s="1" t="str">
+        <f t="shared" si="118"/>
+        <v>80</v>
+      </c>
+      <c r="N462" s="1" t="str">
+        <f t="shared" si="119"/>
+        <v>24</v>
+      </c>
+      <c r="O462" s="1" t="str">
+        <f t="shared" si="120"/>
+        <v>42</v>
+      </c>
+      <c r="P462" s="2">
+        <f t="shared" si="121"/>
+        <v>25.02611111111111</v>
+      </c>
+      <c r="Q462" s="2">
+        <f t="shared" si="122"/>
+        <v>-80.411666666666662</v>
+      </c>
+      <c r="R462" s="16" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="463" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A463" s="1">
+        <v>462</v>
+      </c>
+      <c r="B463" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="C463" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D463" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E463" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="F463" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="G463" s="19" t="s">
+        <v>880</v>
+      </c>
+      <c r="H463" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="I463" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="J463" s="1" t="str">
+        <f t="shared" ref="J463:J481" si="123">MID(E463,1,FIND("°",E463,1)-1)</f>
+        <v>25</v>
+      </c>
+      <c r="K463" s="1" t="str">
+        <f t="shared" ref="K463:K481" si="124">MID(E463,FIND("°",E463,1)+1,(FIND("′",E463,1)-FIND("°",E463,1))-1)</f>
+        <v>02</v>
+      </c>
+      <c r="L463" s="1" t="str">
+        <f t="shared" ref="L463:L481" si="125">MID(E463,FIND("′",E463,1)+1,(FIND("″",E463,1)-FIND("′",E463,1))-1)</f>
+        <v>37</v>
+      </c>
+      <c r="M463" s="1" t="str">
+        <f t="shared" ref="M463:M481" si="126">MID(F463,1,FIND("°",F463,1)-1)</f>
+        <v xml:space="preserve"> 80</v>
+      </c>
+      <c r="N463" s="1" t="str">
+        <f t="shared" ref="N463:N481" si="127">MID(F463,FIND("°",F463,1)+1,(FIND("′",F463,1)-FIND("°",F463,1))-1)</f>
+        <v>22</v>
+      </c>
+      <c r="O463" s="1" t="str">
+        <f t="shared" ref="O463:O481" si="128">MID(F463,FIND("′",F463,1)+1,(FIND("″",F463,1)-FIND("′",F463,1))-1)</f>
+        <v>49</v>
+      </c>
+      <c r="P463" s="2">
+        <f t="shared" ref="P463:P481" si="129">((((L463/60)+K463)/60)+J463)*IF(C463="S",-1, 1)</f>
+        <v>25.043611111111112</v>
+      </c>
+      <c r="Q463" s="2">
+        <f t="shared" ref="Q463:Q481" si="130">((((O463/60)+N463)/60)+M463)*IF(D463="W",-1, 1)</f>
+        <v>-80.380277777777778</v>
+      </c>
+      <c r="R463" s="16" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="464" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A464" s="1">
+        <v>463</v>
+      </c>
+      <c r="B464" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="C464" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D464" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E464" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="F464" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="G464" s="19" t="s">
+        <v>880</v>
+      </c>
+      <c r="H464" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="I464" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="J464" s="1" t="str">
+        <f t="shared" si="123"/>
+        <v>25</v>
+      </c>
+      <c r="K464" s="1" t="str">
+        <f t="shared" si="124"/>
+        <v>07</v>
+      </c>
+      <c r="L464" s="1" t="str">
+        <f t="shared" si="125"/>
+        <v>00</v>
+      </c>
+      <c r="M464" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>80</v>
+      </c>
+      <c r="N464" s="1" t="str">
+        <f t="shared" si="127"/>
+        <v>21</v>
+      </c>
+      <c r="O464" s="1" t="str">
+        <f t="shared" si="128"/>
+        <v>10</v>
+      </c>
+      <c r="P464" s="2">
+        <f t="shared" si="129"/>
+        <v>25.116666666666667</v>
+      </c>
+      <c r="Q464" s="2">
+        <f t="shared" si="130"/>
+        <v>-80.352777777777774</v>
+      </c>
+      <c r="R464" s="16" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="465" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="G465"/>
+      <c r="J465" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K465" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L465" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M465" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N465" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O465" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P465" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q465" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="466" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="G466"/>
+      <c r="J466" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K466" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L466" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M466" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N466" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O466" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P466" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q466" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="467" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="G467"/>
+      <c r="J467" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K467" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L467" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M467" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N467" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O467" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P467" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q467" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="468" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="G468"/>
+      <c r="J468" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K468" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L468" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M468" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N468" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O468" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P468" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q468" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="469" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="G469"/>
+      <c r="J469" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K469" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L469" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M469" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N469" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O469" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P469" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q469" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="470" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="G470"/>
+      <c r="J470" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K470" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L470" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M470" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N470" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O470" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P470" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q470" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="471" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="G471"/>
+      <c r="J471" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K471" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L471" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M471" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N471" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O471" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P471" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q471" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="472" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="G472"/>
+      <c r="J472" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K472" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L472" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M472" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N472" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O472" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P472" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q472" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="473" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="G473"/>
+      <c r="J473" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K473" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L473" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M473" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N473" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O473" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P473" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q473" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="474" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="G474"/>
+      <c r="J474" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K474" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L474" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M474" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N474" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O474" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P474" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q474" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="475" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="G475"/>
+      <c r="J475" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K475" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L475" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M475" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N475" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O475" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P475" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q475" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="476" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="G476"/>
+      <c r="J476" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K476" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L476" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M476" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N476" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O476" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P476" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q476" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="477" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="J477" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K477" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L477" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M477" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N477" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O477" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P477" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q477" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="478" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="J478" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K478" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L478" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M478" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N478" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O478" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P478" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q478" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="479" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="J479" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K479" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L479" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M479" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N479" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O479" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P479" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q479" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="480" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="J480" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K480" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L480" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M480" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N480" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O480" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P480" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q480" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="481" spans="10:17" x14ac:dyDescent="0.25">
+      <c r="J481" s="1" t="e">
+        <f t="shared" si="123"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K481" s="1" t="e">
+        <f t="shared" si="124"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L481" s="1" t="e">
+        <f t="shared" si="125"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M481" s="1" t="e">
+        <f t="shared" si="126"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N481" s="1" t="e">
+        <f t="shared" si="127"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O481" s="1" t="e">
+        <f t="shared" si="128"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P481" s="2" t="e">
+        <f t="shared" si="129"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q481" s="2" t="e">
+        <f t="shared" si="130"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R454" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R481" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
